--- a/test/generated/Nexent_测试基线.xlsx
+++ b/test/generated/Nexent_测试基线.xlsx
@@ -16,12 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_D5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_功能清单'!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_D1'!$A$1:$AA$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_D2'!$A$1:$AA$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_D3'!$A$1:$AA$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_D4'!$A$1:$AA$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_D5'!$A$1:$AA$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_功能清单'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_D1'!$A$1:$AA$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_D2'!$A$1:$AA$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_D3'!$A$1:$AA$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_D4'!$A$1:$AA$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_D5'!$A$1:$AA$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
@@ -551,11 +551,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
@@ -603,25 +603,79 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>AIDP knowledge base list and creation page refactor</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>AIDP knowledge bases are listed in a card or table overview with an independent name search, a collapsible three-step guide and a full-page file view per knowledge base; creation moves to a dedicated two-step page that carries permission, chunking, retrieval, graph, model and safety-guard configuration. The ES knowledge base path stays untouched.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-001
+AKPR-RULE-002
+AKPR-RULE-003
+AKPR-RULE-004
+AKPR-RULE-005
+AKPR-RULE-006
+AKPR-RULE-007
+AKPR-RULE-008
+AKPR-RULE-009
+AKPR-RULE-010
+AKPR-RULE-011
+AKPR-RULE-012
+AKPR-RULE-013
+AKPR-RULE-014</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>D1
+D2
+D3
+D4
+D5</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>{"requirement_ids":["AKPR-001"],"spec_path":"nexent-doc/nexent/knowledge-base-pages-refactor/proposal.md"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Silent model retry stream visibility</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Successful model attempts stream raw content while failed attempts leave no visible or persisted fragments.</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-013
 CMSR-RULE-014
@@ -631,7 +685,7 @@
 CMSR-RULE-018</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>D1
 D2
@@ -640,14 +694,14 @@
 D5</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>{"requirement_ids":["CMSR-005"],"spec_path":"nexent-doc/docs/Developing/chat-message-model-silent-retry/proposal.md"}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -658,7 +712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -830,33 +884,32 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>CMSR-D1-001</t>
+          <t>AKPR-D1-001</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>CMSR-005</t>
+          <t>AKPR-001</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>CMSR-005</t>
+          <t>AKPR-001</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>CMSR-RULE-013
-CMSR-RULE-014</t>
+          <t>AKPR-RULE-001</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Observer emits safe content before stream completion</t>
+          <t>Overview guide expands, collapses and keeps the fixed three steps</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>SDK-UT</t>
+          <t>FE-COMP</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -876,156 +929,1440 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Verify bounded marker lookahead and attempt state reset.</t>
+          <t>Verify the AIDP-only guide renders the knowledge base explanation with the fixed steps and toggles without disturbing page state.</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>Create an isolated observer and a controlled chunk sequence.</t>
+          <t>Render the AIDP overview component with an empty knowledge base list.</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>{"profile":"mock","sequence":"failed partial, rollback, successful split code and think markers"}</t>
+          <t>{"locale":"zh-CN","profile":"mock"}</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>1. Feed a safe prefix and pause the source. =&gt; The prefix is emitted before flush or commit.
-2. Roll back the first attempt and feed split markers in the second. =&gt; The second output is ordered and contains no first-attempt residue.</t>
+          <t>1. Mount the overview page. =&gt; The guide is expanded and lists create knowledge base, upload files and configure the knowledge base in an agent.
+2. Collapse the guide. =&gt; The guide body is hidden while the reopen entry stays visible and operable.
+3. Reopen the guide. =&gt; The explanation and the three steps are visible again with unchanged search and view state.</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
-          <t>The earliest safe content is observable before completion.
-Split markers retain their original semantics.</t>
+          <t>The explanation and the three documented steps are visible when expanded.
+Collapse hides only the guide body.
+Reopening restores the same content order.</t>
         </is>
       </c>
       <c r="O2" s="5" t="inlineStr">
         <is>
-          <t>No stale fragment crosses attempts.
-No code is executed by the observer.</t>
+          <t>No backend request is issued by expanding or collapsing the guide.
+No search, page or view mode change.</t>
         </is>
       </c>
       <c r="P2" s="5" t="inlineStr">
         <is>
-          <t>{"assertions":["Safe prefix emitted before flush.","Raw code tag retained.","No failed-attempt residue."],"inputs":["normal content","split &lt;think&gt; and &lt;/think&gt;","raw &lt;code&gt; content"],"unit_boundary":"Observer.add_model_new_token and attempt lifecycle"}</t>
+          <t>{"assertions":["Guide content is visible on first entry.","The reopen entry remains visible after collapse.","The three step labels match the fixed order.","Guide toggling issues no request."],"inputs":["initial expanded state","collapse click","reopen click"],"unit_boundary":"AIDP knowledge guide expansion state and fixed step labels"}</t>
         </is>
       </c>
       <c r="Q2" s="5" t="inlineStr"/>
       <c r="R2" s="5" t="inlineStr">
         <is>
-          <t>implemented</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="inlineStr">
-        <is>
-          <t>pytest</t>
-        </is>
-      </c>
-      <c r="T2" s="5" t="inlineStr">
-        <is>
-          <t>test/automation/d1/test_model_attempt_stream.py</t>
-        </is>
-      </c>
-      <c r="U2" s="5" t="inlineStr">
-        <is>
-          <t>test_cmsr_d1_001</t>
-        </is>
-      </c>
-      <c r="V2" s="5" t="inlineStr">
-        <is>
-          <t>mock</t>
-        </is>
-      </c>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr"/>
+      <c r="T2" s="5" t="inlineStr"/>
+      <c r="U2" s="5" t="inlineStr"/>
+      <c r="V2" s="5" t="inlineStr"/>
       <c r="W2" s="5" t="inlineStr"/>
       <c r="X2" s="5" t="inlineStr"/>
       <c r="Y2" s="5" t="inlineStr">
         <is>
-          <t>校验通过</t>
-        </is>
-      </c>
-      <c r="Z2" s="5" t="inlineStr">
-        <is>
-          <t>sha256:625e8c8829b51b9cd91344555d05c5ebfdc7bd766d8485eab99b9f22773f3233</t>
-        </is>
-      </c>
-      <c r="AA2" s="5" t="inlineStr">
-        <is>
-          <t>sha256:242f1aaf8a5fe4427f503e5acb8db2cc6cb5096782c2e4fdf49fcb17ec471420</t>
-        </is>
-      </c>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z2" s="5" t="inlineStr"/>
+      <c r="AA2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
+          <t>AKPR-D1-002</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-002
+AKPR-RULE-004</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Cards are the default view and switching or hiding columns keeps the result set</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Verify default card rendering, table switching and column visibility control over one shared paginated result set.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Render the overview with a fixed page of knowledge bases and a recorded search and page number.</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>{"page_size":10,"profile":"mock","total":23}</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>1. Mount the overview with existing results. =&gt; Knowledge bases render as cards.
+2. Switch to the table view. =&gt; The same records render as table rows with the current keyword and page preserved.
+3. Hide one optional column and then restore defaults. =&gt; The column disappears and returns while the name and action columns stay present throughout.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>The card view is the default.
+Switching views keeps keyword, page and totals identical.
+Hiding and restoring columns changes only local visibility.</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>No mutating endpoint is called by view or column changes.
+No record is dropped or duplicated by switching views.
+Required columns cannot be hidden.</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Initial view mode is cards.","Table switch preserves keyword, page and total.","Hidden optional column is absent and restorable.","Name and action columns stay visible."],"inputs":["default view mode","card to table switch","hidden column set","restore defaults action"],"unit_boundary":"Overview view mode and column visibility state"}</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="inlineStr"/>
+      <c r="V3" s="5" t="inlineStr"/>
+      <c r="W3" s="5" t="inlineStr"/>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr"/>
+      <c r="AA3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-003</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-003</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Independent name search drives the keyword query and resets the page</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Verify the single search box reuses the existing keyword query, resets to page one and keeps table headers free of search controls.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Render the overview with a recorded non-first page and a stubbed list service.</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>{"keyword":"finance","page":3,"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>1. Type a keyword into the page search box and wait for the debounce. =&gt; The list service is called with the keyword and page one for both views.
+2. Clear the search box. =&gt; The unfiltered permission-scoped set is requested again.
+3. Inspect the table header row. =&gt; No column exposes a search or filter control.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>The keyword query is reused with a page reset.
+Clearing restores the unfiltered set.
+Column headers contain no search entry.</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>No request per keystroke outside the debounce.
+No column filter parameter is sent.</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["listKbs receives keyword and page one after debounce.","Clearing the box requests the unfiltered set.","No header search control exists."],"inputs":["keyword text","debounce interval elapse","clear action","table header render"],"unit_boundary":"Overview search debounce and page reset with the existing keyword parameter"}</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr"/>
+      <c r="W4" s="5" t="inlineStr"/>
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z4" s="5" t="inlineStr"/>
+      <c r="AA4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-004</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-005
+AKPR-RULE-009</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>File view targets one knowledge base and restores the previous list state on return</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Verify the full-page file view scoping, the preserved list state on return and the cleanup of the previous base document state.</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Render the overview with two knowledge bases and a recorded search, page, view mode and column setting.</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>{"other_base":"kb-beta","profile":"mock","selected_base":"kb-alpha"}</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>1. Select a knowledge base. =&gt; Only that base files render and the overview is replaced by the full-page file view.
+2. Return to the overview. =&gt; The previous keyword, page, view mode and column setting are intact.
+3. Resolve a delayed document response from the first base after selecting the second. =&gt; The delayed payload is discarded and the second base files remain.</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>Files belong to the selected base only.
+Returning restores the previous list state.
+A stale response never overwrites the current base.</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>No cross-base document leakage.
+No polling left running after leaving the file view.
+No list state reset on return.</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["File list requests carry the selected base id.","Return renders the preserved list state.","A late response for the previous base is ignored.","Polling state is cleared when the view is left."],"inputs":["selected base id","return action","delayed response for a previous base"],"unit_boundary":"List and file view switching, document state reset and polling cleanup"}</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr"/>
+      <c r="U5" s="5" t="inlineStr"/>
+      <c r="V5" s="5" t="inlineStr"/>
+      <c r="W5" s="5" t="inlineStr"/>
+      <c r="X5" s="5" t="inlineStr"/>
+      <c r="Y5" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z5" s="5" t="inlineStr"/>
+      <c r="AA5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-005</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-006</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>AIDP list metadata normalizes real values and marks unknown ones as absent</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>BE-UT</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Verify the list response normalization of private and public type, capacity and missing values without fabricating data.</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Provide raw AIDP list rows with mixed boolean, numeric, string and missing metadata values.</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>{"cases":["is_private true","is_private 0","is_private string true","missing is_private","current_cap 2.5","missing current_cap","missing document count"],"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>1. Normalize rows with boolean, numeric and string forms of is_private. =&gt; A stable personal or enterprise type is produced for every form.
+2. Normalize rows without a type, capacity or count value. =&gt; Those fields are reported as unknown instead of a fabricated default.
+3. Normalize a valid personal capacity. =&gt; The documented unit value is preserved unchanged.</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>Real values survive normalization.
+Unknown values are distinguishable from a real zero.
+Capacity is not estimated from file sizes.</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>No Nexent group permission is used to infer the base type.
+No synthetic zero count or capacity is produced.
+No extra upstream request is issued per row.</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Boolean, integer and string is_private forms normalize consistently.","A missing count is distinguishable from zero.","A missing capacity is reported as unknown.","A valid capacity keeps its unit."],"inputs":["is_private variants","current_cap values","document count presence"],"unit_boundary":"AIDP list metadata normalization helpers"}</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-006</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-007</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Read-only and unavailable knowledge bases expose no modification entry</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Verify that permission and lifecycle restrictions remove every executable modification entry in cards, table rows and the file view.</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Render the overview with one editable, one read-only and one unavailable knowledge base.</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>{"permissions":["EDIT","READ_ONLY"],"profile":"mock","resource_status":["available","unavailable"]}</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>1. Render the card menu and table actions for each permission. =&gt; Only the editable base offers executable edit and delete entries.
+2. Open the file view of a read-only base. =&gt; Upload and delete entries are absent or disabled while browsing stays possible.
+3. Render an unavailable base. =&gt; No executable modification entry is offered and its state stays visible.</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>Modification entries follow the effective permission.
+Unavailable bases stay visible without modification entries.
+No request is emitted from a disabled entry.</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>No modification request for read-only or unavailable bases.
+No hidden menu item remains clickable.
+No downgrade of the existing visibility rules.</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Read-only rows render no executable modification entry.","Unavailable rows keep their lifecycle indicator.","No request leaves a disabled entry."],"inputs":["effective permission","resource_status","menu open state"],"unit_boundary":"Card menu and table action rendering under permission and lifecycle states"}</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr"/>
+      <c r="U7" s="5" t="inlineStr"/>
+      <c r="V7" s="5" t="inlineStr"/>
+      <c r="W7" s="5" t="inlineStr"/>
+      <c r="X7" s="5" t="inlineStr"/>
+      <c r="Y7" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z7" s="5" t="inlineStr"/>
+      <c r="AA7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-007</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-002</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>First-load empty, filtered empty, loading and failure states stay distinct</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Verify the four overview states render distinct messages and remain localized.</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Render the overview with a stubbed service returning an empty set, an empty filtered set, a pending promise and an error.</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>{"locales":["zh","en"],"profile":"mock","states":["first empty","filtered empty","loading","failed"]}</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>1. Resolve an empty list without a keyword. =&gt; A first-use empty state renders instead of a search-empty state.
+2. Resolve an empty list with an active keyword. =&gt; A search-empty state renders with the keyword context.
+3. Keep the request pending and then reject it. =&gt; Loading and failure states render distinctly and the failure state offers a retry path.</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>All four states are distinguishable.
+Both locales resolve every state string.</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>No fabricated placeholder rows.
+No silent failure rendering as an empty state.</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["First empty and filtered empty differ.","Loading state precedes data.","Failure state is distinct and localized.","No placeholder rows are invented."],"inputs":["empty payload","empty filtered payload","pending request","rejected request","locale"],"unit_boundary":"Overview empty, loading and failure state rendering"}</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="inlineStr"/>
+      <c r="T8" s="5" t="inlineStr"/>
+      <c r="U8" s="5" t="inlineStr"/>
+      <c r="V8" s="5" t="inlineStr"/>
+      <c r="W8" s="5" t="inlineStr"/>
+      <c r="X8" s="5" t="inlineStr"/>
+      <c r="Y8" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z8" s="5" t="inlineStr"/>
+      <c r="AA8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-008</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-010</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Two-step creation validates locally, preserves state and creates exactly once</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Verify step navigation without creation, state preservation across steps and single creation before upload.</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Render the AIDP creation page with stubbed create and upload services and a selected local file.</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>{"failing_uploads":1,"files":2,"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>1. Fill step one and press next. =&gt; Validation runs with no create request issued and step two renders.
+2. Return to step one. =&gt; Form values, conditional sections and the selected files are preserved.
+3. Submit with one failing upload. =&gt; Creation happens once and the created base and the failed upload are reported separately.
+4. Submit again after the failed upload. =&gt; No second knowledge base is created and the retry targets the failed file only.</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>Step one never creates a resource.
+State survives backward navigation.
+Creation happens exactly once before uploads.</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>No create request from the next action.
+No duplicate base after retry or double click.
+No upload before a successful create.</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Next issues no create request.","Backward navigation keeps values and files.","Exactly one create request precedes uploads.","A failed upload does not trigger a second create."],"inputs":["step one form values","selected files","upload failure","repeated submit"],"unit_boundary":"Creation page step state, submit guard and create-then-upload sequencing"}</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="inlineStr"/>
+      <c r="T9" s="5" t="inlineStr"/>
+      <c r="U9" s="5" t="inlineStr"/>
+      <c r="V9" s="5" t="inlineStr"/>
+      <c r="W9" s="5" t="inlineStr"/>
+      <c r="X9" s="5" t="inlineStr"/>
+      <c r="Y9" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z9" s="5" t="inlineStr"/>
+      <c r="AA9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-009</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-011</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Creation defaults and chunking mapping follow the confirmed values</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>BE-UT</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Verify preserved creation defaults, the chunk mode enumeration and the overlap-to-token conversion with its bounds.</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Prepare create payloads with missing defaults, both chunk modes and boundary overlap percentages.</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>{"chunk_tokens":[1024,512],"modes":["smart","legal"],"percents":[12.5,50],"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>1. Submit a payload without explicit chunking or retrieval values. =&gt; The existing defaults apply unchanged and the new graph parameters use their documented defaults.
+2. Submit each chunk mode. =&gt; The chunk mode serializes as 0 for smart splitting and 1 for legal clauses.
+3. Submit overlap percentages including the boundaries. =&gt; The overlap becomes the floor conversion in integer tokens and any value above half the chunk size is rejected.</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>Defaults remain 1024 tokens, 128 overlap, 0.0 similarity and Top K 10.
+Chunk modes serialize 0 and 1.
+Overlap conversion is exact and bounded.</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>No silent clamping of an invalid overlap.
+No renamed legacy field in the outgoing payload.
+No change to the ES knowledge base contract.</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Defaults match the existing Nexent values.","Overlap equals the floor conversion.","Overlap above 50 percent of the chunk size is rejected.","Legacy field names stay unchanged."],"inputs":["payload without defaults","chunk mode selection","chunk tokens and overlap percent"],"unit_boundary":"Create default application, chunk mode mapping and overlap conversion"}</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr"/>
+      <c r="U10" s="5" t="inlineStr"/>
+      <c r="V10" s="5" t="inlineStr"/>
+      <c r="W10" s="5" t="inlineStr"/>
+      <c r="X10" s="5" t="inlineStr"/>
+      <c r="Y10" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z10" s="5" t="inlineStr"/>
+      <c r="AA10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-010</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-013</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Graph configuration serializes documented keys with an inverse thinking switch</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>BE-UT</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Verify graph configuration serialization, the inverse thinking mapping, the independent Top K values and the prompt byte limit.</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Prepare graph payloads with the switch on and off, both languages and prompt lengths around the byte limit.</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>{"domains":["general","medical"],"languages":["chinese","english"],"profile":"mock","prompt_bytes":[2048,2049]}</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>1. Submit a graph configuration with the thinking switch enabled. =&gt; The thinking mode field is false and the graph keys use their documented names.
+2. Submit a knowledge base Top K together with a graph Top K. =&gt; The two values are serialized independently without overwriting each other.
+3. Submit prompts at and beyond the byte boundary together with a disabled graph. =&gt; The limit passes at the boundary, longer input is rejected and a disabled graph omits its configuration entirely.</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>The thinking switch maps inversely onto the thinking mode field.
+Both Top K values survive independently.
+The prompt limit is enforced in UTF-8 bytes.</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>No hidden previous graph configuration is submitted when the graph is off.
+No graph Top K overwrites the knowledge base Top K.
+No invented JSON key names.</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["The thinking mode field is false when thinking is enabled.","Graph and knowledge base Top K stay independent.","Prompt length is measured in UTF-8 bytes.","Disabled graph omits its configuration."],"inputs":["graph switch","domain","graph top k","hop count","thinking switch","prompt language","prompt text"],"unit_boundary":"Graph configuration validation and serialization"}</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S11" s="5" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr"/>
+      <c r="U11" s="5" t="inlineStr"/>
+      <c r="V11" s="5" t="inlineStr"/>
+      <c r="W11" s="5" t="inlineStr"/>
+      <c r="X11" s="5" t="inlineStr"/>
+      <c r="Y11" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z11" s="5" t="inlineStr"/>
+      <c r="AA11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-011</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-012</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Graph and multimodal models are queried from separate categories with independent caches</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Verify the model category split, the independent query caches and the omission of hidden model values.</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Render the creation form with stubbed model queries per category and both capability switches toggled.</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>{"categories":["llm","vlm","embedding"],"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>1. Enable the graph section. =&gt; The graph model query uses the llm category and fills the graph model field.
+2. Enable multimodal captioning. =&gt; The multimodal model query uses the vlm category and fills the multimodal field independently.
+3. Disable each capability after a selection. =&gt; The hidden model value is absent from the submitted payload.</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>Each model field is populated from its own category.
+Caches and selections never mix.
+Disabled capabilities submit no model value.</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>No llm result used for the multimodal field.
+No hidden previous model resubmitted.
+No unverified model name silently defaulted.</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Graph query uses llm and multimodal uses vlm.","Caches are keyed independently.","Disabled capability clears its submitted model."],"inputs":["graph switch","multimodal switch","selected models","query cache keys"],"unit_boundary":"Creation form model queries, caches and hidden value handling"}</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S12" s="5" t="inlineStr"/>
+      <c r="T12" s="5" t="inlineStr"/>
+      <c r="U12" s="5" t="inlineStr"/>
+      <c r="V12" s="5" t="inlineStr"/>
+      <c r="W12" s="5" t="inlineStr"/>
+      <c r="X12" s="5" t="inlineStr"/>
+      <c r="Y12" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z12" s="5" t="inlineStr"/>
+      <c r="AA12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-012</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-014</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Safety guard serializes integer 1 and 0 and never omits an explicit disabled value</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>BE-UT</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Verify create and update serialization of the safety guard including the explicit zero and the absent-value distinction.</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Prepare create and update payloads with the guard enabled, explicitly disabled and absent.</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock","values":["enabled 1","explicit 0","absent"]}</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>1. Build a create payload with the guard enabled and disabled. =&gt; The field is present as integer 1 or explicit 0.
+2. Build an update payload that only changes the guard to off. =&gt; The field survives the update whitelist and is forwarded as 0.
+3. Map a query response that lacks the field. =&gt; The state is reported as unknown rather than confirmed off.</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>Integer 1 and 0 are both serialized.
+An explicit 0 is never dropped by filtering.
+Missing data is not reported as a confirmed disabled state.</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>No boolean or string encoding of the field.
+No field nesting inside graph configuration.
+No Nexent-side content interception added.</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Enabled serializes 1 and disabled serializes 0.","The update whitelist forwards the field.","A missing field maps to unknown."],"inputs":["safety switch state","create payload","update payload","query response without the field"],"unit_boundary":"Safety guard request serialization and query mapping"}</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S13" s="5" t="inlineStr"/>
+      <c r="T13" s="5" t="inlineStr"/>
+      <c r="U13" s="5" t="inlineStr"/>
+      <c r="V13" s="5" t="inlineStr"/>
+      <c r="W13" s="5" t="inlineStr"/>
+      <c r="X13" s="5" t="inlineStr"/>
+      <c r="Y13" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z13" s="5" t="inlineStr"/>
+      <c r="AA13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-D1-001</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-005</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-005</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-RULE-013
+CMSR-RULE-014</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Observer emits safe content before stream completion</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>SDK-UT</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Verify bounded marker lookahead and attempt state reset.</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Create an isolated observer and a controlled chunk sequence.</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock","sequence":"failed partial, rollback, successful split code and think markers"}</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>1. Feed a safe prefix and pause the source. =&gt; The prefix is emitted before flush or commit.
+2. Roll back the first attempt and feed split markers in the second. =&gt; The second output is ordered and contains no first-attempt residue.</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>The earliest safe content is observable before completion.
+Split markers retain their original semantics.</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>No stale fragment crosses attempts.
+No code is executed by the observer.</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Safe prefix emitted before flush.","Raw code tag retained.","No failed-attempt residue."],"inputs":["normal content","split &lt;think&gt; and &lt;/think&gt;","raw &lt;code&gt; content"],"unit_boundary":"Observer.add_model_new_token and attempt lifecycle"}</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_model_attempt_stream.py</t>
+        </is>
+      </c>
+      <c r="U14" s="5" t="inlineStr">
+        <is>
+          <t>test_cmsr_d1_001</t>
+        </is>
+      </c>
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="inlineStr"/>
+      <c r="X14" s="5" t="inlineStr"/>
+      <c r="Y14" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z14" s="5" t="inlineStr">
+        <is>
+          <t>sha256:625e8c8829b51b9cd91344555d05c5ebfdc7bd766d8485eab99b9f22773f3233</t>
+        </is>
+      </c>
+      <c r="AA14" s="5" t="inlineStr">
+        <is>
+          <t>sha256:242f1aaf8a5fe4427f503e5acb8db2cc6cb5096782c2e4fdf49fcb17ec471420</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
           <t>CMSR-D1-002</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-014
 CMSR-RULE-015</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Running step labels precede reasoning and survive retry rollback</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>FE-COMP</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Verify immediate running labels, rollback preservation, legacy history and removal of terminal label-only cards.</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>Create the streaming adapter with a controlled SSE fixture.</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","sequences":["step 1, failed attempt, rollback, successful raw code, parse","legacy content before step label"]}</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="M15" s="5" t="inlineStr">
         <is>
           <t>1. Emit a step label before any model content. =&gt; A running reasoning card displays Step 1 immediately.
 2. Roll back a partial attempt and stream successful raw code. =&gt; Step 1 remains during rollback and only successful raw code follows it.
 3. Parse and reload both new and legacy-order history. =&gt; One code card and one labeled nonempty reasoning card remain; a terminal label-only card is absent.</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>Step label appears before first token.
 Rollback preserves the label.
@@ -1033,326 +2370,326 @@
 Old history prepends late labels.</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="O15" s="5" t="inlineStr">
         <is>
           <t>No failed-attempt content.
 No duplicate code card.
 No sibling invocation mutation.</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="P15" s="5" t="inlineStr">
         <is>
           <t>{"assertions":["Running label is visible before content.","Terminal label-only step is hidden.","Successful code is visible after the label before commit.","History equals live output."],"inputs":["step_count","model_attempt_control","model_output_thinking","parse"],"unit_boundary":"Frontend live and history reasoning projection"}</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr"/>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr">
         <is>
           <t>implemented</t>
         </is>
       </c>
-      <c r="S3" s="5" t="inlineStr">
+      <c r="S15" s="5" t="inlineStr">
         <is>
           <t>custom</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr">
+      <c r="T15" s="5" t="inlineStr">
         <is>
           <t>test/automation/d1/test_reasoning_card.ts</t>
         </is>
       </c>
-      <c r="U3" s="5" t="inlineStr">
+      <c r="U15" s="5" t="inlineStr">
         <is>
           <t>CMSR-D1-002</t>
         </is>
       </c>
-      <c r="V3" s="5" t="inlineStr">
+      <c r="V15" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W3" s="5" t="inlineStr"/>
-      <c r="X3" s="5" t="inlineStr"/>
-      <c r="Y3" s="5" t="inlineStr">
+      <c r="W15" s="5" t="inlineStr"/>
+      <c r="X15" s="5" t="inlineStr"/>
+      <c r="Y15" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z3" s="5" t="inlineStr">
+      <c r="Z15" s="5" t="inlineStr">
         <is>
           <t>sha256:b614502639e969ab0f3840d1381f1b12b01cb5b693a0b02d17387192b230b354</t>
         </is>
       </c>
-      <c r="AA3" s="5" t="inlineStr">
+      <c r="AA15" s="5" t="inlineStr">
         <is>
           <t>sha256:03f5fae5200c76ca296c75ab0ebf225f190fb3fe6a7f52c7c8c7e0da2a97d07c</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>CMSR-D1-003</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-014
 CMSR-RULE-016</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>CoreAgent commits streamed valid semantic repair</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>SDK-UT</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>A protocol-invalid first attempt rolls back while its single preceding step label survives and the corrected result streams and commits.</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>A controlled model yields an invalid response then a pausable valid code action at step one.</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","sequence":"invalid code, rollback, corrected code chunks, commit, parse"}</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>1. Begin step one and return protocol-invalid model content. =&gt; Exactly one step label precedes begin; the attempt rolls back and one repair is scheduled.
 2. Pause the valid repair after its first safe chunk. =&gt; That chunk is visible before model completion.
 3. Complete the repair and classify it. =&gt; Its attempt commits and a single parse follows.</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>Corrected content is streamed and committed.
 Only the corrected action is executed.
 Lifecycle logs identify the repair without content.</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="O16" s="5" t="inlineStr">
         <is>
           <t>No failed content after rollback.
 No repair instruction in user output.
 No suppressed successful stream.</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P16" s="5" t="inlineStr">
         <is>
           <t>{"assertions":["Step label occurs before both model attempts and only once.","Successful repair does not set stream suppression.","Corrected attempt commits once.","Invalid attempt rolls back once."],"inputs":["step one","invalid model content","valid streamed &lt;code&gt; action"],"unit_boundary":"CoreAgent semantic repair and deferred model attempt lifecycle"}</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr">
+      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr">
         <is>
           <t>implemented</t>
         </is>
       </c>
-      <c r="S4" s="5" t="inlineStr">
+      <c r="S16" s="5" t="inlineStr">
         <is>
           <t>pytest</t>
         </is>
       </c>
-      <c r="T4" s="5" t="inlineStr">
+      <c r="T16" s="5" t="inlineStr">
         <is>
           <t>test/automation/d1/test_semantic_repair_stream.py</t>
         </is>
       </c>
-      <c r="U4" s="5" t="inlineStr">
+      <c r="U16" s="5" t="inlineStr">
         <is>
           <t>test_cmsr_d1_003</t>
         </is>
       </c>
-      <c r="V4" s="5" t="inlineStr">
+      <c r="V16" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W4" s="5" t="inlineStr"/>
-      <c r="X4" s="5" t="inlineStr"/>
-      <c r="Y4" s="5" t="inlineStr">
+      <c r="W16" s="5" t="inlineStr"/>
+      <c r="X16" s="5" t="inlineStr"/>
+      <c r="Y16" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z4" s="5" t="inlineStr">
+      <c r="Z16" s="5" t="inlineStr">
         <is>
           <t>sha256:7ef8664f2224d068d7deafecf80f09353d734bc10b35a1147b3cc58d1ae6eacd</t>
         </is>
       </c>
-      <c r="AA4" s="5" t="inlineStr">
+      <c r="AA16" s="5" t="inlineStr">
         <is>
           <t>sha256:1dee7e7ce90f70c40d02907f11be7b55665495fdcaa3dfdec3ab478953c5c38c</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>CMSR-D1-004</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-018</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Rejected model output diagnostics distinguish budget exhaustion without default content leakage</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>SDK-UT</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Correlate each protocol rejection to the model response shape and budget while gating bounded raw previews.</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>Use isolated model diagnostics for a reasoning-only length response and a malformed nonempty response.</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","responses":["length with 4096 reasoning-only output tokens","malformed nonempty code Action"]}</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>1. Reject a reasoning-only length response with diagnostics disabled. =&gt; The log records model, attempt, requested and consumed tokens, reasoning and content counts, and reasoning-only budget exhaustion without raw text.
 2. Reject a malformed content response. =&gt; The distinct protocol reason and response shape are logged under its own attempt identifier.
 3. Enable diagnostic content preview for a rejected response longer than the preview cap. =&gt; Only a single escaped bounded prefix of model content and reasoning is logged; the full text remains absent.</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>Each rejection is attributable to one attempt and specific failure class.
 Raw output is absent by default and bounded on explicit opt-in.</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="O17" s="5" t="inlineStr">
         <is>
           <t>No model output or user prompt enters SSE or persisted history from diagnostics.
 No secret or full raw payload is logged by default.
 No retry-budget or execution behavior changes.</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="P17" s="5" t="inlineStr">
         <is>
           <t>{"assertions":["Reasoning-only budget exhaustion flag is accurate.","Logs include attempt and token counts.","Default logs omit raw content.","Opt-in previews are escaped and capped."],"inputs":["finish_reason=length","reasoning_content","invalid code Action","explicit diagnostic flag"],"unit_boundary":"OpenAI model response diagnostics and CoreAgent protocol-error logging"}</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="inlineStr"/>
-      <c r="R5" s="5" t="inlineStr">
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr">
         <is>
           <t>implemented</t>
         </is>
       </c>
-      <c r="S5" s="5" t="inlineStr">
+      <c r="S17" s="5" t="inlineStr">
         <is>
           <t>pytest</t>
         </is>
       </c>
-      <c r="T5" s="5" t="inlineStr">
+      <c r="T17" s="5" t="inlineStr">
         <is>
           <t>test/automation/d1/test_protocol_rejection_diagnostics.py</t>
         </is>
       </c>
-      <c r="U5" s="5" t="inlineStr">
+      <c r="U17" s="5" t="inlineStr">
         <is>
           <t>test_cmsr_d1_004</t>
         </is>
       </c>
-      <c r="V5" s="5" t="inlineStr">
+      <c r="V17" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W5" s="5" t="inlineStr"/>
-      <c r="X5" s="5" t="inlineStr"/>
-      <c r="Y5" s="5" t="inlineStr">
+      <c r="W17" s="5" t="inlineStr"/>
+      <c r="X17" s="5" t="inlineStr"/>
+      <c r="Y17" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z5" s="5" t="inlineStr">
+      <c r="Z17" s="5" t="inlineStr">
         <is>
           <t>sha256:9f06a6565fff8e542fdcb89725b5fc7f669ad52b07301bdc99aa3e2eba23552c</t>
         </is>
       </c>
-      <c r="AA5" s="5" t="inlineStr">
+      <c r="AA17" s="5" t="inlineStr">
         <is>
           <t>sha256:a53056127d5f2efce4a9d98c92c9c97892451de0d1d353603584612c0a9ef1ba</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1363,7 +2700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1535,20 +2872,452 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>AKPR-D2-001</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-002
+AKPR-RULE-006</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Knowledge base list keeps its contract and adds optional display fields</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>CONTRACT</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Verify the paginated AIDP list proxy keeps its existing request and response contract while exposing the optional display metadata.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>An authenticated request reaches the AIDP management proxy with a controllable upstream fixture.</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>{"keyword":"alpha","page":1,"page_size":10,"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>1. Request the first page with a keyword. =&gt; The proxy forwards page, page_size and keyword and applies the existing permission intersection.
+2. Inspect the response payload. =&gt; Existing fields keep their names and types and the optional display fields appear only when the upstream returns them.
+3. Request a later page. =&gt; Ordering and totals remain consistent with the unfiltered permission-scoped set.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Existing request parameters and response fields are unchanged.
+Optional display metadata is additive.
+Pagination order and totals stay stable.</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>No column filter parameter is introduced.
+No fabricated default replaces a missing metadata value.
+No ES knowledge base endpoint is touched.</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>{"endpoint":"/aidp-mgmt/knowledge-bases","method":"GET","protocol":"HTTP","request_expectations":["page, page_size and keyword behave as before.","The permission-scoped access set is resolved before pagination.","No new required parameter is added."],"response_expectations":["Existing fields keep their current names and types.","Optional display fields are additive and omit a value the upstream did not return.","Page totals equal the permission-scoped count."]}</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr"/>
+      <c r="T2" s="5" t="inlineStr"/>
+      <c r="U2" s="5" t="inlineStr"/>
+      <c r="V2" s="5" t="inlineStr"/>
+      <c r="W2" s="5" t="inlineStr"/>
+      <c r="X2" s="5" t="inlineStr"/>
+      <c r="Y2" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z2" s="5" t="inlineStr"/>
+      <c r="AA2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D2-002</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-010
+AKPR-RULE-011
+AKPR-RULE-012
+AKPR-RULE-013</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Creation request carries the new configuration and keeps legacy field names</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>API-IT</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Verify the create proxy forwards chunking, retrieval, graph, model and safety fields while preserving legacy field names and existing defaults.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>An authenticated create request reaches the AIDP management proxy with a recorded upstream payload.</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>{"chunk_mode":[0,1],"graph_enabled":[true,false],"multimodal":[true,false],"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>1. Submit the minimal creation payload. =&gt; Existing defaults still apply and the legacy field names remain unchanged.
+2. Submit a payload with chunking, retrieval and graph configuration. =&gt; The chunk mode, chunk token fields, similarity, knowledge base Top K and a serialized graph configuration reach the upstream payload.
+3. Submit with the graph and multimodal capabilities disabled. =&gt; The graph configuration and the hidden model fields are absent from the upstream payload.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>New configuration fields reach the upstream request.
+Legacy field names and defaults are preserved.
+Disabled capabilities submit no hidden configuration.</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>No ES knowledge base request shape change.
+No invented graph JSON keys.
+No model value submitted for a disabled capability.</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>{"endpoint":"/aidp-mgmt/knowledge-bases","method":"POST","protocol":"HTTP","request_expectations":["Chunk mode, chunk token and overlap values follow the documented types and bounds.","Graph configuration is serialized as the documented string payload.","Legacy field names remain in place for existing callers."],"response_expectations":["The created knowledge base identifier is returned as before.","Permission and group handling keeps its existing behavior.","A failed upstream create surfaces a stable error without partial local state."]}</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="inlineStr"/>
+      <c r="V3" s="5" t="inlineStr"/>
+      <c r="W3" s="5" t="inlineStr"/>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr"/>
+      <c r="AA3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D2-003</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-014</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Update request forwards an explicit disabled safety guard and reports partial failure</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>CONTRACT</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Verify the safety guard survives the update whitelist, an explicit zero is forwarded and permission success stays distinguishable from metadata failure.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>An authenticated update reaches the AIDP management proxy for a base the caller may edit.</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>{"guard":["enabled to disabled","unchanged","disabled to enabled"],"metadata_failure":true,"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>1. Disable the safety guard and save. =&gt; The upstream metadata payload contains the field as integer 0.
+2. Save again without changing the guard. =&gt; The field is not resent when nothing changed.
+3. Make the upstream metadata update fail after the permission write. =&gt; The response distinguishes saved permissions from a failed metadata update and the readback keeps the previous guard value.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>An explicit 0 is forwarded and an unchanged value is omitted.
+Permission and metadata outcomes are separately reported.
+A metadata failure is never presented as a saved guard value.</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>No silent drop of the disabled value by the field whitelist.
+No boolean encoding.
+No claimed success on upstream failure.</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>{"endpoint":"/aidp-mgmt/knowledge-bases/{kds_id}/permission","method":"PATCH","protocol":"HTTP","request_expectations":["Only explicitly changed metadata fields are sent.","The safety guard is forwarded as an integer when it changed.","Permission and group fields keep their existing rules."],"response_expectations":["Permission save status and metadata update status are reported separately.","A failed metadata update yields a non-success result with the unchanged readback value.","Cache invalidation follows a successful metadata update."]}</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr"/>
+      <c r="W4" s="5" t="inlineStr"/>
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z4" s="5" t="inlineStr"/>
+      <c r="AA4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D2-004</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-012</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Model queries select a single category per control</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>CONTRACT</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Verify the model query proxy passes one category per request and returns only models applicable to the knowledge base application.</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>A controllable upstream model fixture serves distinct payloads per category.</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>{"categories":["llm","vlm","embedding"],"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>1. Query the graph model list. =&gt; The request carries the llm category and the response exposes only llm models.
+2. Query the multimodal model list. =&gt; The request carries the vlm category and the response exposes only vlm models.
+3. Query an unsupported or failing category. =&gt; A stable error or an empty result is returned without falling back to another category.</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>One category is requested per control.
+Responses are not reused across categories.
+Failures do not silently substitute another category.</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>No shared cache entry across categories.
+No fabricated model identifier on failure.
+No change to existing non-AIDP model endpoints.</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>{"endpoint":"/aidp-mgmt/models","method":"GET","protocol":"HTTP","request_expectations":["The service parameter carries exactly one requested category.","The application parameter keeps the knowledge base scope.","No credential is returned to the browser."],"response_expectations":["Only models of the requested category are returned.","An unavailable category yields a stable error or an empty list.","Results are filtered to the knowledge base application scope."]}</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr"/>
+      <c r="U5" s="5" t="inlineStr"/>
+      <c r="V5" s="5" t="inlineStr"/>
+      <c r="W5" s="5" t="inlineStr"/>
+      <c r="X5" s="5" t="inlineStr"/>
+      <c r="Y5" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z5" s="5" t="inlineStr"/>
+      <c r="AA5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
           <t>CMSR-D2-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-013
 CMSR-RULE-014
@@ -1556,47 +3325,47 @@
 CMSR-RULE-016</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>SSE preserves successful retry deltas and attempt controls</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>CONTRACT</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Verify event ordering and prompt publication at the API stream boundary.</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>An authenticated Agent run uses a controllable model-provider fixture.</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","sequences":["transport partial failure then success","semantic invalid response then valid streamed repair"]}</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>1. Begin step one and pause the provider before its first token. =&gt; SSE already contains one step_count before begin and before model content.
 2. Pause the provider after the first safe success fragment. =&gt; The SSE client has already received that fragment with the success attempt ID.
@@ -1604,71 +3373,71 @@
 4. Repeat with step-one protocol-invalid output then valid repair. =&gt; SSE orders one step_count, begin, rollback, begin, corrected content, commit and one parse; corrected content is visible before completion.</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>SSE yields one step label before model output.
 Safe content follows the label before provider completion.
 Every model fragment carries its attempt ID.</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>No duplicate execution event.
 No control event persisted as a message unit.
 No failed semantic output in committed units.</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>{"endpoint":"/agent/run","method":"POST","protocol":"SSE","request_expectations":["The request selects a configured test Agent."],"response_expectations":["Control and model output preserve attempt order.","Successful content is published before completion."]}</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr"/>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr">
         <is>
           <t>implemented</t>
         </is>
       </c>
-      <c r="S2" s="5" t="inlineStr">
+      <c r="S6" s="5" t="inlineStr">
         <is>
           <t>pytest</t>
         </is>
       </c>
-      <c r="T2" s="5" t="inlineStr">
+      <c r="T6" s="5" t="inlineStr">
         <is>
           <t>test/automation/d2/test_model_attempt_sse.py</t>
         </is>
       </c>
-      <c r="U2" s="5" t="inlineStr">
+      <c r="U6" s="5" t="inlineStr">
         <is>
           <t>test_cmsr_d2_001</t>
         </is>
       </c>
-      <c r="V2" s="5" t="inlineStr">
+      <c r="V6" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W2" s="5" t="inlineStr"/>
-      <c r="X2" s="5" t="inlineStr"/>
-      <c r="Y2" s="5" t="inlineStr">
-        <is>
-          <t>校验通过</t>
-        </is>
-      </c>
-      <c r="Z2" s="5" t="inlineStr">
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr">
+        <is>
+          <t>实现哈希失效</t>
+        </is>
+      </c>
+      <c r="Z6" s="5" t="inlineStr">
         <is>
           <t>sha256:9e5d436508638774329620f8bea1420eab531ad470095c935fac5fccc69e894c</t>
         </is>
       </c>
-      <c r="AA2" s="5" t="inlineStr">
+      <c r="AA6" s="5" t="inlineStr">
         <is>
           <t>sha256:570d7db5b7480c6b3a3a3adcc953158f7c496e44a79e90ad1ca3a4df676d573f</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA2"/>
+  <autoFilter ref="A1:AA6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1679,7 +3448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1687,7 +3456,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -1851,20 +3620,255 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>AKPR-D3-001</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-011
+AKPR-RULE-013
+AKPR-RULE-014</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Real AIDP create, readback and safety guard update close the loop</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>INTEGRATION</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Verify against a reachable AIDP service that a created knowledge base returns the submitted chunking, graph and safety configuration and that a later safety guard change is visible on readback. This case stays blocked until the upstream safety guard contract is available on the target environment.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>A reachable AIDP service accepts Nexent credentials.
+The upstream build that exposes the safety guard field is deployed.
+A disposable tenant and user group are available.</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>{"chunk_mode":0,"guard":[1,0],"profile":"real_smoke"}</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>1. Create a knowledge base with chunking, retrieval, graph and safety configuration through the Nexent proxy. =&gt; The upstream accepts the payload and returns a knowledge base identifier.
+2. Read the created knowledge base back. =&gt; The chunking, retrieval, graph and safety values match the submitted configuration.
+3. Disable the safety guard and read it back again. =&gt; The readback reports the disabled state instead of the previous value.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Submitted configuration is readable from the upstream.
+The safety guard round trip works in both directions.
+Failure of the upstream metadata update is distinguishable from success.</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>No duplicate knowledge base created by retries.
+No permission row created without its knowledge base.
+No test data left in a shared tenant.</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>{"cleanup":["Delete the created knowledge base through the proxy.","Remove local permission rows and document tag associations created by the case."],"integration_boundary":["Nexent AIDP knowledge base proxy","Upstream AIDP knowledge base API","Nexent AIDP permission store"],"observations":["Outgoing create payload field names and types","Readback values per configuration group","Permission row and metadata update status after each step"]}</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"real_smoke","required_services":["knowledge-provider"]}]}</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr"/>
+      <c r="T2" s="5" t="inlineStr"/>
+      <c r="U2" s="5" t="inlineStr"/>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>real_smoke</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr"/>
+      <c r="X2" s="5" t="inlineStr"/>
+      <c r="Y2" s="5" t="inlineStr">
+        <is>
+          <t>无需绑定</t>
+        </is>
+      </c>
+      <c r="Z2" s="5" t="inlineStr"/>
+      <c r="AA2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D3-002</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-012</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Real model categories return only their own models and survive readback</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>INTEGRATION</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Verify against a reachable AIDP service that each model control receives its own category and that a configuration selected from real models is accepted and readable. This case stays blocked until a real AIDP environment with a model inventory is reachable.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>A reachable AIDP service exposes llm, vlm and embedding model inventories.
+At least one model exists in the llm and vlm categories.</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>{"categories":["llm","vlm","embedding"],"profile":"real_smoke"}</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>1. Query each model category through the Nexent proxy. =&gt; Each response contains only models of the requested category and scope.
+2. Create a knowledge base using a real llm model for the graph and a real vlm model for multimodal captioning. =&gt; The upstream accepts both model fields.
+3. Read the knowledge base back. =&gt; The graph and multimodal model fields match the submitted values.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Category queries stay separated.
+Both model fields are accepted and readable.
+No unverified default model replaces a missing selection.</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>No model from one category submitted through another category control.
+No credential exposed to the browser.
+No change to non-AIDP model configuration.</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>{"cleanup":["Delete the created knowledge base through the proxy.","Discard recorded model identifiers that are environment specific."],"integration_boundary":["Nexent AIDP model query proxy","Upstream AIDP model inventory API","Nexent AIDP knowledge base create path"],"observations":["Requested category per query","Returned model identifiers and their categories","Readback values for both model fields"]}</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"real_smoke","required_services":["knowledge-provider"]}]}</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="inlineStr"/>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>real_smoke</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr"/>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>无需绑定</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr"/>
+      <c r="AA3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
           <t>CMSR-D3-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-013
 CMSR-RULE-014
@@ -1872,47 +3876,47 @@
 CMSR-RULE-016</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Agent retry streams success and persists only committed output</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>AGENT-IT</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Verify the full Nexent Agent, observer, SSE and persistence path with controlled provider failure.</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>Local Nexent services and a disposable test conversation are available.</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","sequences":["partial transport failure then success","step-one protocol invalid then valid paused repair"]}</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>1. Start the Agent and fail its first response after a visible fragment. =&gt; Step 1 is emitted before begin and remains after rollback.
 2. Pause the successful response after safe content. =&gt; The SSE consumer receives it before provider completion.
@@ -1920,7 +3924,7 @@
 4. Repeat with semantic repair and inspect database units. =&gt; Only corrected raw model output is stored; its fragments appeared before completion.</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>Step 1 precedes all model chunks and is stored once.
 Successful text is incremental.
@@ -1928,61 +3932,61 @@
 History matches committed SSE.</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>No failed-fragment persistence.
 No duplicate tool execution.
 No extra model request.</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>{"cleanup":["Delete the disposable conversation and provider fixture."],"integration_boundary":["Agent runtime to provider fixture","Observer to SSE","SSE to conversation persistence"],"observations":["Attempt control order","SSE arrival before provider release","persisted message units","sanitized repair lifecycle logs"]}</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>{"profiles":[{"name":"mock","required_services":["model-provider"]},{"name":"real_smoke","required_services":["model-provider"]}]}</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="S2" s="5" t="inlineStr"/>
-      <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr"/>
-      <c r="V2" s="5" t="inlineStr">
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>mock
 real_smoke</t>
         </is>
       </c>
-      <c r="W2" s="5" t="inlineStr">
+      <c r="W4" s="5" t="inlineStr">
         <is>
           <t>model-provider</t>
         </is>
       </c>
-      <c r="X2" s="5" t="inlineStr"/>
-      <c r="Y2" s="5" t="inlineStr">
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z2" s="5" t="inlineStr">
+      <c r="Z4" s="5" t="inlineStr">
         <is>
           <t>sha256:f6ba2ceeb76ca6051b3f305afac2f932ad4f1148a2201ea8471d0cbaae207b6e</t>
         </is>
       </c>
-      <c r="AA2" s="5" t="inlineStr">
+      <c r="AA4" s="5" t="inlineStr">
         <is>
           <t>sha256:4f53cda18c2baa0c0354bb5f9a3ecbe5ed12ab4d8e11ba873c2f11161202b945</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA2"/>
+  <autoFilter ref="A1:AA4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1993,7 +3997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2165,20 +4169,499 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>AKPR-D4-001</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-001
+AKPR-RULE-002
+AKPR-RULE-003
+AKPR-RULE-004
+AKPR-RULE-005</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Overview journey keeps the guide, search, view and column state across the file view</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Verify the complete overview journey in a browser against a deployed instance. This case stays blocked until a disposable Nexent deployment with the AIDP flag enabled and reachable AIDP data is available.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>A deployed Nexent instance runs this worktree with the AIDP flag enabled.
+The test tenant can see more than one knowledge base.
+A writable knowledge base with at least one document exists.</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>{"keyword":"alpha","page_size":10,"profile":"real_smoke"}</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>1. Open the knowledge base page and inspect the guide. =&gt; The explanation and the three steps are visible, collapse and reopen work, and cards are the default view.
+2. Search a name, move to a later page, switch to the table and hide one column. =&gt; The table shows the filtered result set on the same page and the hidden column disappears.
+3. Open a knowledge base from the table. =&gt; The full-page file view shows only that base files.
+4. Return to the overview. =&gt; The keyword, page, table view and hidden column state are restored.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>The guide, card default, search, view switch and column setting all work in the browser.
+The file view is scoped to the selected base.
+Returning restores the earlier overview state.</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>No modification request from view or column changes.
+No state reset after returning.
+No ES knowledge base page rendered while the AIDP flag is enabled.</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>{"actor":"Authenticated test tenant user","failure_evidence":["Retain browser screenshot, network log and console trace on failure."],"final_business_result":["A user can browse, filter and configure the knowledge base overview and reach one base file view without losing context."],"journey":["Open the knowledge base overview.","Expand and collapse the guide.","Search, page and switch views while hiding a column.","Open a knowledge base and return to the overview."]}</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"real_smoke","required_services":["knowledge-provider"]}]}</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr"/>
+      <c r="T2" s="5" t="inlineStr"/>
+      <c r="U2" s="5" t="inlineStr"/>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>real_smoke</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr"/>
+      <c r="X2" s="5" t="inlineStr"/>
+      <c r="Y2" s="5" t="inlineStr">
+        <is>
+          <t>无需绑定</t>
+        </is>
+      </c>
+      <c r="Z2" s="5" t="inlineStr"/>
+      <c r="AA2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D4-002</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-009</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>File view journey uploads, polls, downloads and deletes under permission control</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Verify the restored file operations in a browser against a deployed instance. This case stays blocked until a disposable Nexent deployment with reachable AIDP upload and document services is available.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>A deployed Nexent instance runs this worktree with the AIDP flag enabled.
+The test user owns an editable knowledge base and can read another one.
+A small local document is prepared for upload.</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>{"documents":2,"one_failing_upload":true,"profile":"real_smoke"}</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>1. Open the writable knowledge base and upload a document. =&gt; The document appears and its processing status reaches a terminal state through polling.
+2. Download the processed document. =&gt; The browser receives the original file with its name.
+3. Delete the document and confirm the dialog. =&gt; The document disappears from the list and the deletion reports its own result.
+4. Open the read-only knowledge base and attempt the same operations. =&gt; Upload and delete are unavailable while browsing and download remain permitted.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Upload reaches a terminal processing state.
+The downloaded file matches the uploaded original.
+Deletion removes the document after confirmation.
+Permission gates match the documented read and edit rules.</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>No upload or delete entry for a read-only base.
+No polling continues after leaving the file view.
+No document of another base rendered in the current view.</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>{"actor":"Authenticated test tenant user","failure_evidence":["Retain browser screenshot, network log, downloaded file metadata and console trace on failure."],"final_business_result":["A user with edit permission can add, retrieve and remove documents while a read-only user can only browse and download them."],"journey":["Open a writable knowledge base file view.","Upload and wait for processing to finish.","Download the document.","Delete the document with confirmation.","Check the same controls on a read-only base."]}</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"real_smoke","required_services":["knowledge-provider"]}]}</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="inlineStr"/>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>real_smoke</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr"/>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>无需绑定</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr"/>
+      <c r="AA3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D4-003</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-010
+AKPR-RULE-011
+AKPR-RULE-012
+AKPR-RULE-013
+AKPR-RULE-014</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Creation page journey configures two steps and reports creation and upload results separately</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Verify the dedicated two-step creation page in a browser including conditional graph and multimodal sections and the separate creation and upload outcomes. This case stays blocked until a disposable Nexent deployment with reachable AIDP services is available.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>A deployed Nexent instance runs this worktree with the AIDP flag enabled.
+The test user belongs to a valid group for a shared permission.
+A local document and an intentionally rejected document are prepared.</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>{"chunk_mode":1,"graph_enabled":true,"multimodal":true,"profile":"real_smoke"}</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>1. Open the creation page, fill the first step and toggle the graph and multimodal sections. =&gt; The conditional sections appear with their own model selections and permission fields stay in the first step.
+2. Press next and then return to the first step. =&gt; No knowledge base exists yet and the form values and selected files are preserved.
+3. Submit with one accepted and one rejected file. =&gt; The knowledge base is created once, the accepted file processes and the rejected file is reported as a separate failure.
+4. Retry only the failed file. =&gt; No second knowledge base is created and the retry targets the failed file only.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>The two-step flow holds its state and creates nothing early.
+Conditional graph and multimodal configuration is submitted with the chosen models.
+Creation and upload outcomes are reported separately and retrying never duplicates the base.</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>No knowledge base created before final submission or twice after a retry.
+No hidden graph or multimodal configuration submitted when disabled.
+No upload attempted before a successful creation.</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>{"actor":"Authenticated test tenant user","failure_evidence":["Retain browser screenshot, network log of create and upload requests, and console trace on failure."],"final_business_result":["A user can create one properly configured knowledge base and see which files were accepted and which failed without creating duplicates."],"journey":["Open the dedicated creation page.","Configure the first step including permissions and capabilities.","Advance to the upload step and back.","Submit with a partially failing file set.","Retry the failed file."]}</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"real_smoke","required_services":["knowledge-provider"]}]}</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>real_smoke</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr"/>
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>无需绑定</t>
+        </is>
+      </c>
+      <c r="Z4" s="5" t="inlineStr"/>
+      <c r="AA4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D4-004</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-008</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>ES deployment still renders the original knowledge base page</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Verify that with the AIDP flag disabled the original ES knowledge base page renders unchanged. This case stays blocked until a disposable deployment or a flag configuration switch is available for browser verification.</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>A deployed Nexent instance can run with the AIDP flag disabled.
+The same instance serves the ES knowledge base data.</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>{"aidp_flag":false,"profile":"real_smoke"}</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>1. Open the knowledge base page with the AIDP flag disabled. =&gt; The original ES knowledge base page renders without the AIDP guide, card overview or AIDP file view.
+2. Exercise the original list, creation and document interactions. =&gt; Existing ES behavior is unchanged.
+3. Inspect the requests issued by the page. =&gt; No AIDP management endpoint is called.</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>The ES page is untouched.
+No AIDP component renders in the ES path.
+No AIDP request is issued.</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>No AIDP request from the ES page.
+No visual or behavioral change to the ES list and document flows.
+No new ES write request.</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>{"actor":"Authenticated test tenant user","failure_evidence":["Retain browser screenshot, network log and console trace on failure."],"final_business_result":["An ES deployment keeps its original knowledge base experience with no AIDP leakage."],"journey":["Switch the deployment flag off.","Open the knowledge base page.","Exercise the original list and document interactions."]}</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"real_smoke","required_services":[]}]}</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr"/>
+      <c r="U5" s="5" t="inlineStr"/>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>real_smoke</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr"/>
+      <c r="X5" s="5" t="inlineStr"/>
+      <c r="Y5" s="5" t="inlineStr">
+        <is>
+          <t>无需绑定</t>
+        </is>
+      </c>
+      <c r="Z5" s="5" t="inlineStr"/>
+      <c r="AA5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
           <t>CMSR-D4-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-013
 CMSR-RULE-014
@@ -2186,48 +4669,48 @@
 CMSR-RULE-016</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Browser shows retry output incrementally without blank steps</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>E2E</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Verify a user sees only successful raw code and one executed action in a real conversation.</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>A local Nexent instance
 test tenant and controllable model provider are configured.</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","sequences":["failed transport partial then success","step-one invalid protocol then valid paused repair"]}</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>1. Open Agent chat and send the fixed prompt. =&gt; Step 1 appears before the first model token; the first partial output is then rolled back while the label remains.
 2. Pause the second provider response after its first safe fragment. =&gt; The reasoning card displays the successful raw fragment before provider completion.
@@ -2235,7 +4718,7 @@
 4. Repeat in a new conversation with semantic repair at step one. =&gt; Corrected raw code is visible during the pause and after refresh; Connecting does not persist.</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>Running Step 1 is visible before content.
 No terminal label-only reasoning card.
@@ -2243,59 +4726,59 @@
 Refreshed history matches the final UI.</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>No failed partial text after rollback.
 No duplicate execution card.</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>{"actor":"Authenticated test tenant user","failure_evidence":["Retain browser screenshot","network timing and console trace on failure."],"final_business_result":["Only the committed attempt and its single executed code action are visible."],"journey":["Open the Agent conversation.","Trigger controlled retry.","Observe streaming.","Reload and inspect history."]}</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>{"profiles":[{"name":"mock","required_services":["model-provider"]}]}</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="R6" s="5" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="S2" s="5" t="inlineStr"/>
-      <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr"/>
-      <c r="V2" s="5" t="inlineStr">
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W2" s="5" t="inlineStr">
+      <c r="W6" s="5" t="inlineStr">
         <is>
           <t>model-provider</t>
         </is>
       </c>
-      <c r="X2" s="5" t="inlineStr"/>
-      <c r="Y2" s="5" t="inlineStr">
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z2" s="5" t="inlineStr">
+      <c r="Z6" s="5" t="inlineStr">
         <is>
           <t>sha256:f110f582fe091286fdaa5301f8bdc22703bf583fc7c6c95214ae8c8187a612a1</t>
         </is>
       </c>
-      <c r="AA2" s="5" t="inlineStr">
+      <c r="AA6" s="5" t="inlineStr">
         <is>
           <t>sha256:4f53cda18c2baa0c0354bb5f9a3ecbe5ed12ab4d8e11ba873c2f11161202b945</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA2"/>
+  <autoFilter ref="A1:AA6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2306,7 +4789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2320,12 +4803,12 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="42" customWidth="1" min="11" max="11"/>
-    <col width="33" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
     <col width="42" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
     <col width="42" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="42" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
@@ -2478,20 +4961,488 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>AKPR-D5-001</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-007
+AKPR-RULE-014</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Restricted users never reach a modification endpoint</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>SECURITY</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Verify across the overview, file view and creation page that permission and group rules block modification requests at the boundary. This case stays blocked until a disposable deployment with multiple permission roles is available.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>A deployed instance has a read-only user, a group-less user and an edit user on one knowledge base.
+Request logging is available.</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"real_smoke","roles":["READ_ONLY","USER without group","EDIT"]}</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>1. As the read-only user, open the base and attempt edit, upload, delete and safety guard changes. =&gt; No modification entry is executable and no modification request is issued.
+2. As a user without a valid group, submit the creation first step with a shared permission. =&gt; The submission is rejected and no knowledge base is created.
+3. As the edit user, perform the same operations. =&gt; Only the permitted operations issue requests and they succeed.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Disabled or hidden entries emit no request.
+Group validation rejects an invalid shared permission before creation.
+Permitted operations behave normally.</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>No modification request from a restricted role.
+No local-only permission change without the upstream counterpart.
+No exposure of upstream credentials in any error path.</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>{"condition":["Read-only permission on the selected knowledge base.","Shared permission without a valid same-tenant group.","Unavailable resource state."],"metrics":["Count of modification requests by a restricted role.","Count of knowledge bases created from an invalid group submission."],"recovery_expectations":["After the rejected attempt the UI keeps the previous state and reports the failure without claiming success."],"risk":"A user without edit permission could modify a knowledge base or its safety configuration through a stale or unguarded UI entry.","risk_type":"SECURITY","thresholds":["Zero modification requests from restricted roles.","Zero resources created from an invalid group submission."]}</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"real_smoke","required_services":["knowledge-provider"]}]}</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr"/>
+      <c r="T2" s="5" t="inlineStr"/>
+      <c r="U2" s="5" t="inlineStr"/>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>real_smoke</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr"/>
+      <c r="X2" s="5" t="inlineStr"/>
+      <c r="Y2" s="5" t="inlineStr">
+        <is>
+          <t>无需绑定</t>
+        </is>
+      </c>
+      <c r="Z2" s="5" t="inlineStr"/>
+      <c r="AA2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D5-002</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-005
+AKPR-RULE-009</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Delayed responses and polling never cross knowledge base boundaries</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>RELIABILITY</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Verify that switching or leaving the file view discards in-flight results, stops polling and never renders another base document list. This case stays blocked until a deployment with a controllable slow upstream is available.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>A deployed instance can delay document responses.
+Two knowledge bases with distinct documents exist.</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>{"bases":2,"delay_seconds":5,"profile":"real_smoke"}</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>1. Open the first base and immediately switch to the second. =&gt; The first base documents never render in the second and the later response is discarded.
+2. Upload a document and leave the file view before processing completes. =&gt; Polling stops after leaving and no late update reaches the overview.
+3. Repeat the switch several times and inspect the rendered list. =&gt; Only the current base documents appear and the list state matches the last selection.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>No stale document list is rendered.
+Polling stops when the view is left.
+The current base is always the one displayed.</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>No orphan polling loop after navigation.
+No document count or status from another base.
+No duplicate document rows after repeated switching.</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>{"condition":["Slow upstream document responses.","Rapid switching between knowledge bases.","Navigating away while uploads are processing."],"metrics":["Count of discarded late responses.","Polling cycles after leaving the file view.","Rendered document count per base."],"recovery_expectations":["Reopening a base shows its own current documents and a correct processing state."],"risk":"A late response from a previously opened knowledge base can overwrite the current file view or leave polling running.","risk_type":"RELIABILITY","thresholds":["Zero cross-base document renders.","Zero polling cycles after leaving the view."]}</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"real_smoke","required_services":["knowledge-provider"]}]}</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="inlineStr"/>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>real_smoke</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr"/>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>无需绑定</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr"/>
+      <c r="AA3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D5-003</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-012
+AKPR-RULE-013
+AKPR-RULE-014</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Disabled capabilities and missing remote values are never reported as active or saved</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>SECURITY</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Verify that hidden configuration is not resubmitted, that missing remote values stay unknown and that a failed save is never presented as success. This case stays blocked until a deployment with a controllable upstream failure mode and the upstream safety contract is available.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>A deployed instance can reject a metadata update on demand.
+A knowledge base created before the safety field existed is available for readback.</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>{"graph":[true,false],"guard_absent":true,"multimodal":[true,false],"profile":"real_smoke"}</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>1. Create a knowledge base with the graph and multimodal capabilities disabled. =&gt; No graph configuration and no hidden model field reaches the upstream request.
+2. Read back a knowledge base whose response omits the safety field. =&gt; The UI reports the state as unknown instead of confirmed disabled.
+3. Fail the metadata update after the guard change and inspect the UI. =&gt; The change is reported as not saved and the previous value remains displayed.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Hidden configuration stays out of requests.
+Missing remote values are not converted into confirmed states.
+Failed saves are visible as failures.</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>No resubmission of a previously selected hidden model.
+No success message after a failed upstream update.
+No safety field nested inside graph configuration.</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>{"condition":["Graph or multimodal capability disabled after a selection.","Upstream response without the safety field.","Metadata update failure after a permission save."],"metrics":["Count of hidden configuration fields in outgoing payloads.","Count of success messages after failed updates."],"recovery_expectations":["After a failed save the previous remote value stays displayed and a retry re-sends the explicit value."],"risk":"A user could believe a safety guard or graph configuration is active while the remote state is unknown or a save failed.","risk_type":"SECURITY","thresholds":["Zero hidden configuration fields in requests.","Zero false success reports."]}</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"real_smoke","required_services":["knowledge-provider"]}]}</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>real_smoke</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr"/>
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>无需绑定</t>
+        </is>
+      </c>
+      <c r="Z4" s="5" t="inlineStr"/>
+      <c r="AA4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D5-004</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-010</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Creation and upload failures leave exactly one consistent knowledge base</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>RELIABILITY</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Verify that failures around creation and upload never produce duplicate knowledge bases or permission rows without their knowledge base. This case stays blocked until a deployment with controllable upstream create and upload failures is available.</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>A deployed instance can fail creation and file uploads on demand.
+Permission rows are inspectable for the test tenant.</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>{"create_failures":1,"profile":"real_smoke","upload_failures":2}</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>1. Fail the create request and inspect local state. =&gt; No knowledge base and no orphan permission row remain.
+2. Create successfully with two failing uploads and retry them. =&gt; One knowledge base exists and the retries never create another.
+3. Interrupt the submission and reload the creation page. =&gt; No duplicate resource appears and the user can identify the outcome of the previous attempt.</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>Exactly one knowledge base exists after retries.
+Permission rows always belong to an existing knowledge base.
+Interrupted submissions do not silently duplicate resources.</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>No duplicate knowledge base after retry or reload.
+No orphan permission row.
+No upload executed before a successful create.</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>{"condition":["Create failure.","Partial upload failure with retry.","Submission interrupted before a response arrives."],"metrics":["Knowledge bases created per submission attempt.","Orphan permission rows.","Upload attempts before a successful create."],"recovery_expectations":["The created knowledge base stays usable and the failed files can be retried without creating a new base."],"risk":"Retrying a partially failed creation can create duplicate knowledge bases or inconsistent permission records.","risk_type":"RELIABILITY","thresholds":["At most one knowledge base per intended submission.","Zero orphan permission rows."]}</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"real_smoke","required_services":["knowledge-provider"]}]}</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr"/>
+      <c r="U5" s="5" t="inlineStr"/>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>real_smoke</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr"/>
+      <c r="X5" s="5" t="inlineStr"/>
+      <c r="Y5" s="5" t="inlineStr">
+        <is>
+          <t>无需绑定</t>
+        </is>
+      </c>
+      <c r="Z5" s="5" t="inlineStr"/>
+      <c r="AA5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
           <t>CMSR-D5-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-014
 CMSR-RULE-015
@@ -2500,47 +5451,47 @@
 CMSR-RULE-018</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Repeated partial failures never leak across attempts or siblings</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>RELIABILITY</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Verify rollback isolation under repeated partial streams and parallel sub-agent output.</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>A controlled provider can interleave parent and sibling outputs.</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>{"failures":4,"profile":"mock"}</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>1. Inject four partial failures and a fifth successful response while sibling output interleaves. =&gt; The retry budget is respected.
 2. Inspect final UI and stored output. =&gt; Only fifth-attempt and sibling content remain.
@@ -2549,58 +5500,58 @@
 5. Inject repeated reasoning-only length responses with diagnostic preview disabled. =&gt; Each rejection is correlated to its budget and attempt while no raw reasoning or user text enters logs or persisted output.</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>Successful and sibling content are complete.
 Failed attempts leave zero fragments.</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>No sixth provider call.
 No cross-invocation deletion.
 No failed-fragment persistence.</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>{"condition":["Four partial failures followed by a success.","Parallel sibling output."],"metrics":["Provider request count.","Failed-fragment count in SSE projection and persisted units."],"recovery_expectations":["The committed attempt and sibling output remain readable after refresh."],"risk":"Stale partial output can leak after repeated retries or corrupt sibling cards.","risk_type":"RELIABILITY","thresholds":["At most five physical requests.","Zero failed fragments after rollback."]}</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr"/>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="S2" s="5" t="inlineStr"/>
-      <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr"/>
-      <c r="V2" s="5" t="inlineStr"/>
-      <c r="W2" s="5" t="inlineStr">
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr">
         <is>
           <t>model-provider</t>
         </is>
       </c>
-      <c r="X2" s="5" t="inlineStr"/>
-      <c r="Y2" s="5" t="inlineStr">
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z2" s="5" t="inlineStr">
+      <c r="Z6" s="5" t="inlineStr">
         <is>
           <t>sha256:50b69a0b1ee496cbb14b84e51bb80e7f92f3aaecd2d694c095013d056f678861</t>
         </is>
       </c>
-      <c r="AA2" s="5" t="inlineStr">
+      <c r="AA6" s="5" t="inlineStr">
         <is>
           <t>sha256:4f53cda18c2baa0c0354bb5f9a3ecbe5ed12ab4d8e11ba873c2f11161202b945</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA2"/>
+  <autoFilter ref="A1:AA6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/test/generated/Nexent_测试基线.xlsx
+++ b/test/generated/Nexent_测试基线.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AA4" s="5" t="inlineStr">
         <is>
-          <t>sha256:1dee7e7ce90f70c40d02907f11be7b55665495fdcaa3dfdec3ab478953c5c38c</t>
+          <t>sha256:1e23ba2952b874e8029345d74ff832663be433870e57e403ccac4370e9237916</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AA2" s="5" t="inlineStr">
         <is>
-          <t>sha256:570d7db5b7480c6b3a3a3adcc953158f7c496e44a79e90ad1ca3a4df676d573f</t>
+          <t>sha256:f8f1bc3e7a01d6ffd739d9fbe695e28533e4c410847a09b6405a7dbd4c2e948a</t>
         </is>
       </c>
     </row>

--- a/test/generated/Nexent_测试基线.xlsx
+++ b/test/generated/Nexent_测试基线.xlsx
@@ -16,11 +16,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_D5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_功能清单'!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_D1'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_功能清单'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_D1'!$A$1:$AA$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_D2'!$A$1:$AA$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_D3'!$A$1:$AA$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_D4'!$A$1:$AA$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_D4'!$A$1:$AA$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_D5'!$A$1:$AA$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -551,10 +551,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
@@ -603,25 +603,67 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>AGENT-LIST-VIEWS</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Agent list grid and table views</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Switch between the existing agent cards and a data-backed table without changing page-level content or agent operations.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-LIST-RULE-001
+AGENT-LIST-RULE-002
+AGENT-LIST-RULE-003
+AGENT-LIST-RULE-004
+AGENT-LIST-RULE-005</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>D1
+D4</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>{"notes":"User request and same-page WeMeeting high-fidelity reference; no Edge window inspected.","requirement_ids":["AGENT-LIST-REQ-001","AGENT-LIST-REQ-002"],"spec_path":"docs/handoffs/2026-10-08-agent-list-high-fidelity.md"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Silent model retry stream visibility</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Successful model attempts stream raw content while failed attempts leave no visible or persisted fragments.</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-013
 CMSR-RULE-014
@@ -631,7 +673,7 @@
 CMSR-RULE-018</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>D1
 D2
@@ -640,14 +682,14 @@
 D5</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>{"requirement_ids":["CMSR-005"],"spec_path":"nexent-doc/docs/Developing/chat-message-model-silent-retry/proposal.md"}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -658,13 +700,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -681,7 +723,7 @@
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="25" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -830,38 +872,42 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>CMSR-D1-001</t>
+          <t>AGENT-LIST-D1-001</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>CMSR-005</t>
+          <t>AGENT-LIST-VIEWS</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>CMSR-005</t>
+          <t>AGENT-LIST-REQ-001
+AGENT-LIST-REQ-002</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>CMSR-RULE-013
-CMSR-RULE-014</t>
+          <t>AGENT-LIST-RULE-001
+AGENT-LIST-RULE-002
+AGENT-LIST-RULE-003
+AGENT-LIST-RULE-004
+AGENT-LIST-RULE-005</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Observer emits safe content before stream completion</t>
+          <t>Render table view with data-backed agent metadata</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>SDK-UT</t>
+          <t>FE-COMP</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
@@ -876,40 +922,47 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Verify bounded marker lookahead and attempt state reset.</t>
+          <t>Verify Ant Design table rendering, including header separators and content-based sizing constraints, plus columns, row data, update-time source, and action callbacks without changing the card view contract.</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>Create an isolated observer and a controlled chunk sequence.</t>
+          <t>Render the table with agents containing author, tags, status, and update_time values.
+Render a second agent without update_time but with create_time.</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>{"profile":"mock","sequence":"failed partial, rollback, successful split code and think markers"}</t>
+          <t>{"no_update_agent":{"author":null,"create_time":"2026-09-17T10:30:00","update_time":null},"profile":"mock","updated_agent":{"author":"刘晨","tags":["保健"],"update_time":"2026-09-18T10:30:00"}}</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>1. Feed a safe prefix and pause the source. =&gt; The prefix is emitted before flush or commit.
-2. Roll back the first attempt and feed split markers in the second. =&gt; The second output is ordered and contains no first-attempt residue.</t>
+          <t>1. Render the table with the mocked agent rows. =&gt; The seven columns appear in the specified order in StandardTable backed by Ant Design Table; internal header columns have 1px
+2. Render a row whose update_time is absent and whose create_time is present. =&gt; The update-time cell shows the missing-value placeholder rather than the creation date.
+3. Trigger the row's detail, configure, and publish actions. =&gt; Each callback receives the corresponding agent or numeric agent ID.</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
-          <t>The earliest safe content is observable before completion.
-Split markers retain their original semantics.</t>
+          <t>The table labels include 更新时间 and do not label agents as knowledge bases.
+The table is rendered through StandardTable with the documented typography, backgrounds, 40px rows,
+The table wrapper uses content-based height up to 500px and internal overflow scrolling; it is not forced to fill unused space.
+Update time is formatted from update_time only; missing or invalid timestamps do not fall back to create_time.
+Creator uses author when present and a placeholder when absent.
+The card component and its data behavior remain unchanged.</t>
         </is>
       </c>
       <c r="O2" s="5" t="inlineStr">
         <is>
-          <t>No stale fragment crosses attempts.
-No code is executed by the observer.</t>
+          <t>Do not modify page title, guide area, tabs, or card-mode content.
+Do not add or change backend requests or response contracts.
+Do not fabricate creator or update-time values.</t>
         </is>
       </c>
       <c r="P2" s="5" t="inlineStr">
         <is>
-          <t>{"assertions":["Safe prefix emitted before flush.","Raw code tag retained.","No failed-attempt residue."],"inputs":["normal content","split &lt;think&gt; and &lt;/think&gt;","raw &lt;code&gt; content"],"unit_boundary":"Observer.add_model_new_token and attempt lifecycle"}</t>
+          <t>{"assertions":["Table headers render in the required order.","Update time never falls back to create_time.","Missing creator and timestamp values render placeholders.","Action callbacks receive the correct row data.","Header separators are 14px high, vertically centered, and","The scroll wrapper is content-sized with a 500px maximum rather than flex-growing to fill unused space."],"inputs":["agent rows","locale strings","row-action callbacks"],"unit_boundary":"AgentListTable React component with mocked callbacks and translation."}</t>
         </is>
       </c>
       <c r="Q2" s="5" t="inlineStr"/>
@@ -920,17 +973,17 @@
       </c>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>pytest</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="T2" s="5" t="inlineStr">
         <is>
-          <t>test/automation/d1/test_model_attempt_stream.py</t>
+          <t>test/automation/d1/run_agent_list_table_test.mjs</t>
         </is>
       </c>
       <c r="U2" s="5" t="inlineStr">
         <is>
-          <t>test_cmsr_d1_001</t>
+          <t>agentListTable.test.tsx</t>
         </is>
       </c>
       <c r="V2" s="5" t="inlineStr">
@@ -947,85 +1000,214 @@
       </c>
       <c r="Z2" s="5" t="inlineStr">
         <is>
-          <t>sha256:625e8c8829b51b9cd91344555d05c5ebfdc7bd766d8485eab99b9f22773f3233</t>
+          <t>sha256:42084a90cedb1ae8ffba7cbe7cf1411f12a57a0d42205e6580e12ad08042aeb9</t>
         </is>
       </c>
       <c r="AA2" s="5" t="inlineStr">
         <is>
-          <t>sha256:242f1aaf8a5fe4427f503e5acb8db2cc6cb5096782c2e4fdf49fcb17ec471420</t>
+          <t>sha256:6dd34b7871a706a8b5fc3aa75f7a0dce8d785c1dbc328369e21a9b47cebef59e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
+          <t>CMSR-D1-001</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-005</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-005</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-RULE-013
+CMSR-RULE-014</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Observer emits safe content before stream completion</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>SDK-UT</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Verify bounded marker lookahead and attempt state reset.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Create an isolated observer and a controlled chunk sequence.</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock","sequence":"failed partial, rollback, successful split code and think markers"}</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>1. Feed a safe prefix and pause the source. =&gt; The prefix is emitted before flush or commit.
+2. Roll back the first attempt and feed split markers in the second. =&gt; The second output is ordered and contains no first-attempt residue.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>The earliest safe content is observable before completion.
+Split markers retain their original semantics.</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>No stale fragment crosses attempts.
+No code is executed by the observer.</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Safe prefix emitted before flush.","Raw code tag retained.","No failed-attempt residue."],"inputs":["normal content","split &lt;think&gt; and &lt;/think&gt;","raw &lt;code&gt; content"],"unit_boundary":"Observer.add_model_new_token and attempt lifecycle"}</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_model_attempt_stream.py</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>test_cmsr_d1_001</t>
+        </is>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr"/>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr">
+        <is>
+          <t>sha256:625e8c8829b51b9cd91344555d05c5ebfdc7bd766d8485eab99b9f22773f3233</t>
+        </is>
+      </c>
+      <c r="AA3" s="5" t="inlineStr">
+        <is>
+          <t>sha256:242f1aaf8a5fe4427f503e5acb8db2cc6cb5096782c2e4fdf49fcb17ec471420</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
           <t>CMSR-D1-002</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-014
 CMSR-RULE-015</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Running step labels precede reasoning and survive retry rollback</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>FE-COMP</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Verify immediate running labels, rollback preservation, legacy history and removal of terminal label-only cards.</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>Create the streaming adapter with a controlled SSE fixture.</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","sequences":["step 1, failed attempt, rollback, successful raw code, parse","legacy content before step label"]}</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>1. Emit a step label before any model content. =&gt; A running reasoning card displays Step 1 immediately.
 2. Roll back a partial attempt and stream successful raw code. =&gt; Step 1 remains during rollback and only successful raw code follows it.
 3. Parse and reload both new and legacy-order history. =&gt; One code card and one labeled nonempty reasoning card remain; a terminal label-only card is absent.</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>Step label appears before first token.
 Rollback preserves the label.
@@ -1033,326 +1215,326 @@
 Old history prepends late labels.</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>No failed-attempt content.
 No duplicate code card.
 No sibling invocation mutation.</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>{"assertions":["Running label is visible before content.","Terminal label-only step is hidden.","Successful code is visible after the label before commit.","History equals live output."],"inputs":["step_count","model_attempt_control","model_output_thinking","parse"],"unit_boundary":"Frontend live and history reasoning projection"}</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr"/>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>implemented</t>
         </is>
       </c>
-      <c r="S3" s="5" t="inlineStr">
+      <c r="S4" s="5" t="inlineStr">
         <is>
           <t>custom</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr">
+      <c r="T4" s="5" t="inlineStr">
         <is>
           <t>test/automation/d1/test_reasoning_card.ts</t>
         </is>
       </c>
-      <c r="U3" s="5" t="inlineStr">
+      <c r="U4" s="5" t="inlineStr">
         <is>
           <t>CMSR-D1-002</t>
         </is>
       </c>
-      <c r="V3" s="5" t="inlineStr">
+      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W3" s="5" t="inlineStr"/>
-      <c r="X3" s="5" t="inlineStr"/>
-      <c r="Y3" s="5" t="inlineStr">
+      <c r="W4" s="5" t="inlineStr"/>
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z3" s="5" t="inlineStr">
+      <c r="Z4" s="5" t="inlineStr">
         <is>
           <t>sha256:b614502639e969ab0f3840d1381f1b12b01cb5b693a0b02d17387192b230b354</t>
         </is>
       </c>
-      <c r="AA3" s="5" t="inlineStr">
+      <c r="AA4" s="5" t="inlineStr">
         <is>
           <t>sha256:03f5fae5200c76ca296c75ab0ebf225f190fb3fe6a7f52c7c8c7e0da2a97d07c</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>CMSR-D1-003</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-014
 CMSR-RULE-016</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>CoreAgent commits streamed valid semantic repair</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>SDK-UT</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>A protocol-invalid first attempt rolls back while its single preceding step label survives and the corrected result streams and commits.</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>A controlled model yields an invalid response then a pausable valid code action at step one.</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","sequence":"invalid code, rollback, corrected code chunks, commit, parse"}</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>1. Begin step one and return protocol-invalid model content. =&gt; Exactly one step label precedes begin; the attempt rolls back and one repair is scheduled.
 2. Pause the valid repair after its first safe chunk. =&gt; That chunk is visible before model completion.
 3. Complete the repair and classify it. =&gt; Its attempt commits and a single parse follows.</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>Corrected content is streamed and committed.
 Only the corrected action is executed.
 Lifecycle logs identify the repair without content.</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>No failed content after rollback.
 No repair instruction in user output.
 No suppressed successful stream.</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>{"assertions":["Step label occurs before both model attempts and only once.","Successful repair does not set stream suppression.","Corrected attempt commits once.","Invalid attempt rolls back once."],"inputs":["step one","invalid model content","valid streamed &lt;code&gt; action"],"unit_boundary":"CoreAgent semantic repair and deferred model attempt lifecycle"}</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr">
+      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>implemented</t>
         </is>
       </c>
-      <c r="S4" s="5" t="inlineStr">
+      <c r="S5" s="5" t="inlineStr">
         <is>
           <t>pytest</t>
         </is>
       </c>
-      <c r="T4" s="5" t="inlineStr">
+      <c r="T5" s="5" t="inlineStr">
         <is>
           <t>test/automation/d1/test_semantic_repair_stream.py</t>
         </is>
       </c>
-      <c r="U4" s="5" t="inlineStr">
+      <c r="U5" s="5" t="inlineStr">
         <is>
           <t>test_cmsr_d1_003</t>
         </is>
       </c>
-      <c r="V4" s="5" t="inlineStr">
+      <c r="V5" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W4" s="5" t="inlineStr"/>
-      <c r="X4" s="5" t="inlineStr"/>
-      <c r="Y4" s="5" t="inlineStr">
+      <c r="W5" s="5" t="inlineStr"/>
+      <c r="X5" s="5" t="inlineStr"/>
+      <c r="Y5" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z4" s="5" t="inlineStr">
+      <c r="Z5" s="5" t="inlineStr">
         <is>
           <t>sha256:7ef8664f2224d068d7deafecf80f09353d734bc10b35a1147b3cc58d1ae6eacd</t>
         </is>
       </c>
-      <c r="AA4" s="5" t="inlineStr">
+      <c r="AA5" s="5" t="inlineStr">
         <is>
           <t>sha256:1dee7e7ce90f70c40d02907f11be7b55665495fdcaa3dfdec3ab478953c5c38c</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>CMSR-D1-004</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-018</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Rejected model output diagnostics distinguish budget exhaustion without default content leakage</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>SDK-UT</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Correlate each protocol rejection to the model response shape and budget while gating bounded raw previews.</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Use isolated model diagnostics for a reasoning-only length response and a malformed nonempty response.</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","responses":["length with 4096 reasoning-only output tokens","malformed nonempty code Action"]}</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>1. Reject a reasoning-only length response with diagnostics disabled. =&gt; The log records model, attempt, requested and consumed tokens, reasoning and content counts, and reasoning-only budget exhaustion without raw text.
 2. Reject a malformed content response. =&gt; The distinct protocol reason and response shape are logged under its own attempt identifier.
 3. Enable diagnostic content preview for a rejected response longer than the preview cap. =&gt; Only a single escaped bounded prefix of model content and reasoning is logged; the full text remains absent.</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>Each rejection is attributable to one attempt and specific failure class.
 Raw output is absent by default and bounded on explicit opt-in.</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>No model output or user prompt enters SSE or persisted history from diagnostics.
 No secret or full raw payload is logged by default.
 No retry-budget or execution behavior changes.</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>{"assertions":["Reasoning-only budget exhaustion flag is accurate.","Logs include attempt and token counts.","Default logs omit raw content.","Opt-in previews are escaped and capped."],"inputs":["finish_reason=length","reasoning_content","invalid code Action","explicit diagnostic flag"],"unit_boundary":"OpenAI model response diagnostics and CoreAgent protocol-error logging"}</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="inlineStr"/>
-      <c r="R5" s="5" t="inlineStr">
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr">
         <is>
           <t>implemented</t>
         </is>
       </c>
-      <c r="S5" s="5" t="inlineStr">
+      <c r="S6" s="5" t="inlineStr">
         <is>
           <t>pytest</t>
         </is>
       </c>
-      <c r="T5" s="5" t="inlineStr">
+      <c r="T6" s="5" t="inlineStr">
         <is>
           <t>test/automation/d1/test_protocol_rejection_diagnostics.py</t>
         </is>
       </c>
-      <c r="U5" s="5" t="inlineStr">
+      <c r="U6" s="5" t="inlineStr">
         <is>
           <t>test_cmsr_d1_004</t>
         </is>
       </c>
-      <c r="V5" s="5" t="inlineStr">
+      <c r="V6" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W5" s="5" t="inlineStr"/>
-      <c r="X5" s="5" t="inlineStr"/>
-      <c r="Y5" s="5" t="inlineStr">
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z5" s="5" t="inlineStr">
+      <c r="Z6" s="5" t="inlineStr">
         <is>
           <t>sha256:9f06a6565fff8e542fdcb89725b5fc7f669ad52b07301bdc99aa3e2eba23552c</t>
         </is>
       </c>
-      <c r="AA5" s="5" t="inlineStr">
+      <c r="AA6" s="5" t="inlineStr">
         <is>
           <t>sha256:a53056127d5f2efce4a9d98c92c9c97892451de0d1d353603584612c0a9ef1ba</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1653,7 +1835,7 @@
       <c r="X2" s="5" t="inlineStr"/>
       <c r="Y2" s="5" t="inlineStr">
         <is>
-          <t>校验通过</t>
+          <t>实现哈希失效</t>
         </is>
       </c>
       <c r="Z2" s="5" t="inlineStr">
@@ -1993,12 +2175,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -2013,10 +2195,10 @@
     <col width="42" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="42" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="42" customWidth="1" min="20" max="20"/>
+    <col width="34" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -2165,20 +2347,160 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>AGENT-LIST-D4-001</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-LIST-VIEWS</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-LIST-REQ-001
+AGENT-LIST-REQ-002</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-LIST-RULE-001
+AGENT-LIST-RULE-002
+AGENT-LIST-RULE-003
+AGENT-LIST-RULE-004
+AGENT-LIST-RULE-005</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Switch between the agent card and table presentations</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Verify Ant Design table separators and content-responsive sizing at desktop and constrained viewport widths, and confirm that table view retains existing list workflows.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Open the agent list with at least two mocked agents, including one with update_time and one without it.</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>{"agent_count":8,"profile":"mock","viewport":{"height":1080,"width":1920}}</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>1. Switch from card mode to table mode. =&gt; The page heading, guide, and tabs remain unchanged while the table and its pagination appear.
+2. Verify columns and representative row values. =&gt; The column order is 名称、类型、描述、状态、创建人、更新时间、操作; timestamps reflect update_time only.
+3. Inspect the header separators and table height with eight rendered rows, then search to a single matching row. =&gt; Internal header columns have 1px
+4. Search for an agent, activate its configure action, then return and switch back to card mode. =&gt; Search and navigation still work, and the card presentation returns with its prior layout and metadata.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>At 1920×1080 the table occupies the measured 1807px content width; its height follows its rendered rows, grows no higher than 500px, and does not fill unused space.
+The table uses StandardTable with 14px/#191919/0px typography, white rows, a
+Narrow filter headers show both the label and icon with 8px horizontal padding.
+When rows exceed the 500px cap or the available list area, scrolling stays inside the table body and pagination remains below it.
+Search, configure, publish, import, and view switching remain usable.
+Page-level content above the list and existing card mode are unchanged.</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>No backend API or data mutation is introduced by switching views.
+Do not use create_time as update_time.
+Do not add body vertical separators or an outer table border; header separators remain centered and shorter than the 40px header cell.</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>{"actor":"Agent list user","failure_evidence":["Missing/incorrect table headings or row values.","Search, navigation, pagination, or view switching fails.","The table changes content above the list or mutates agent data."],"final_business_result":["The same agent collection remains available in either presentation.","Existing list operations remain reachable."],"journey":["Open the agent list.","Switch between card and table modes.","Search and open an agent configuration."]}</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d4/run_agent_list_views_e2e.mjs</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>agent-list-high-fidelity.spec.ts</t>
+        </is>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr"/>
+      <c r="X2" s="5" t="inlineStr"/>
+      <c r="Y2" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z2" s="5" t="inlineStr">
+        <is>
+          <t>sha256:1093e9eea123f868058b2922bcb8becb7058e0378301e97276df51156c4ba9fc</t>
+        </is>
+      </c>
+      <c r="AA2" s="5" t="inlineStr">
+        <is>
+          <t>sha256:a905ec4d8fcce1e93354988f937f8f560872b64738f762662e6250e2413b9b8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
           <t>CMSR-D4-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-013
 CMSR-RULE-014
@@ -2186,48 +2508,48 @@
 CMSR-RULE-016</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Browser shows retry output incrementally without blank steps</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>E2E</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Verify a user sees only successful raw code and one executed action in a real conversation.</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>A local Nexent instance
 test tenant and controllable model provider are configured.</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","sequences":["failed transport partial then success","step-one invalid protocol then valid paused repair"]}</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>1. Open Agent chat and send the fixed prompt. =&gt; Step 1 appears before the first model token; the first partial output is then rolled back while the label remains.
 2. Pause the second provider response after its first safe fragment. =&gt; The reasoning card displays the successful raw fragment before provider completion.
@@ -2235,7 +2557,7 @@
 4. Repeat in a new conversation with semantic repair at step one. =&gt; Corrected raw code is visible during the pause and after refresh; Connecting does not persist.</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>Running Step 1 is visible before content.
 No terminal label-only reasoning card.
@@ -2243,59 +2565,59 @@
 Refreshed history matches the final UI.</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>No failed partial text after rollback.
 No duplicate execution card.</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>{"actor":"Authenticated test tenant user","failure_evidence":["Retain browser screenshot","network timing and console trace on failure."],"final_business_result":["Only the committed attempt and its single executed code action are visible."],"journey":["Open the Agent conversation.","Trigger controlled retry.","Observe streaming.","Reload and inspect history."]}</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>{"profiles":[{"name":"mock","required_services":["model-provider"]}]}</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="S2" s="5" t="inlineStr"/>
-      <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr"/>
-      <c r="V2" s="5" t="inlineStr">
+      <c r="S3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="inlineStr"/>
+      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W2" s="5" t="inlineStr">
+      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>model-provider</t>
         </is>
       </c>
-      <c r="X2" s="5" t="inlineStr"/>
-      <c r="Y2" s="5" t="inlineStr">
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z2" s="5" t="inlineStr">
+      <c r="Z3" s="5" t="inlineStr">
         <is>
           <t>sha256:f110f582fe091286fdaa5301f8bdc22703bf583fc7c6c95214ae8c8187a612a1</t>
         </is>
       </c>
-      <c r="AA2" s="5" t="inlineStr">
+      <c r="AA3" s="5" t="inlineStr">
         <is>
           <t>sha256:4f53cda18c2baa0c0354bb5f9a3ecbe5ed12ab4d8e11ba873c2f11161202b945</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA2"/>
+  <autoFilter ref="A1:AA3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/test/generated/Nexent_测试基线.xlsx
+++ b/test/generated/Nexent_测试基线.xlsx
@@ -16,12 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_D5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_功能清单'!$A$1:$G$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_D1'!$A$1:$AA$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_D2'!$A$1:$AA$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_D3'!$A$1:$AA$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_D4'!$A$1:$AA$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_D5'!$A$1:$AA$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_功能清单'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_D1'!$A$1:$AA$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_D2'!$A$1:$AA$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_D3'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_D4'!$A$1:$AA$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_D5'!$A$1:$AA$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -603,25 +603,73 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>AKDT-001</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>AIDP knowledge base detail page</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Open an AIDP knowledge base from its name or card and manage its ingested files, upload task history, configuration and group permissions on a full-page detail view. Files and upload tasks are queried live from AIDP and are not stored in Nexent PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>AKDT-RULE-001
+AKDT-RULE-002
+AKDT-RULE-003
+AKDT-RULE-004
+AKDT-RULE-005
+AKDT-RULE-006
+AKDT-RULE-007
+AKDT-RULE-008</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>D1
+D2
+D3
+D4
+D5</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>{"requirement_ids":["AKDT-001"],"spec_path":"uploads/knowledge-base-detail-design/proposal.md"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
           <t>AKPR-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>AIDP knowledge base list and creation page refactor</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>AIDP knowledge bases are listed in a card or table overview with an independent name search, a collapsible three-step guide and a full-page file view per knowledge base; creation moves to a dedicated two-step page that carries permission, chunking, retrieval, graph, model and safety-guard configuration. The ES knowledge base path stays untouched.</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>AIDP knowledge bases are listed in a card or table overview with an independent name search, a collapsible three-step guide and a full-page file view per knowledge base; creation moves to a dedicated two-step page that carries permission, chunking, retrieval, graph and model configuration. The ES knowledge base path stays untouched.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>AKPR-RULE-001
 AKPR-RULE-002
@@ -636,10 +684,11 @@
 AKPR-RULE-011
 AKPR-RULE-012
 AKPR-RULE-013
-AKPR-RULE-014</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
+AKPR-RULE-015
+AKPR-RULE-016</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>D1
 D2
@@ -648,34 +697,34 @@
 D5</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>{"requirement_ids":["AKPR-001"],"spec_path":"nexent-doc/nexent/knowledge-base-pages-refactor/proposal.md"}</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Silent model retry stream visibility</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Successful model attempts stream raw content while failed attempts leave no visible or persisted fragments.</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-013
 CMSR-RULE-014
@@ -685,7 +734,7 @@
 CMSR-RULE-018</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>D1
 D2
@@ -694,14 +743,14 @@
 D5</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>{"requirement_ids":["CMSR-005"],"spec_path":"nexent-doc/docs/Developing/chat-message-model-silent-retry/proposal.md"}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -712,1995 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="42" customWidth="1" min="10" max="10"/>
-    <col width="42" customWidth="1" min="11" max="11"/>
-    <col width="42" customWidth="1" min="12" max="12"/>
-    <col width="42" customWidth="1" min="13" max="13"/>
-    <col width="42" customWidth="1" min="14" max="14"/>
-    <col width="42" customWidth="1" min="15" max="15"/>
-    <col width="42" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="42" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col hidden="1" width="42" customWidth="1" min="26" max="26"/>
-    <col hidden="1" width="42" customWidth="1" min="27" max="27"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>用例ID</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>功能ID</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>需求ID</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>业务规则ID</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>标题</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>类型</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>优先级</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>自动化</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>目标</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>前置条件</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>测试数据</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>操作步骤及步骤预期</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>最终预期</t>
-        </is>
-      </c>
-      <c r="O1" s="4" t="inlineStr">
-        <is>
-          <t>禁止副作用</t>
-        </is>
-      </c>
-      <c r="P1" s="4" t="inlineStr">
-        <is>
-          <t>阶段专属字段</t>
-        </is>
-      </c>
-      <c r="Q1" s="4" t="inlineStr">
-        <is>
-          <t>执行配置</t>
-        </is>
-      </c>
-      <c r="R1" s="4" t="inlineStr">
-        <is>
-          <t>自动化实现状态</t>
-        </is>
-      </c>
-      <c r="S1" s="4" t="inlineStr">
-        <is>
-          <t>测试框架</t>
-        </is>
-      </c>
-      <c r="T1" s="4" t="inlineStr">
-        <is>
-          <t>脚本路径</t>
-        </is>
-      </c>
-      <c r="U1" s="4" t="inlineStr">
-        <is>
-          <t>Selector</t>
-        </is>
-      </c>
-      <c r="V1" s="4" t="inlineStr">
-        <is>
-          <t>执行Profile</t>
-        </is>
-      </c>
-      <c r="W1" s="4" t="inlineStr">
-        <is>
-          <t>所需Mock服务</t>
-        </is>
-      </c>
-      <c r="X1" s="4" t="inlineStr">
-        <is>
-          <t>所需测试资产</t>
-        </is>
-      </c>
-      <c r="Y1" s="4" t="inlineStr">
-        <is>
-          <t>Manifest校验状态</t>
-        </is>
-      </c>
-      <c r="Z1" s="4" t="inlineStr">
-        <is>
-          <t>契约哈希</t>
-        </is>
-      </c>
-      <c r="AA1" s="4" t="inlineStr">
-        <is>
-          <t>实现哈希</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-D1-001</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-RULE-001</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>Overview guide expands, collapses and keeps the fixed three steps</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>FE-COMP</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>Verify the AIDP-only guide renders the knowledge base explanation with the fixed steps and toggles without disturbing page state.</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>Render the AIDP overview component with an empty knowledge base list.</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>{"locale":"zh-CN","profile":"mock"}</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>1. Mount the overview page. =&gt; The guide is expanded and lists create knowledge base, upload files and configure the knowledge base in an agent.
-2. Collapse the guide. =&gt; The guide body is hidden while the reopen entry stays visible and operable.
-3. Reopen the guide. =&gt; The explanation and the three steps are visible again with unchanged search and view state.</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr">
-        <is>
-          <t>The explanation and the three documented steps are visible when expanded.
-Collapse hides only the guide body.
-Reopening restores the same content order.</t>
-        </is>
-      </c>
-      <c r="O2" s="5" t="inlineStr">
-        <is>
-          <t>No backend request is issued by expanding or collapsing the guide.
-No search, page or view mode change.</t>
-        </is>
-      </c>
-      <c r="P2" s="5" t="inlineStr">
-        <is>
-          <t>{"assertions":["Guide content is visible on first entry.","The reopen entry remains visible after collapse.","The three step labels match the fixed order.","Guide toggling issues no request."],"inputs":["initial expanded state","collapse click","reopen click"],"unit_boundary":"AIDP knowledge guide expansion state and fixed step labels"}</t>
-        </is>
-      </c>
-      <c r="Q2" s="5" t="inlineStr"/>
-      <c r="R2" s="5" t="inlineStr">
-        <is>
-          <t>unbound</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="inlineStr"/>
-      <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr"/>
-      <c r="V2" s="5" t="inlineStr"/>
-      <c r="W2" s="5" t="inlineStr"/>
-      <c r="X2" s="5" t="inlineStr"/>
-      <c r="Y2" s="5" t="inlineStr">
-        <is>
-          <t>未绑定</t>
-        </is>
-      </c>
-      <c r="Z2" s="5" t="inlineStr"/>
-      <c r="AA2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-D1-002</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-RULE-002
-AKPR-RULE-004</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>Cards are the default view and switching or hiding columns keeps the result set</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>FE-COMP</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>Verify default card rendering, table switching and column visibility control over one shared paginated result set.</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>Render the overview with a fixed page of knowledge bases and a recorded search and page number.</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>{"page_size":10,"profile":"mock","total":23}</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>1. Mount the overview with existing results. =&gt; Knowledge bases render as cards.
-2. Switch to the table view. =&gt; The same records render as table rows with the current keyword and page preserved.
-3. Hide one optional column and then restore defaults. =&gt; The column disappears and returns while the name and action columns stay present throughout.</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>The card view is the default.
-Switching views keeps keyword, page and totals identical.
-Hiding and restoring columns changes only local visibility.</t>
-        </is>
-      </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>No mutating endpoint is called by view or column changes.
-No record is dropped or duplicated by switching views.
-Required columns cannot be hidden.</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>{"assertions":["Initial view mode is cards.","Table switch preserves keyword, page and total.","Hidden optional column is absent and restorable.","Name and action columns stay visible."],"inputs":["default view mode","card to table switch","hidden column set","restore defaults action"],"unit_boundary":"Overview view mode and column visibility state"}</t>
-        </is>
-      </c>
-      <c r="Q3" s="5" t="inlineStr"/>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>unbound</t>
-        </is>
-      </c>
-      <c r="S3" s="5" t="inlineStr"/>
-      <c r="T3" s="5" t="inlineStr"/>
-      <c r="U3" s="5" t="inlineStr"/>
-      <c r="V3" s="5" t="inlineStr"/>
-      <c r="W3" s="5" t="inlineStr"/>
-      <c r="X3" s="5" t="inlineStr"/>
-      <c r="Y3" s="5" t="inlineStr">
-        <is>
-          <t>未绑定</t>
-        </is>
-      </c>
-      <c r="Z3" s="5" t="inlineStr"/>
-      <c r="AA3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-D1-003</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-RULE-003</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Independent name search drives the keyword query and resets the page</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>FE-COMP</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>Verify the single search box reuses the existing keyword query, resets to page one and keeps table headers free of search controls.</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>Render the overview with a recorded non-first page and a stubbed list service.</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>{"keyword":"finance","page":3,"profile":"mock"}</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>1. Type a keyword into the page search box and wait for the debounce. =&gt; The list service is called with the keyword and page one for both views.
-2. Clear the search box. =&gt; The unfiltered permission-scoped set is requested again.
-3. Inspect the table header row. =&gt; No column exposes a search or filter control.</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>The keyword query is reused with a page reset.
-Clearing restores the unfiltered set.
-Column headers contain no search entry.</t>
-        </is>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>No request per keystroke outside the debounce.
-No column filter parameter is sent.</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="inlineStr">
-        <is>
-          <t>{"assertions":["listKbs receives keyword and page one after debounce.","Clearing the box requests the unfiltered set.","No header search control exists."],"inputs":["keyword text","debounce interval elapse","clear action","table header render"],"unit_boundary":"Overview search debounce and page reset with the existing keyword parameter"}</t>
-        </is>
-      </c>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>unbound</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr"/>
-      <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr"/>
-      <c r="V4" s="5" t="inlineStr"/>
-      <c r="W4" s="5" t="inlineStr"/>
-      <c r="X4" s="5" t="inlineStr"/>
-      <c r="Y4" s="5" t="inlineStr">
-        <is>
-          <t>未绑定</t>
-        </is>
-      </c>
-      <c r="Z4" s="5" t="inlineStr"/>
-      <c r="AA4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-D1-004</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-RULE-005
-AKPR-RULE-009</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>File view targets one knowledge base and restores the previous list state on return</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>FE-COMP</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>Verify the full-page file view scoping, the preserved list state on return and the cleanup of the previous base document state.</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>Render the overview with two knowledge bases and a recorded search, page, view mode and column setting.</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>{"other_base":"kb-beta","profile":"mock","selected_base":"kb-alpha"}</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>1. Select a knowledge base. =&gt; Only that base files render and the overview is replaced by the full-page file view.
-2. Return to the overview. =&gt; The previous keyword, page, view mode and column setting are intact.
-3. Resolve a delayed document response from the first base after selecting the second. =&gt; The delayed payload is discarded and the second base files remain.</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>Files belong to the selected base only.
-Returning restores the previous list state.
-A stale response never overwrites the current base.</t>
-        </is>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>No cross-base document leakage.
-No polling left running after leaving the file view.
-No list state reset on return.</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>{"assertions":["File list requests carry the selected base id.","Return renders the preserved list state.","A late response for the previous base is ignored.","Polling state is cleared when the view is left."],"inputs":["selected base id","return action","delayed response for a previous base"],"unit_boundary":"List and file view switching, document state reset and polling cleanup"}</t>
-        </is>
-      </c>
-      <c r="Q5" s="5" t="inlineStr"/>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>unbound</t>
-        </is>
-      </c>
-      <c r="S5" s="5" t="inlineStr"/>
-      <c r="T5" s="5" t="inlineStr"/>
-      <c r="U5" s="5" t="inlineStr"/>
-      <c r="V5" s="5" t="inlineStr"/>
-      <c r="W5" s="5" t="inlineStr"/>
-      <c r="X5" s="5" t="inlineStr"/>
-      <c r="Y5" s="5" t="inlineStr">
-        <is>
-          <t>未绑定</t>
-        </is>
-      </c>
-      <c r="Z5" s="5" t="inlineStr"/>
-      <c r="AA5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-D1-005</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-RULE-006</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>AIDP list metadata normalizes real values and marks unknown ones as absent</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>BE-UT</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>Verify the list response normalization of private and public type, capacity and missing values without fabricating data.</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>Provide raw AIDP list rows with mixed boolean, numeric, string and missing metadata values.</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>{"cases":["is_private true","is_private 0","is_private string true","missing is_private","current_cap 2.5","missing current_cap","missing document count"],"profile":"mock"}</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>1. Normalize rows with boolean, numeric and string forms of is_private. =&gt; A stable personal or enterprise type is produced for every form.
-2. Normalize rows without a type, capacity or count value. =&gt; Those fields are reported as unknown instead of a fabricated default.
-3. Normalize a valid personal capacity. =&gt; The documented unit value is preserved unchanged.</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>Real values survive normalization.
-Unknown values are distinguishable from a real zero.
-Capacity is not estimated from file sizes.</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>No Nexent group permission is used to infer the base type.
-No synthetic zero count or capacity is produced.
-No extra upstream request is issued per row.</t>
-        </is>
-      </c>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>{"assertions":["Boolean, integer and string is_private forms normalize consistently.","A missing count is distinguishable from zero.","A missing capacity is reported as unknown.","A valid capacity keeps its unit."],"inputs":["is_private variants","current_cap values","document count presence"],"unit_boundary":"AIDP list metadata normalization helpers"}</t>
-        </is>
-      </c>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>unbound</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr"/>
-      <c r="V6" s="5" t="inlineStr"/>
-      <c r="W6" s="5" t="inlineStr"/>
-      <c r="X6" s="5" t="inlineStr"/>
-      <c r="Y6" s="5" t="inlineStr">
-        <is>
-          <t>未绑定</t>
-        </is>
-      </c>
-      <c r="Z6" s="5" t="inlineStr"/>
-      <c r="AA6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-D1-006</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-RULE-007</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Read-only and unavailable knowledge bases expose no modification entry</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>FE-COMP</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>Verify that permission and lifecycle restrictions remove every executable modification entry in cards, table rows and the file view.</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>Render the overview with one editable, one read-only and one unavailable knowledge base.</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>{"permissions":["EDIT","READ_ONLY"],"profile":"mock","resource_status":["available","unavailable"]}</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>1. Render the card menu and table actions for each permission. =&gt; Only the editable base offers executable edit and delete entries.
-2. Open the file view of a read-only base. =&gt; Upload and delete entries are absent or disabled while browsing stays possible.
-3. Render an unavailable base. =&gt; No executable modification entry is offered and its state stays visible.</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>Modification entries follow the effective permission.
-Unavailable bases stay visible without modification entries.
-No request is emitted from a disabled entry.</t>
-        </is>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>No modification request for read-only or unavailable bases.
-No hidden menu item remains clickable.
-No downgrade of the existing visibility rules.</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="inlineStr">
-        <is>
-          <t>{"assertions":["Read-only rows render no executable modification entry.","Unavailable rows keep their lifecycle indicator.","No request leaves a disabled entry."],"inputs":["effective permission","resource_status","menu open state"],"unit_boundary":"Card menu and table action rendering under permission and lifecycle states"}</t>
-        </is>
-      </c>
-      <c r="Q7" s="5" t="inlineStr"/>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>unbound</t>
-        </is>
-      </c>
-      <c r="S7" s="5" t="inlineStr"/>
-      <c r="T7" s="5" t="inlineStr"/>
-      <c r="U7" s="5" t="inlineStr"/>
-      <c r="V7" s="5" t="inlineStr"/>
-      <c r="W7" s="5" t="inlineStr"/>
-      <c r="X7" s="5" t="inlineStr"/>
-      <c r="Y7" s="5" t="inlineStr">
-        <is>
-          <t>未绑定</t>
-        </is>
-      </c>
-      <c r="Z7" s="5" t="inlineStr"/>
-      <c r="AA7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-D1-007</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-RULE-002</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>First-load empty, filtered empty, loading and failure states stay distinct</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>FE-COMP</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>Verify the four overview states render distinct messages and remain localized.</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>Render the overview with a stubbed service returning an empty set, an empty filtered set, a pending promise and an error.</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>{"locales":["zh","en"],"profile":"mock","states":["first empty","filtered empty","loading","failed"]}</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>1. Resolve an empty list without a keyword. =&gt; A first-use empty state renders instead of a search-empty state.
-2. Resolve an empty list with an active keyword. =&gt; A search-empty state renders with the keyword context.
-3. Keep the request pending and then reject it. =&gt; Loading and failure states render distinctly and the failure state offers a retry path.</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>All four states are distinguishable.
-Both locales resolve every state string.</t>
-        </is>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>No fabricated placeholder rows.
-No silent failure rendering as an empty state.</t>
-        </is>
-      </c>
-      <c r="P8" s="5" t="inlineStr">
-        <is>
-          <t>{"assertions":["First empty and filtered empty differ.","Loading state precedes data.","Failure state is distinct and localized.","No placeholder rows are invented."],"inputs":["empty payload","empty filtered payload","pending request","rejected request","locale"],"unit_boundary":"Overview empty, loading and failure state rendering"}</t>
-        </is>
-      </c>
-      <c r="Q8" s="5" t="inlineStr"/>
-      <c r="R8" s="5" t="inlineStr">
-        <is>
-          <t>unbound</t>
-        </is>
-      </c>
-      <c r="S8" s="5" t="inlineStr"/>
-      <c r="T8" s="5" t="inlineStr"/>
-      <c r="U8" s="5" t="inlineStr"/>
-      <c r="V8" s="5" t="inlineStr"/>
-      <c r="W8" s="5" t="inlineStr"/>
-      <c r="X8" s="5" t="inlineStr"/>
-      <c r="Y8" s="5" t="inlineStr">
-        <is>
-          <t>未绑定</t>
-        </is>
-      </c>
-      <c r="Z8" s="5" t="inlineStr"/>
-      <c r="AA8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-D1-008</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-RULE-010</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Two-step creation validates locally, preserves state and creates exactly once</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>FE-COMP</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>Verify step navigation without creation, state preservation across steps and single creation before upload.</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>Render the AIDP creation page with stubbed create and upload services and a selected local file.</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>{"failing_uploads":1,"files":2,"profile":"mock"}</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>1. Fill step one and press next. =&gt; Validation runs with no create request issued and step two renders.
-2. Return to step one. =&gt; Form values, conditional sections and the selected files are preserved.
-3. Submit with one failing upload. =&gt; Creation happens once and the created base and the failed upload are reported separately.
-4. Submit again after the failed upload. =&gt; No second knowledge base is created and the retry targets the failed file only.</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="inlineStr">
-        <is>
-          <t>Step one never creates a resource.
-State survives backward navigation.
-Creation happens exactly once before uploads.</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>No create request from the next action.
-No duplicate base after retry or double click.
-No upload before a successful create.</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr">
-        <is>
-          <t>{"assertions":["Next issues no create request.","Backward navigation keeps values and files.","Exactly one create request precedes uploads.","A failed upload does not trigger a second create."],"inputs":["step one form values","selected files","upload failure","repeated submit"],"unit_boundary":"Creation page step state, submit guard and create-then-upload sequencing"}</t>
-        </is>
-      </c>
-      <c r="Q9" s="5" t="inlineStr"/>
-      <c r="R9" s="5" t="inlineStr">
-        <is>
-          <t>unbound</t>
-        </is>
-      </c>
-      <c r="S9" s="5" t="inlineStr"/>
-      <c r="T9" s="5" t="inlineStr"/>
-      <c r="U9" s="5" t="inlineStr"/>
-      <c r="V9" s="5" t="inlineStr"/>
-      <c r="W9" s="5" t="inlineStr"/>
-      <c r="X9" s="5" t="inlineStr"/>
-      <c r="Y9" s="5" t="inlineStr">
-        <is>
-          <t>未绑定</t>
-        </is>
-      </c>
-      <c r="Z9" s="5" t="inlineStr"/>
-      <c r="AA9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-D1-009</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-RULE-011</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Creation defaults and chunking mapping follow the confirmed values</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>BE-UT</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>Verify preserved creation defaults, the chunk mode enumeration and the overlap-to-token conversion with its bounds.</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>Prepare create payloads with missing defaults, both chunk modes and boundary overlap percentages.</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>{"chunk_tokens":[1024,512],"modes":["smart","legal"],"percents":[12.5,50],"profile":"mock"}</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>1. Submit a payload without explicit chunking or retrieval values. =&gt; The existing defaults apply unchanged and the new graph parameters use their documented defaults.
-2. Submit each chunk mode. =&gt; The chunk mode serializes as 0 for smart splitting and 1 for legal clauses.
-3. Submit overlap percentages including the boundaries. =&gt; The overlap becomes the floor conversion in integer tokens and any value above half the chunk size is rejected.</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="inlineStr">
-        <is>
-          <t>Defaults remain 1024 tokens, 128 overlap, 0.0 similarity and Top K 10.
-Chunk modes serialize 0 and 1.
-Overlap conversion is exact and bounded.</t>
-        </is>
-      </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>No silent clamping of an invalid overlap.
-No renamed legacy field in the outgoing payload.
-No change to the ES knowledge base contract.</t>
-        </is>
-      </c>
-      <c r="P10" s="5" t="inlineStr">
-        <is>
-          <t>{"assertions":["Defaults match the existing Nexent values.","Overlap equals the floor conversion.","Overlap above 50 percent of the chunk size is rejected.","Legacy field names stay unchanged."],"inputs":["payload without defaults","chunk mode selection","chunk tokens and overlap percent"],"unit_boundary":"Create default application, chunk mode mapping and overlap conversion"}</t>
-        </is>
-      </c>
-      <c r="Q10" s="5" t="inlineStr"/>
-      <c r="R10" s="5" t="inlineStr">
-        <is>
-          <t>unbound</t>
-        </is>
-      </c>
-      <c r="S10" s="5" t="inlineStr"/>
-      <c r="T10" s="5" t="inlineStr"/>
-      <c r="U10" s="5" t="inlineStr"/>
-      <c r="V10" s="5" t="inlineStr"/>
-      <c r="W10" s="5" t="inlineStr"/>
-      <c r="X10" s="5" t="inlineStr"/>
-      <c r="Y10" s="5" t="inlineStr">
-        <is>
-          <t>未绑定</t>
-        </is>
-      </c>
-      <c r="Z10" s="5" t="inlineStr"/>
-      <c r="AA10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-D1-010</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-RULE-013</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Graph configuration serializes documented keys with an inverse thinking switch</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>BE-UT</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>Verify graph configuration serialization, the inverse thinking mapping, the independent Top K values and the prompt byte limit.</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>Prepare graph payloads with the switch on and off, both languages and prompt lengths around the byte limit.</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>{"domains":["general","medical"],"languages":["chinese","english"],"profile":"mock","prompt_bytes":[2048,2049]}</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>1. Submit a graph configuration with the thinking switch enabled. =&gt; The thinking mode field is false and the graph keys use their documented names.
-2. Submit a knowledge base Top K together with a graph Top K. =&gt; The two values are serialized independently without overwriting each other.
-3. Submit prompts at and beyond the byte boundary together with a disabled graph. =&gt; The limit passes at the boundary, longer input is rejected and a disabled graph omits its configuration entirely.</t>
-        </is>
-      </c>
-      <c r="N11" s="5" t="inlineStr">
-        <is>
-          <t>The thinking switch maps inversely onto the thinking mode field.
-Both Top K values survive independently.
-The prompt limit is enforced in UTF-8 bytes.</t>
-        </is>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>No hidden previous graph configuration is submitted when the graph is off.
-No graph Top K overwrites the knowledge base Top K.
-No invented JSON key names.</t>
-        </is>
-      </c>
-      <c r="P11" s="5" t="inlineStr">
-        <is>
-          <t>{"assertions":["The thinking mode field is false when thinking is enabled.","Graph and knowledge base Top K stay independent.","Prompt length is measured in UTF-8 bytes.","Disabled graph omits its configuration."],"inputs":["graph switch","domain","graph top k","hop count","thinking switch","prompt language","prompt text"],"unit_boundary":"Graph configuration validation and serialization"}</t>
-        </is>
-      </c>
-      <c r="Q11" s="5" t="inlineStr"/>
-      <c r="R11" s="5" t="inlineStr">
-        <is>
-          <t>unbound</t>
-        </is>
-      </c>
-      <c r="S11" s="5" t="inlineStr"/>
-      <c r="T11" s="5" t="inlineStr"/>
-      <c r="U11" s="5" t="inlineStr"/>
-      <c r="V11" s="5" t="inlineStr"/>
-      <c r="W11" s="5" t="inlineStr"/>
-      <c r="X11" s="5" t="inlineStr"/>
-      <c r="Y11" s="5" t="inlineStr">
-        <is>
-          <t>未绑定</t>
-        </is>
-      </c>
-      <c r="Z11" s="5" t="inlineStr"/>
-      <c r="AA11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-D1-011</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-RULE-012</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Graph and multimodal models are queried from separate categories with independent caches</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>FE-COMP</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>Verify the model category split, the independent query caches and the omission of hidden model values.</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>Render the creation form with stubbed model queries per category and both capability switches toggled.</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>{"categories":["llm","vlm","embedding"],"profile":"mock"}</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>1. Enable the graph section. =&gt; The graph model query uses the llm category and fills the graph model field.
-2. Enable multimodal captioning. =&gt; The multimodal model query uses the vlm category and fills the multimodal field independently.
-3. Disable each capability after a selection. =&gt; The hidden model value is absent from the submitted payload.</t>
-        </is>
-      </c>
-      <c r="N12" s="5" t="inlineStr">
-        <is>
-          <t>Each model field is populated from its own category.
-Caches and selections never mix.
-Disabled capabilities submit no model value.</t>
-        </is>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>No llm result used for the multimodal field.
-No hidden previous model resubmitted.
-No unverified model name silently defaulted.</t>
-        </is>
-      </c>
-      <c r="P12" s="5" t="inlineStr">
-        <is>
-          <t>{"assertions":["Graph query uses llm and multimodal uses vlm.","Caches are keyed independently.","Disabled capability clears its submitted model."],"inputs":["graph switch","multimodal switch","selected models","query cache keys"],"unit_boundary":"Creation form model queries, caches and hidden value handling"}</t>
-        </is>
-      </c>
-      <c r="Q12" s="5" t="inlineStr"/>
-      <c r="R12" s="5" t="inlineStr">
-        <is>
-          <t>unbound</t>
-        </is>
-      </c>
-      <c r="S12" s="5" t="inlineStr"/>
-      <c r="T12" s="5" t="inlineStr"/>
-      <c r="U12" s="5" t="inlineStr"/>
-      <c r="V12" s="5" t="inlineStr"/>
-      <c r="W12" s="5" t="inlineStr"/>
-      <c r="X12" s="5" t="inlineStr"/>
-      <c r="Y12" s="5" t="inlineStr">
-        <is>
-          <t>未绑定</t>
-        </is>
-      </c>
-      <c r="Z12" s="5" t="inlineStr"/>
-      <c r="AA12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-D1-012</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-RULE-014</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Safety guard serializes integer 1 and 0 and never omits an explicit disabled value</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>BE-UT</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>Verify create and update serialization of the safety guard including the explicit zero and the absent-value distinction.</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>Prepare create and update payloads with the guard enabled, explicitly disabled and absent.</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>{"profile":"mock","values":["enabled 1","explicit 0","absent"]}</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>1. Build a create payload with the guard enabled and disabled. =&gt; The field is present as integer 1 or explicit 0.
-2. Build an update payload that only changes the guard to off. =&gt; The field survives the update whitelist and is forwarded as 0.
-3. Map a query response that lacks the field. =&gt; The state is reported as unknown rather than confirmed off.</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="inlineStr">
-        <is>
-          <t>Integer 1 and 0 are both serialized.
-An explicit 0 is never dropped by filtering.
-Missing data is not reported as a confirmed disabled state.</t>
-        </is>
-      </c>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>No boolean or string encoding of the field.
-No field nesting inside graph configuration.
-No Nexent-side content interception added.</t>
-        </is>
-      </c>
-      <c r="P13" s="5" t="inlineStr">
-        <is>
-          <t>{"assertions":["Enabled serializes 1 and disabled serializes 0.","The update whitelist forwards the field.","A missing field maps to unknown."],"inputs":["safety switch state","create payload","update payload","query response without the field"],"unit_boundary":"Safety guard request serialization and query mapping"}</t>
-        </is>
-      </c>
-      <c r="Q13" s="5" t="inlineStr"/>
-      <c r="R13" s="5" t="inlineStr">
-        <is>
-          <t>unbound</t>
-        </is>
-      </c>
-      <c r="S13" s="5" t="inlineStr"/>
-      <c r="T13" s="5" t="inlineStr"/>
-      <c r="U13" s="5" t="inlineStr"/>
-      <c r="V13" s="5" t="inlineStr"/>
-      <c r="W13" s="5" t="inlineStr"/>
-      <c r="X13" s="5" t="inlineStr"/>
-      <c r="Y13" s="5" t="inlineStr">
-        <is>
-          <t>未绑定</t>
-        </is>
-      </c>
-      <c r="Z13" s="5" t="inlineStr"/>
-      <c r="AA13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>CMSR-D1-001</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>CMSR-005</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>CMSR-005</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>CMSR-RULE-013
-CMSR-RULE-014</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Observer emits safe content before stream completion</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>SDK-UT</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>Verify bounded marker lookahead and attempt state reset.</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>Create an isolated observer and a controlled chunk sequence.</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>{"profile":"mock","sequence":"failed partial, rollback, successful split code and think markers"}</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>1. Feed a safe prefix and pause the source. =&gt; The prefix is emitted before flush or commit.
-2. Roll back the first attempt and feed split markers in the second. =&gt; The second output is ordered and contains no first-attempt residue.</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="inlineStr">
-        <is>
-          <t>The earliest safe content is observable before completion.
-Split markers retain their original semantics.</t>
-        </is>
-      </c>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>No stale fragment crosses attempts.
-No code is executed by the observer.</t>
-        </is>
-      </c>
-      <c r="P14" s="5" t="inlineStr">
-        <is>
-          <t>{"assertions":["Safe prefix emitted before flush.","Raw code tag retained.","No failed-attempt residue."],"inputs":["normal content","split &lt;think&gt; and &lt;/think&gt;","raw &lt;code&gt; content"],"unit_boundary":"Observer.add_model_new_token and attempt lifecycle"}</t>
-        </is>
-      </c>
-      <c r="Q14" s="5" t="inlineStr"/>
-      <c r="R14" s="5" t="inlineStr">
-        <is>
-          <t>implemented</t>
-        </is>
-      </c>
-      <c r="S14" s="5" t="inlineStr">
-        <is>
-          <t>pytest</t>
-        </is>
-      </c>
-      <c r="T14" s="5" t="inlineStr">
-        <is>
-          <t>test/automation/d1/test_model_attempt_stream.py</t>
-        </is>
-      </c>
-      <c r="U14" s="5" t="inlineStr">
-        <is>
-          <t>test_cmsr_d1_001</t>
-        </is>
-      </c>
-      <c r="V14" s="5" t="inlineStr">
-        <is>
-          <t>mock</t>
-        </is>
-      </c>
-      <c r="W14" s="5" t="inlineStr"/>
-      <c r="X14" s="5" t="inlineStr"/>
-      <c r="Y14" s="5" t="inlineStr">
-        <is>
-          <t>校验通过</t>
-        </is>
-      </c>
-      <c r="Z14" s="5" t="inlineStr">
-        <is>
-          <t>sha256:625e8c8829b51b9cd91344555d05c5ebfdc7bd766d8485eab99b9f22773f3233</t>
-        </is>
-      </c>
-      <c r="AA14" s="5" t="inlineStr">
-        <is>
-          <t>sha256:242f1aaf8a5fe4427f503e5acb8db2cc6cb5096782c2e4fdf49fcb17ec471420</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>CMSR-D1-002</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>CMSR-005</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>CMSR-005</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>CMSR-RULE-014
-CMSR-RULE-015</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Running step labels precede reasoning and survive retry rollback</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>FE-COMP</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>Verify immediate running labels, rollback preservation, legacy history and removal of terminal label-only cards.</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>Create the streaming adapter with a controlled SSE fixture.</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>{"profile":"mock","sequences":["step 1, failed attempt, rollback, successful raw code, parse","legacy content before step label"]}</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>1. Emit a step label before any model content. =&gt; A running reasoning card displays Step 1 immediately.
-2. Roll back a partial attempt and stream successful raw code. =&gt; Step 1 remains during rollback and only successful raw code follows it.
-3. Parse and reload both new and legacy-order history. =&gt; One code card and one labeled nonempty reasoning card remain; a terminal label-only card is absent.</t>
-        </is>
-      </c>
-      <c r="N15" s="5" t="inlineStr">
-        <is>
-          <t>Step label appears before first token.
-Rollback preserves the label.
-Successful original content remains after the label.
-Old history prepends late labels.</t>
-        </is>
-      </c>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>No failed-attempt content.
-No duplicate code card.
-No sibling invocation mutation.</t>
-        </is>
-      </c>
-      <c r="P15" s="5" t="inlineStr">
-        <is>
-          <t>{"assertions":["Running label is visible before content.","Terminal label-only step is hidden.","Successful code is visible after the label before commit.","History equals live output."],"inputs":["step_count","model_attempt_control","model_output_thinking","parse"],"unit_boundary":"Frontend live and history reasoning projection"}</t>
-        </is>
-      </c>
-      <c r="Q15" s="5" t="inlineStr"/>
-      <c r="R15" s="5" t="inlineStr">
-        <is>
-          <t>implemented</t>
-        </is>
-      </c>
-      <c r="S15" s="5" t="inlineStr">
-        <is>
-          <t>custom</t>
-        </is>
-      </c>
-      <c r="T15" s="5" t="inlineStr">
-        <is>
-          <t>test/automation/d1/test_reasoning_card.ts</t>
-        </is>
-      </c>
-      <c r="U15" s="5" t="inlineStr">
-        <is>
-          <t>CMSR-D1-002</t>
-        </is>
-      </c>
-      <c r="V15" s="5" t="inlineStr">
-        <is>
-          <t>mock</t>
-        </is>
-      </c>
-      <c r="W15" s="5" t="inlineStr"/>
-      <c r="X15" s="5" t="inlineStr"/>
-      <c r="Y15" s="5" t="inlineStr">
-        <is>
-          <t>校验通过</t>
-        </is>
-      </c>
-      <c r="Z15" s="5" t="inlineStr">
-        <is>
-          <t>sha256:b614502639e969ab0f3840d1381f1b12b01cb5b693a0b02d17387192b230b354</t>
-        </is>
-      </c>
-      <c r="AA15" s="5" t="inlineStr">
-        <is>
-          <t>sha256:03f5fae5200c76ca296c75ab0ebf225f190fb3fe6a7f52c7c8c7e0da2a97d07c</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>CMSR-D1-003</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>CMSR-005</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>CMSR-005</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>CMSR-RULE-014
-CMSR-RULE-016</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>CoreAgent commits streamed valid semantic repair</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>SDK-UT</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>A protocol-invalid first attempt rolls back while its single preceding step label survives and the corrected result streams and commits.</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>A controlled model yields an invalid response then a pausable valid code action at step one.</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>{"profile":"mock","sequence":"invalid code, rollback, corrected code chunks, commit, parse"}</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>1. Begin step one and return protocol-invalid model content. =&gt; Exactly one step label precedes begin; the attempt rolls back and one repair is scheduled.
-2. Pause the valid repair after its first safe chunk. =&gt; That chunk is visible before model completion.
-3. Complete the repair and classify it. =&gt; Its attempt commits and a single parse follows.</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="inlineStr">
-        <is>
-          <t>Corrected content is streamed and committed.
-Only the corrected action is executed.
-Lifecycle logs identify the repair without content.</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>No failed content after rollback.
-No repair instruction in user output.
-No suppressed successful stream.</t>
-        </is>
-      </c>
-      <c r="P16" s="5" t="inlineStr">
-        <is>
-          <t>{"assertions":["Step label occurs before both model attempts and only once.","Successful repair does not set stream suppression.","Corrected attempt commits once.","Invalid attempt rolls back once."],"inputs":["step one","invalid model content","valid streamed &lt;code&gt; action"],"unit_boundary":"CoreAgent semantic repair and deferred model attempt lifecycle"}</t>
-        </is>
-      </c>
-      <c r="Q16" s="5" t="inlineStr"/>
-      <c r="R16" s="5" t="inlineStr">
-        <is>
-          <t>implemented</t>
-        </is>
-      </c>
-      <c r="S16" s="5" t="inlineStr">
-        <is>
-          <t>pytest</t>
-        </is>
-      </c>
-      <c r="T16" s="5" t="inlineStr">
-        <is>
-          <t>test/automation/d1/test_semantic_repair_stream.py</t>
-        </is>
-      </c>
-      <c r="U16" s="5" t="inlineStr">
-        <is>
-          <t>test_cmsr_d1_003</t>
-        </is>
-      </c>
-      <c r="V16" s="5" t="inlineStr">
-        <is>
-          <t>mock</t>
-        </is>
-      </c>
-      <c r="W16" s="5" t="inlineStr"/>
-      <c r="X16" s="5" t="inlineStr"/>
-      <c r="Y16" s="5" t="inlineStr">
-        <is>
-          <t>校验通过</t>
-        </is>
-      </c>
-      <c r="Z16" s="5" t="inlineStr">
-        <is>
-          <t>sha256:7ef8664f2224d068d7deafecf80f09353d734bc10b35a1147b3cc58d1ae6eacd</t>
-        </is>
-      </c>
-      <c r="AA16" s="5" t="inlineStr">
-        <is>
-          <t>sha256:1dee7e7ce90f70c40d02907f11be7b55665495fdcaa3dfdec3ab478953c5c38c</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>CMSR-D1-004</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>CMSR-005</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>CMSR-005</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>CMSR-RULE-018</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Rejected model output diagnostics distinguish budget exhaustion without default content leakage</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>SDK-UT</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>Correlate each protocol rejection to the model response shape and budget while gating bounded raw previews.</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>Use isolated model diagnostics for a reasoning-only length response and a malformed nonempty response.</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>{"profile":"mock","responses":["length with 4096 reasoning-only output tokens","malformed nonempty code Action"]}</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>1. Reject a reasoning-only length response with diagnostics disabled. =&gt; The log records model, attempt, requested and consumed tokens, reasoning and content counts, and reasoning-only budget exhaustion without raw text.
-2. Reject a malformed content response. =&gt; The distinct protocol reason and response shape are logged under its own attempt identifier.
-3. Enable diagnostic content preview for a rejected response longer than the preview cap. =&gt; Only a single escaped bounded prefix of model content and reasoning is logged; the full text remains absent.</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="inlineStr">
-        <is>
-          <t>Each rejection is attributable to one attempt and specific failure class.
-Raw output is absent by default and bounded on explicit opt-in.</t>
-        </is>
-      </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>No model output or user prompt enters SSE or persisted history from diagnostics.
-No secret or full raw payload is logged by default.
-No retry-budget or execution behavior changes.</t>
-        </is>
-      </c>
-      <c r="P17" s="5" t="inlineStr">
-        <is>
-          <t>{"assertions":["Reasoning-only budget exhaustion flag is accurate.","Logs include attempt and token counts.","Default logs omit raw content.","Opt-in previews are escaped and capped."],"inputs":["finish_reason=length","reasoning_content","invalid code Action","explicit diagnostic flag"],"unit_boundary":"OpenAI model response diagnostics and CoreAgent protocol-error logging"}</t>
-        </is>
-      </c>
-      <c r="Q17" s="5" t="inlineStr"/>
-      <c r="R17" s="5" t="inlineStr">
-        <is>
-          <t>implemented</t>
-        </is>
-      </c>
-      <c r="S17" s="5" t="inlineStr">
-        <is>
-          <t>pytest</t>
-        </is>
-      </c>
-      <c r="T17" s="5" t="inlineStr">
-        <is>
-          <t>test/automation/d1/test_protocol_rejection_diagnostics.py</t>
-        </is>
-      </c>
-      <c r="U17" s="5" t="inlineStr">
-        <is>
-          <t>test_cmsr_d1_004</t>
-        </is>
-      </c>
-      <c r="V17" s="5" t="inlineStr">
-        <is>
-          <t>mock</t>
-        </is>
-      </c>
-      <c r="W17" s="5" t="inlineStr"/>
-      <c r="X17" s="5" t="inlineStr"/>
-      <c r="Y17" s="5" t="inlineStr">
-        <is>
-          <t>校验通过</t>
-        </is>
-      </c>
-      <c r="Z17" s="5" t="inlineStr">
-        <is>
-          <t>sha256:9f06a6565fff8e542fdcb89725b5fc7f669ad52b07301bdc99aa3e2eba23552c</t>
-        </is>
-      </c>
-      <c r="AA17" s="5" t="inlineStr">
-        <is>
-          <t>sha256:a53056127d5f2efce4a9d98c92c9c97892451de0d1d353603584612c0a9ef1ba</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:AA17"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AA21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2872,33 +933,34 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>AKPR-D2-001</t>
+          <t>AKDT-D1-001</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>AKPR-001</t>
+          <t>AKDT-001</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AKPR-001</t>
+          <t>AKDT-001</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AKPR-RULE-002
-AKPR-RULE-006</t>
+          <t>AKDT-RULE-002
+AKDT-RULE-004
+AKDT-RULE-006</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Knowledge base list keeps its contract and adds optional display fields</t>
+          <t>Task state display separates filter values from returned status</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>FE-COMP</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -2918,43 +980,42 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Verify the paginated AIDP list proxy keeps its existing request and response contract while exposing the optional display metadata.</t>
+          <t>Verify each documented numeric filter stays separate from returned status strings, provisional mappings remain explicit, and unknown raw values are preserved.</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>An authenticated request reaches the AIDP management proxy with a controllable upstream fixture.</t>
+          <t>Render the task status helpers and table with statuses COMPLETED, EXTRACTING, FAILED, UPLOADING, GRAPHFAILED and an unknown provider value.</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>{"keyword":"alpha","page":1,"page_size":10,"profile":"mock"}</t>
+          <t>{"filter_values":[0,1,2,3,4,5],"profile":"mock"}</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>1. Request the first page with a keyword. =&gt; The proxy forwards page, page_size and keyword and applies the existing permission intersection.
-2. Inspect the response payload. =&gt; Existing fields keep their names and types and the optional display fields appear only when the upstream returns them.
-3. Request a later page. =&gt; Ordering and totals remain consistent with the unfiltered permission-scoped set.</t>
+          <t>1. Select each task status filter. =&gt; The request receives the matching integer 0, 1, 2, 3, 4 or 5, including 0 for All.
+2. Render records with the listed provider statuses. =&gt; Known statuses show their documented labels, FAILED and UPLOADING use the recorded provisional mappings, and an unknown value remains visible as unknown with its raw value.
+3. Open failure details for a record without an error code or update time. =&gt; Missing fields show an em dash and do not use retry metadata or the current time.</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
-          <t>Existing request parameters and response fields are unchanged.
-Optional display metadata is additive.
-Pagination order and totals stay stable.</t>
+          <t>Request filters are numeric and never use a returned status string.
+The provisional mappings are isolated in one conversion function.
+Unknown or absent provider fields are not reported as success or as a specific failure.</t>
         </is>
       </c>
       <c r="O2" s="5" t="inlineStr">
         <is>
-          <t>No column filter parameter is introduced.
-No fabricated default replaces a missing metadata value.
-No ES knowledge base endpoint is touched.</t>
+          <t>No status is inferred from the selected filter.
+No missing error code is fabricated from a retry response.</t>
         </is>
       </c>
       <c r="P2" s="5" t="inlineStr">
         <is>
-          <t>{"endpoint":"/aidp-mgmt/knowledge-bases","method":"GET","protocol":"HTTP","request_expectations":["page, page_size and keyword behave as before.","The permission-scoped access set is resolved before pagination.","No new required parameter is added."],"response_expectations":["Existing fields keep their current names and types.","Optional display fields are additive and omit a value the upstream did not return.","Page totals equal the permission-scoped count."]}</t>
+          <t>{"assertions":["All sends status 0 and the other labels send their defined values through 5.","FAILED and UPLOADING are visibly documented as provisional mappings.","Unknown raw statuses are retained and missing error values render as an em dash."],"inputs":["status filter selection","raw task status","optional error fields"],"unit_boundary":"AIDP detail task status conversion and failure drawer field projection"}</t>
         </is>
       </c>
       <c r="Q2" s="5" t="inlineStr"/>
@@ -2980,35 +1041,33 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>AKPR-D2-002</t>
+          <t>AKDT-D1-002</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>AKPR-001</t>
+          <t>AKDT-001</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AKPR-001</t>
+          <t>AKDT-001</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AKPR-RULE-010
-AKPR-RULE-011
-AKPR-RULE-012
-AKPR-RULE-013</t>
+          <t>AKDT-RULE-001
+AKDT-RULE-007</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Creation request carries the new configuration and keeps legacy field names</t>
+          <t>Detail information reads graph configuration and group access without truthiness coercion</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>API-IT</t>
+          <t>FE-COMP</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -3028,43 +1087,43 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Verify the create proxy forwards chunking, retrieval, graph, model and safety fields while preserving legacy field names and existing defaults.</t>
+          <t>Verify the detail page projects the returned configuration and local group permission while preserving false, zero and unknown values.</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>An authenticated create request reaches the AIDP management proxy with a recorded upstream payload.</t>
+          <t>Render a KB detail response with graph_config represented once as JSON text and once as an object.
+Include explicit false and zero values, private/shared permission variants and one missing safety value.</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>{"chunk_mode":[0,1],"graph_enabled":[true,false],"multimodal":[true,false],"profile":"mock"}</t>
+          <t>{"graph_config_forms":["json_string","object"],"profile":"mock"}</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>1. Submit the minimal creation payload. =&gt; Existing defaults still apply and the legacy field names remain unchanged.
-2. Submit a payload with chunking, retrieval and graph configuration. =&gt; The chunk mode, chunk token fields, similarity, knowledge base Top K and a serialized graph configuration reach the upstream payload.
-3. Submit with the graph and multimodal capabilities disabled. =&gt; The graph configuration and the hidden model fields are absent from the upstream payload.</t>
+          <t>1. Render the configuration and graph sections for each response shape. =&gt; Values appear in their corresponding named fields and a model name is not duplicated.
+2. Inspect false, zero and missing values. =&gt; False and zero remain off/zero; a missing safety value is shown as unknown.
+3. Render private and shared permission records with group IDs. =&gt; Scope and group names follow local permission data and the viewer's group-read permission.</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
-          <t>New configuration fields reach the upstream request.
-Legacy field names and defaults are preserved.
-Disabled capabilities submit no hidden configuration.</t>
+          <t>JSON text and object graph settings render consistently.
+Boolean false and numeric zero remain distinct from missing values.
+Effective permission and available group names come from the permission layer.</t>
         </is>
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>No ES knowledge base request shape change.
-No invented graph JSON keys.
-No model value submitted for a disabled capability.</t>
+          <t>No group IDs or AIDP task history are written during rendering.
+No missing setting is presented as enabled or disabled.</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>{"endpoint":"/aidp-mgmt/knowledge-bases","method":"POST","protocol":"HTTP","request_expectations":["Chunk mode, chunk token and overlap values follow the documented types and bounds.","Graph configuration is serialized as the documented string payload.","Legacy field names remain in place for existing callers."],"response_expectations":["The created knowledge base identifier is returned as before.","Permission and group handling keeps its existing behavior.","A failed upstream create surfaces a stable error without partial local state."]}</t>
+          <t>{"assertions":["Graph fields and the two separate Top K values render under the correct labels.","Explicit false and zero are preserved while absent values remain unknown.","Group names render only with group:read permission."],"inputs":["AIDP detail payload","graph_config value","local group permission record"],"unit_boundary":"AIDP knowledge detail configuration parsing and permission presentation"}</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr"/>
@@ -3090,7 +1149,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>AKPR-D2-003</t>
+          <t>AKPR-D1-001</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -3105,17 +1164,17 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>AKPR-RULE-014</t>
+          <t>AKPR-RULE-001</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Update request forwards an explicit disabled safety guard and reports partial failure</t>
+          <t>Overview guide expands, collapses and keeps the fixed three steps</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>FE-COMP</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -3135,43 +1194,42 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>Verify the safety guard survives the update whitelist, an explicit zero is forwarded and permission success stays distinguishable from metadata failure.</t>
+          <t>Verify the AIDP-only guide renders the knowledge base explanation with the fixed steps and toggles without disturbing page state.</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>An authenticated update reaches the AIDP management proxy for a base the caller may edit.</t>
+          <t>Render the AIDP overview component with an empty knowledge base list.</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>{"guard":["enabled to disabled","unchanged","disabled to enabled"],"metadata_failure":true,"profile":"mock"}</t>
+          <t>{"locale":"zh-CN","profile":"mock"}</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>1. Disable the safety guard and save. =&gt; The upstream metadata payload contains the field as integer 0.
-2. Save again without changing the guard. =&gt; The field is not resent when nothing changed.
-3. Make the upstream metadata update fail after the permission write. =&gt; The response distinguishes saved permissions from a failed metadata update and the readback keeps the previous guard value.</t>
+          <t>1. Mount the overview page. =&gt; The guide is expanded and lists create knowledge base, upload files and configure the knowledge base in an agent.
+2. Collapse the guide. =&gt; The guide body is hidden while the reopen entry stays visible and operable.
+3. Reopen the guide. =&gt; The explanation and the three steps are visible again with unchanged search and view state.</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>An explicit 0 is forwarded and an unchanged value is omitted.
-Permission and metadata outcomes are separately reported.
-A metadata failure is never presented as a saved guard value.</t>
+          <t>The explanation and the three documented steps are visible when expanded.
+Collapse hides only the guide body.
+Reopening restores the same content order.</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>No silent drop of the disabled value by the field whitelist.
-No boolean encoding.
-No claimed success on upstream failure.</t>
+          <t>No backend request is issued by expanding or collapsing the guide.
+No search, page or view mode change.</t>
         </is>
       </c>
       <c r="P4" s="5" t="inlineStr">
         <is>
-          <t>{"endpoint":"/aidp-mgmt/knowledge-bases/{kds_id}/permission","method":"PATCH","protocol":"HTTP","request_expectations":["Only explicitly changed metadata fields are sent.","The safety guard is forwarded as an integer when it changed.","Permission and group fields keep their existing rules."],"response_expectations":["Permission save status and metadata update status are reported separately.","A failed metadata update yields a non-success result with the unchanged readback value.","Cache invalidation follows a successful metadata update."]}</t>
+          <t>{"assertions":["Guide content is visible on first entry.","The reopen entry remains visible after collapse.","The three step labels match the fixed order.","Guide toggling issues no request."],"inputs":["initial expanded state","collapse click","reopen click"],"unit_boundary":"AIDP knowledge guide expansion state and fixed step labels"}</t>
         </is>
       </c>
       <c r="Q4" s="5" t="inlineStr"/>
@@ -3197,7 +1255,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>AKPR-D2-004</t>
+          <t>AKPR-D1-002</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -3212,17 +1270,18 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AKPR-RULE-012</t>
+          <t>AKPR-RULE-002
+AKPR-RULE-004</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Model queries select a single category per control</t>
+          <t>Cards are the default view and switching or hiding columns keeps the result set</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>CONTRACT</t>
+          <t>FE-COMP</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -3242,43 +1301,43 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Verify the model query proxy passes one category per request and returns only models applicable to the knowledge base application.</t>
+          <t>Verify default card rendering, table switching and column visibility control over one shared paginated result set.</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>A controllable upstream model fixture serves distinct payloads per category.</t>
+          <t>Render the overview with a fixed page of knowledge bases and a recorded search and page number.</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>{"categories":["llm","vlm","embedding"],"profile":"mock"}</t>
+          <t>{"page_size":10,"profile":"mock","total":23}</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>1. Query the graph model list. =&gt; The request carries the llm category and the response exposes only llm models.
-2. Query the multimodal model list. =&gt; The request carries the vlm category and the response exposes only vlm models.
-3. Query an unsupported or failing category. =&gt; A stable error or an empty result is returned without falling back to another category.</t>
+          <t>1. Mount the overview with existing results. =&gt; Knowledge bases render as cards.
+2. Switch to the table view. =&gt; The same records render as table rows with the current keyword and page preserved.
+3. Hide one optional column and then restore defaults. =&gt; The column disappears and returns while the name and action columns stay present throughout.</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>One category is requested per control.
-Responses are not reused across categories.
-Failures do not silently substitute another category.</t>
+          <t>The card view is the default.
+Switching views keeps keyword, page and totals identical.
+Hiding and restoring columns changes only local visibility.</t>
         </is>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
-          <t>No shared cache entry across categories.
-No fabricated model identifier on failure.
-No change to existing non-AIDP model endpoints.</t>
+          <t>No mutating endpoint is called by view or column changes.
+No record is dropped or duplicated by switching views.
+Required columns cannot be hidden.</t>
         </is>
       </c>
       <c r="P5" s="5" t="inlineStr">
         <is>
-          <t>{"endpoint":"/aidp-mgmt/models","method":"GET","protocol":"HTTP","request_expectations":["The service parameter carries exactly one requested category.","The application parameter keeps the knowledge base scope.","No credential is returned to the browser."],"response_expectations":["Only models of the requested category are returned.","An unavailable category yields a stable error or an empty list.","Results are filtered to the knowledge base application scope."]}</t>
+          <t>{"assertions":["Initial view mode is cards.","Table switch preserves keyword, page and total.","Hidden optional column is absent and restorable.","Name and action columns stay visible."],"inputs":["default view mode","card to table switch","hidden column set","restore defaults action"],"unit_boundary":"Overview view mode and column visibility state"}</t>
         </is>
       </c>
       <c r="Q5" s="5" t="inlineStr"/>
@@ -3304,20 +1363,2756 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>AKPR-D1-003</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-003</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Independent name search drives the keyword query and resets the page</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Verify the single search box reuses the existing keyword query, resets to page one and keeps table headers free of search controls.</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Render the overview with a recorded non-first page and a stubbed list service.</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>{"keyword":"finance","page":3,"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>1. Type a keyword into the page search box and wait for the debounce. =&gt; The list service is called with the keyword and page one for both views.
+2. Clear the search box. =&gt; The unfiltered permission-scoped set is requested again.
+3. Inspect the table header row. =&gt; No column exposes a search or filter control.</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>The keyword query is reused with a page reset.
+Clearing restores the unfiltered set.
+Column headers contain no search entry.</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>No request per keystroke outside the debounce.
+No column filter parameter is sent.</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["listKbs receives keyword and page one after debounce.","Clearing the box requests the unfiltered set.","No header search control exists."],"inputs":["keyword text","debounce interval elapse","clear action","table header render"],"unit_boundary":"Overview search debounce and page reset with the existing keyword parameter"}</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-004</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-005
+AKPR-RULE-009</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>File view targets one knowledge base and restores the previous list state on return</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Verify the full-page file view scoping, the preserved list state on return and the cleanup of the previous base document state.</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Render the overview with two knowledge bases and a recorded search, page, view mode and column setting.</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>{"other_base":"kb-beta","profile":"mock","selected_base":"kb-alpha"}</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>1. Select a knowledge base. =&gt; Only that base files render and the overview is replaced by the full-page file view.
+2. Return to the overview. =&gt; The previous keyword, page, view mode and column setting are intact.
+3. Resolve a delayed document response from the first base after selecting the second. =&gt; The delayed payload is discarded and the second base files remain.</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>Files belong to the selected base only.
+Returning restores the previous list state.
+A stale response never overwrites the current base.</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>No cross-base document leakage.
+No polling left running after leaving the file view.
+No list state reset on return.</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["File list requests carry the selected base id.","Return renders the preserved list state.","A late response for the previous base is ignored.","Polling state is cleared when the view is left."],"inputs":["selected base id","return action","delayed response for a previous base"],"unit_boundary":"List and file view switching, document state reset and polling cleanup"}</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr"/>
+      <c r="U7" s="5" t="inlineStr"/>
+      <c r="V7" s="5" t="inlineStr"/>
+      <c r="W7" s="5" t="inlineStr"/>
+      <c r="X7" s="5" t="inlineStr"/>
+      <c r="Y7" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z7" s="5" t="inlineStr"/>
+      <c r="AA7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-005</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-006</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>AIDP list metadata normalizes real values and marks unknown ones as absent</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>BE-UT</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Verify the list response normalization of private and public type, capacity and missing values without fabricating data.</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Provide raw AIDP list rows with mixed boolean, numeric, string and missing metadata values.</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>{"cases":["is_private true","is_private 0","is_private string true","missing is_private","current_cap 2.5","missing current_cap","missing document count"],"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>1. Normalize rows with boolean, numeric and string forms of is_private. =&gt; A stable personal or enterprise type is produced for every form.
+2. Normalize rows without a type, capacity or count value. =&gt; Those fields are reported as unknown instead of a fabricated default.
+3. Normalize a valid personal capacity. =&gt; The documented unit value is preserved unchanged.</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>Real values survive normalization.
+Unknown values are distinguishable from a real zero.
+Capacity is not estimated from file sizes.</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>No Nexent group permission is used to infer the base type.
+No synthetic zero count or capacity is produced.
+No extra upstream request is issued per row.</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Boolean, integer and string is_private forms normalize consistently.","A missing count is distinguishable from zero.","A missing capacity is reported as unknown.","A valid capacity keeps its unit."],"inputs":["is_private variants","current_cap values","document count presence"],"unit_boundary":"AIDP list metadata normalization helpers"}</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="inlineStr"/>
+      <c r="T8" s="5" t="inlineStr"/>
+      <c r="U8" s="5" t="inlineStr"/>
+      <c r="V8" s="5" t="inlineStr"/>
+      <c r="W8" s="5" t="inlineStr"/>
+      <c r="X8" s="5" t="inlineStr"/>
+      <c r="Y8" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z8" s="5" t="inlineStr"/>
+      <c r="AA8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-006</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-007</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Read-only and unavailable knowledge bases expose no modification entry</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Verify that permission and lifecycle restrictions remove every executable modification entry in cards, table rows and the file view.</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Render the overview with one editable, one read-only and one unavailable knowledge base.</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>{"permissions":["EDIT","READ_ONLY"],"profile":"mock","resource_status":["available","unavailable"]}</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>1. Render the card menu and table actions for each permission. =&gt; Only the editable base offers executable edit and delete entries.
+2. Open the file view of a read-only base. =&gt; Upload and delete entries are absent or disabled while browsing stays possible.
+3. Render an unavailable base. =&gt; No executable modification entry is offered and its state stays visible.</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>Modification entries follow the effective permission.
+Unavailable bases stay visible without modification entries.
+No request is emitted from a disabled entry.</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>No modification request for read-only or unavailable bases.
+No hidden menu item remains clickable.
+No downgrade of the existing visibility rules.</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Read-only rows render no executable modification entry.","Unavailable rows keep their lifecycle indicator.","No request leaves a disabled entry."],"inputs":["effective permission","resource_status","menu open state"],"unit_boundary":"Card menu and table action rendering under permission and lifecycle states"}</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="inlineStr"/>
+      <c r="T9" s="5" t="inlineStr"/>
+      <c r="U9" s="5" t="inlineStr"/>
+      <c r="V9" s="5" t="inlineStr"/>
+      <c r="W9" s="5" t="inlineStr"/>
+      <c r="X9" s="5" t="inlineStr"/>
+      <c r="Y9" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z9" s="5" t="inlineStr"/>
+      <c r="AA9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-007</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-002</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>First-load empty, filtered empty, loading and failure states stay distinct</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Verify the four overview states render distinct messages and remain localized.</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Render the overview with a stubbed service returning an empty set, an empty filtered set, a pending promise and an error.</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>{"locales":["zh","en"],"profile":"mock","states":["first empty","filtered empty","loading","failed"]}</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>1. Resolve an empty list without a keyword. =&gt; A first-use empty state renders instead of a search-empty state.
+2. Resolve an empty list with an active keyword. =&gt; A search-empty state renders with the keyword context.
+3. Keep the request pending and then reject it. =&gt; Loading and failure states render distinctly and the failure state offers a retry path.</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>All four states are distinguishable.
+Both locales resolve every state string.</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>No fabricated placeholder rows.
+No silent failure rendering as an empty state.</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["First empty and filtered empty differ.","Loading state precedes data.","Failure state is distinct and localized.","No placeholder rows are invented."],"inputs":["empty payload","empty filtered payload","pending request","rejected request","locale"],"unit_boundary":"Overview empty, loading and failure state rendering"}</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr"/>
+      <c r="U10" s="5" t="inlineStr"/>
+      <c r="V10" s="5" t="inlineStr"/>
+      <c r="W10" s="5" t="inlineStr"/>
+      <c r="X10" s="5" t="inlineStr"/>
+      <c r="Y10" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z10" s="5" t="inlineStr"/>
+      <c r="AA10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-008</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-010</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Two-step creation validates locally, preserves state and creates exactly once</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Verify step navigation without creation, state preservation across steps and single creation before upload.</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Render the AIDP creation page with stubbed create and upload services and a selected local file.</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>{"failing_uploads":1,"files":2,"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>1. Fill step one and press next. =&gt; Validation runs with no create request issued and step two renders.
+2. Return to step one. =&gt; Form values, conditional sections and the selected files are preserved.
+3. Submit with one failing upload. =&gt; Creation happens once and the created base and the failed upload are reported separately.
+4. Submit again after the failed upload. =&gt; No second knowledge base is created and the retry targets the failed file only.</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>Step one never creates a resource.
+State survives backward navigation.
+Creation happens exactly once before uploads.</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>No create request from the next action.
+No duplicate base after retry or double click.
+No upload before a successful create.</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Next issues no create request.","Backward navigation keeps values and files.","Exactly one create request precedes uploads.","A failed upload does not trigger a second create."],"inputs":["step one form values","selected files","upload failure","repeated submit"],"unit_boundary":"Creation page step state, submit guard and create-then-upload sequencing"}</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S11" s="5" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr"/>
+      <c r="U11" s="5" t="inlineStr"/>
+      <c r="V11" s="5" t="inlineStr"/>
+      <c r="W11" s="5" t="inlineStr"/>
+      <c r="X11" s="5" t="inlineStr"/>
+      <c r="Y11" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z11" s="5" t="inlineStr"/>
+      <c r="AA11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-009</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-011</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Creation defaults and chunking mapping follow the confirmed values</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>BE-UT</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Verify preserved creation defaults, the chunk mode enumeration and the overlap-to-token conversion with its bounds.</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>Prepare create payloads with missing defaults, both chunk modes and boundary overlap percentages.</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>{"chunk_tokens":[1024,512],"modes":["smart","legal"],"percents":[12.5,50],"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>1. Submit a payload without explicit chunking or retrieval values. =&gt; The existing defaults apply unchanged and the new graph parameters use their documented defaults.
+2. Submit each chunk mode. =&gt; The chunk mode serializes as 0 for smart splitting and 1 for legal clauses.
+3. Submit overlap percentages including the boundaries. =&gt; The overlap becomes the floor conversion in integer tokens and any value above half the chunk size is rejected.</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>Defaults remain 1024 tokens, 128 overlap, 0.0 similarity and Top K 10.
+Chunk modes serialize 0 and 1.
+Overlap conversion is exact and bounded.</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>No silent clamping of an invalid overlap.
+No renamed legacy field in the outgoing payload.
+No change to the ES knowledge base contract.</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Defaults match the existing Nexent values.","Overlap equals the floor conversion.","Overlap above 50 percent of the chunk size is rejected.","Legacy field names stay unchanged."],"inputs":["payload without defaults","chunk mode selection","chunk tokens and overlap percent"],"unit_boundary":"Create default application, chunk mode mapping and overlap conversion"}</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S12" s="5" t="inlineStr"/>
+      <c r="T12" s="5" t="inlineStr"/>
+      <c r="U12" s="5" t="inlineStr"/>
+      <c r="V12" s="5" t="inlineStr"/>
+      <c r="W12" s="5" t="inlineStr"/>
+      <c r="X12" s="5" t="inlineStr"/>
+      <c r="Y12" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z12" s="5" t="inlineStr"/>
+      <c r="AA12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-010</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-013</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Graph configuration serializes documented keys with an inverse thinking switch</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>BE-UT</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Verify graph configuration serialization, the inverse thinking mapping, the independent Top K values and the prompt byte limit.</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>Prepare graph payloads with the switch on and off, both languages and prompt lengths around the byte limit.</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>{"domains":["general","medical"],"languages":["chinese","english"],"profile":"mock","prompt_bytes":[2048,2049]}</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>1. Submit a graph configuration with the thinking switch enabled. =&gt; The thinking mode field is false and the graph keys use their documented names.
+2. Submit a knowledge base Top K together with a graph Top K. =&gt; The two values are serialized independently without overwriting each other.
+3. Submit prompts at and beyond the byte boundary together with a disabled graph. =&gt; The limit passes at the boundary, longer input is rejected and a disabled graph omits its configuration entirely.</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>The thinking switch maps inversely onto the thinking mode field.
+Both Top K values survive independently.
+The prompt limit is enforced in UTF-8 bytes.</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>No hidden previous graph configuration is submitted when the graph is off.
+No graph Top K overwrites the knowledge base Top K.
+No invented JSON key names.</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["The thinking mode field is false when thinking is enabled.","Graph and knowledge base Top K stay independent.","Prompt length is measured in UTF-8 bytes.","Disabled graph omits its configuration."],"inputs":["graph switch","domain","graph top k","hop count","thinking switch","prompt language","prompt text"],"unit_boundary":"Graph configuration validation and serialization"}</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S13" s="5" t="inlineStr"/>
+      <c r="T13" s="5" t="inlineStr"/>
+      <c r="U13" s="5" t="inlineStr"/>
+      <c r="V13" s="5" t="inlineStr"/>
+      <c r="W13" s="5" t="inlineStr"/>
+      <c r="X13" s="5" t="inlineStr"/>
+      <c r="Y13" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z13" s="5" t="inlineStr"/>
+      <c r="AA13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-011</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-012</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Graph and multimodal models are queried from separate categories with independent caches</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Verify the model category split, the independent query caches and the omission of hidden model values.</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Render the creation form with stubbed model queries per category and both capability switches toggled.</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>{"categories":["llm","vlm","embedding"],"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>1. Enable the graph section. =&gt; The graph model query uses the llm category and fills the graph model field.
+2. Enable multimodal captioning. =&gt; The multimodal model query uses the vlm category and fills the multimodal field independently.
+3. Disable each capability after a selection. =&gt; The hidden model value is absent from the submitted payload.</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>Each model field is populated from its own category.
+Caches and selections never mix.
+Disabled capabilities submit no model value.</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>No llm result used for the multimodal field.
+No hidden previous model resubmitted.
+No unverified model name silently defaulted.</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Graph query uses llm and multimodal uses vlm.","Caches are keyed independently.","Disabled capability clears its submitted model."],"inputs":["graph switch","multimodal switch","selected models","query cache keys"],"unit_boundary":"Creation form model queries, caches and hidden value handling"}</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S14" s="5" t="inlineStr"/>
+      <c r="T14" s="5" t="inlineStr"/>
+      <c r="U14" s="5" t="inlineStr"/>
+      <c r="V14" s="5" t="inlineStr"/>
+      <c r="W14" s="5" t="inlineStr"/>
+      <c r="X14" s="5" t="inlineStr"/>
+      <c r="Y14" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z14" s="5" t="inlineStr"/>
+      <c r="AA14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-012</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Safety guard serializes integer 1 and 0 and never omits an explicit disabled value</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>BE-UT</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>retired</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Retired because AIDP knowledge-base safety guard support was removed from the product scope.</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>Prepare create and update payloads with the guard enabled, explicitly disabled and absent.</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock","values":["enabled 1","explicit 0","absent"]}</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>1. Build a create payload with the guard enabled and disabled. =&gt; The field is present as integer 1 or explicit 0.
+2. Build an update payload that only changes the guard to off. =&gt; The field survives the update whitelist and is forwarded as 0.
+3. Map a query response that lacks the field. =&gt; The state is reported as unknown rather than confirmed off.</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>Integer 1 and 0 are both serialized.
+An explicit 0 is never dropped by filtering.
+Missing data is not reported as a confirmed disabled state.</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>No boolean or string encoding of the field.
+No field nesting inside graph configuration.
+No Nexent-side content interception added.</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Enabled serializes 1 and disabled serializes 0.","The update whitelist forwards the field.","A missing field maps to unknown."],"inputs":["safety switch state","create payload","update payload","query response without the field"],"unit_boundary":"Safety guard request serialization and query mapping"}</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S15" s="5" t="inlineStr"/>
+      <c r="T15" s="5" t="inlineStr"/>
+      <c r="U15" s="5" t="inlineStr"/>
+      <c r="V15" s="5" t="inlineStr"/>
+      <c r="W15" s="5" t="inlineStr"/>
+      <c r="X15" s="5" t="inlineStr"/>
+      <c r="Y15" s="5" t="inlineStr">
+        <is>
+          <t>无需绑定</t>
+        </is>
+      </c>
+      <c r="Z15" s="5" t="inlineStr"/>
+      <c r="AA15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-013</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-001
+AKPR-RULE-002
+AKPR-RULE-015</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Overview tutorial and knowledge cards follow the approved visual hierarchy</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Verify the overview structure keeps clear guide spacing and the prototype card layout without changing the shared list state.</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>Render the AIDP overview with four knowledge bases and a 1382-pixel desktop viewport.</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>{"card_count":4,"profile":"mock","viewport_width":1382}</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>1. Render the expanded guide. =&gt; The explanation heading and paragraph are distinct from three step cards with at least 24 pixels of separation.
+2. Inspect one knowledge card. =&gt; The fixed icon, name and menu occupy the first row, description uses the full card width, and update time, file count and capacity share one footer row.
+3. Render a final page with fewer cards. =&gt; Remaining cards keep the same width and height and the page footer stays at the bottom of the content area.</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>Tutorial content has readable vertical separation and matches the three-step design.
+Card descriptions do not share a narrow icon column.
+Card metadata aligns on one row and cards do not stretch to fill unused grid space.</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>No fabricated timestamps, file counts or capacity values are rendered.
+No ES page component or global style changes are required.</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["The guide paragraph and step cards have a rendered gap of at least 24 pixels.","Every card exposes one footer row containing update time, document count and capacity.","Card grid uses auto-fit columns and a short last page leaves card dimensions unchanged."],"inputs":["expanded guide","card metadata","short final page"],"unit_boundary":"AIDP guide and card DOM structure at desktop viewport"}</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr"/>
+      <c r="T16" s="5" t="inlineStr"/>
+      <c r="U16" s="5" t="inlineStr"/>
+      <c r="V16" s="5" t="inlineStr"/>
+      <c r="W16" s="5" t="inlineStr"/>
+      <c r="X16" s="5" t="inlineStr"/>
+      <c r="Y16" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z16" s="5" t="inlineStr"/>
+      <c r="AA16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-014</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-010
+AKPR-RULE-016</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Creation page keeps switches beside labels and aligns paired controls</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Verify the AIDP create page is full-width, section controls have the designed visual grouping, and paired controls share a baseline.</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>Render the first creation step at desktop width with safety, graph and VLM controls visible.</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>{"chunk_modes":[0,1],"profile":"mock","viewport_width":1382}</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>1. Render the page header and form. =&gt; The creation form uses the available content width and the breadcrumb reads knowledge base / create knowledge base.
+2. Inspect safety, graph and VLM toggle groups. =&gt; Each switch sits beside its corresponding label and help icon.
+3. Inspect fields that share a row. =&gt; Both controls use the same label structure and their input or slider starts differ by no more than one pixel.</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>No fixed narrow modal-sized content column constrains the create page.
+Switches are adjacent to their own labels rather than the far edge of the row.
+Paired model, chunking and retrieval controls align consistently.</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>No global Ant Design or ES knowledge-base style override is introduced.
+No change to values submitted for chunk_mode 0 or 1.</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["The creation header and form fill the available page content width.","Switches are grouped within 12 pixels of their labels.","Paired controls use consistent label and field alignment."],"inputs":["desktop viewport","graph toggle","VLM toggle","paired model controls"],"unit_boundary":"AIDP create form section layout and toggle grouping"}</t>
+        </is>
+      </c>
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S17" s="5" t="inlineStr"/>
+      <c r="T17" s="5" t="inlineStr"/>
+      <c r="U17" s="5" t="inlineStr"/>
+      <c r="V17" s="5" t="inlineStr"/>
+      <c r="W17" s="5" t="inlineStr"/>
+      <c r="X17" s="5" t="inlineStr"/>
+      <c r="Y17" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z17" s="5" t="inlineStr"/>
+      <c r="AA17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-D1-001</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-005</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-005</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-RULE-013
+CMSR-RULE-014</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Observer emits safe content before stream completion</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>SDK-UT</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Verify bounded marker lookahead and attempt state reset.</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Create an isolated observer and a controlled chunk sequence.</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock","sequence":"failed partial, rollback, successful split code and think markers"}</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>1. Feed a safe prefix and pause the source. =&gt; The prefix is emitted before flush or commit.
+2. Roll back the first attempt and feed split markers in the second. =&gt; The second output is ordered and contains no first-attempt residue.</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>The earliest safe content is observable before completion.
+Split markers retain their original semantics.</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>No stale fragment crosses attempts.
+No code is executed by the observer.</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Safe prefix emitted before flush.","Raw code tag retained.","No failed-attempt residue."],"inputs":["normal content","split &lt;think&gt; and &lt;/think&gt;","raw &lt;code&gt; content"],"unit_boundary":"Observer.add_model_new_token and attempt lifecycle"}</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S18" s="5" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_model_attempt_stream.py</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="inlineStr">
+        <is>
+          <t>test_cmsr_d1_001</t>
+        </is>
+      </c>
+      <c r="V18" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W18" s="5" t="inlineStr"/>
+      <c r="X18" s="5" t="inlineStr"/>
+      <c r="Y18" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z18" s="5" t="inlineStr">
+        <is>
+          <t>sha256:625e8c8829b51b9cd91344555d05c5ebfdc7bd766d8485eab99b9f22773f3233</t>
+        </is>
+      </c>
+      <c r="AA18" s="5" t="inlineStr">
+        <is>
+          <t>sha256:242f1aaf8a5fe4427f503e5acb8db2cc6cb5096782c2e4fdf49fcb17ec471420</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-D1-002</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-005</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-005</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-RULE-014
+CMSR-RULE-015</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Running step labels precede reasoning and survive retry rollback</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Verify immediate running labels, rollback preservation, legacy history and removal of terminal label-only cards.</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Create the streaming adapter with a controlled SSE fixture.</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock","sequences":["step 1, failed attempt, rollback, successful raw code, parse","legacy content before step label"]}</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>1. Emit a step label before any model content. =&gt; A running reasoning card displays Step 1 immediately.
+2. Roll back a partial attempt and stream successful raw code. =&gt; Step 1 remains during rollback and only successful raw code follows it.
+3. Parse and reload both new and legacy-order history. =&gt; One code card and one labeled nonempty reasoning card remain; a terminal label-only card is absent.</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>Step label appears before first token.
+Rollback preserves the label.
+Successful original content remains after the label.
+Old history prepends late labels.</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>No failed-attempt content.
+No duplicate code card.
+No sibling invocation mutation.</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Running label is visible before content.","Terminal label-only step is hidden.","Successful code is visible after the label before commit.","History equals live output."],"inputs":["step_count","model_attempt_control","model_output_thinking","parse"],"unit_boundary":"Frontend live and history reasoning projection"}</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_reasoning_card.ts</t>
+        </is>
+      </c>
+      <c r="U19" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-D1-002</t>
+        </is>
+      </c>
+      <c r="V19" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W19" s="5" t="inlineStr"/>
+      <c r="X19" s="5" t="inlineStr"/>
+      <c r="Y19" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z19" s="5" t="inlineStr">
+        <is>
+          <t>sha256:b614502639e969ab0f3840d1381f1b12b01cb5b693a0b02d17387192b230b354</t>
+        </is>
+      </c>
+      <c r="AA19" s="5" t="inlineStr">
+        <is>
+          <t>sha256:03f5fae5200c76ca296c75ab0ebf225f190fb3fe6a7f52c7c8c7e0da2a97d07c</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-D1-003</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-005</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-005</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-RULE-014
+CMSR-RULE-016</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>CoreAgent commits streamed valid semantic repair</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>SDK-UT</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>A protocol-invalid first attempt rolls back while its single preceding step label survives and the corrected result streams and commits.</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>A controlled model yields an invalid response then a pausable valid code action at step one.</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock","sequence":"invalid code, rollback, corrected code chunks, commit, parse"}</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>1. Begin step one and return protocol-invalid model content. =&gt; Exactly one step label precedes begin; the attempt rolls back and one repair is scheduled.
+2. Pause the valid repair after its first safe chunk. =&gt; That chunk is visible before model completion.
+3. Complete the repair and classify it. =&gt; Its attempt commits and a single parse follows.</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>Corrected content is streamed and committed.
+Only the corrected action is executed.
+Lifecycle logs identify the repair without content.</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>No failed content after rollback.
+No repair instruction in user output.
+No suppressed successful stream.</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Step label occurs before both model attempts and only once.","Successful repair does not set stream suppression.","Corrected attempt commits once.","Invalid attempt rolls back once."],"inputs":["step one","invalid model content","valid streamed &lt;code&gt; action"],"unit_boundary":"CoreAgent semantic repair and deferred model attempt lifecycle"}</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S20" s="5" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_semantic_repair_stream.py</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="inlineStr">
+        <is>
+          <t>test_cmsr_d1_003</t>
+        </is>
+      </c>
+      <c r="V20" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W20" s="5" t="inlineStr"/>
+      <c r="X20" s="5" t="inlineStr"/>
+      <c r="Y20" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z20" s="5" t="inlineStr">
+        <is>
+          <t>sha256:7ef8664f2224d068d7deafecf80f09353d734bc10b35a1147b3cc58d1ae6eacd</t>
+        </is>
+      </c>
+      <c r="AA20" s="5" t="inlineStr">
+        <is>
+          <t>sha256:1dee7e7ce90f70c40d02907f11be7b55665495fdcaa3dfdec3ab478953c5c38c</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-D1-004</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-005</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-005</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-RULE-018</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Rejected model output diagnostics distinguish budget exhaustion without default content leakage</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>SDK-UT</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Correlate each protocol rejection to the model response shape and budget while gating bounded raw previews.</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Use isolated model diagnostics for a reasoning-only length response and a malformed nonempty response.</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock","responses":["length with 4096 reasoning-only output tokens","malformed nonempty code Action"]}</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>1. Reject a reasoning-only length response with diagnostics disabled. =&gt; The log records model, attempt, requested and consumed tokens, reasoning and content counts, and reasoning-only budget exhaustion without raw text.
+2. Reject a malformed content response. =&gt; The distinct protocol reason and response shape are logged under its own attempt identifier.
+3. Enable diagnostic content preview for a rejected response longer than the preview cap. =&gt; Only a single escaped bounded prefix of model content and reasoning is logged; the full text remains absent.</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>Each rejection is attributable to one attempt and specific failure class.
+Raw output is absent by default and bounded on explicit opt-in.</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>No model output or user prompt enters SSE or persisted history from diagnostics.
+No secret or full raw payload is logged by default.
+No retry-budget or execution behavior changes.</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Reasoning-only budget exhaustion flag is accurate.","Logs include attempt and token counts.","Default logs omit raw content.","Opt-in previews are escaped and capped."],"inputs":["finish_reason=length","reasoning_content","invalid code Action","explicit diagnostic flag"],"unit_boundary":"OpenAI model response diagnostics and CoreAgent protocol-error logging"}</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S21" s="5" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_protocol_rejection_diagnostics.py</t>
+        </is>
+      </c>
+      <c r="U21" s="5" t="inlineStr">
+        <is>
+          <t>test_cmsr_d1_004</t>
+        </is>
+      </c>
+      <c r="V21" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W21" s="5" t="inlineStr"/>
+      <c r="X21" s="5" t="inlineStr"/>
+      <c r="Y21" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z21" s="5" t="inlineStr">
+        <is>
+          <t>sha256:9f06a6565fff8e542fdcb89725b5fc7f669ad52b07301bdc99aa3e2eba23552c</t>
+        </is>
+      </c>
+      <c r="AA21" s="5" t="inlineStr">
+        <is>
+          <t>sha256:a53056127d5f2efce4a9d98c92c9c97892451de0d1d353603584612c0a9ef1ba</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:AA21"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AA9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="13" max="13"/>
+    <col width="42" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="15" max="15"/>
+    <col width="42" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="42" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col hidden="1" width="42" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="42" customWidth="1" min="27" max="27"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>用例ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>功能ID</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>需求ID</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>业务规则ID</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>自动化</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>目标</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>前置条件</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>测试数据</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>操作步骤及步骤预期</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>最终预期</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>禁止副作用</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>阶段专属字段</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>执行配置</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>自动化实现状态</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>测试框架</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>脚本路径</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>Selector</t>
+        </is>
+      </c>
+      <c r="V1" s="4" t="inlineStr">
+        <is>
+          <t>执行Profile</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>所需Mock服务</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>所需测试资产</t>
+        </is>
+      </c>
+      <c r="Y1" s="4" t="inlineStr">
+        <is>
+          <t>Manifest校验状态</t>
+        </is>
+      </c>
+      <c r="Z1" s="4" t="inlineStr">
+        <is>
+          <t>契约哈希</t>
+        </is>
+      </c>
+      <c r="AA1" s="4" t="inlineStr">
+        <is>
+          <t>实现哈希</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>AKDT-D2-001</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>AKDT-001</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>AKDT-001</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>AKDT-RULE-002
+AKDT-RULE-003</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Ingested-file endpoint queries only the AIDP file listing</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>CONTRACT</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Verify file search and paging proxy only successfully ingested AIDP files and never substitutes History records or local PG rows.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>An authenticated caller has READ access to one AIDP knowledge base.
+The AIDP fixture contains one completed document and one processing History record with different IDs.</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>{"keyword":"handbook","page":2,"page_size":20,"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>1. Request the file page with a keyword and page size. =&gt; The request is forwarded to the AIDP KnowledgeFiles listing with page, page_size and keyword.
+2. Inspect the file result and total. =&gt; Only records from the ingested-file listing appear and the response reports its paging fields.
+3. Deny READ access and repeat the request. =&gt; The proxy rejects the request before contacting AIDP.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>File endpoint data comes only from the live ingested-file endpoint.
+Supported query fields are forwarded and totals are not computed from a task page.
+READ permission is enforced.</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>No History request is used as a file-list fallback.
+No file or task record is read from Nexent PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>{"endpoint":"/aidp-mgmt/knowledge-bases/{kds_id}/files","method":"GET","protocol":"HTTP","request_expectations":["page and page_size are positive; page_size is bounded to 100.","keyword is forwarded when non-empty.","READ permission is checked before the upstream request."],"response_expectations":["value contains only ingested-file records.","total_count, has_more and total_reliable reflect the upstream listing/count result."]}</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr"/>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr"/>
+      <c r="T2" s="5" t="inlineStr"/>
+      <c r="U2" s="5" t="inlineStr"/>
+      <c r="V2" s="5" t="inlineStr"/>
+      <c r="W2" s="5" t="inlineStr"/>
+      <c r="X2" s="5" t="inlineStr"/>
+      <c r="Y2" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z2" s="5" t="inlineStr"/>
+      <c r="AA2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>AKDT-D2-002</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>AKDT-001</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>AKDT-001</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>AKDT-RULE-002
+AKDT-RULE-003
+AKDT-RULE-004</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Upload-task endpoint forwards page, search, numeric status and local-upload directory</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>CONTRACT</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Verify task queries use AIDP History with the knowledge-base file-system ID, dir_path /{kds_id}, and the supported request fields while returning AIDP statistics.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>An authenticated caller has READ access and the AIDP channel lookup returns an fs_id for the selected knowledge base.</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>{"dir_path":"/12","keyword":"policy","page":2,"page_size":10,"profile":"mock","status":0}</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>1. Request task page 2 with a name keyword and status 0. =&gt; The proxy sends page, page_size, keyword, status, fs_id and dir_path /{kds_id} to the AIDP History endpoint.
+2. Repeat for statuses 1 through 5. =&gt; Each numeric filter is forwarded unchanged and does not replace the response-record status.
+3. Inspect total, processing, failed and success counts. =&gt; Each count comes from the corresponding History response field, not the current page.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>All supported task request fields are passed to AIDP History.
+dir_path is constructed as a slash followed by the current knowledge base ID.
+Statistics and records remain upstream values and file records are separate.</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>No page-one-only result is sliced locally and labeled as an upstream page.
+No count is calculated from visible page rows.
+No task data is persisted in Nexent PostgreSQL.</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>{"endpoint":"/aidp-mgmt/knowledge-bases/{kds_id}/upload-tasks","method":"GET","protocol":"HTTP","request_expectations":["page, page_size, keyword and status are forwarded; status accepts integer 0 through 5, including 0.","History body includes fs_id returned for the current KB and dir_path /{kds_id}.","READ permission is checked before querying History."],"response_expectations":["value contains the requested page of History records.","total_record_count, processing_record_count, failed_record_count and success_record_count preserve AIDP statistics.","total_count and pagination flags match the History response."]}</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="inlineStr"/>
+      <c r="V3" s="5" t="inlineStr"/>
+      <c r="W3" s="5" t="inlineStr"/>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr"/>
+      <c r="AA3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>AKDT-D2-003</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>AKDT-001</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>AKDT-001</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>AKDT-RULE-005
+AKDT-RULE-007</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Retry forwards one or more selected file UUIDs and rejects unauthorized or empty requests</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>CONTRACT</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Verify the retry proxy checks EDIT permission, validates an explicit non-empty UUID array and uses the AIDP documented request example.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>An authenticated caller and a valid knowledge base exist.</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>{"file_uuids":["uuid-a","uuid-b"],"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>1. Submit one valid file UUID and then multiple valid UUIDs. =&gt; The upstream body contains file_uuids as the same explicit array and no speculative fields.
+2. Submit an empty array or malformed UUID. =&gt; The request is rejected and AIDP is not called.
+3. Submit as a READ_ONLY caller. =&gt; The request is rejected before AIDP is called.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Both single-file and multiple-file arrays are accepted when valid.
+Empty or malformed arrays are rejected.
+EDIT permission is required.</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>Empty input never means retry all files.
+No retry request contains retry_file_info or only_retry_graph.
+No retry request for a different knowledge base is issued.</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>{"endpoint":"/aidp-mgmt/knowledge-bases/{kds_id}/upload-tasks/retry","method":"POST","protocol":"HTTP","request_expectations":["Body requires a non-empty file_uuids array of UUIDs and deduplicates repeated IDs.","EDIT permission is checked before upstream access.","Upstream endpoint is POST KnowledgeFiles/Retry with only file_uuids in the body."],"response_expectations":["AIDP success_list and failed_list are preserved per file.","Partial success is not collapsed into a blanket success response."]}</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr"/>
+      <c r="W4" s="5" t="inlineStr"/>
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z4" s="5" t="inlineStr"/>
+      <c r="AA4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D2-001</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-002
+AKPR-RULE-006</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Knowledge base list keeps its contract and adds optional display fields</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>CONTRACT</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Verify the paginated AIDP list proxy keeps its existing request and response contract while exposing the optional display metadata.</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>An authenticated request reaches the AIDP management proxy with a controllable upstream fixture.</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>{"keyword":"alpha","page":1,"page_size":10,"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>1. Request the first page with a keyword. =&gt; The proxy forwards page, page_size and keyword and applies the existing permission intersection.
+2. Inspect the response payload. =&gt; Existing fields keep their names and types and the optional display fields appear only when the upstream returns them.
+3. Request a later page. =&gt; Ordering and totals remain consistent with the unfiltered permission-scoped set.</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>Existing request parameters and response fields are unchanged.
+Optional display metadata is additive.
+Pagination order and totals stay stable.</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>No column filter parameter is introduced.
+No fabricated default replaces a missing metadata value.
+No ES knowledge base endpoint is touched.</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>{"endpoint":"/aidp-mgmt/knowledge-bases","method":"GET","protocol":"HTTP","request_expectations":["page, page_size and keyword behave as before.","The permission-scoped access set is resolved before pagination.","No new required parameter is added."],"response_expectations":["Existing fields keep their current names and types.","Optional display fields are additive and omit a value the upstream did not return.","Page totals equal the permission-scoped count."]}</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr"/>
+      <c r="U5" s="5" t="inlineStr"/>
+      <c r="V5" s="5" t="inlineStr"/>
+      <c r="W5" s="5" t="inlineStr"/>
+      <c r="X5" s="5" t="inlineStr"/>
+      <c r="Y5" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z5" s="5" t="inlineStr"/>
+      <c r="AA5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D2-002</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-010
+AKPR-RULE-011
+AKPR-RULE-012
+AKPR-RULE-013</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Creation request carries the new configuration and keeps legacy field names</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>API-IT</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Verify the create proxy forwards chunking, retrieval, graph, model and safety fields while preserving legacy field names and existing defaults.</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>An authenticated create request reaches the AIDP management proxy with a recorded upstream payload.</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>{"chunk_mode":[0,1],"graph_enabled":[true,false],"multimodal":[true,false],"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>1. Submit the minimal creation payload. =&gt; Existing defaults still apply and the legacy field names remain unchanged.
+2. Submit a payload with chunking, retrieval and graph configuration. =&gt; The chunk mode, chunk token fields, similarity, knowledge base Top K and a serialized graph configuration reach the upstream payload.
+3. Submit with the graph and multimodal capabilities disabled. =&gt; The graph configuration and the hidden model fields are absent from the upstream payload.</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>New configuration fields reach the upstream request.
+Legacy field names and defaults are preserved.
+Disabled capabilities submit no hidden configuration.</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>No ES knowledge base request shape change.
+No invented graph JSON keys.
+No model value submitted for a disabled capability.</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>{"endpoint":"/aidp-mgmt/knowledge-bases","method":"POST","protocol":"HTTP","request_expectations":["Chunk mode, chunk token and overlap values follow the documented types and bounds.","Graph configuration is serialized as the documented string payload.","Legacy field names remain in place for existing callers."],"response_expectations":["The created knowledge base identifier is returned as before.","Permission and group handling keeps its existing behavior.","A failed upstream create surfaces a stable error without partial local state."]}</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr"/>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D2-003</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Update request changes metadata and reports partial failure</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>CONTRACT</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Verify that permission success stays distinguishable from a failed knowledge-base name or description update.</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>An authenticated update reaches the AIDP management proxy for a base the caller may edit.</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>{"metadata_change":["name","description"],"metadata_failure":true,"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>1. Change the knowledge-base name or description and save. =&gt; Only the changed name or description is sent to AIDP.
+2. Save again without changing metadata. =&gt; No unchanged metadata field is resent.
+3. Make the upstream metadata update fail after the permission write. =&gt; The response distinguishes saved permissions from a failed metadata update and readback keeps the previous name and description.</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>Only changed metadata is forwarded and unchanged values are omitted.
+Permission and metadata outcomes are separately reported.
+A metadata failure is never presented as a successful metadata save.</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>No claimed success on upstream failure.</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>{"endpoint":"/aidp-mgmt/knowledge-bases/{kds_id}/permission","method":"PATCH","protocol":"HTTP","request_expectations":["Only explicitly changed metadata fields are sent.","Permission and group fields keep their existing rules."],"response_expectations":["Permission save status and metadata update status are reported separately.","A failed metadata update yields a non-success result with the unchanged readback value.","Cache invalidation follows a successful metadata update."]}</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr"/>
+      <c r="U7" s="5" t="inlineStr"/>
+      <c r="V7" s="5" t="inlineStr"/>
+      <c r="W7" s="5" t="inlineStr"/>
+      <c r="X7" s="5" t="inlineStr"/>
+      <c r="Y7" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z7" s="5" t="inlineStr"/>
+      <c r="AA7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D2-004</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-012</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Model queries select a single category per control</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>CONTRACT</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Verify the model query proxy passes one category per request and returns only models applicable to the knowledge base application.</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>A controllable upstream model fixture serves distinct payloads per category.</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>{"categories":["llm","vlm","embedding"],"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>1. Query the graph model list. =&gt; The request carries the llm category and the response exposes only llm models.
+2. Query the multimodal model list. =&gt; The request carries the vlm category and the response exposes only vlm models.
+3. Query an unsupported or failing category. =&gt; A stable error or an empty result is returned without falling back to another category.</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>One category is requested per control.
+Responses are not reused across categories.
+Failures do not silently substitute another category.</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>No shared cache entry across categories.
+No fabricated model identifier on failure.
+No change to existing non-AIDP model endpoints.</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>{"endpoint":"/aidp-mgmt/models","method":"GET","protocol":"HTTP","request_expectations":["The service parameter carries exactly one requested category.","The application parameter keeps the knowledge base scope.","No credential is returned to the browser."],"response_expectations":["Only models of the requested category are returned.","An unavailable category yields a stable error or an empty list.","Results are filtered to the knowledge base application scope."]}</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="inlineStr"/>
+      <c r="T8" s="5" t="inlineStr"/>
+      <c r="U8" s="5" t="inlineStr"/>
+      <c r="V8" s="5" t="inlineStr"/>
+      <c r="W8" s="5" t="inlineStr"/>
+      <c r="X8" s="5" t="inlineStr"/>
+      <c r="Y8" s="5" t="inlineStr">
+        <is>
+          <t>未绑定</t>
+        </is>
+      </c>
+      <c r="Z8" s="5" t="inlineStr"/>
+      <c r="AA8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
           <t>CMSR-D2-001</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-013
 CMSR-RULE-014
@@ -3325,47 +4120,47 @@
 CMSR-RULE-016</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>SSE preserves successful retry deltas and attempt controls</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>CONTRACT</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Verify event ordering and prompt publication at the API stream boundary.</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>An authenticated Agent run uses a controllable model-provider fixture.</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","sequences":["transport partial failure then success","semantic invalid response then valid streamed repair"]}</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>1. Begin step one and pause the provider before its first token. =&gt; SSE already contains one step_count before begin and before model content.
 2. Pause the provider after the first safe success fragment. =&gt; The SSE client has already received that fragment with the success attempt ID.
@@ -3373,71 +4168,71 @@
 4. Repeat with step-one protocol-invalid output then valid repair. =&gt; SSE orders one step_count, begin, rollback, begin, corrected content, commit and one parse; corrected content is visible before completion.</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>SSE yields one step label before model output.
 Safe content follows the label before provider completion.
 Every model fragment carries its attempt ID.</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>No duplicate execution event.
 No control event persisted as a message unit.
 No failed semantic output in committed units.</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="P9" s="5" t="inlineStr">
         <is>
           <t>{"endpoint":"/agent/run","method":"POST","protocol":"SSE","request_expectations":["The request selects a configured test Agent."],"response_expectations":["Control and model output preserve attempt order.","Successful content is published before completion."]}</t>
         </is>
       </c>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr">
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr">
         <is>
           <t>implemented</t>
         </is>
       </c>
-      <c r="S6" s="5" t="inlineStr">
+      <c r="S9" s="5" t="inlineStr">
         <is>
           <t>pytest</t>
         </is>
       </c>
-      <c r="T6" s="5" t="inlineStr">
+      <c r="T9" s="5" t="inlineStr">
         <is>
           <t>test/automation/d2/test_model_attempt_sse.py</t>
         </is>
       </c>
-      <c r="U6" s="5" t="inlineStr">
+      <c r="U9" s="5" t="inlineStr">
         <is>
           <t>test_cmsr_d2_001</t>
         </is>
       </c>
-      <c r="V6" s="5" t="inlineStr">
+      <c r="V9" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W6" s="5" t="inlineStr"/>
-      <c r="X6" s="5" t="inlineStr"/>
-      <c r="Y6" s="5" t="inlineStr">
+      <c r="W9" s="5" t="inlineStr"/>
+      <c r="X9" s="5" t="inlineStr"/>
+      <c r="Y9" s="5" t="inlineStr">
         <is>
           <t>实现哈希失效</t>
         </is>
       </c>
-      <c r="Z6" s="5" t="inlineStr">
+      <c r="Z9" s="5" t="inlineStr">
         <is>
           <t>sha256:9e5d436508638774329620f8bea1420eab531ad470095c935fac5fccc69e894c</t>
         </is>
       </c>
-      <c r="AA6" s="5" t="inlineStr">
+      <c r="AA9" s="5" t="inlineStr">
         <is>
           <t>sha256:570d7db5b7480c6b3a3a3adcc953158f7c496e44a79e90ad1ca3a4df676d573f</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA6"/>
+  <autoFilter ref="A1:AA9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3448,7 +4243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AA5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3473,7 +4268,7 @@
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="17" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col hidden="1" width="42" customWidth="1" min="26" max="26"/>
@@ -3620,29 +4415,29 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>AKPR-D3-001</t>
+          <t>AKDT-D3-001</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>AKPR-001</t>
+          <t>AKDT-001</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AKPR-001</t>
+          <t>AKDT-001</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AKPR-RULE-011
-AKPR-RULE-013
-AKPR-RULE-014</t>
+          <t>AKDT-RULE-002
+AKDT-RULE-003
+AKDT-RULE-005</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Real AIDP create, readback and safety guard update close the loop</t>
+          <t>AIDP mock keeps completed files separate from paged upload history and retries</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -3657,7 +4452,7 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -3667,50 +4462,48 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Verify against a reachable AIDP service that a created knowledge base returns the submitted chunking, graph and safety configuration and that a later safety guard change is visible on readback. This case stays blocked until the upstream safety guard contract is available on the target environment.</t>
+          <t>Verify the local AIDP mock exercises the separate file and History sources, request paging and filtering, and array-based retry without local database history.</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>A reachable AIDP service accepts Nexent credentials.
-The upstream build that exposes the safety guard field is deployed.
-A disposable tenant and user group are available.</t>
+          <t>Nexent config service and the AIDP management mock run in the declared local mock profile.
+Mock data includes completed and non-completed statuses for the same knowledge base.</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>{"chunk_mode":0,"guard":[1,0],"profile":"real_smoke"}</t>
+          <t>{"kds_id":"aidp-kb-faq","page_size":10,"profile":"mock","status":[0,1,2,3,4,5]}</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>1. Create a knowledge base with chunking, retrieval, graph and safety configuration through the Nexent proxy. =&gt; The upstream accepts the payload and returns a knowledge base identifier.
-2. Read the created knowledge base back. =&gt; The chunking, retrieval, graph and safety values match the submitted configuration.
-3. Disable the safety guard and read it back again. =&gt; The readback reports the disabled state instead of the previous value.</t>
+          <t>1. Query the files and upload-tasks endpoints for one knowledge base. =&gt; The file response contains only completed records while task response includes History statuses and AIDP counts.
+2. Query tasks with page, keyword and each numeric status. =&gt; The mock applies the request fields, returns the matching rows and provides correct pagination/statistics.
+3. Retry an explicit array containing one file UUID. =&gt; The mock accepts the documented file_uuids body and records only the selected retry.</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
-          <t>Submitted configuration is readable from the upstream.
-The safety guard round trip works in both directions.
-Failure of the upstream metadata update is distinguishable from success.</t>
+          <t>Mock behavior makes accidental History/file mixing observable.
+Mock task filters and statistics match its fixture data.
+Mock retry behavior matches the adapter's documented sample shape.</t>
         </is>
       </c>
       <c r="O2" s="5" t="inlineStr">
         <is>
-          <t>No duplicate knowledge base created by retries.
-No permission row created without its knowledge base.
-No test data left in a shared tenant.</t>
+          <t>No Nexent PG file or task-history record is created.
+No retry outside the requested UUID array is changed.</t>
         </is>
       </c>
       <c r="P2" s="5" t="inlineStr">
         <is>
-          <t>{"cleanup":["Delete the created knowledge base through the proxy.","Remove local permission rows and document tag associations created by the case."],"integration_boundary":["Nexent AIDP knowledge base proxy","Upstream AIDP knowledge base API","Nexent AIDP permission store"],"observations":["Outgoing create payload field names and types","Readback values per configuration group","Permission row and metadata update status after each step"]}</t>
+          <t>{"cleanup":["Restore mock fixture state using the repository's isolated test state directory.","Do not reset the user's persistent local mock state during browser acceptance."],"integration_boundary":["Nexent FastAPI AIDP management routes.","Local AIDP management mock KnowledgeFiles endpoints.","Existing Nexent permission data only for authorization decisions."],"observations":["Captured request path and JSON body at the mock boundary.","File and task response rows, counts and pagination metadata.","Database writes limited to existing permission behavior; no file-history writes."]}</t>
         </is>
       </c>
       <c r="Q2" s="5" t="inlineStr">
         <is>
-          <t>{"profiles":[{"name":"real_smoke","required_services":["knowledge-provider"]}]}</t>
+          <t>{"profiles":[{"name":"mock","required_services":["knowledge-provider"]}]}</t>
         </is>
       </c>
       <c r="R2" s="5" t="inlineStr">
@@ -3723,14 +4516,18 @@
       <c r="U2" s="5" t="inlineStr"/>
       <c r="V2" s="5" t="inlineStr">
         <is>
-          <t>real_smoke</t>
-        </is>
-      </c>
-      <c r="W2" s="5" t="inlineStr"/>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>knowledge-provider</t>
+        </is>
+      </c>
       <c r="X2" s="5" t="inlineStr"/>
       <c r="Y2" s="5" t="inlineStr">
         <is>
-          <t>无需绑定</t>
+          <t>未绑定</t>
         </is>
       </c>
       <c r="Z2" s="5" t="inlineStr"/>
@@ -3739,7 +4536,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>AKPR-D3-002</t>
+          <t>AKPR-D3-001</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -3754,12 +4551,13 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AKPR-RULE-012</t>
+          <t>AKPR-RULE-011
+AKPR-RULE-013</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Real model categories return only their own models and survive readback</t>
+          <t>Real AIDP create and readback close the loop</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -3784,44 +4582,41 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Verify against a reachable AIDP service that each model control receives its own category and that a configuration selected from real models is accepted and readable. This case stays blocked until a real AIDP environment with a model inventory is reachable.</t>
+          <t>Verify against a reachable AIDP service that a created knowledge base returns the submitted chunking, retrieval and graph configuration.</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>A reachable AIDP service exposes llm, vlm and embedding model inventories.
-At least one model exists in the llm and vlm categories.</t>
+          <t>A reachable AIDP service accepts Nexent credentials.
+A disposable tenant and user group are available.</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>{"categories":["llm","vlm","embedding"],"profile":"real_smoke"}</t>
+          <t>{"chunk_mode":0,"profile":"real_smoke"}</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>1. Query each model category through the Nexent proxy. =&gt; Each response contains only models of the requested category and scope.
-2. Create a knowledge base using a real llm model for the graph and a real vlm model for multimodal captioning. =&gt; The upstream accepts both model fields.
-3. Read the knowledge base back. =&gt; The graph and multimodal model fields match the submitted values.</t>
+          <t>1. Create a knowledge base with chunking, retrieval and graph configuration through the Nexent proxy. =&gt; The upstream accepts the payload and returns a knowledge base identifier.
+2. Read the created knowledge base back. =&gt; The chunking, retrieval and graph values match the submitted configuration.</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
-          <t>Category queries stay separated.
-Both model fields are accepted and readable.
-No unverified default model replaces a missing selection.</t>
+          <t>Submitted configuration is readable from the upstream.</t>
         </is>
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>No model from one category submitted through another category control.
-No credential exposed to the browser.
-No change to non-AIDP model configuration.</t>
+          <t>No duplicate knowledge base created by retries.
+No permission row created without its knowledge base.
+No test data left in a shared tenant.</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>{"cleanup":["Delete the created knowledge base through the proxy.","Discard recorded model identifiers that are environment specific."],"integration_boundary":["Nexent AIDP model query proxy","Upstream AIDP model inventory API","Nexent AIDP knowledge base create path"],"observations":["Requested category per query","Returned model identifiers and their categories","Readback values for both model fields"]}</t>
+          <t>{"cleanup":["Delete the created knowledge base through the proxy.","Remove local permission rows and document tag associations created by the case."],"integration_boundary":["Nexent AIDP knowledge base proxy","Upstream AIDP knowledge base API","Nexent AIDP permission store"],"observations":["Outgoing create payload field names and types","Readback values per configuration group","Permission row and configuration readback after creation"]}</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
@@ -3855,20 +4650,136 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
+          <t>AKPR-D3-002</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-012</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Real model categories return only their own models and survive readback</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>INTEGRATION</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Verify against a reachable AIDP service that each model control receives its own category and that a configuration selected from real models is accepted and readable. This case stays blocked until a real AIDP environment with a model inventory is reachable.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>A reachable AIDP service exposes llm, vlm and embedding model inventories.
+At least one model exists in the llm and vlm categories.</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>{"categories":["llm","vlm","embedding"],"profile":"real_smoke"}</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>1. Query each model category through the Nexent proxy. =&gt; Each response contains only models of the requested category and scope.
+2. Create a knowledge base using a real llm model for the graph and a real vlm model for multimodal captioning. =&gt; The upstream accepts both model fields.
+3. Read the knowledge base back. =&gt; The graph and multimodal model fields match the submitted values.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Category queries stay separated.
+Both model fields are accepted and readable.
+No unverified default model replaces a missing selection.</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>No model from one category submitted through another category control.
+No credential exposed to the browser.
+No change to non-AIDP model configuration.</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>{"cleanup":["Delete the created knowledge base through the proxy.","Discard recorded model identifiers that are environment specific."],"integration_boundary":["Nexent AIDP model query proxy","Upstream AIDP model inventory API","Nexent AIDP knowledge base create path"],"observations":["Requested category per query","Returned model identifiers and their categories","Readback values for both model fields"]}</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"real_smoke","required_services":["knowledge-provider"]}]}</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>real_smoke</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr"/>
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>无需绑定</t>
+        </is>
+      </c>
+      <c r="Z4" s="5" t="inlineStr"/>
+      <c r="AA4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
           <t>CMSR-D3-001</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-013
 CMSR-RULE-014
@@ -3876,47 +4787,47 @@
 CMSR-RULE-016</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Agent retry streams success and persists only committed output</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>AGENT-IT</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Verify the full Nexent Agent, observer, SSE and persistence path with controlled provider failure.</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>Local Nexent services and a disposable test conversation are available.</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","sequences":["partial transport failure then success","step-one protocol invalid then valid paused repair"]}</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>1. Start the Agent and fail its first response after a visible fragment. =&gt; Step 1 is emitted before begin and remains after rollback.
 2. Pause the successful response after safe content. =&gt; The SSE consumer receives it before provider completion.
@@ -3924,7 +4835,7 @@
 4. Repeat with semantic repair and inspect database units. =&gt; Only corrected raw model output is stored; its fragments appeared before completion.</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>Step 1 precedes all model chunks and is stored once.
 Successful text is incremental.
@@ -3932,61 +4843,61 @@
 History matches committed SSE.</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>No failed-fragment persistence.
 No duplicate tool execution.
 No extra model request.</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>{"cleanup":["Delete the disposable conversation and provider fixture."],"integration_boundary":["Agent runtime to provider fixture","Observer to SSE","SSE to conversation persistence"],"observations":["Attempt control order","SSE arrival before provider release","persisted message units","sanitized repair lifecycle logs"]}</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>{"profiles":[{"name":"mock","required_services":["model-provider"]},{"name":"real_smoke","required_services":["model-provider"]}]}</t>
         </is>
       </c>
-      <c r="R4" s="5" t="inlineStr">
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="S4" s="5" t="inlineStr"/>
-      <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr"/>
-      <c r="V4" s="5" t="inlineStr">
+      <c r="S5" s="5" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr"/>
+      <c r="U5" s="5" t="inlineStr"/>
+      <c r="V5" s="5" t="inlineStr">
         <is>
           <t>mock
 real_smoke</t>
         </is>
       </c>
-      <c r="W4" s="5" t="inlineStr">
+      <c r="W5" s="5" t="inlineStr">
         <is>
           <t>model-provider</t>
         </is>
       </c>
-      <c r="X4" s="5" t="inlineStr"/>
-      <c r="Y4" s="5" t="inlineStr">
+      <c r="X5" s="5" t="inlineStr"/>
+      <c r="Y5" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z4" s="5" t="inlineStr">
+      <c r="Z5" s="5" t="inlineStr">
         <is>
           <t>sha256:f6ba2ceeb76ca6051b3f305afac2f932ad4f1148a2201ea8471d0cbaae207b6e</t>
         </is>
       </c>
-      <c r="AA4" s="5" t="inlineStr">
+      <c r="AA5" s="5" t="inlineStr">
         <is>
           <t>sha256:4f53cda18c2baa0c0354bb5f9a3ecbe5ed12ab4d8e11ba873c2f11161202b945</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA4"/>
+  <autoFilter ref="A1:AA5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3997,7 +4908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4022,7 +4933,7 @@
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col hidden="1" width="42" customWidth="1" min="26" max="26"/>
@@ -4169,20 +5080,149 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>AKDT-D4-001</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>AKDT-001</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>AKDT-001</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>AKDT-RULE-001
+AKDT-RULE-002
+AKDT-RULE-004
+AKDT-RULE-005
+AKDT-RULE-006
+AKDT-RULE-007</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Knowledge base detail journey separates files, tasks and settings</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Verify the complete detail-page journey against the AIDP mock, including navigation, task filtering, failure details, row retry, configuration and permission controls.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>The authenticated test account has EDIT access to one seeded AIDP knowledge base and READ access to one shared base.
+The mock returns completed files and a mixture of recent task statuses, including one retryable failure with a reason.
+The browser has the AIDP knowledge-base feature enabled.</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>{"locale":"zh-CN","profile":"mock","status_values":[0,1,2,3,4,5],"task_retention_days":30}</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>1. Open the overview and click a card or knowledge-base name. =&gt; A full-width detail page opens with a breadcrumb, header and the three tabs Files, Upload tasks and Details; no list edit action remains.
+2. Inspect Files and search by file name. =&gt; Only ingested files appear; download and delete follow the user's permission; pagination and table controls stay in the detail page.
+3. Open Upload tasks, search a name and choose each status filter. =&gt; The page states tasks are retained for 30 days, status values 0-5 are sent, statistics remain independent from the current page, and processing rows do not appear as ingested files.
+4. Open a failed task's failure details and retry it from the row action. =&gt; The drawer shows returned values only; retry submits a one-item file_uuids array and subsequent refresh reads the changed task status.
+5. Open Details and edit supported name/description, a supported setting and group permissions. =&gt; Each save sends only its own changed fields and updates the returned value; unsupported similarity edits are absent.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>The page has the exact three tabs and full content width.
+Ingested files and upload history remain separate live AIDP sources.
+Status filters, raw status rendering, failure details and single-file retry follow the contract.
+Detail settings and group permissions use separate authorized save operations.</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>No task-history record is written to Nexent PostgreSQL.
+No operation from a READ_ONLY user changes upstream or local configuration.
+No list/card menu edits a knowledge base.</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>{"actor":"Authenticated AIDP tenant user","failure_evidence":["Retain screenshots for the three tabs and failure drawer, browser request evidence, and console errors."],"final_business_result":["The user can identify successfully ingested files separately from recent upload work and manage the knowledge base using the returned configuration and permission values."],"journey":["Enter the detail page from the overview.","Inspect and search completed files.","Inspect task statistics, filters and failure details.","Retry one failed task and verify refresh behavior.","Review and modify supported detail settings and permission groups."]}</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"mock","required_services":["knowledge-provider"]}]}</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr"/>
+      <c r="T2" s="5" t="inlineStr"/>
+      <c r="U2" s="5" t="inlineStr"/>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>knowledge-provider</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr"/>
+      <c r="Y2" s="5" t="inlineStr">
+        <is>
+          <t>无需绑定</t>
+        </is>
+      </c>
+      <c r="Z2" s="5" t="inlineStr"/>
+      <c r="AA2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
           <t>AKPR-D4-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>AKPR-001</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>AKPR-001</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>AKPR-RULE-001
 AKPR-RULE-002
@@ -4191,49 +5231,49 @@
 AKPR-RULE-005</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Overview journey keeps the guide, search, view and column state across the file view</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>E2E</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Verify the complete overview journey in a browser against a deployed instance. This case stays blocked until a disposable Nexent deployment with the AIDP flag enabled and reachable AIDP data is available.</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>A deployed Nexent instance runs this worktree with the AIDP flag enabled.
 The test tenant can see more than one knowledge base.
 A writable knowledge base with at least one document exists.</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>{"keyword":"alpha","page_size":10,"profile":"real_smoke"}</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>1. Open the knowledge base page and inspect the guide. =&gt; The explanation and the three steps are visible, collapse and reopen work, and cards are the default view.
 2. Search a name, move to a later page, switch to the table and hide one column. =&gt; The table shows the filtered result set on the same page and the hidden column disappears.
@@ -4241,142 +5281,23 @@
 4. Return to the overview. =&gt; The keyword, page, table view and hidden column state are restored.</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>The guide, card default, search, view switch and column setting all work in the browser.
 The file view is scoped to the selected base.
 Returning restores the earlier overview state.</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>No modification request from view or column changes.
 No state reset after returning.
 No ES knowledge base page rendered while the AIDP flag is enabled.</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>{"actor":"Authenticated test tenant user","failure_evidence":["Retain browser screenshot, network log and console trace on failure."],"final_business_result":["A user can browse, filter and configure the knowledge base overview and reach one base file view without losing context."],"journey":["Open the knowledge base overview.","Expand and collapse the guide.","Search, page and switch views while hiding a column.","Open a knowledge base and return to the overview."]}</t>
-        </is>
-      </c>
-      <c r="Q2" s="5" t="inlineStr">
-        <is>
-          <t>{"profiles":[{"name":"real_smoke","required_services":["knowledge-provider"]}]}</t>
-        </is>
-      </c>
-      <c r="R2" s="5" t="inlineStr">
-        <is>
-          <t>unbound</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="inlineStr"/>
-      <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr"/>
-      <c r="V2" s="5" t="inlineStr">
-        <is>
-          <t>real_smoke</t>
-        </is>
-      </c>
-      <c r="W2" s="5" t="inlineStr"/>
-      <c r="X2" s="5" t="inlineStr"/>
-      <c r="Y2" s="5" t="inlineStr">
-        <is>
-          <t>无需绑定</t>
-        </is>
-      </c>
-      <c r="Z2" s="5" t="inlineStr"/>
-      <c r="AA2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-D4-002</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-001</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>AKPR-RULE-009</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>File view journey uploads, polls, downloads and deletes under permission control</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>E2E</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>automated</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>Verify the restored file operations in a browser against a deployed instance. This case stays blocked until a disposable Nexent deployment with reachable AIDP upload and document services is available.</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>A deployed Nexent instance runs this worktree with the AIDP flag enabled.
-The test user owns an editable knowledge base and can read another one.
-A small local document is prepared for upload.</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>{"documents":2,"one_failing_upload":true,"profile":"real_smoke"}</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>1. Open the writable knowledge base and upload a document. =&gt; The document appears and its processing status reaches a terminal state through polling.
-2. Download the processed document. =&gt; The browser receives the original file with its name.
-3. Delete the document and confirm the dialog. =&gt; The document disappears from the list and the deletion reports its own result.
-4. Open the read-only knowledge base and attempt the same operations. =&gt; Upload and delete are unavailable while browsing and download remain permitted.</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>Upload reaches a terminal processing state.
-The downloaded file matches the uploaded original.
-Deletion removes the document after confirmation.
-Permission gates match the documented read and edit rules.</t>
-        </is>
-      </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>No upload or delete entry for a read-only base.
-No polling continues after leaving the file view.
-No document of another base rendered in the current view.</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>{"actor":"Authenticated test tenant user","failure_evidence":["Retain browser screenshot, network log, downloaded file metadata and console trace on failure."],"final_business_result":["A user with edit permission can add, retrieve and remove documents while a read-only user can only browse and download them."],"journey":["Open a writable knowledge base file view.","Upload and wait for processing to finish.","Download the document.","Delete the document with confirmation.","Check the same controls on a read-only base."]}</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
@@ -4410,7 +5331,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>AKPR-D4-003</t>
+          <t>AKPR-D4-002</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -4425,16 +5346,12 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>AKPR-RULE-010
-AKPR-RULE-011
-AKPR-RULE-012
-AKPR-RULE-013
-AKPR-RULE-014</t>
+          <t>AKPR-RULE-009</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Creation page journey configures two steps and reports creation and upload results separately</t>
+          <t>File view journey uploads, polls, downloads and deletes under permission control</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -4459,46 +5376,47 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>Verify the dedicated two-step creation page in a browser including conditional graph and multimodal sections and the separate creation and upload outcomes. This case stays blocked until a disposable Nexent deployment with reachable AIDP services is available.</t>
+          <t>Verify the restored file operations in a browser against a deployed instance. This case stays blocked until a disposable Nexent deployment with reachable AIDP upload and document services is available.</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
           <t>A deployed Nexent instance runs this worktree with the AIDP flag enabled.
-The test user belongs to a valid group for a shared permission.
-A local document and an intentionally rejected document are prepared.</t>
+The test user owns an editable knowledge base and can read another one.
+A small local document is prepared for upload.</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>{"chunk_mode":1,"graph_enabled":true,"multimodal":true,"profile":"real_smoke"}</t>
+          <t>{"documents":2,"one_failing_upload":true,"profile":"real_smoke"}</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>1. Open the creation page, fill the first step and toggle the graph and multimodal sections. =&gt; The conditional sections appear with their own model selections and permission fields stay in the first step.
-2. Press next and then return to the first step. =&gt; No knowledge base exists yet and the form values and selected files are preserved.
-3. Submit with one accepted and one rejected file. =&gt; The knowledge base is created once, the accepted file processes and the rejected file is reported as a separate failure.
-4. Retry only the failed file. =&gt; No second knowledge base is created and the retry targets the failed file only.</t>
+          <t>1. Open the writable knowledge base and upload a document. =&gt; The document appears and its processing status reaches a terminal state through polling.
+2. Download the processed document. =&gt; The browser receives the original file with its name.
+3. Delete the document and confirm the dialog. =&gt; The document disappears from the list and the deletion reports its own result.
+4. Open the read-only knowledge base and attempt the same operations. =&gt; Upload and delete are unavailable while browsing and download remain permitted.</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>The two-step flow holds its state and creates nothing early.
-Conditional graph and multimodal configuration is submitted with the chosen models.
-Creation and upload outcomes are reported separately and retrying never duplicates the base.</t>
+          <t>Upload reaches a terminal processing state.
+The downloaded file matches the uploaded original.
+Deletion removes the document after confirmation.
+Permission gates match the documented read and edit rules.</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>No knowledge base created before final submission or twice after a retry.
-No hidden graph or multimodal configuration submitted when disabled.
-No upload attempted before a successful creation.</t>
+          <t>No upload or delete entry for a read-only base.
+No polling continues after leaving the file view.
+No document of another base rendered in the current view.</t>
         </is>
       </c>
       <c r="P4" s="5" t="inlineStr">
         <is>
-          <t>{"actor":"Authenticated test tenant user","failure_evidence":["Retain browser screenshot, network log of create and upload requests, and console trace on failure."],"final_business_result":["A user can create one properly configured knowledge base and see which files were accepted and which failed without creating duplicates."],"journey":["Open the dedicated creation page.","Configure the first step including permissions and capabilities.","Advance to the upload step and back.","Submit with a partially failing file set.","Retry the failed file."]}</t>
+          <t>{"actor":"Authenticated test tenant user","failure_evidence":["Retain browser screenshot, network log, downloaded file metadata and console trace on failure."],"final_business_result":["A user with edit permission can add, retrieve and remove documents while a read-only user can only browse and download them."],"journey":["Open a writable knowledge base file view.","Upload and wait for processing to finish.","Download the document.","Delete the document with confirmation.","Check the same controls on a read-only base."]}</t>
         </is>
       </c>
       <c r="Q4" s="5" t="inlineStr">
@@ -4532,7 +5450,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>AKPR-D4-004</t>
+          <t>AKPR-D4-003</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -4547,12 +5465,15 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AKPR-RULE-008</t>
+          <t>AKPR-RULE-010
+AKPR-RULE-011
+AKPR-RULE-012
+AKPR-RULE-013</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>ES deployment still renders the original knowledge base page</t>
+          <t>Creation page journey configures two steps and reports creation and upload results separately</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -4577,49 +5498,51 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Verify that with the AIDP flag disabled the original ES knowledge base page renders unchanged. This case stays blocked until a disposable deployment or a flag configuration switch is available for browser verification.</t>
+          <t>Verify the dedicated two-step creation page in a browser including conditional graph and multimodal sections and the separate creation and upload outcomes. This case stays blocked until a disposable Nexent deployment with reachable AIDP services is available.</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>A deployed Nexent instance can run with the AIDP flag disabled.
-The same instance serves the ES knowledge base data.</t>
+          <t>A deployed Nexent instance runs this worktree with the AIDP flag enabled.
+The test user belongs to a valid group for a shared permission.
+A local document and an intentionally rejected document are prepared.</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>{"aidp_flag":false,"profile":"real_smoke"}</t>
+          <t>{"chunk_mode":1,"graph_enabled":true,"multimodal":true,"profile":"real_smoke"}</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>1. Open the knowledge base page with the AIDP flag disabled. =&gt; The original ES knowledge base page renders without the AIDP guide, card overview or AIDP file view.
-2. Exercise the original list, creation and document interactions. =&gt; Existing ES behavior is unchanged.
-3. Inspect the requests issued by the page. =&gt; No AIDP management endpoint is called.</t>
+          <t>1. Open the creation page, fill the first step and toggle the graph and multimodal sections. =&gt; The conditional sections appear with their own model selections and permission fields stay in the first step.
+2. Press next and then return to the first step. =&gt; No knowledge base exists yet and the form values and selected files are preserved.
+3. Submit with one accepted and one rejected file. =&gt; The knowledge base is created once, the accepted file processes and the rejected file is reported as a separate failure.
+4. Retry only the failed file. =&gt; No second knowledge base is created and the retry targets the failed file only.</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>The ES page is untouched.
-No AIDP component renders in the ES path.
-No AIDP request is issued.</t>
+          <t>The two-step flow holds its state and creates nothing early.
+Conditional graph and multimodal configuration is submitted with the chosen models.
+Creation and upload outcomes are reported separately and retrying never duplicates the base.</t>
         </is>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
-          <t>No AIDP request from the ES page.
-No visual or behavioral change to the ES list and document flows.
-No new ES write request.</t>
+          <t>No knowledge base created before final submission or twice after a retry.
+No hidden graph or multimodal configuration submitted when disabled.
+No upload attempted before a successful creation.</t>
         </is>
       </c>
       <c r="P5" s="5" t="inlineStr">
         <is>
-          <t>{"actor":"Authenticated test tenant user","failure_evidence":["Retain browser screenshot, network log and console trace on failure."],"final_business_result":["An ES deployment keeps its original knowledge base experience with no AIDP leakage."],"journey":["Switch the deployment flag off.","Open the knowledge base page.","Exercise the original list and document interactions."]}</t>
+          <t>{"actor":"Authenticated test tenant user","failure_evidence":["Retain browser screenshot, network log of create and upload requests, and console trace on failure."],"final_business_result":["A user can create one properly configured knowledge base and see which files were accepted and which failed without creating duplicates."],"journey":["Open the dedicated creation page.","Configure the first step including permissions and capabilities.","Advance to the upload step and back.","Submit with a partially failing file set.","Retry the failed file."]}</t>
         </is>
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>{"profiles":[{"name":"real_smoke","required_services":[]}]}</t>
+          <t>{"profiles":[{"name":"real_smoke","required_services":["knowledge-provider"]}]}</t>
         </is>
       </c>
       <c r="R5" s="5" t="inlineStr">
@@ -4648,20 +5571,259 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>AKPR-D4-004</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-008</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>ES deployment still renders the original knowledge base page</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Verify that with the AIDP flag disabled the original ES knowledge base page renders unchanged. This case stays blocked until a disposable deployment or a flag configuration switch is available for browser verification.</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>A deployed Nexent instance can run with the AIDP flag disabled.
+The same instance serves the ES knowledge base data.</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>{"aidp_flag":false,"profile":"real_smoke"}</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>1. Open the knowledge base page with the AIDP flag disabled. =&gt; The original ES knowledge base page renders without the AIDP guide, card overview or AIDP file view.
+2. Exercise the original list, creation and document interactions. =&gt; Existing ES behavior is unchanged.
+3. Inspect the requests issued by the page. =&gt; No AIDP management endpoint is called.</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>The ES page is untouched.
+No AIDP component renders in the ES path.
+No AIDP request is issued.</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>No AIDP request from the ES page.
+No visual or behavioral change to the ES list and document flows.
+No new ES write request.</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>{"actor":"Authenticated test tenant user","failure_evidence":["Retain browser screenshot, network log and console trace on failure."],"final_business_result":["An ES deployment keeps its original knowledge base experience with no AIDP leakage."],"journey":["Switch the deployment flag off.","Open the knowledge base page.","Exercise the original list and document interactions."]}</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"real_smoke","required_services":[]}]}</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>real_smoke</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr">
+        <is>
+          <t>无需绑定</t>
+        </is>
+      </c>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D4-005</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-015
+AKPR-RULE-016</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Overview and creation pages match their approved desktop layout</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Verify the rendered guide, knowledge cards, pagination, inline switches and paired create-form controls against the AIDP design at desktop and narrow widths.</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>The AIDP-enabled instance is reachable with the authenticated test account.
+The instance has multiple knowledge bases with realistic metadata and an empty creation form.
+A fixed Playwright browser profile can access the local AIDP mock.</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>{"desktop_viewport":[1920,1080],"narrow_viewport":[1024,768],"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>1. Open the overview and capture the expanded guide and first card row. =&gt; At desktop width each row contains four 148px-high cards with 16px horizontal gaps and 12px vertical gaps. Cards have 24px horizontal and 16px vertical padding, a 40px icon, a 16px/500/24px title, a full-width two-line 12px/20px description, and one 12px/18px metadata row. The toolbar search is 360px by 32px, the primary button is 32px high, and the selected view uses the primary blue background. Pagination is aligned right, uses 32px controls, puts page-size selection before page numbers, and has a pale-blue selected page with no primary border.
+2. Switch to table view and inspect the toolbar and column controls. =&gt; The create and view buttons align at the right, table column control follows them, and no edit operation appears in the overview. The table header and data rows are 40px high with 14px/22px body text and pale
+3. Open creation and inspect the page header, switches and paired fields at both viewport sizes. =&gt; The page uses the available width, switches sit beside their labels, and paired inputs or sliders align without page-level horizontal overflow.</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>The running AIDP pages match the accepted layout and preserve Nexent visual conventions.
+The expanded guide uses the pale-blue gradient introduction panel with 24px padding, a configuration-flow heading and three 156px-high step cards; the step content stays create, upload and configure an agent, and collapse or reopen preserves the overview state.
+The narrow viewport remains usable without overlapping labels or page-level horizontal scrolling.
+Collapsing the guide preserves the keyword and page; changing page size resets to page one; the last partial page keeps the same content-panel height; a valid page jump navigates without a mutating request.
+No write request is issued while visually inspecting the pages.</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>No knowledge base is created, edited or deleted during this journey.
+No global style or ES page behavior is changed.</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>{"actor":"Authenticated AIDP tenant user","failure_evidence":["Save screenshots, computed layout measurements and browser console errors for both viewport sizes."],"final_business_result":["Users see the intended list and creation composition before beginning a knowledge-base operation."],"journey":["Inspect the overview guide and cards.","Inspect the table toolbar and pagination.","Inspect the full-page creation layout at desktop and narrow widths."]}</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"mock","required_services":["knowledge-provider"]}]}</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr"/>
+      <c r="U7" s="5" t="inlineStr"/>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr">
+        <is>
+          <t>knowledge-provider</t>
+        </is>
+      </c>
+      <c r="X7" s="5" t="inlineStr"/>
+      <c r="Y7" s="5" t="inlineStr">
+        <is>
+          <t>无需绑定</t>
+        </is>
+      </c>
+      <c r="Z7" s="5" t="inlineStr"/>
+      <c r="AA7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
           <t>CMSR-D4-001</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-013
 CMSR-RULE-014
@@ -4669,48 +5831,48 @@
 CMSR-RULE-016</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Browser shows retry output incrementally without blank steps</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>E2E</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Verify a user sees only successful raw code and one executed action in a real conversation.</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>A local Nexent instance
 test tenant and controllable model provider are configured.</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","sequences":["failed transport partial then success","step-one invalid protocol then valid paused repair"]}</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="M8" s="5" t="inlineStr">
         <is>
           <t>1. Open Agent chat and send the fixed prompt. =&gt; Step 1 appears before the first model token; the first partial output is then rolled back while the label remains.
 2. Pause the second provider response after its first safe fragment. =&gt; The reasoning card displays the successful raw fragment before provider completion.
@@ -4718,7 +5880,7 @@
 4. Repeat in a new conversation with semantic repair at step one. =&gt; Corrected raw code is visible during the pause and after refresh; Connecting does not persist.</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>Running Step 1 is visible before content.
 No terminal label-only reasoning card.
@@ -4726,59 +5888,59 @@
 Refreshed history matches the final UI.</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="O8" s="5" t="inlineStr">
         <is>
           <t>No failed partial text after rollback.
 No duplicate execution card.</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="P8" s="5" t="inlineStr">
         <is>
           <t>{"actor":"Authenticated test tenant user","failure_evidence":["Retain browser screenshot","network timing and console trace on failure."],"final_business_result":["Only the committed attempt and its single executed code action are visible."],"journey":["Open the Agent conversation.","Trigger controlled retry.","Observe streaming.","Reload and inspect history."]}</t>
         </is>
       </c>
-      <c r="Q6" s="5" t="inlineStr">
+      <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>{"profiles":[{"name":"mock","required_services":["model-provider"]}]}</t>
         </is>
       </c>
-      <c r="R6" s="5" t="inlineStr">
+      <c r="R8" s="5" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr"/>
-      <c r="V6" s="5" t="inlineStr">
+      <c r="S8" s="5" t="inlineStr"/>
+      <c r="T8" s="5" t="inlineStr"/>
+      <c r="U8" s="5" t="inlineStr"/>
+      <c r="V8" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W6" s="5" t="inlineStr">
+      <c r="W8" s="5" t="inlineStr">
         <is>
           <t>model-provider</t>
         </is>
       </c>
-      <c r="X6" s="5" t="inlineStr"/>
-      <c r="Y6" s="5" t="inlineStr">
+      <c r="X8" s="5" t="inlineStr"/>
+      <c r="Y8" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z6" s="5" t="inlineStr">
+      <c r="Z8" s="5" t="inlineStr">
         <is>
           <t>sha256:f110f582fe091286fdaa5301f8bdc22703bf583fc7c6c95214ae8c8187a612a1</t>
         </is>
       </c>
-      <c r="AA6" s="5" t="inlineStr">
+      <c r="AA8" s="5" t="inlineStr">
         <is>
           <t>sha256:4f53cda18c2baa0c0354bb5f9a3ecbe5ed12ab4d8e11ba873c2f11161202b945</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA6"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4789,7 +5951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AA7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4814,7 +5976,7 @@
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col hidden="1" width="42" customWidth="1" min="26" max="26"/>
@@ -4961,28 +6123,30 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>AKPR-D5-001</t>
+          <t>AKDT-D5-001</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>AKPR-001</t>
+          <t>AKDT-001</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AKPR-001</t>
+          <t>AKDT-001</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AKPR-RULE-007
-AKPR-RULE-014</t>
+          <t>AKDT-RULE-003
+AKDT-RULE-005
+AKDT-RULE-007
+AKDT-RULE-008</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Restricted users never reach a modification endpoint</t>
+          <t>Detail operations preserve tenant boundaries and keep files live-only</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -5007,49 +6171,50 @@
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Verify across the overview, file view and creation page that permission and group rules block modification requests at the boundary. This case stays blocked until a disposable deployment with multiple permission roles is available.</t>
+          <t>Verify user-group authorization protects detail reads and writes, retries cannot target another knowledge base's files, and no task/file history is written to Nexent storage.</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>A deployed instance has a read-only user, a group-less user and an edit user on one knowledge base.
-Request logging is available.</t>
+          <t>A disposable AIDP test tenant has private, shared-read and shared-edit knowledge bases with distinct file UUIDs.
+The AIDP mock and Nexent services are configured to record upstream calls and persistence operations.</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>{"profile":"real_smoke","roles":["READ_ONLY","USER without group","EDIT"]}</t>
+          <t>{"cross_tenant_retry":true,"profile":"mock","users":["owner","group_reader","group_editor","unrelated_tenant"]}</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>1. As the read-only user, open the base and attempt edit, upload, delete and safety guard changes. =&gt; No modification entry is executable and no modification request is issued.
-2. As a user without a valid group, submit the creation first step with a shared permission. =&gt; The submission is rejected and no knowledge base is created.
-3. As the edit user, perform the same operations. =&gt; Only the permitted operations issue requests and they succeed.</t>
+          <t>1. Query details, files, tasks and retry as each user role. =&gt; Reads and edits match the local group permission matrix, and a retry with a UUID belonging to another base is rejected before upstream access.
+2. Inspect Nexent database writes during file/task queries, retry, and detail edits. =&gt; Only the existing group-permission/config records that are explicitly changed are persisted; file and task history are not stored.
+3. Render the same overview after disabling the AIDP feature flag in a disposable ES deployment. =&gt; The original ES page renders without AIDP detail components or calls.</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr">
         <is>
-          <t>Disabled or hidden entries emit no request.
-Group validation rejects an invalid shared permission before creation.
-Permitted operations behave normally.</t>
+          <t>Unauthorized group members cannot read or mutate private or unrelated resources.
+Retry is scoped to files of the selected knowledge base and rejects invalid ownership.
+File/task records are queried live and are absent from Nexent PG history tables.
+ES knowledge-base UI and endpoints are unaffected.</t>
         </is>
       </c>
       <c r="O2" s="5" t="inlineStr">
         <is>
-          <t>No modification request from a restricted role.
-No local-only permission change without the upstream counterpart.
-No exposure of upstream credentials in any error path.</t>
+          <t>No cross-tenant or cross-KB file disclosure or retry.
+No persistent copy of AIDP files, task records or task statistics.
+No AIDP request from the ES page.</t>
         </is>
       </c>
       <c r="P2" s="5" t="inlineStr">
         <is>
-          <t>{"condition":["Read-only permission on the selected knowledge base.","Shared permission without a valid same-tenant group.","Unavailable resource state."],"metrics":["Count of modification requests by a restricted role.","Count of knowledge bases created from an invalid group submission."],"recovery_expectations":["After the rejected attempt the UI keeps the previous state and reports the failure without claiming success."],"risk":"A user without edit permission could modify a knowledge base or its safety configuration through a stale or unguarded UI entry.","risk_type":"SECURITY","thresholds":["Zero modification requests from restricted roles.","Zero resources created from an invalid group submission."]}</t>
+          <t>{"condition":["Users with different group membership access the same tenant.","A retry body contains an ID not belonging to the selected knowledge base.","The page is rendered with the AIDP feature flag disabled."],"metrics":["Unauthorized detail, file, task and retry requests accepted.","Cross-knowledge-base UUIDs forwarded to AIDP.","Writes to local file/task-history storage during read or retry flows.","AIDP requests issued by the ES page."],"recovery_expectations":["Rejected requests leave remote files and permission state unchanged and return an actionable authorization error.","The ES page continues to work with its original local knowledge base services."],"risk":"A missing permission check or accidentally persisted remote record could expose another group's AIDP data or create a misleading stale local copy.","risk_type":"SECURITY","thresholds":["Zero unauthorized reads or writes accepted.","Zero cross-KB retry UUIDs forwarded upstream.","Zero file/task history writes to Nexent PG.","Zero AIDP endpoint calls from the ES route."]}</t>
         </is>
       </c>
       <c r="Q2" s="5" t="inlineStr">
         <is>
-          <t>{"profiles":[{"name":"real_smoke","required_services":["knowledge-provider"]}]}</t>
+          <t>{"profiles":[{"name":"mock","required_services":["knowledge-provider"]}]}</t>
         </is>
       </c>
       <c r="R2" s="5" t="inlineStr">
@@ -5062,10 +6227,14 @@
       <c r="U2" s="5" t="inlineStr"/>
       <c r="V2" s="5" t="inlineStr">
         <is>
-          <t>real_smoke</t>
-        </is>
-      </c>
-      <c r="W2" s="5" t="inlineStr"/>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>knowledge-provider</t>
+        </is>
+      </c>
       <c r="X2" s="5" t="inlineStr"/>
       <c r="Y2" s="5" t="inlineStr">
         <is>
@@ -5078,7 +6247,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>AKPR-D5-002</t>
+          <t>AKPR-D5-001</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -5093,23 +6262,22 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AKPR-RULE-005
-AKPR-RULE-009</t>
+          <t>AKPR-RULE-007</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Delayed responses and polling never cross knowledge base boundaries</t>
+          <t>Restricted users never reach a modification endpoint</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>RELIABILITY</t>
+          <t>SECURITY</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -5124,44 +6292,44 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Verify that switching or leaving the file view discards in-flight results, stops polling and never renders another base document list. This case stays blocked until a deployment with a controllable slow upstream is available.</t>
+          <t>Verify across the overview, file view and creation page that permission and group rules block modification requests at the boundary. This case stays blocked until a disposable deployment with multiple permission roles is available.</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>A deployed instance can delay document responses.
-Two knowledge bases with distinct documents exist.</t>
+          <t>A deployed instance has a read-only user, a group-less user and an edit user on one knowledge base.
+Request logging is available.</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>{"bases":2,"delay_seconds":5,"profile":"real_smoke"}</t>
+          <t>{"profile":"real_smoke","roles":["READ_ONLY","USER without group","EDIT"]}</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>1. Open the first base and immediately switch to the second. =&gt; The first base documents never render in the second and the later response is discarded.
-2. Upload a document and leave the file view before processing completes. =&gt; Polling stops after leaving and no late update reaches the overview.
-3. Repeat the switch several times and inspect the rendered list. =&gt; Only the current base documents appear and the list state matches the last selection.</t>
+          <t>1. As the read-only user, open the base and attempt edit, upload and delete. =&gt; No modification entry is executable and no modification request is issued.
+2. As a user without a valid group, submit the creation first step with a shared permission. =&gt; The submission is rejected and no knowledge base is created.
+3. As the edit user, perform the same operations. =&gt; Only the permitted operations issue requests and they succeed.</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
-          <t>No stale document list is rendered.
-Polling stops when the view is left.
-The current base is always the one displayed.</t>
+          <t>Disabled or hidden entries emit no request.
+Group validation rejects an invalid shared permission before creation.
+Permitted operations behave normally.</t>
         </is>
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>No orphan polling loop after navigation.
-No document count or status from another base.
-No duplicate document rows after repeated switching.</t>
+          <t>No modification request from a restricted role.
+No local-only permission change without the upstream counterpart.
+No exposure of upstream credentials in any error path.</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>{"condition":["Slow upstream document responses.","Rapid switching between knowledge bases.","Navigating away while uploads are processing."],"metrics":["Count of discarded late responses.","Polling cycles after leaving the file view.","Rendered document count per base."],"recovery_expectations":["Reopening a base shows its own current documents and a correct processing state."],"risk":"A late response from a previously opened knowledge base can overwrite the current file view or leave polling running.","risk_type":"RELIABILITY","thresholds":["Zero cross-base document renders.","Zero polling cycles after leaving the view."]}</t>
+          <t>{"condition":["Read-only permission on the selected knowledge base.","Shared permission without a valid same-tenant group.","Unavailable resource state."],"metrics":["Count of modification requests by a restricted role.","Count of knowledge bases created from an invalid group submission."],"recovery_expectations":["After the rejected attempt the UI keeps the previous state and reports the failure without claiming success."],"risk":"A user without edit permission could modify a knowledge base through a stale or unguarded UI entry.","risk_type":"SECURITY","thresholds":["Zero modification requests from restricted roles.","Zero resources created from an invalid group submission."]}</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
@@ -5195,7 +6363,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>AKPR-D5-003</t>
+          <t>AKPR-D5-002</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -5210,24 +6378,23 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>AKPR-RULE-012
-AKPR-RULE-013
-AKPR-RULE-014</t>
+          <t>AKPR-RULE-005
+AKPR-RULE-009</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Disabled capabilities and missing remote values are never reported as active or saved</t>
+          <t>Delayed responses and polling never cross knowledge base boundaries</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>RELIABILITY</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -5242,44 +6409,44 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>Verify that hidden configuration is not resubmitted, that missing remote values stay unknown and that a failed save is never presented as success. This case stays blocked until a deployment with a controllable upstream failure mode and the upstream safety contract is available.</t>
+          <t>Verify that switching or leaving the file view discards in-flight results, stops polling and never renders another base document list. This case stays blocked until a deployment with a controllable slow upstream is available.</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>A deployed instance can reject a metadata update on demand.
-A knowledge base created before the safety field existed is available for readback.</t>
+          <t>A deployed instance can delay document responses.
+Two knowledge bases with distinct documents exist.</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>{"graph":[true,false],"guard_absent":true,"multimodal":[true,false],"profile":"real_smoke"}</t>
+          <t>{"bases":2,"delay_seconds":5,"profile":"real_smoke"}</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>1. Create a knowledge base with the graph and multimodal capabilities disabled. =&gt; No graph configuration and no hidden model field reaches the upstream request.
-2. Read back a knowledge base whose response omits the safety field. =&gt; The UI reports the state as unknown instead of confirmed disabled.
-3. Fail the metadata update after the guard change and inspect the UI. =&gt; The change is reported as not saved and the previous value remains displayed.</t>
+          <t>1. Open the first base and immediately switch to the second. =&gt; The first base documents never render in the second and the later response is discarded.
+2. Upload a document and leave the file view before processing completes. =&gt; Polling stops after leaving and no late update reaches the overview.
+3. Repeat the switch several times and inspect the rendered list. =&gt; Only the current base documents appear and the list state matches the last selection.</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>Hidden configuration stays out of requests.
-Missing remote values are not converted into confirmed states.
-Failed saves are visible as failures.</t>
+          <t>No stale document list is rendered.
+Polling stops when the view is left.
+The current base is always the one displayed.</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>No resubmission of a previously selected hidden model.
-No success message after a failed upstream update.
-No safety field nested inside graph configuration.</t>
+          <t>No orphan polling loop after navigation.
+No document count or status from another base.
+No duplicate document rows after repeated switching.</t>
         </is>
       </c>
       <c r="P4" s="5" t="inlineStr">
         <is>
-          <t>{"condition":["Graph or multimodal capability disabled after a selection.","Upstream response without the safety field.","Metadata update failure after a permission save."],"metrics":["Count of hidden configuration fields in outgoing payloads.","Count of success messages after failed updates."],"recovery_expectations":["After a failed save the previous remote value stays displayed and a retry re-sends the explicit value."],"risk":"A user could believe a safety guard or graph configuration is active while the remote state is unknown or a save failed.","risk_type":"SECURITY","thresholds":["Zero hidden configuration fields in requests.","Zero false success reports."]}</t>
+          <t>{"condition":["Slow upstream document responses.","Rapid switching between knowledge bases.","Navigating away while uploads are processing."],"metrics":["Count of discarded late responses.","Polling cycles after leaving the file view.","Rendered document count per base."],"recovery_expectations":["Reopening a base shows its own current documents and a correct processing state."],"risk":"A late response from a previously opened knowledge base can overwrite the current file view or leave polling running.","risk_type":"RELIABILITY","thresholds":["Zero cross-base document renders.","Zero polling cycles after leaving the view."]}</t>
         </is>
       </c>
       <c r="Q4" s="5" t="inlineStr">
@@ -5313,7 +6480,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>AKPR-D5-004</t>
+          <t>AKPR-D5-003</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -5328,22 +6495,23 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AKPR-RULE-010</t>
+          <t>AKPR-RULE-012
+AKPR-RULE-013</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Creation and upload failures leave exactly one consistent knowledge base</t>
+          <t>Disabled capabilities and missing remote values are never reported as active or saved</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>RELIABILITY</t>
+          <t>SECURITY</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -5358,44 +6526,40 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Verify that failures around creation and upload never produce duplicate knowledge bases or permission rows without their knowledge base. This case stays blocked until a deployment with controllable upstream create and upload failures is available.</t>
+          <t>Verify that hidden configuration is not resubmitted and that a failed metadata save is never presented as success. This case stays blocked until a deployment with a controllable upstream failure mode is available.</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>A deployed instance can fail creation and file uploads on demand.
-Permission rows are inspectable for the test tenant.</t>
+          <t>A deployed instance can reject a metadata update on demand.</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>{"create_failures":1,"profile":"real_smoke","upload_failures":2}</t>
+          <t>{"graph":[true,false],"multimodal":[true,false],"profile":"real_smoke"}</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>1. Fail the create request and inspect local state. =&gt; No knowledge base and no orphan permission row remain.
-2. Create successfully with two failing uploads and retry them. =&gt; One knowledge base exists and the retries never create another.
-3. Interrupt the submission and reload the creation page. =&gt; No duplicate resource appears and the user can identify the outcome of the previous attempt.</t>
+          <t>1. Create a knowledge base with the graph and multimodal capabilities disabled. =&gt; No graph configuration and no hidden model field reaches the upstream request.
+2. Change the knowledge-base name or description, fail the metadata update and inspect the UI. =&gt; The change is reported as not saved and the previous value remains displayed.</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>Exactly one knowledge base exists after retries.
-Permission rows always belong to an existing knowledge base.
-Interrupted submissions do not silently duplicate resources.</t>
+          <t>Hidden configuration stays out of requests.
+Failed saves are visible as failures.</t>
         </is>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
-          <t>No duplicate knowledge base after retry or reload.
-No orphan permission row.
-No upload executed before a successful create.</t>
+          <t>No resubmission of a previously selected hidden model.
+No success message after a failed upstream update.</t>
         </is>
       </c>
       <c r="P5" s="5" t="inlineStr">
         <is>
-          <t>{"condition":["Create failure.","Partial upload failure with retry.","Submission interrupted before a response arrives."],"metrics":["Knowledge bases created per submission attempt.","Orphan permission rows.","Upload attempts before a successful create."],"recovery_expectations":["The created knowledge base stays usable and the failed files can be retried without creating a new base."],"risk":"Retrying a partially failed creation can create duplicate knowledge bases or inconsistent permission records.","risk_type":"RELIABILITY","thresholds":["At most one knowledge base per intended submission.","Zero orphan permission rows."]}</t>
+          <t>{"condition":["Graph or multimodal capability disabled after a selection.","Metadata update failure after a permission save."],"metrics":["Count of hidden configuration fields in outgoing payloads.","Count of success messages after failed updates."],"recovery_expectations":["After a failed save the previous remote value stays displayed and a retry re-sends the explicit value."],"risk":"A user could believe a graph or multimodal configuration is active while remote state is unknown, or believe metadata was saved when the update failed.","risk_type":"SECURITY","thresholds":["Zero hidden configuration fields in requests.","Zero false success reports."]}</t>
         </is>
       </c>
       <c r="Q5" s="5" t="inlineStr">
@@ -5429,20 +6593,136 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>AKPR-D5-004</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-001</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-RULE-010</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Creation and upload failures leave exactly one consistent knowledge base</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>RELIABILITY</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Verify that failures around creation and upload never produce duplicate knowledge bases or permission rows without their knowledge base. This case stays blocked until a deployment with controllable upstream create and upload failures is available.</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>A deployed instance can fail creation and file uploads on demand.
+Permission rows are inspectable for the test tenant.</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>{"create_failures":1,"profile":"real_smoke","upload_failures":2}</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>1. Fail the create request and inspect local state. =&gt; No knowledge base and no orphan permission row remain.
+2. Create successfully with two failing uploads and retry them. =&gt; One knowledge base exists and the retries never create another.
+3. Interrupt the submission and reload the creation page. =&gt; No duplicate resource appears and the user can identify the outcome of the previous attempt.</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>Exactly one knowledge base exists after retries.
+Permission rows always belong to an existing knowledge base.
+Interrupted submissions do not silently duplicate resources.</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>No duplicate knowledge base after retry or reload.
+No orphan permission row.
+No upload executed before a successful create.</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>{"condition":["Create failure.","Partial upload failure with retry.","Submission interrupted before a response arrives."],"metrics":["Knowledge bases created per submission attempt.","Orphan permission rows.","Upload attempts before a successful create."],"recovery_expectations":["The created knowledge base stays usable and the failed files can be retried without creating a new base."],"risk":"Retrying a partially failed creation can create duplicate knowledge bases or inconsistent permission records.","risk_type":"RELIABILITY","thresholds":["At most one knowledge base per intended submission.","Zero orphan permission rows."]}</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"real_smoke","required_services":["knowledge-provider"]}]}</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>unbound</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>real_smoke</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr">
+        <is>
+          <t>无需绑定</t>
+        </is>
+      </c>
+      <c r="Z6" s="5" t="inlineStr"/>
+      <c r="AA6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
           <t>CMSR-D5-001</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-014
 CMSR-RULE-015
@@ -5451,47 +6731,47 @@
 CMSR-RULE-018</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Repeated partial failures never leak across attempts or siblings</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>RELIABILITY</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Verify rollback isolation under repeated partial streams and parallel sub-agent output.</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>A controlled provider can interleave parent and sibling outputs.</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>{"failures":4,"profile":"mock"}</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>1. Inject four partial failures and a fifth successful response while sibling output interleaves. =&gt; The retry budget is respected.
 2. Inspect final UI and stored output. =&gt; Only fifth-attempt and sibling content remain.
@@ -5500,58 +6780,58 @@
 5. Inject repeated reasoning-only length responses with diagnostic preview disabled. =&gt; Each rejection is correlated to its budget and attempt while no raw reasoning or user text enters logs or persisted output.</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Successful and sibling content are complete.
 Failed attempts leave zero fragments.</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>No sixth provider call.
 No cross-invocation deletion.
 No failed-fragment persistence.</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>{"condition":["Four partial failures followed by a success.","Parallel sibling output."],"metrics":["Provider request count.","Failed-fragment count in SSE projection and persisted units."],"recovery_expectations":["The committed attempt and sibling output remain readable after refresh."],"risk":"Stale partial output can leak after repeated retries or corrupt sibling cards.","risk_type":"RELIABILITY","thresholds":["At most five physical requests.","Zero failed fragments after rollback."]}</t>
         </is>
       </c>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr">
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr"/>
-      <c r="V6" s="5" t="inlineStr"/>
-      <c r="W6" s="5" t="inlineStr">
+      <c r="S7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr"/>
+      <c r="U7" s="5" t="inlineStr"/>
+      <c r="V7" s="5" t="inlineStr"/>
+      <c r="W7" s="5" t="inlineStr">
         <is>
           <t>model-provider</t>
         </is>
       </c>
-      <c r="X6" s="5" t="inlineStr"/>
-      <c r="Y6" s="5" t="inlineStr">
+      <c r="X7" s="5" t="inlineStr"/>
+      <c r="Y7" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z6" s="5" t="inlineStr">
+      <c r="Z7" s="5" t="inlineStr">
         <is>
           <t>sha256:50b69a0b1ee496cbb14b84e51bb80e7f92f3aaecd2d694c095013d056f678861</t>
         </is>
       </c>
-      <c r="AA6" s="5" t="inlineStr">
+      <c r="AA7" s="5" t="inlineStr">
         <is>
           <t>sha256:4f53cda18c2baa0c0354bb5f9a3ecbe5ed12ab4d8e11ba873c2f11161202b945</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA6"/>
+  <autoFilter ref="A1:AA7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/test/generated/Nexent_测试基线.xlsx
+++ b/test/generated/Nexent_测试基线.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AIDP knowledge bases are listed in a card or table overview with an independent name search, a collapsible three-step guide and a full-page file view per knowledge base; creation moves to a dedicated two-step page that carries permission, chunking, retrieval, graph and model configuration. The ES knowledge base path stays untouched.</t>
+          <t>AIDP knowledge bases are listed in a card or table overview with an independent name search, a collapsible three-step guide and a full-page file view per knowledge base; creation uses one dedicated full-page form for permissions, chunking, retrieval, graph and model configuration, submits directly, and leaves file upload to the detail page. The ES knowledge base path stays untouched.</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -685,7 +685,8 @@
 AKPR-RULE-012
 AKPR-RULE-013
 AKPR-RULE-015
-AKPR-RULE-016</t>
+AKPR-RULE-016
+AKPR-RULE-017</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -2552,12 +2553,13 @@
       <c r="D17" s="5" t="inlineStr">
         <is>
           <t>AKPR-RULE-010
-AKPR-RULE-016</t>
+AKPR-RULE-016
+AKPR-RULE-017</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Creation page keeps switches beside labels and aligns paired controls</t>
+          <t>Creation page uses 18px titles and submits directly from its single form</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -2582,12 +2584,12 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Verify the AIDP create page is full-width, section controls have the designed visual grouping, and paired controls share a baseline.</t>
+          <t>Verify the AIDP create page uses the approved title sizes and single-page submit flow while keeping section controls aligned.</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>Render the first creation step at desktop width with safety, graph and VLM controls visible.</t>
+          <t>Render the AIDP creation page at desktop width with a valid mock create response.</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
@@ -2597,14 +2599,18 @@
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>1. Render the page header and form. =&gt; The creation form uses the available content width and the breadcrumb reads knowledge base / create knowledge base.
-2. Inspect safety, graph and VLM toggle groups. =&gt; Each switch sits beside its corresponding label and help icon.
-3. Inspect fields that share a row. =&gt; Both controls use the same label structure and their input or slider starts differ by no more than one pixel.</t>
+          <t>1. Render the page header and form. =&gt; The creation form uses the available content width; breadcrumb labels are 18px and no step indicator or optional upload stage is rendered.
+2. Inspect graph and VLM toggle groups. =&gt; Each switch sits beside its corresponding label and help icon.
+3. Inspect section headings and fields that share a row. =&gt; Both controls use the same label structure and their input or slider starts differ by no more than one pixel.
+4. Fill required fields and submit the create form. =&gt; One create request is sent, no upload request is sent, and success navigates to the created knowledge base detail page.
+5. Render the detail information tab for a seeded knowledge base. =&gt; The detail breadcrumb and configuration, graph and permission section headings use 18px text.</t>
         </is>
       </c>
       <c r="N17" s="5" t="inlineStr">
         <is>
           <t>No fixed narrow modal-sized content column constrains the create page.
+The create breadcrumb title and form section headings use 18px text.
+The form creates the knowledge base directly without an intermediate step or upload stage.
 Switches are adjacent to their own labels rather than the far edge of the row.
 Paired model, chunking and retrieval controls align consistently.</t>
         </is>
@@ -2617,7 +2623,7 @@
       </c>
       <c r="P17" s="5" t="inlineStr">
         <is>
-          <t>{"assertions":["The creation header and form fill the available page content width.","Switches are grouped within 12 pixels of their labels.","Paired controls use consistent label and field alignment."],"inputs":["desktop viewport","graph toggle","VLM toggle","paired model controls"],"unit_boundary":"AIDP create form section layout and toggle grouping"}</t>
+          <t>{"assertions":["The creation header and form fill the available page content width.","The current create breadcrumb and section heading computed font sizes are 18px.","The current detail breadcrumb and detail information section heading computed font sizes are 18px.","No stepper or optional-upload control is rendered; one submit calls create once and does not call upload.","Switches are grouped within 12 pixels of their labels.","Paired controls use consistent label and field alignment."],"inputs":["desktop viewport","graph toggle","VLM toggle","paired model controls","valid create response"],"unit_boundary":"AIDP create form title, direct-submit flow, section layout and toggle grouping"}</t>
         </is>
       </c>
       <c r="Q17" s="5" t="inlineStr"/>
@@ -5702,8 +5708,10 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AKPR-RULE-015
-AKPR-RULE-016</t>
+          <t>AKPR-RULE-010
+AKPR-RULE-015
+AKPR-RULE-016
+AKPR-RULE-017</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -5733,7 +5741,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Verify the rendered guide, knowledge cards, pagination, inline switches and paired create-form controls against the AIDP design at desktop and narrow widths.</t>
+          <t>Verify the rendered guide, knowledge cards, pagination, inline switches, title typography and direct create flow against the AIDP design at desktop and narrow widths.</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
@@ -5752,27 +5760,31 @@
         <is>
           <t>1. Open the overview and capture the expanded guide and first card row. =&gt; At desktop width each row contains four 148px-high cards with 16px horizontal gaps and 12px vertical gaps. Cards have 24px horizontal and 16px vertical padding, a 40px icon, a 16px/500/24px title, a full-width two-line 12px/20px description, and one 12px/18px metadata row. The toolbar search is 360px by 32px, the primary button is 32px high, and the selected view uses the primary blue background. Pagination is aligned right, uses 32px controls, puts page-size selection before page numbers, and has a pale-blue selected page with no primary border.
 2. Switch to table view and inspect the toolbar and column controls. =&gt; The create and view buttons align at the right, table column control follows them, and no edit operation appears in the overview. The table header and data rows are 40px high with 14px/22px body text and pale
-3. Open creation and inspect the page header, switches and paired fields at both viewport sizes. =&gt; The page uses the available width, switches sit beside their labels, and paired inputs or sliders align without page-level horizontal overflow.</t>
+3. Open creation and inspect the page title, section titles, switches and paired fields at both viewport sizes. =&gt; Breadcrumb labels and form section headings use 18px text, there is no step indicator or optional import stage, the page uses the available width, switches sit beside their labels, and paired inputs or sliders align without page-level horizontal overflow.
+4. Fill the required configuration and submit the create form. =&gt; The knowledge base is created directly with one create request, the browser opens its detail page, and no upload request is issued from creation.
+5. Open the detail page's information tab. =&gt; The detail breadcrumb and configuration, graph and permission section headings render at 18px.</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
           <t>The running AIDP pages match the accepted layout and preserve Nexent visual conventions.
+The create and detail current page titles and detail information section headings use 18px text.
+The create flow has no stepper or optional upload stage; file upload remains in the knowledge base detail page.
 The expanded guide uses the pale-blue gradient introduction panel with 24px padding, a configuration-flow heading and three 156px-high step cards; the step content stays create, upload and configure an agent, and collapse or reopen preserves the overview state.
 The narrow viewport remains usable without overlapping labels or page-level horizontal scrolling.
 Collapsing the guide preserves the keyword and page; changing page size resets to page one; the last partial page keeps the same content-panel height; a valid page jump navigates without a mutating request.
-No write request is issued while visually inspecting the pages.</t>
+No write request is issued while inspecting pages before the explicit create submit.</t>
         </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
-          <t>No knowledge base is created, edited or deleted during this journey.
+          <t>No knowledge base is created before the explicit submit, edited, or deleted; the submit issues exactly one create request and no upload request.
 No global style or ES page behavior is changed.</t>
         </is>
       </c>
       <c r="P7" s="5" t="inlineStr">
         <is>
-          <t>{"actor":"Authenticated AIDP tenant user","failure_evidence":["Save screenshots, computed layout measurements and browser console errors for both viewport sizes."],"final_business_result":["Users see the intended list and creation composition before beginning a knowledge-base operation."],"journey":["Inspect the overview guide and cards.","Inspect the table toolbar and pagination.","Inspect the full-page creation layout at desktop and narrow widths."]}</t>
+          <t>{"actor":"Authenticated AIDP tenant user","failure_evidence":["Save screenshots, computed layout measurements and browser console errors for both viewport sizes."],"final_business_result":["Users can inspect the intended list and create composition, then create a knowledge base directly and continue to its detail page."],"journey":["Inspect the overview guide and cards.","Inspect the table toolbar and pagination.","Inspect the full-page creation layout at desktop and narrow widths."]}</t>
         </is>
       </c>
       <c r="Q7" s="5" t="inlineStr">

--- a/test/generated/Nexent_测试基线.xlsx
+++ b/test/generated/Nexent_测试基线.xlsx
@@ -630,7 +630,8 @@
 AKDT-RULE-005
 AKDT-RULE-006
 AKDT-RULE-007
-AKDT-RULE-008</t>
+AKDT-RULE-008
+AKDT-RULE-009</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -1058,12 +1059,13 @@
       <c r="D3" s="5" t="inlineStr">
         <is>
           <t>AKDT-RULE-001
-AKDT-RULE-007</t>
+AKDT-RULE-007
+AKDT-RULE-009</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Detail information reads graph configuration and group access without truthiness coercion</t>
+          <t>Detail information reads configuration and keeps edit controls scoped</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -1088,32 +1090,36 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Verify the detail page projects the returned configuration and local group permission while preserving false, zero and unknown values.</t>
+          <t>Verify the detail page projects returned configuration, preserves false and zero values, and keeps metadata, permission and Top K edits in their intended controls.</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Render a KB detail response with graph_config represented once as JSON text and once as an object.
-Include explicit false and zero values, private/shared permission variants and one missing safety value.</t>
+Include explicit false and zero values, private/shared permission variants and one missing safety value.
+Grant edit access and provide an available user-group option for the edit-control checks.</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>{"graph_config_forms":["json_string","object"],"profile":"mock"}</t>
+          <t>{"graph_config_forms":["json_string","object"],"profile":"mock","topk_range":[1,100]}</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
           <t>1. Render the configuration and graph sections for each response shape. =&gt; Values appear in their corresponding named fields and a model name is not duplicated.
 2. Inspect false, zero and missing values. =&gt; False and zero remain off/zero; a missing safety value is shown as unknown.
-3. Render private and shared permission records with group IDs. =&gt; Scope and group names follow local permission data and the viewer's group-read permission.</t>
+3. Render private and shared permission records with group IDs. =&gt; Scope and group names follow local permission data and the viewer's group-read permission.
+4. Open the header edit, lower permission edit and vector Top K edit. =&gt; The header form shows name, description and visible permission/group fields without a collapsed advanced section; the lower editor contains only permission and group fields; Top K uses the create-page slider and numeric value control.</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
           <t>JSON text and object graph settings render consistently.
 Boolean false and numeric zero remain distinct from missing values.
-Effective permission and available group names come from the permission layer.</t>
+Effective permission and available group names come from the permission layer.
+The lower permission save sends only permission/group fields; the header form remains the only name/description editor.
+The Top K editor uses a 1-100 slider with a numeric value control.</t>
         </is>
       </c>
       <c r="O3" s="5" t="inlineStr">
@@ -1124,7 +1130,7 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>{"assertions":["Graph fields and the two separate Top K values render under the correct labels.","Explicit false and zero are preserved while absent values remain unknown.","Group names render only with group:read permission."],"inputs":["AIDP detail payload","graph_config value","local group permission record"],"unit_boundary":"AIDP knowledge detail configuration parsing and permission presentation"}</t>
+          <t>{"assertions":["Graph fields and the two separate Top K values render under the correct labels.","Explicit false and zero are preserved while absent values remain unknown.","Group names render only with group:read permission.","Header and lower permission edit forms expose their separate allowed fields and omit the advanced-options collapse.","The vector Top K edit control matches the creation page slider layout and range."],"inputs":["AIDP detail payload","graph_config value","local group permission record","header and permission edit modes","vector Top K value"],"unit_boundary":"AIDP knowledge detail configuration, permission presentation and edit controls"}</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr"/>
@@ -5148,16 +5154,16 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>{"locale":"zh-CN","profile":"mock","status_values":[0,1,2,3,4,5],"task_retention_days":30}</t>
+          <t>{"locale":"zh-CN","profile":"mock","status_values":[0,1,2,3,4,5],"task_retention_days":30,"vector_topk_range":[1,100]}</t>
         </is>
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>1. Open the overview and click a card or knowledge-base name. =&gt; A full-width detail page opens with a breadcrumb, header and the three tabs Files, Upload tasks and Details; no list edit action remains.
+          <t>1. Open the overview and click a card or knowledge-base name. =&gt; A full-width detail page opens with a breadcrumb, header and the three tabs Files, Upload tasks and Details; no list edit action remains, and the console has no deprecated AIDP Modal or Drawer API warnings.
 2. Inspect Files and search by file name. =&gt; Only ingested files appear; download and delete follow the user's permission; pagination and table controls stay in the detail page.
 3. Open Upload tasks, search a name and choose each status filter. =&gt; The page states tasks are retained for 30 days, status values 0-5 are sent, statistics remain independent from the current page, and processing rows do not appear as ingested files.
 4. Open a failed task's failure details and retry it from the row action. =&gt; The drawer shows returned values only; retry submits a one-item file_uuids array and subsequent refresh reads the changed task status.
-5. Open Details and edit supported name/description, a supported setting and group permissions. =&gt; Each save sends only its own changed fields and updates the returned value; unsupported similarity edits are absent.</t>
+5. Open Details and edit metadata from the header, a supported setting, then permission and groups from the permission section. =&gt; Header edit shows name, description and directly visible permission/group controls; the lower editor contains only permission/group controls and sends no metadata fields; vector Top K uses the create-page slider style; unsupported similarity edits are absent.</t>
         </is>
       </c>
       <c r="N2" s="5" t="inlineStr">
@@ -5165,7 +5171,9 @@
           <t>The page has the exact three tabs and full content width.
 Ingested files and upload history remain separate live AIDP sources.
 Status filters, raw status rendering, failure details and single-file retry follow the contract.
-Detail settings and group permissions use separate authorized save operations.</t>
+Detail settings and group permissions use separate authorized save operations.
+The header edit is the only path that submits a changed name or description; the lower permission editor submits only permission and group values.
+The vector Top K editor uses the same slider and numeric value control as the creation form.</t>
         </is>
       </c>
       <c r="O2" s="5" t="inlineStr">
@@ -5760,7 +5768,7 @@
         <is>
           <t>1. Open the overview and capture the expanded guide and first card row. =&gt; At desktop width each row contains four 148px-high cards with 16px horizontal gaps and 12px vertical gaps. Cards have 24px horizontal and 16px vertical padding, a 40px icon, a 16px/500/24px title, a full-width two-line 12px/20px description, and one 12px/18px metadata row. The toolbar search is 360px by 32px, the primary button is 32px high, and the selected view uses the primary blue background. Pagination is aligned right, uses 32px controls, puts page-size selection before page numbers, and has a pale-blue selected page with no primary border.
 2. Switch to table view and inspect the toolbar and column controls. =&gt; The create and view buttons align at the right, table column control follows them, and no edit operation appears in the overview. The table header and data rows are 40px high with 14px/22px body text and pale
-3. Open creation and inspect the page title, section titles, switches and paired fields at both viewport sizes. =&gt; Breadcrumb labels and form section headings use 18px text, there is no step indicator or optional import stage, the page uses the available width, switches sit beside their labels, and paired inputs or sliders align without page-level horizontal overflow.
+3. Open creation and inspect the page title, section titles, switches and paired fields at both viewport sizes. =&gt; Breadcrumb labels and form section headings use 18px text, there is no step indicator or optional import stage, the page uses the available width, switches sit beside their labels, and paired inputs or sliders align without page-level horizontal overflow. The browser console has no deprecated Ant Design Modal, Drawer or Alert API warnings.
 4. Fill the required configuration and submit the create form. =&gt; The knowledge base is created directly with one create request, the browser opens its detail page, and no upload request is issued from creation.
 5. Open the detail page's information tab. =&gt; The detail breadcrumb and configuration, graph and permission section headings render at 18px.</t>
         </is>

--- a/test/generated/Nexent_测试基线.xlsx
+++ b/test/generated/Nexent_测试基线.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_功能清单'!$A$1:$G$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_D1'!$A$1:$AA$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_D1'!$A$1:$AA$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_D2'!$A$1:$AA$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_D3'!$A$1:$AA$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_D4'!$A$1:$AA$8</definedName>
@@ -687,7 +687,8 @@
 AKPR-RULE-013
 AKPR-RULE-015
 AKPR-RULE-016
-AKPR-RULE-017</t>
+AKPR-RULE-017
+AKPR-RULE-018</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -763,7 +764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA21"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -784,9 +785,9 @@
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="25" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -2655,33 +2656,32 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>CMSR-D1-001</t>
+          <t>AKPR-D1-015</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>CMSR-005</t>
+          <t>AKPR-001</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>CMSR-005</t>
+          <t>AKPR-001</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>CMSR-RULE-013
-CMSR-RULE-014</t>
+          <t>AKPR-RULE-018</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Observer emits safe content before stream completion</t>
+          <t>AIDP import drawer uploads on selection and keeps results until confirmation</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>SDK-UT</t>
+          <t>FE-COMP</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -2701,40 +2701,45 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Verify bounded marker lookahead and attempt state reset.</t>
+          <t>Verify selection immediately uploads valid files, actual transfer progress is distinct from AIDP acceptance, and Confirm closes without a second upload.</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>Create an isolated observer and a controlled chunk sequence.</t>
+          <t>Render the import drawer with a writable mock knowledge base and a mocked upload API response.</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>{"profile":"mock","sequence":"failed partial, rollback, successful split code and think markers"}</t>
+          <t>{"file":"guide.txt","profile":"mock","upload_bytes":[716800,2621440]}</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>1. Feed a safe prefix and pause the source. =&gt; The prefix is emitted before flush or commit.
-2. Roll back the first attempt and feed split markers in the second. =&gt; The second output is ordered and contains no first-attempt residue.</t>
+          <t>1. Select multiple supported files together. =&gt; One multipart batch starts automatically; every row has a dashed gray border and Confirm is disabled while the request is active.
+2. Report intermediate progress, then complete browser transfer without resolving the upload response. =&gt; Each uploading ring shows the same batch percentage; the second line only shows the file size. Transfer completion changes rings to waiting indicators, borders stay dashed, Confirm remains disabled, and no delete action is present.
+3. Resolve the upload response as accepted. =&gt; The row changes to a solid near-black border and the accepted file id is passed to the parent refresh flow; the drawer remains open.
+4. Click Confirm. =&gt; The drawer closes and no additional upload request is sent.</t>
         </is>
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>The earliest safe content is observable before completion.
-Split markers retain their original semantics.</t>
+          <t>Choosing a valid file immediately uploads it through the existing AIDP route.
+Progress text and ring are derived from the upload event, not a timer.
+A successful response changes the row border to solid near-black.
+Results remain visible until Confirm, which never sends files again.</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>No stale fragment crosses attempts.
-No code is executed by the observer.</t>
+          <t>No per-file transferred-byte text or batch-progress label is rendered.
+No retry action is rendered in the import row.
+No change to the ES upload component.</t>
         </is>
       </c>
       <c r="P18" s="5" t="inlineStr">
         <is>
-          <t>{"assertions":["Safe prefix emitted before flush.","Raw code tag retained.","No failed-attempt residue."],"inputs":["normal content","split &lt;think&gt; and &lt;/think&gt;","raw &lt;code&gt; content"],"unit_boundary":"Observer.add_model_new_token and attempt lifecycle"}</t>
+          <t>{"assertions":["The upload API is called on selection and not on confirmation.","The rows share batch percentage rings and display only their own total file sizes while uploading.","Mixed responses map by file name; accepted rows become solid near-black and are reported to their parent. Only failed rows show delete; deleting removes a frontend row without any network call. Network errors mark all rows failed and enable Confirm. A 50-file selection makes one request, and further batches contain only newly selected files."],"inputs":["mock knowledge base","supported file","progress event","accepted upload response"],"unit_boundary":"AIDP import drawer automatic upload, progress, result retention and confirmation"}</t>
         </is>
       </c>
       <c r="Q18" s="5" t="inlineStr"/>
@@ -2745,17 +2750,20 @@
       </c>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>pytest</t>
+          <t>vitest
+vitest</t>
         </is>
       </c>
       <c r="T18" s="5" t="inlineStr">
         <is>
-          <t>test/automation/d1/test_model_attempt_stream.py</t>
+          <t>test/automation/d1/AidpImportDrawer.test.tsx
+test/automation/d1/AidpUploadService.test.tsx</t>
         </is>
       </c>
       <c r="U18" s="5" t="inlineStr">
         <is>
-          <t>test_cmsr_d1_001</t>
+          <t>AKPR-D1-015
+AKPR-D1-015</t>
         </is>
       </c>
       <c r="V18" s="5" t="inlineStr">
@@ -2772,85 +2780,214 @@
       </c>
       <c r="Z18" s="5" t="inlineStr">
         <is>
-          <t>sha256:625e8c8829b51b9cd91344555d05c5ebfdc7bd766d8485eab99b9f22773f3233</t>
+          <t>sha256:6c4a5f0c2060b7e3780c73a01331faeae9528c1f10de5bb60e37c8fcdfb54355</t>
         </is>
       </c>
       <c r="AA18" s="5" t="inlineStr">
         <is>
-          <t>sha256:242f1aaf8a5fe4427f503e5acb8db2cc6cb5096782c2e4fdf49fcb17ec471420</t>
+          <t>sha256:2bd0dcafdd0bd3669182569189845378bce21ae3c9ce22083b83b9fdca5ad631</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
+          <t>CMSR-D1-001</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-005</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-005</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>CMSR-RULE-013
+CMSR-RULE-014</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Observer emits safe content before stream completion</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>SDK-UT</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Verify bounded marker lookahead and attempt state reset.</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Create an isolated observer and a controlled chunk sequence.</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock","sequence":"failed partial, rollback, successful split code and think markers"}</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>1. Feed a safe prefix and pause the source. =&gt; The prefix is emitted before flush or commit.
+2. Roll back the first attempt and feed split markers in the second. =&gt; The second output is ordered and contains no first-attempt residue.</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>The earliest safe content is observable before completion.
+Split markers retain their original semantics.</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>No stale fragment crosses attempts.
+No code is executed by the observer.</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Safe prefix emitted before flush.","Raw code tag retained.","No failed-attempt residue."],"inputs":["normal content","split &lt;think&gt; and &lt;/think&gt;","raw &lt;code&gt; content"],"unit_boundary":"Observer.add_model_new_token and attempt lifecycle"}</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_model_attempt_stream.py</t>
+        </is>
+      </c>
+      <c r="U19" s="5" t="inlineStr">
+        <is>
+          <t>test_cmsr_d1_001</t>
+        </is>
+      </c>
+      <c r="V19" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W19" s="5" t="inlineStr"/>
+      <c r="X19" s="5" t="inlineStr"/>
+      <c r="Y19" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z19" s="5" t="inlineStr">
+        <is>
+          <t>sha256:625e8c8829b51b9cd91344555d05c5ebfdc7bd766d8485eab99b9f22773f3233</t>
+        </is>
+      </c>
+      <c r="AA19" s="5" t="inlineStr">
+        <is>
+          <t>sha256:242f1aaf8a5fe4427f503e5acb8db2cc6cb5096782c2e4fdf49fcb17ec471420</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
           <t>CMSR-D1-002</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-014
 CMSR-RULE-015</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Running step labels precede reasoning and survive retry rollback</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>FE-COMP</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Verify immediate running labels, rollback preservation, legacy history and removal of terminal label-only cards.</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>Create the streaming adapter with a controlled SSE fixture.</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","sequences":["step 1, failed attempt, rollback, successful raw code, parse","legacy content before step label"]}</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="M20" s="5" t="inlineStr">
         <is>
           <t>1. Emit a step label before any model content. =&gt; A running reasoning card displays Step 1 immediately.
 2. Roll back a partial attempt and stream successful raw code. =&gt; Step 1 remains during rollback and only successful raw code follows it.
 3. Parse and reload both new and legacy-order history. =&gt; One code card and one labeled nonempty reasoning card remain; a terminal label-only card is absent.</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>Step label appears before first token.
 Rollback preserves the label.
@@ -2858,326 +2995,326 @@
 Old history prepends late labels.</t>
         </is>
       </c>
-      <c r="O19" s="5" t="inlineStr">
+      <c r="O20" s="5" t="inlineStr">
         <is>
           <t>No failed-attempt content.
 No duplicate code card.
 No sibling invocation mutation.</t>
         </is>
       </c>
-      <c r="P19" s="5" t="inlineStr">
+      <c r="P20" s="5" t="inlineStr">
         <is>
           <t>{"assertions":["Running label is visible before content.","Terminal label-only step is hidden.","Successful code is visible after the label before commit.","History equals live output."],"inputs":["step_count","model_attempt_control","model_output_thinking","parse"],"unit_boundary":"Frontend live and history reasoning projection"}</t>
         </is>
       </c>
-      <c r="Q19" s="5" t="inlineStr"/>
-      <c r="R19" s="5" t="inlineStr">
+      <c r="Q20" s="5" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr">
         <is>
           <t>implemented</t>
         </is>
       </c>
-      <c r="S19" s="5" t="inlineStr">
+      <c r="S20" s="5" t="inlineStr">
         <is>
           <t>custom</t>
         </is>
       </c>
-      <c r="T19" s="5" t="inlineStr">
+      <c r="T20" s="5" t="inlineStr">
         <is>
           <t>test/automation/d1/test_reasoning_card.ts</t>
         </is>
       </c>
-      <c r="U19" s="5" t="inlineStr">
+      <c r="U20" s="5" t="inlineStr">
         <is>
           <t>CMSR-D1-002</t>
         </is>
       </c>
-      <c r="V19" s="5" t="inlineStr">
+      <c r="V20" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W19" s="5" t="inlineStr"/>
-      <c r="X19" s="5" t="inlineStr"/>
-      <c r="Y19" s="5" t="inlineStr">
+      <c r="W20" s="5" t="inlineStr"/>
+      <c r="X20" s="5" t="inlineStr"/>
+      <c r="Y20" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z19" s="5" t="inlineStr">
+      <c r="Z20" s="5" t="inlineStr">
         <is>
           <t>sha256:b614502639e969ab0f3840d1381f1b12b01cb5b693a0b02d17387192b230b354</t>
         </is>
       </c>
-      <c r="AA19" s="5" t="inlineStr">
+      <c r="AA20" s="5" t="inlineStr">
         <is>
           <t>sha256:03f5fae5200c76ca296c75ab0ebf225f190fb3fe6a7f52c7c8c7e0da2a97d07c</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>CMSR-D1-003</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-014
 CMSR-RULE-016</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>CoreAgent commits streamed valid semantic repair</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>SDK-UT</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>A protocol-invalid first attempt rolls back while its single preceding step label survives and the corrected result streams and commits.</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>A controlled model yields an invalid response then a pausable valid code action at step one.</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","sequence":"invalid code, rollback, corrected code chunks, commit, parse"}</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>1. Begin step one and return protocol-invalid model content. =&gt; Exactly one step label precedes begin; the attempt rolls back and one repair is scheduled.
 2. Pause the valid repair after its first safe chunk. =&gt; That chunk is visible before model completion.
 3. Complete the repair and classify it. =&gt; Its attempt commits and a single parse follows.</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>Corrected content is streamed and committed.
 Only the corrected action is executed.
 Lifecycle logs identify the repair without content.</t>
         </is>
       </c>
-      <c r="O20" s="5" t="inlineStr">
+      <c r="O21" s="5" t="inlineStr">
         <is>
           <t>No failed content after rollback.
 No repair instruction in user output.
 No suppressed successful stream.</t>
         </is>
       </c>
-      <c r="P20" s="5" t="inlineStr">
+      <c r="P21" s="5" t="inlineStr">
         <is>
           <t>{"assertions":["Step label occurs before both model attempts and only once.","Successful repair does not set stream suppression.","Corrected attempt commits once.","Invalid attempt rolls back once."],"inputs":["step one","invalid model content","valid streamed &lt;code&gt; action"],"unit_boundary":"CoreAgent semantic repair and deferred model attempt lifecycle"}</t>
         </is>
       </c>
-      <c r="Q20" s="5" t="inlineStr"/>
-      <c r="R20" s="5" t="inlineStr">
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr">
         <is>
           <t>implemented</t>
         </is>
       </c>
-      <c r="S20" s="5" t="inlineStr">
+      <c r="S21" s="5" t="inlineStr">
         <is>
           <t>pytest</t>
         </is>
       </c>
-      <c r="T20" s="5" t="inlineStr">
+      <c r="T21" s="5" t="inlineStr">
         <is>
           <t>test/automation/d1/test_semantic_repair_stream.py</t>
         </is>
       </c>
-      <c r="U20" s="5" t="inlineStr">
+      <c r="U21" s="5" t="inlineStr">
         <is>
           <t>test_cmsr_d1_003</t>
         </is>
       </c>
-      <c r="V20" s="5" t="inlineStr">
+      <c r="V21" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W20" s="5" t="inlineStr"/>
-      <c r="X20" s="5" t="inlineStr"/>
-      <c r="Y20" s="5" t="inlineStr">
+      <c r="W21" s="5" t="inlineStr"/>
+      <c r="X21" s="5" t="inlineStr"/>
+      <c r="Y21" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z20" s="5" t="inlineStr">
+      <c r="Z21" s="5" t="inlineStr">
         <is>
           <t>sha256:7ef8664f2224d068d7deafecf80f09353d734bc10b35a1147b3cc58d1ae6eacd</t>
         </is>
       </c>
-      <c r="AA20" s="5" t="inlineStr">
+      <c r="AA21" s="5" t="inlineStr">
         <is>
           <t>sha256:1dee7e7ce90f70c40d02907f11be7b55665495fdcaa3dfdec3ab478953c5c38c</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>CMSR-D1-004</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-018</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Rejected model output diagnostics distinguish budget exhaustion without default content leakage</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>SDK-UT</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Correlate each protocol rejection to the model response shape and budget while gating bounded raw previews.</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>Use isolated model diagnostics for a reasoning-only length response and a malformed nonempty response.</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","responses":["length with 4096 reasoning-only output tokens","malformed nonempty code Action"]}</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M22" s="5" t="inlineStr">
         <is>
           <t>1. Reject a reasoning-only length response with diagnostics disabled. =&gt; The log records model, attempt, requested and consumed tokens, reasoning and content counts, and reasoning-only budget exhaustion without raw text.
 2. Reject a malformed content response. =&gt; The distinct protocol reason and response shape are logged under its own attempt identifier.
 3. Enable diagnostic content preview for a rejected response longer than the preview cap. =&gt; Only a single escaped bounded prefix of model content and reasoning is logged; the full text remains absent.</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>Each rejection is attributable to one attempt and specific failure class.
 Raw output is absent by default and bounded on explicit opt-in.</t>
         </is>
       </c>
-      <c r="O21" s="5" t="inlineStr">
+      <c r="O22" s="5" t="inlineStr">
         <is>
           <t>No model output or user prompt enters SSE or persisted history from diagnostics.
 No secret or full raw payload is logged by default.
 No retry-budget or execution behavior changes.</t>
         </is>
       </c>
-      <c r="P21" s="5" t="inlineStr">
+      <c r="P22" s="5" t="inlineStr">
         <is>
           <t>{"assertions":["Reasoning-only budget exhaustion flag is accurate.","Logs include attempt and token counts.","Default logs omit raw content.","Opt-in previews are escaped and capped."],"inputs":["finish_reason=length","reasoning_content","invalid code Action","explicit diagnostic flag"],"unit_boundary":"OpenAI model response diagnostics and CoreAgent protocol-error logging"}</t>
         </is>
       </c>
-      <c r="Q21" s="5" t="inlineStr"/>
-      <c r="R21" s="5" t="inlineStr">
+      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr">
         <is>
           <t>implemented</t>
         </is>
       </c>
-      <c r="S21" s="5" t="inlineStr">
+      <c r="S22" s="5" t="inlineStr">
         <is>
           <t>pytest</t>
         </is>
       </c>
-      <c r="T21" s="5" t="inlineStr">
+      <c r="T22" s="5" t="inlineStr">
         <is>
           <t>test/automation/d1/test_protocol_rejection_diagnostics.py</t>
         </is>
       </c>
-      <c r="U21" s="5" t="inlineStr">
+      <c r="U22" s="5" t="inlineStr">
         <is>
           <t>test_cmsr_d1_004</t>
         </is>
       </c>
-      <c r="V21" s="5" t="inlineStr">
+      <c r="V22" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W21" s="5" t="inlineStr"/>
-      <c r="X21" s="5" t="inlineStr"/>
-      <c r="Y21" s="5" t="inlineStr">
+      <c r="W22" s="5" t="inlineStr"/>
+      <c r="X22" s="5" t="inlineStr"/>
+      <c r="Y22" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z21" s="5" t="inlineStr">
+      <c r="Z22" s="5" t="inlineStr">
         <is>
           <t>sha256:9f06a6565fff8e542fdcb89725b5fc7f669ad52b07301bdc99aa3e2eba23552c</t>
         </is>
       </c>
-      <c r="AA21" s="5" t="inlineStr">
+      <c r="AA22" s="5" t="inlineStr">
         <is>
           <t>sha256:a53056127d5f2efce4a9d98c92c9c97892451de0d1d353603584612c0a9ef1ba</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA21"/>
+  <autoFilter ref="A1:AA22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5407,15 +5544,18 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>1. Open the writable knowledge base and upload a document. =&gt; The document appears and its processing status reaches a terminal state through polling.
-2. Download the processed document. =&gt; The browser receives the original file with its name.
-3. Delete the document and confirm the dialog. =&gt; The document disappears from the list and the deletion reports its own result.
-4. Open the read-only knowledge base and attempt the same operations. =&gt; Upload and delete are unavailable while browsing and download remain permitted.</t>
+          <t>1. Open the writable knowledge base and choose Import files. =&gt; A 764px right-side drawer opens with the click-or-drop area, supported-format notes, a scrollable file list and fixed Cancel/Confirm actions.
+2. Select or drop a supported document, wait for the upload response and then activate Confirm. =&gt; Selection starts upload immediately; transfer completion shows waiting until AIDP responds. Accepted rows become solid near-black and remain visible; Confirm closes without uploading again.
+3. Wait for the accepted document's processing status to reach a terminal state. =&gt; The document appears and its processing status reaches a terminal state through polling.
+4. Download the processed document. =&gt; The browser receives the original file with its name.
+5. Delete the document and confirm the dialog. =&gt; The document disappears from the list and the deletion reports its own result.
+6. Open the read-only knowledge base and attempt the same operations. =&gt; Upload and delete are unavailable while browsing and download remain permitted.</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
           <t>Upload reaches a terminal processing state.
+The import drawer keeps completed and failed rows visible, with independent scrolling and fixed Confirm action; it exposes no retry action.
 The downloaded file matches the uploaded original.
 Deletion removes the document after confirmation.
 Permission gates match the documented read and edit rules.</t>
@@ -5430,7 +5570,7 @@
       </c>
       <c r="P4" s="5" t="inlineStr">
         <is>
-          <t>{"actor":"Authenticated test tenant user","failure_evidence":["Retain browser screenshot, network log, downloaded file metadata and console trace on failure."],"final_business_result":["A user with edit permission can add, retrieve and remove documents while a read-only user can only browse and download them."],"journey":["Open a writable knowledge base file view.","Upload and wait for processing to finish.","Download the document.","Delete the document with confirmation.","Check the same controls on a read-only base."]}</t>
+          <t>{"actor":"Authenticated test tenant user","failure_evidence":["Retain browser screenshot, network log, downloaded file metadata and console trace on failure."],"final_business_result":["A user with edit permission can add, retrieve and remove documents while a read-only user can only browse and download them."],"journey":["Open a writable knowledge base file view and its import drawer.","Select a supported document, observe its automatic upload, confirm the drawer and wait for processing to finish.","Download the document.","Delete the document with confirmation.","Check the same controls on a read-only base."]}</t>
         </is>
       </c>
       <c r="Q4" s="5" t="inlineStr">

--- a/test/generated/Nexent_测试基线.xlsx
+++ b/test/generated/Nexent_测试基线.xlsx
@@ -2164,43 +2164,43 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Verify graph configuration serialization, the inverse thinking mapping, the independent Top K values and the prompt byte limit.</t>
+          <t>Verify live graph configuration serialization, the inverse Chinese thinking mapping, absence of graph Top K and the 1 to 4096 character prompt limit.</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>Prepare graph payloads with the switch on and off, both languages and prompt lengths around the byte limit.</t>
+          <t>Prepare graph payloads with the switch on and off, both languages and Unicode prompt lengths around the character limit.</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>{"domains":["general","medical"],"languages":["chinese","english"],"profile":"mock","prompt_bytes":[2048,2049]}</t>
+          <t>{"domains":["常规","医疗","法律法规"],"languages":["中文","英文"],"profile":"mock","prompt_characters":[0,1,4096,4097]}</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>1. Submit a graph configuration with the thinking switch enabled. =&gt; The thinking mode field is false and the graph keys use their documented names.
-2. Submit a knowledge base Top K together with a graph Top K. =&gt; The two values are serialized independently without overwriting each other.
-3. Submit prompts at and beyond the byte boundary together with a disabled graph. =&gt; The limit passes at the boundary, longer input is rejected and a disabled graph omits its configuration entirely.</t>
+          <t>1. Submit a graph configuration with the thinking switch enabled. =&gt; The no_think_mode field is the Chinese string 否 and only the seven template keys plus llm_model_name are forwarded.
+2. Submit a knowledge base Top K with an obsolete graph Top K key. =&gt; The outer topk is preserved and the obsolete graph key is not forwarded.
+3. Submit prompts at and beyond the character boundary together with a disabled graph. =&gt; The limit passes at the boundary, longer input is rejected and a disabled graph omits its configuration entirely.</t>
         </is>
       </c>
       <c r="N13" s="5" t="inlineStr">
         <is>
           <t>The thinking switch maps inversely onto the thinking mode field.
-Both Top K values survive independently.
-The prompt limit is enforced in UTF-8 bytes.</t>
+Only the outer knowledge-base topk is submitted.
+The prompt limit is enforced as 1 to 4096 Unicode characters.</t>
         </is>
       </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
           <t>No hidden previous graph configuration is submitted when the graph is off.
-No graph Top K overwrites the knowledge base Top K.
+No graph Top K key reaches AIDP.
 No invented JSON key names.</t>
         </is>
       </c>
       <c r="P13" s="5" t="inlineStr">
         <is>
-          <t>{"assertions":["The thinking mode field is false when thinking is enabled.","Graph and knowledge base Top K stay independent.","Prompt length is measured in UTF-8 bytes.","Disabled graph omits its configuration."],"inputs":["graph switch","domain","graph top k","hop count","thinking switch","prompt language","prompt text"],"unit_boundary":"Graph configuration validation and serialization"}</t>
+          <t>{"assertions":["The thinking mode field is 否 when thinking is enabled.","Only outer knowledge-base topk survives.","Prompt length is measured in Unicode characters.","Disabled graph omits its configuration."],"inputs":["graph switch","domain","obsolete graph top k","hop count","thinking switch","prompt language","prompt text"],"unit_boundary":"Graph configuration validation and serialization"}</t>
         </is>
       </c>
       <c r="Q13" s="5" t="inlineStr"/>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Graph and multimodal models are queried from separate categories with independent caches</t>
+          <t>One model query populates three categories and graph templates preserve edited prompts</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -2271,12 +2271,12 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Verify the model category split, the independent query caches and the omission of hidden model values.</t>
+          <t>Verify one model query, category separation by model_type, label and identifier mapping, hidden value omission and graph template interaction.</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>Render the creation form with stubbed model queries per category and both capability switches toggled.</t>
+          <t>Render the creation form with one model response, graph templates in both languages and both capability switches toggled.</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -2286,49 +2286,76 @@
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>1. Enable the graph section. =&gt; The graph model query uses the llm category and fills the graph model field.
-2. Enable multimodal captioning. =&gt; The multimodal model query uses the vlm category and fills the multimodal field independently.
+          <t>1. Enable the graph section. =&gt; One all-category query fills separate embedding, llm and vlm controls by model_type; graph activation reads the template endpoint.
+2. Enable multimodal captioning. =&gt; The multimodal field uses the vlm entries from the existing model result without another request.
 3. Disable each capability after a selection. =&gt; The hidden model value is absent from the submitted payload.</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
-          <t>Each model field is populated from its own category.
-Caches and selections never mix.
+          <t>Each field is populated from its model_type, displays display_name and submits model_name.
+A shared model cache never mixes category selections. Domain and language changes preserve manual prompts, and restore uses the current template. Template failures block graph-enabled creation.
 Disabled capabilities submit no model value.</t>
         </is>
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
-          <t>No llm result used for the multimodal field.
+          <t>No llm result used for the multimodal or embedding field.
 No hidden previous model resubmitted.
 No unverified model name silently defaulted.</t>
         </is>
       </c>
       <c r="P14" s="5" t="inlineStr">
         <is>
-          <t>{"assertions":["Graph query uses llm and multimodal uses vlm.","Caches are keyed independently.","Disabled capability clears its submitted model."],"inputs":["graph switch","multimodal switch","selected models","query cache keys"],"unit_boundary":"Creation form model queries, caches and hidden value handling"}</t>
+          <t>{"assertions":["One query returns all categories and controls filter by model_type.","Model data uses one shared query cache; templates are cached by language.","Disabled capability clears its submitted model."],"inputs":["graph switch","multimodal switch","selected models","query cache keys"],"unit_boundary":"Creation form model queries, caches and hidden value handling"}</t>
         </is>
       </c>
       <c r="Q14" s="5" t="inlineStr"/>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>unbound</t>
-        </is>
-      </c>
-      <c r="S14" s="5" t="inlineStr"/>
-      <c r="T14" s="5" t="inlineStr"/>
-      <c r="U14" s="5" t="inlineStr"/>
-      <c r="V14" s="5" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>vitest
+vitest</t>
+        </is>
+      </c>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/AidpCreateKbPage.test.tsx
+test/automation/d1/AidpCreateKbSections.test.tsx</t>
+        </is>
+      </c>
+      <c r="U14" s="5" t="inlineStr">
+        <is>
+          <t>AKPR-D1-011
+AKPR-D1-011</t>
+        </is>
+      </c>
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
       <c r="W14" s="5" t="inlineStr"/>
       <c r="X14" s="5" t="inlineStr"/>
       <c r="Y14" s="5" t="inlineStr">
         <is>
-          <t>未绑定</t>
-        </is>
-      </c>
-      <c r="Z14" s="5" t="inlineStr"/>
-      <c r="AA14" s="5" t="inlineStr"/>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z14" s="5" t="inlineStr">
+        <is>
+          <t>sha256:f2872957a3d2f7e49abdaf84e15a0bb4b0ac6bc46b8d5116ac7c58ced7988633</t>
+        </is>
+      </c>
+      <c r="AA14" s="5" t="inlineStr">
+        <is>
+          <t>sha256:0074537ecfe51f517f3d749371770d0d8b5e1f7a3b96bef2a13e16f63fc18cbd</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -2775,7 +2802,7 @@
       <c r="X18" s="5" t="inlineStr"/>
       <c r="Y18" s="5" t="inlineStr">
         <is>
-          <t>校验通过</t>
+          <t>实现哈希失效</t>
         </is>
       </c>
       <c r="Z18" s="5" t="inlineStr">
@@ -3978,7 +4005,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Verify the create proxy forwards chunking, retrieval, graph, model and safety fields while preserving legacy field names and existing defaults.</t>
+          <t>Verify the create proxy forwards the verified chunking, retrieval and model fields and graph JSON string, omits obsolete graph Top K and smartsplit, and preserves existing product defaults.</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -4161,7 +4188,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Model queries select a single category per control</t>
+          <t>Model query returns all advertised types when no service filter is supplied</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -4186,12 +4213,12 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Verify the model query proxy passes one category per request and returns only models applicable to the knowledge base application.</t>
+          <t>Verify the model query proxy omits the service filter for the unified query and returns models applicable to KnowledgeBase with their types, display names and identifiers.</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>A controllable upstream model fixture serves distinct payloads per category.</t>
+          <t>A controllable upstream model fixture serves an all-category payload and optional category-filtered responses.</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
@@ -4201,28 +4228,28 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>1. Query the graph model list. =&gt; The request carries the llm category and the response exposes only llm models.
-2. Query the multimodal model list. =&gt; The request carries the vlm category and the response exposes only vlm models.
+          <t>1. Query all models without a service parameter. =&gt; The request has app=KnowledgeBase without service and exposes embedding, llm and vlm models with model_type.
+2. Query models with an explicit vlm service filter. =&gt; The request carries the vlm category and the response exposes only vlm models.
 3. Query an unsupported or failing category. =&gt; A stable error or an empty result is returned without falling back to another category.</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
-          <t>One category is requested per control.
-Responses are not reused across categories.
+          <t>One query populates all three controls.
+Controls split the returned model types without changing identifiers.
 Failures do not silently substitute another category.</t>
         </is>
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>No shared cache entry across categories.
+          <t>No model_type category mixing.
 No fabricated model identifier on failure.
 No change to existing non-AIDP model endpoints.</t>
         </is>
       </c>
       <c r="P8" s="5" t="inlineStr">
         <is>
-          <t>{"endpoint":"/aidp-mgmt/models","method":"GET","protocol":"HTTP","request_expectations":["The service parameter carries exactly one requested category.","The application parameter keeps the knowledge base scope.","No credential is returned to the browser."],"response_expectations":["Only models of the requested category are returned.","An unavailable category yields a stable error or an empty list.","Results are filtered to the knowledge base application scope."]}</t>
+          <t>{"endpoint":"/aidp-mgmt/models","method":"GET","protocol":"HTTP","request_expectations":["The service parameter is optional; omitting it retrieves all categories.","The application parameter keeps the knowledge base scope.","No credential is returned to the browser."],"response_expectations":["Model response preserves model_type, model_name and display_name for applicable models.","An unavailable category yields a stable error or an empty list.","Results are filtered to the knowledge base application scope."]}</t>
         </is>
       </c>
       <c r="Q8" s="5" t="inlineStr"/>

--- a/test/generated/Nexent_测试基线.xlsx
+++ b/test/generated/Nexent_测试基线.xlsx
@@ -16,11 +16,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_D5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_功能清单'!$A$1:$G$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_D1'!$A$1:$AA$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_功能清单'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_D1'!$A$1:$AA$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_D2'!$A$1:$AA$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_D3'!$A$1:$AA$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_D4'!$A$1:$AA$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_D4'!$A$1:$AA$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_D5'!$A$1:$AA$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -551,11 +551,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
@@ -603,25 +603,153 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>AGENT-CONFIG-LAYOUT</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>High-fidelity Agent configuration layout</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Present an existing empty Agent draft using the measured four-card editor, actionable resource entries, and a five-question addition limit while preserving existing configuration and workflow contracts.</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-RULE-001
+AGENT-CONFIG-RULE-002
+AGENT-CONFIG-RULE-003
+AGENT-CONFIG-RULE-004
+AGENT-CONFIG-RULE-005
+AGENT-CONFIG-RULE-006
+AGENT-CONFIG-RULE-007
+AGENT-CONFIG-RULE-008
+AGENT-CONFIG-RULE-009
+AGENT-CONFIG-RULE-010
+AGENT-CONFIG-RULE-011</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>D1
+D4</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>{"notes":"The2026-10-08 partial handoff is historical. Current geometry comes from the2026-10-09 inspector handoff and user authorization. The2026-10-10 selected-tools/child-Agent bug directly extends this baseline; shell geometry reuses measured knowledge rows, while descendant values are frozen screenshot-based choices rather than new inspector claims. D1 proves component contracts; D4 proves browser geometry/scroll/workflow. D2,D3,D5 are excluded with boundary reasons in the formal design; no exact font or artwork parity is claimed without matching assets.","requirement_ids":["AGENT-CONFIG-REQ-001","AGENT-CONFIG-REQ-002","AGENT-CONFIG-REQ-003"],"spec_path":"../nexent-doc/docs/Developing/agt-editor-empty-configuration-layout/proposal.md"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CREATION-GUIDE</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Agent first-creation guide</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Explain four measured configuration workflow regions after new Agent creation.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-GUIDE-RULE-001
+AGENT-GUIDE-RULE-002
+AGENT-GUIDE-RULE-003</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>D1
+D4</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>{"notes":"Same-page inspector analysis precedes code. D2/D3/D5 excluded for unchanged protocol/provider/deployment. Browser preference has no server synchronization; proprietary font glyph parity unverified.","requirement_ids":["AGENT-GUIDE-REQ-001"],"spec_path":"../nexent-doc/docs/Developing/agt-editor-first-creation-guide/proposal.md"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-DEBUG-LAYOUT</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Measured Agent debug panel</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Present draft debug below the shared editor identity row with measured welcome, single-column questions and composer while preserving chat controls.</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-DEBUG-RULE-001
+AGENT-DEBUG-RULE-002
+AGENT-DEBUG-RULE-003</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>D1
+D4</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>{"notes":"Inspector numeric values are frozen in product handoff. D2/D3/D5 excluded for unchanged protocol/provider/deployment. Font glyph parity and unexposed gradient positions are unverified.","requirement_ids":["AGENT-DEBUG-REQ-001"],"spec_path":"../nexent-doc/docs/Developing/agt-editor-debug-panel-layout/proposal.md"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
           <t>AGENT-LIST-VIEWS</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Agent list grid and table views</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Switch between the existing agent cards and a data-backed table without changing page-level content or agent operations.</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>AGENT-LIST-RULE-001
 AGENT-LIST-RULE-002
@@ -630,40 +758,40 @@
 AGENT-LIST-RULE-005</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>D1
 D4</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>{"notes":"User request and same-page WeMeeting high-fidelity reference; no Edge window inspected.","requirement_ids":["AGENT-LIST-REQ-001","AGENT-LIST-REQ-002"],"spec_path":"docs/handoffs/2026-10-08-agent-list-high-fidelity.md"}</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Silent model retry stream visibility</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Successful model attempts stream raw content while failed attempts leave no visible or persisted fragments.</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-013
 CMSR-RULE-014
@@ -673,7 +801,7 @@
 CMSR-RULE-018</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>D1
 D2
@@ -682,14 +810,14 @@
 D5</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>{"requirement_ids":["CMSR-005"],"spec_path":"nexent-doc/docs/Developing/chat-message-model-silent-retry/proposal.md"}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -700,12 +828,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -719,11 +847,11 @@
     <col width="42" customWidth="1" min="14" max="14"/>
     <col width="42" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="42" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
-    <col width="25" customWidth="1" min="21" max="21"/>
+    <col width="42" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -872,21 +1000,996 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>AGENT-CONFIG-D1-001</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-LAYOUT</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-REQ-001
+AGENT-CONFIG-REQ-002</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-RULE-001
+AGENT-CONFIG-RULE-002
+AGENT-CONFIG-RULE-003
+AGENT-CONFIG-RULE-004
+AGENT-CONFIG-RULE-005</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Regroup the empty draft into four cards without breaking section focus or action gates</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Verify four-card composition, preserved section state/focus, guardrail reachability, action validation/permission gates, and absence of writes from render/collapse using the AgentConfig component boundary.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Render AgentConfig with an initialized Agent draft and mocked existing section components.
+Control mocked save outcomes and read-only state; expose localized keys as visible text.</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>{"card_count":4,"draft":{"asset_ref":"empty_agent_draft"},"profile":"mock","resource_order":["knowledge_base","conversation_guide","skills","tools","collaborative_agents"]}</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>1. Render AgentConfig with an initialized Agent draft. =&gt; Basic, model/prompt, shared-resource, and permission/advanced cards appear in one scroll region; all existing field groups including guardrail remain reachable, resources follow the design order, outer category tabs are absent, and workflow actions remain outside that region.
+2. Collapse a collapsible resource section, then issue matching NL2Agent resource and nested prompt focus requests. =&gt; The requested section reopens and scrolls into view, nested prompt targeting remains supported, and each request clears without losing draft values.
+3. Invoke unlock, debug, and publish actions. =&gt; Unlock and debug call their existing callbacks; publish validates and awaits save before opening the existing modal.
+4. Repeat debug/publish with rejected validation, failed save, and a read-only draft. =&gt; Failed validation/save prevents downstream actions; read-only disables editing/publication, while existing allowed read-only inspection remains reachable.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Exactly four outer card groups exist in one scroll region, including all existing field groups and guardrail.
+Shared resources follow knowledge/welcome/skills/tools/child-Agent order and start expanded.
+Section collapse and NL2Agent focus preserve draft values, reopen and scroll to the exact target.
+Successful actions retain callbacks; invalid or unsaved drafts do not invoke downstream debug/publication.
+Rendering, collapsing and focusing do not request backend updates; read-only prevents mutation/publication.</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Do not omit or duplicate any existing configuration section.
+Do not invoke backend services or mutate persisted Agent data as a result of rendering or collapsing sections.
+Do not bypass save/validation/permission checks or move workflow actions into the scrolling module list.</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Exactly four outer cards group existing field components; no outer category tabs appear.","Resources are in the specified order and guardrail remains available.","Collapse/focus reopens the targeted resource without dropping state and calls scrollIntoView.","Unlock/debug callbacks and publish modal occur only after applicable successful validation/save/permission gates.","Render/collapse/focus do not persist changes."],"inputs":["initialized Agent draft","localized strings","focus request","section interactions","action callbacks","save failure","read-only state"],"unit_boundary":"AgentConfig React component rendered inside Ant Design App and Form providers, with existing section components, Agent store, route query, translations, and save guard mocked."}</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"mock","required_services":[]}]}</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>vitest
+vitest</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/agent-config-layout.test.tsx
+test/automation/d1/agent-config-prompt.test.tsx</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-D1-001
+AGENT-CONFIG-D1-001</t>
+        </is>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr"/>
+      <c r="X2" s="5" t="inlineStr"/>
+      <c r="Y2" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z2" s="5" t="inlineStr">
+        <is>
+          <t>sha256:1b1b2c4ca225df799d587e0fd3d3d8c8104d29fe6a848848a6eda91cf3a9e1b4</t>
+        </is>
+      </c>
+      <c r="AA2" s="5" t="inlineStr">
+        <is>
+          <t>sha256:ea731f17afcbdf014ef62b5400aa16c1b3dca7d2002b2304d8c1b1d8c6fbe117</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-D1-002</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-LAYOUT</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-REQ-002</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-RULE-005
+AGENT-CONFIG-RULE-007</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Limit new preset questions to five without truncating legacy drafts</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Execute the real AgentGuide component against controlled draft state to prove five-item additions, value-preserving edits/removal, and legacy six-item load compatibility.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Render the real AgentGuide inside Ant Design Form/App with a mocked Agent store update callback and translations.
+Provide separate logical drafts with zero, four, five, and six stored questions.</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>{"legacy_draft":{"asset_ref":"agent_draft_six_questions"},"question_counts":[0,4,5,6]}</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>1. Render zero questions and add one; edit its value and the greeting. =&gt; The localized counter uses maximum five and update callbacks retain the entered question/greeting values.
+2. Render four questions and add the fifth, then render the updated five-question state. =&gt; The callback appends exactly one empty question and add becomes disabled at5/5.
+3. Remove one of five questions and render the four-question result. =&gt; The correct item is removed, other values remain intact, and add re-enables.
+4. Render a legacy six-question draft without interacting. =&gt; All six question values remain rendered, add is disabled, and no update callback occurs from load.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>The effective maximum for additions and localized count/tooltip is five.
+Add is enabled below five and disabled at five or above.
+Greeting/question edits and removal retain the existing update contract and unaffected values.
+Legacy six-item drafts are not truncated or automatically saved.</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Do not discard legacy questions, make a write during render, or introduce a backend schema/API change.</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["The fifth addition appends one item and the add control disables at the boundary.","Removal from five retains the other values and permits a new addition.","Six question values render unchanged without a load-time update.","Counter translation receives maximum5 and edits preserve expected payload values."],"inputs":["zero-question draft","four-question draft","five-question draft","legacy six-question draft","edit and remove interactions"],"unit_boundary":"Real AgentGuide component with controlled Agent-store state; UI behavior is not replaced by a mocked child."}</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"mock","required_services":[]}]}</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>vitest</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/agent-config-guide.test.tsx</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-D1-002</t>
+        </is>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr"/>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr">
+        <is>
+          <t>sha256:39a5d953b19d09f70343d9924881bd86e99d9753b149df34d69f60674f48b59a</t>
+        </is>
+      </c>
+      <c r="AA3" s="5" t="inlineStr">
+        <is>
+          <t>sha256:4eb7abaf1a8199a4b3e5675079e93b771d0dc6ad9987f71f20d46c0444811b04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-D1-003</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-LAYOUT</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-REQ-002</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-RULE-001
+AGENT-CONFIG-RULE-005
+AGENT-CONFIG-RULE-008
+AGENT-CONFIG-RULE-011</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Render ordered selected tool and child-Agent rows with actionable resource entries and preserved configuration/removal</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Execute the real resource-add control, ToolManagement and CollaborativeAgent to prove empty-entry compatibility, ordered compact selected rows, real metadata, configuration/removal callbacks and read-only behavior without render-time writes.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Render the actual new or existing resource-add presentation with empty resources and explicit association/create callbacks.
+Mock existing resource services/state without replacing the add control or owning resource component.
+Render real populated ToolManagement and CollaborativeAgent in high-fidelity mode with logical catalog, saved child-version, internal/external relation and read-only fixtures; keep store/service hooks controlled.</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>{"association_count":0,"entry_height":48,"grid_gap":8,"reference_entry_width":602.5,"reference_row_width":1213,"selected_child_agents":{"asset_ref":"selected_internal_external_agents_with_saved_versions"},"selected_row":{"action_glyph_size":14,"action_target_size":24,"border_color":"#DFDFDF","child_avatar_size":32,"content_gap":8,"height":48,"horizontal_padding":12,"name_color":"#191919","name_font_size":14,"name_font_weight":400,"name_line_height":22,"radius":4,"tag_color":"#777777","tag_font_size":12,"tag_line_height":18,"tool_icon_size":24,"vertical_padding":8},"selected_tools":{"asset_ref":"selected_tools_with_managed_knowledge_tool"}}</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>1. Render the empty resource module without interacting. =&gt; A two-column row contains a first-column add entry with48px height, radius8, padding8/12 and3%
+2. Activate the add entry. =&gt; The association-selection path opens exactly once, with creation/manage callback untouched.
+3. Activate the separate new/manage action. =&gt; The creation/management path opens with association callback untouched.
+4. Repeat with a read-only resource module. =&gt; Mutation actions are disabled and do not invoke association/create callbacks.
+5. Render populated tool and child-Agent modules, including missing optional labels, a managed knowledge tool and a saved child version differing from the latest catalog version. =&gt; Visible resources keep their selection order in a two-column grid; names and real neutral tags share compact48px rows, full names and saved child versions remain available in tooltips, the add entry follows selected rows, managed knowledge tools remain hidden without removal from state, and rendering makes no mutation or relation request.
+6. Open settings on a configurable selected tool, remove one selected tool, then remove an internal and an external child Agent through their existing actions. =&gt; Tool configuration retains canonical parameters and prerequisites; tool removal preserves other tools including managed knowledge tools; internal removal updates matching ID/relation entries without changing other snapshots; external removal uses the existing relation-service callback and only updates selection on its successful result.
+7. Render populated read-only and default-mode modules and attempt disabled selected-row actions. =&gt; Read-only tool settings/removal and child removal do not mutate state; default mode retains its grouped tool and internal/external child presentation, and missing optional catalog labels produce no invented tag values.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Add remains in the left column and does not become a full-width dashed placeholder.
+Measured48px height,8px gap/radius and3% background are represented by the actual control.
+Association and creation callbacks are separate and permission gated.
+Real selected tool and child-Agent rows use the frozen common shell, names/tags, icon/avatar sizes and always-visible24px action targets, followed by the add entry.
+Real labels, full names and saved child versions remain available without invented screenshot data; managed knowledge tools stay in state but are not displayed.
+Configuration and internal/external removals retain existing callbacks, unaffected selections and read-only gates; default presentation remains compatible.</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>Do not persist a resource, duplicate associations, or call a creation API merely by rendering or opening selection.
+Do not remove managed knowledge tools, overwrite retained child versions, fabricate optional metadata, or restyle knowledge rows/association drawers.</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Two-column layout and first-column add entry retain measured styling.","Add and create interactions each call only their own workflow.","Render and disabled controls issue no mutation callback.","Selected rows represent the frozen shell/name/tag/icon/action contract and preserve selected order with the add entry last.","Settings opens the actual existing tool configuration path; removals change only intended selections/relations and preserve managed knowledge tools and other snapshots.","Read-only prevents selected-row mutations; missing optional metadata stays absent; saved-version/full-name tooltips and default presentation remain available."],"inputs":["empty resources","association callback","creation callback","read-only state","ordered populated tool and child-Agent selections","managed knowledge tool","canonical tool parameters and missing optional labels","saved child version and internal/external removal results","default presentation mode"],"unit_boundary":"Actual resource-add control, ToolManagement and CollaborativeAgent rendered with Ant Design providers and existing query/store/service hooks controlled; selected-row components and actions are not replaced by mocks."}</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"mock","required_services":[]}]}</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>vitest
+vitest
+vitest</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/agent-config-resources.test.tsx
+test/automation/d1/agent-config-selected-tools.test.tsx
+test/automation/d1/agent-config-selected-child-agents.test.tsx</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-D1-003
+AGENT-CONFIG-D1-003
+AGENT-CONFIG-D1-003</t>
+        </is>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr"/>
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z4" s="5" t="inlineStr">
+        <is>
+          <t>sha256:402c8dfd7414a39feca412292b5eb1208615c0ff7c20bb1ac19bea4518e02ff9</t>
+        </is>
+      </c>
+      <c r="AA4" s="5" t="inlineStr">
+        <is>
+          <t>sha256:3f76518606adc1486ff89c288c6cc27973bef01d7f4cbb2b0e8b6f9d50a7a53a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-D1-004</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-LAYOUT</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-REQ-002</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-RULE-005
+AGENT-CONFIG-RULE-009</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Enforce measured text-entry limits without truncating stored drafts</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Exercise real AgentInfo, AgentGuide, and AgentPrompt inputs to verify measured high-fidelity limits, exact boundary entry, preserved legacy overlong values, and default-mode compatibility.</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Render real field components with Ant Design providers and controlled Agent-store callbacks.
+Provide separate empty, exact-boundary, and overlong legacy values without replacing the inputs with mocks.</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>{"description_limit":200,"duty_limit":1000,"greeting_limit":200,"legacy_description_length":201,"legacy_duty_length":1001,"legacy_greeting_length":201}</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>1. Render high-fidelity inputs and enter exactly 200 description/greeting characters and 1000 duty characters. =&gt; Entry limits expose the measured boundaries and existing callbacks retain complete boundary values.
+2. Render legacy overlong stored values without interaction, then shorten them below their measured limits. =&gt; Complete stored values remain visible without a load-time update; shortening produces the exact reduced value through the existing callback.
+3. Render default component mode with its preexisting field limits. =&gt; Default limits and legacy editing behavior remain compatible; the new high-fidelity limit is not applied globally.</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>High-fidelity description and greeting entry use a 200-character limit; duty uses 1000.
+Exact boundary values remain complete, and legacy overlong values are never sliced or silently persisted on load.
+Shortening stored overlong content remains possible and preserves expected callback payloads.
+Default-mode field constraints remain unchanged.</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>Do not truncate persisted content, write on render, or change backend request/response contracts.</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Actual input limits match 200, 200, and 1000 in high-fidelity mode.","Callback values preserve the full exact-boundary or shortened text.","Legacy values render intact without automatic callbacks.","Default-mode limits match the existing component contract."],"inputs":["empty values","boundary text","overlong legacy values","shortened text","default component mode"],"unit_boundary":"Real AgentInfo, AgentGuide, and AgentPrompt controls with store/query/resource dependencies controlled at their existing hook boundaries."}</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"mock","required_services":[]}]}</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>vitest
+vitest
+vitest</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/agent-config-info.test.tsx
+test/automation/d1/agent-config-guide.test.tsx
+test/automation/d1/agent-config-prompt.test.tsx</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-D1-004
+AGENT-CONFIG-D1-004
+AGENT-CONFIG-D1-004</t>
+        </is>
+      </c>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr"/>
+      <c r="X5" s="5" t="inlineStr"/>
+      <c r="Y5" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z5" s="5" t="inlineStr">
+        <is>
+          <t>sha256:5f33024788d9fdd9d967a2964c21b46f11e124a70f694e2afa90ec680e795aa4</t>
+        </is>
+      </c>
+      <c r="AA5" s="5" t="inlineStr">
+        <is>
+          <t>sha256:7e2095b8a8c40bf6eda6b16139471fe337fedecbb0d4cc3824f9eaf86f2cdd13</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-D1-005</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-LAYOUT</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-REQ-003</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-RULE-010</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Reuse the resource drawer and preserve controlled model membership and order</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Verify actual common drawer controls, scroll/mask, controlled model add/remove and no render-time selection callback.</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Render real AddResourceDrawer and AddModelDrawer with existing model query controlled at its hook boundary.</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>{"model_ids":[2,1],"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>1. Open shared drawer and inspect right placement,mask,header and close/confirm controls. =&gt; Existing shared drawer design renders; close and confirm invoke only their supplied callbacks.
+2. Render model drawer with ordered configured IDs, remove a configured model and select a new model. =&gt; Callbacks retain remaining order and append new IDs without replacing priority or mutating on render.</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>Shared right drawer is reused with original close/confirm callbacks.
+Controlled model add/remove preserves order and no callback occurs on render.
+Standalone drawer defaults remain compatible.</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>Do not save on render/open/close or discard retained model IDs/overrides.</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Right masked drawer and scroll region render.","Model callbacks preserve remaining IDs and append newly selected ID.","Rendering does not change selection."],"inputs":["ordered model IDs","catalog","close/confirm interactions"],"unit_boundary":"Real shared drawer and model selector components with model query mocked."}</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"mock","required_services":[]}]}</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>vitest</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/agent-config-drawers.test.tsx</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-D1-005</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z6" s="5" t="inlineStr">
+        <is>
+          <t>sha256:24f0b216ba67e0b9afc79033ba7c9a5d9ef8e4e816372d7826ec2ce091d460ce</t>
+        </is>
+      </c>
+      <c r="AA6" s="5" t="inlineStr">
+        <is>
+          <t>sha256:e21f3380f462f54d1161a964b9ad41a485e43eda860cd66a055c6027889cda87</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-DEBUG-D1-001</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-DEBUG-LAYOUT</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-DEBUG-REQ-001</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-DEBUG-RULE-002
+AGENT-DEBUG-RULE-003</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Draft welcome and preset selection preserve data and only fill composer</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Verify real debug welcome/questions with changing draft values, empty values and legacy arrays without request or configuration writes.</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Render real welcome and suggestions with a controlled composer callback and logical draft data.</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>{"draft":{"asset_ref":"debug_agent_draft"},"profile":"mock","question_count":6}</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>1. Render name and greeting plus six stored questions. =&gt; Draft name/greeting and all six questions appear without truncation or source mutation.
+2. Select one question, then rerender with changed name/greeting and no questions. =&gt; Exact text is supplied once to the composer callback only; changed draft values replace prior text and empty questions omit the suggestion section.</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>Dynamic values render exactly; selection calls composer only; empty and legacy values are preserved.</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>No HTTP/provider invocation
+no Agent update or automatic question send.</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["All six stored questions render; callback receives selected text once; no source data mutation; empty section omitted; rerender updates draft text."],"inputs":["draft name","greeting","six questions","changed values","empty questions","selection callback"],"unit_boundary":"Real debug welcome and suggestion React components with controlled selection callback"}</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"mock","required_services":[]}]}</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="inlineStr">
+        <is>
+          <t>vitest</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/agent-debug-layout.test.tsx</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-DEBUG-D1-001</t>
+        </is>
+      </c>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr"/>
+      <c r="X7" s="5" t="inlineStr"/>
+      <c r="Y7" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z7" s="5" t="inlineStr">
+        <is>
+          <t>sha256:fcc7927d11dea62a1dca00601a71032de78c6c3e21b4892668141efe56716e55</t>
+        </is>
+      </c>
+      <c r="AA7" s="5" t="inlineStr">
+        <is>
+          <t>sha256:8ad5aeaa20600915a969d2c6f9fdf9c8a2415d87618086a9ddff3aad2115208c</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-GUIDE-D1-001</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CREATION-GUIDE</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-GUIDE-REQ-001</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-GUIDE-RULE-002
+AGENT-GUIDE-RULE-003</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Guide eligibility and completion remain scoped explanatory state</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>FE-COMP</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Prove creation-only eligibility, identity isolation, denied-storage fallback and navigation/dismissal without business effects.</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Render real guide with controlled identity/draft readiness and deterministic Tour boundary; use isolated browser storage.</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>{"draft":{"asset_ref":"newly_created_agent"},"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>1. Render creation entry and change loading/read-only/identity/completed conditions. =&gt; Only ready editable uncompleted creation context opens; ordinary entry, missing identity and completed identity remain closed.
+2. Navigate all steps, finish and skip, then change tenant/user and deny storage access. =&gt; Ordered targets and labels remain correct; completion is scoped; denied storage permits dismissal and suppresses same-session replay.</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>Creation-only eligibility; per-user/tenant isolation; working navigation and dismissal with storage failure.</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>No Agent update
+debug action
+publication or provider request caused by guide.</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Ready creation opens only once; stale/loading/read-only excluded; previous/next bounded; skip and finish recorded; other identities unaffected; storage failure contained; no business callbacks."],"inputs":["entry flag","identity","draft readiness","permission","completion state","denied storage","navigation callbacks"],"unit_boundary":"Real guide component and local preference functions with controlled Tour and editor anchors"}</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"mock","required_services":[]}]}</t>
+        </is>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>vitest</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/agent-creation-guide.test.tsx</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-GUIDE-D1-001</t>
+        </is>
+      </c>
+      <c r="V8" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W8" s="5" t="inlineStr"/>
+      <c r="X8" s="5" t="inlineStr"/>
+      <c r="Y8" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z8" s="5" t="inlineStr">
+        <is>
+          <t>sha256:9bed58aed86f9578a3896b70744479064c37aeac79986c31c271160363c86fa0</t>
+        </is>
+      </c>
+      <c r="AA8" s="5" t="inlineStr">
+        <is>
+          <t>sha256:bd0d36fa1d6ac309b24cb9a36355fdae5aaffe2307d5d4d7fd0d8a91e61d3e43</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
           <t>AGENT-LIST-D1-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>AGENT-LIST-VIEWS</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>AGENT-LIST-REQ-001
 AGENT-LIST-REQ-002</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>AGENT-LIST-RULE-001
 AGENT-LIST-RULE-002
@@ -895,55 +1998,55 @@
 AGENT-LIST-RULE-005</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Render table view with data-backed agent metadata</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>FE-COMP</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Verify Ant Design table rendering, including header separators and content-based sizing constraints, plus columns, row data, update-time source, and action callbacks without changing the card view contract.</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>Render the table with agents containing author, tags, status, and update_time values.
 Render a second agent without update_time but with create_time.</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>{"no_update_agent":{"author":null,"create_time":"2026-09-17T10:30:00","update_time":null},"profile":"mock","updated_agent":{"author":"刘晨","tags":["保健"],"update_time":"2026-09-18T10:30:00"}}</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>1. Render the table with the mocked agent rows. =&gt; The seven columns appear in the specified order in StandardTable backed by Ant Design Table; internal header columns have 1px
 2. Render a row whose update_time is absent and whose create_time is present. =&gt; The update-time cell shows the missing-value placeholder rather than the creation date.
 3. Trigger the row's detail, configure, and publish actions. =&gt; Each callback receives the corresponding agent or numeric agent ID.</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>The table labels include 更新时间 and do not label agents as knowledge bases.
 The table is rendered through StandardTable with the documented typography, backgrounds, 40px rows,
@@ -953,261 +2056,261 @@
 The card component and its data behavior remain unchanged.</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>Do not modify page title, guide area, tabs, or card-mode content.
 Do not add or change backend requests or response contracts.
 Do not fabricate creator or update-time values.</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="P9" s="5" t="inlineStr">
         <is>
           <t>{"assertions":["Table headers render in the required order.","Update time never falls back to create_time.","Missing creator and timestamp values render placeholders.","Action callbacks receive the correct row data.","Header separators are 14px high, vertically centered, and","The scroll wrapper is content-sized with a 500px maximum rather than flex-growing to fill unused space."],"inputs":["agent rows","locale strings","row-action callbacks"],"unit_boundary":"AgentListTable React component with mocked callbacks and translation."}</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr"/>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr">
         <is>
           <t>implemented</t>
         </is>
       </c>
-      <c r="S2" s="5" t="inlineStr">
+      <c r="S9" s="5" t="inlineStr">
         <is>
           <t>custom</t>
         </is>
       </c>
-      <c r="T2" s="5" t="inlineStr">
+      <c r="T9" s="5" t="inlineStr">
         <is>
           <t>test/automation/d1/run_agent_list_table_test.mjs</t>
         </is>
       </c>
-      <c r="U2" s="5" t="inlineStr">
+      <c r="U9" s="5" t="inlineStr">
         <is>
           <t>agentListTable.test.tsx</t>
         </is>
       </c>
-      <c r="V2" s="5" t="inlineStr">
+      <c r="V9" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W2" s="5" t="inlineStr"/>
-      <c r="X2" s="5" t="inlineStr"/>
-      <c r="Y2" s="5" t="inlineStr">
+      <c r="W9" s="5" t="inlineStr"/>
+      <c r="X9" s="5" t="inlineStr"/>
+      <c r="Y9" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z2" s="5" t="inlineStr">
+      <c r="Z9" s="5" t="inlineStr">
         <is>
           <t>sha256:42084a90cedb1ae8ffba7cbe7cf1411f12a57a0d42205e6580e12ad08042aeb9</t>
         </is>
       </c>
-      <c r="AA2" s="5" t="inlineStr">
+      <c r="AA9" s="5" t="inlineStr">
         <is>
           <t>sha256:6dd34b7871a706a8b5fc3aa75f7a0dce8d785c1dbc328369e21a9b47cebef59e</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>CMSR-D1-001</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-013
 CMSR-RULE-014</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Observer emits safe content before stream completion</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>SDK-UT</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Verify bounded marker lookahead and attempt state reset.</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>Create an isolated observer and a controlled chunk sequence.</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","sequence":"failed partial, rollback, successful split code and think markers"}</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="M10" s="5" t="inlineStr">
         <is>
           <t>1. Feed a safe prefix and pause the source. =&gt; The prefix is emitted before flush or commit.
 2. Roll back the first attempt and feed split markers in the second. =&gt; The second output is ordered and contains no first-attempt residue.</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>The earliest safe content is observable before completion.
 Split markers retain their original semantics.</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="O10" s="5" t="inlineStr">
         <is>
           <t>No stale fragment crosses attempts.
 No code is executed by the observer.</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="P10" s="5" t="inlineStr">
         <is>
           <t>{"assertions":["Safe prefix emitted before flush.","Raw code tag retained.","No failed-attempt residue."],"inputs":["normal content","split &lt;think&gt; and &lt;/think&gt;","raw &lt;code&gt; content"],"unit_boundary":"Observer.add_model_new_token and attempt lifecycle"}</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr"/>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr">
         <is>
           <t>implemented</t>
         </is>
       </c>
-      <c r="S3" s="5" t="inlineStr">
+      <c r="S10" s="5" t="inlineStr">
         <is>
           <t>pytest</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr">
+      <c r="T10" s="5" t="inlineStr">
         <is>
           <t>test/automation/d1/test_model_attempt_stream.py</t>
         </is>
       </c>
-      <c r="U3" s="5" t="inlineStr">
+      <c r="U10" s="5" t="inlineStr">
         <is>
           <t>test_cmsr_d1_001</t>
         </is>
       </c>
-      <c r="V3" s="5" t="inlineStr">
+      <c r="V10" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W3" s="5" t="inlineStr"/>
-      <c r="X3" s="5" t="inlineStr"/>
-      <c r="Y3" s="5" t="inlineStr">
+      <c r="W10" s="5" t="inlineStr"/>
+      <c r="X10" s="5" t="inlineStr"/>
+      <c r="Y10" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z3" s="5" t="inlineStr">
+      <c r="Z10" s="5" t="inlineStr">
         <is>
           <t>sha256:625e8c8829b51b9cd91344555d05c5ebfdc7bd766d8485eab99b9f22773f3233</t>
         </is>
       </c>
-      <c r="AA3" s="5" t="inlineStr">
+      <c r="AA10" s="5" t="inlineStr">
         <is>
           <t>sha256:242f1aaf8a5fe4427f503e5acb8db2cc6cb5096782c2e4fdf49fcb17ec471420</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>CMSR-D1-002</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-014
 CMSR-RULE-015</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Running step labels precede reasoning and survive retry rollback</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>FE-COMP</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Verify immediate running labels, rollback preservation, legacy history and removal of terminal label-only cards.</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>Create the streaming adapter with a controlled SSE fixture.</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","sequences":["step 1, failed attempt, rollback, successful raw code, parse","legacy content before step label"]}</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>1. Emit a step label before any model content. =&gt; A running reasoning card displays Step 1 immediately.
 2. Roll back a partial attempt and stream successful raw code. =&gt; Step 1 remains during rollback and only successful raw code follows it.
 3. Parse and reload both new and legacy-order history. =&gt; One code card and one labeled nonempty reasoning card remain; a terminal label-only card is absent.</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>Step label appears before first token.
 Rollback preserves the label.
@@ -1215,326 +2318,326 @@
 Old history prepends late labels.</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="O11" s="5" t="inlineStr">
         <is>
           <t>No failed-attempt content.
 No duplicate code card.
 No sibling invocation mutation.</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P11" s="5" t="inlineStr">
         <is>
           <t>{"assertions":["Running label is visible before content.","Terminal label-only step is hidden.","Successful code is visible after the label before commit.","History equals live output."],"inputs":["step_count","model_attempt_control","model_output_thinking","parse"],"unit_boundary":"Frontend live and history reasoning projection"}</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr">
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr">
         <is>
           <t>implemented</t>
         </is>
       </c>
-      <c r="S4" s="5" t="inlineStr">
+      <c r="S11" s="5" t="inlineStr">
         <is>
           <t>custom</t>
         </is>
       </c>
-      <c r="T4" s="5" t="inlineStr">
+      <c r="T11" s="5" t="inlineStr">
         <is>
           <t>test/automation/d1/test_reasoning_card.ts</t>
         </is>
       </c>
-      <c r="U4" s="5" t="inlineStr">
+      <c r="U11" s="5" t="inlineStr">
         <is>
           <t>CMSR-D1-002</t>
         </is>
       </c>
-      <c r="V4" s="5" t="inlineStr">
+      <c r="V11" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W4" s="5" t="inlineStr"/>
-      <c r="X4" s="5" t="inlineStr"/>
-      <c r="Y4" s="5" t="inlineStr">
+      <c r="W11" s="5" t="inlineStr"/>
+      <c r="X11" s="5" t="inlineStr"/>
+      <c r="Y11" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z4" s="5" t="inlineStr">
+      <c r="Z11" s="5" t="inlineStr">
         <is>
           <t>sha256:b614502639e969ab0f3840d1381f1b12b01cb5b693a0b02d17387192b230b354</t>
         </is>
       </c>
-      <c r="AA4" s="5" t="inlineStr">
+      <c r="AA11" s="5" t="inlineStr">
         <is>
           <t>sha256:03f5fae5200c76ca296c75ab0ebf225f190fb3fe6a7f52c7c8c7e0da2a97d07c</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>CMSR-D1-003</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-014
 CMSR-RULE-016</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>CoreAgent commits streamed valid semantic repair</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>SDK-UT</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>A protocol-invalid first attempt rolls back while its single preceding step label survives and the corrected result streams and commits.</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>A controlled model yields an invalid response then a pausable valid code action at step one.</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","sequence":"invalid code, rollback, corrected code chunks, commit, parse"}</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>1. Begin step one and return protocol-invalid model content. =&gt; Exactly one step label precedes begin; the attempt rolls back and one repair is scheduled.
 2. Pause the valid repair after its first safe chunk. =&gt; That chunk is visible before model completion.
 3. Complete the repair and classify it. =&gt; Its attempt commits and a single parse follows.</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>Corrected content is streamed and committed.
 Only the corrected action is executed.
 Lifecycle logs identify the repair without content.</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="O12" s="5" t="inlineStr">
         <is>
           <t>No failed content after rollback.
 No repair instruction in user output.
 No suppressed successful stream.</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="P12" s="5" t="inlineStr">
         <is>
           <t>{"assertions":["Step label occurs before both model attempts and only once.","Successful repair does not set stream suppression.","Corrected attempt commits once.","Invalid attempt rolls back once."],"inputs":["step one","invalid model content","valid streamed &lt;code&gt; action"],"unit_boundary":"CoreAgent semantic repair and deferred model attempt lifecycle"}</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="inlineStr"/>
-      <c r="R5" s="5" t="inlineStr">
+      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="R12" s="5" t="inlineStr">
         <is>
           <t>implemented</t>
         </is>
       </c>
-      <c r="S5" s="5" t="inlineStr">
+      <c r="S12" s="5" t="inlineStr">
         <is>
           <t>pytest</t>
         </is>
       </c>
-      <c r="T5" s="5" t="inlineStr">
+      <c r="T12" s="5" t="inlineStr">
         <is>
           <t>test/automation/d1/test_semantic_repair_stream.py</t>
         </is>
       </c>
-      <c r="U5" s="5" t="inlineStr">
+      <c r="U12" s="5" t="inlineStr">
         <is>
           <t>test_cmsr_d1_003</t>
         </is>
       </c>
-      <c r="V5" s="5" t="inlineStr">
+      <c r="V12" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W5" s="5" t="inlineStr"/>
-      <c r="X5" s="5" t="inlineStr"/>
-      <c r="Y5" s="5" t="inlineStr">
+      <c r="W12" s="5" t="inlineStr"/>
+      <c r="X12" s="5" t="inlineStr"/>
+      <c r="Y12" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z5" s="5" t="inlineStr">
+      <c r="Z12" s="5" t="inlineStr">
         <is>
           <t>sha256:7ef8664f2224d068d7deafecf80f09353d734bc10b35a1147b3cc58d1ae6eacd</t>
         </is>
       </c>
-      <c r="AA5" s="5" t="inlineStr">
+      <c r="AA12" s="5" t="inlineStr">
         <is>
           <t>sha256:1dee7e7ce90f70c40d02907f11be7b55665495fdcaa3dfdec3ab478953c5c38c</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>CMSR-D1-004</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-018</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Rejected model output diagnostics distinguish budget exhaustion without default content leakage</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>SDK-UT</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Correlate each protocol rejection to the model response shape and budget while gating bounded raw previews.</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>Use isolated model diagnostics for a reasoning-only length response and a malformed nonempty response.</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","responses":["length with 4096 reasoning-only output tokens","malformed nonempty code Action"]}</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>1. Reject a reasoning-only length response with diagnostics disabled. =&gt; The log records model, attempt, requested and consumed tokens, reasoning and content counts, and reasoning-only budget exhaustion without raw text.
 2. Reject a malformed content response. =&gt; The distinct protocol reason and response shape are logged under its own attempt identifier.
 3. Enable diagnostic content preview for a rejected response longer than the preview cap. =&gt; Only a single escaped bounded prefix of model content and reasoning is logged; the full text remains absent.</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>Each rejection is attributable to one attempt and specific failure class.
 Raw output is absent by default and bounded on explicit opt-in.</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="O13" s="5" t="inlineStr">
         <is>
           <t>No model output or user prompt enters SSE or persisted history from diagnostics.
 No secret or full raw payload is logged by default.
 No retry-budget or execution behavior changes.</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="P13" s="5" t="inlineStr">
         <is>
           <t>{"assertions":["Reasoning-only budget exhaustion flag is accurate.","Logs include attempt and token counts.","Default logs omit raw content.","Opt-in previews are escaped and capped."],"inputs":["finish_reason=length","reasoning_content","invalid code Action","explicit diagnostic flag"],"unit_boundary":"OpenAI model response diagnostics and CoreAgent protocol-error logging"}</t>
         </is>
       </c>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr">
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr">
         <is>
           <t>implemented</t>
         </is>
       </c>
-      <c r="S6" s="5" t="inlineStr">
+      <c r="S13" s="5" t="inlineStr">
         <is>
           <t>pytest</t>
         </is>
       </c>
-      <c r="T6" s="5" t="inlineStr">
+      <c r="T13" s="5" t="inlineStr">
         <is>
           <t>test/automation/d1/test_protocol_rejection_diagnostics.py</t>
         </is>
       </c>
-      <c r="U6" s="5" t="inlineStr">
+      <c r="U13" s="5" t="inlineStr">
         <is>
           <t>test_cmsr_d1_004</t>
         </is>
       </c>
-      <c r="V6" s="5" t="inlineStr">
+      <c r="V13" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W6" s="5" t="inlineStr"/>
-      <c r="X6" s="5" t="inlineStr"/>
-      <c r="Y6" s="5" t="inlineStr">
+      <c r="W13" s="5" t="inlineStr"/>
+      <c r="X13" s="5" t="inlineStr"/>
+      <c r="Y13" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z6" s="5" t="inlineStr">
+      <c r="Z13" s="5" t="inlineStr">
         <is>
           <t>sha256:9f06a6565fff8e542fdcb89725b5fc7f669ad52b07301bdc99aa3e2eba23552c</t>
         </is>
       </c>
-      <c r="AA6" s="5" t="inlineStr">
+      <c r="AA13" s="5" t="inlineStr">
         <is>
           <t>sha256:a53056127d5f2efce4a9d98c92c9c97892451de0d1d353603584612c0a9ef1ba</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA6"/>
+  <autoFilter ref="A1:AA13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2175,12 +3278,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -2347,21 +3450,460 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>AGENT-CONFIG-D4-001</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-LAYOUT</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-REQ-002
+AGENT-CONFIG-REQ-003</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-RULE-001
+AGENT-CONFIG-RULE-002
+AGENT-CONFIG-RULE-003
+AGENT-CONFIG-RULE-004
+AGENT-CONFIG-RULE-005
+AGENT-CONFIG-RULE-006
+AGENT-CONFIG-RULE-007
+AGENT-CONFIG-RULE-008
+AGENT-CONFIG-RULE-009
+AGENT-CONFIG-RULE-010
+AGENT-CONFIG-RULE-011</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Configure an empty draft through the measured editor without losing save or permission gates</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Prove actual desktop geometry, internal scrolling, actionable resources, question boundary, autosaved edits and validation/read-only outcomes in one deterministic browser journey.</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>A local frontend is running and all backend/provider HTTP requests are routed to deterministic logical fixtures.
+Logical fixtures expose an editable draft, an empty draft, resource/model choices, and a read-only draft; updates are captured only in fixture state.
+A populated fixture exposes selected tools plus a managed knowledge tool and selected internal/external child Agents with real catalog labels and saved version snapshots; knowledge-base rows use the current fixture presentation.</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>{"constrained_viewport":{"height":800,"width":1280},"editable_draft":{"asset_ref":"empty_agent_draft"},"geometry_tolerance_px":1,"profile":"mock","read_only_draft":{"asset_ref":"read_only_agent_draft"},"selected_child_agents":{"asset_ref":"selected_internal_external_agents_with_saved_versions"},"selected_row":{"action_glyph_size":14,"action_target_size":24,"border_color":"#DFDFDF","child_avatar_size":32,"gap":8,"height":48,"horizontal_padding":12,"name_color":"#191919","name_font_size":14,"name_font_weight":400,"name_line_height":22,"radius":4,"tag_color":"#777777","tag_font_size":12,"tag_line_height":18,"tool_icon_size":24,"vertical_padding":8},"selected_tools":{"asset_ref":"selected_tools_with_managed_knowledge_tool"},"viewport":{"height":1080,"width":1920}}</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>1. Open the initialized editable empty draft at the desktop reference viewport. =&gt; Navigation64px, conversation561px, remaining configuration1295px fit the1920px viewport without horizontal overflow; tab64px and identity74px precede four white radius8 cards with gap12 and no universal outer stroke/shadow.
+2. Inspect the empty card/resource geometry and selected title/description styles. =&gt; Basic/model empty reference heights are224/268px where reference children apply; avatar preview is100px, basic columns share width equally with16px gap and description textarea is100px; resources share one card in knowledge/welcome/skills/tools/child order, add row is two columns gap8 with a left48px entry and3% dark background, titles16px/24px weight500
+3. Scroll to lower resources/advanced controls, collapse and reopen a resource, and open add-resource selection separately from create/manage. =&gt; Scrolling stays inside the configuration pane and identity/action controls remain reachable; no association update occurs before selection confirmation, and model/prompt/guardrail capabilities remain reachable.
+4. Edit a greeting and add/edit five preset questions, then attempt another addition and remove one. =&gt; Existing update payloads retain edited values; addition disables at five and re-enables below five without writes from initial render.
+5. Invoke debug/publication with missing required data, then provide valid required fields and wait for autosave before invoking debug/publication entry again. =&gt; Validation prevents downstream actions for invalid data; valid debug/publication entry follows existing validation/idle-save flow and publication modal, without publishing to a real backend.
+6. Reopen captured fixture draft, then load a read-only fixture and resize to the constrained viewport. =&gt; Saved edits remain visible, read-only prevents edits/publication, controls stay usable without horizontal overflow or clipped populated content.
+7. Open model, knowledge, skill, tool and child-Agent association entries, inspect the right drawer and close each without edits. =&gt; All five entries reuse the shared right drawer; association data and existing save count remain unchanged.
+8. Open the populated fixture and inspect selected tools, child Agents, add-entry order and the existing knowledge-base row at desktop and constrained widths, then resize below the small-screen breakpoint. =&gt; Tools/child Agents use two equal columns with8px gaps and48px white rows with4px radius,1px#DFDFDF border,12px/8px padding and the current knowledge shell shadow; names are14px/22px regular400#191919 with ellipsis/full-name tooltips, real neutral tags are12px/18px#777777 and8px from the name, marks/avatars are24px/32px, and14px action glyphs stay visible in24px targets. The add entry follows all selected rows; below sm the grid uses one column without horizontal overflow. Knowledge rows and selector drawers retain their existing presentation.
+9. Open a selected tool configuration, inspect a saved child-version tooltip, remove one selected tool and one internal child Agent, wait for fixture autosave, then reopen the captured draft and repeat mutation attempts with a read-only populated fixture. =&gt; Existing configuration prerequisites and saved version metadata remain reachable; only the intended tool/child selection is removed and persisted through existing fixture payloads, the managed knowledge tool and other child snapshots remain intact, and read-only controls prevent mutation. Initial rendering and tooltip inspection generate no association writes.</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Desktop measured layout fits the available box model with at most1px geometry tolerance rather than hardcoding overflowing source widths.
+Four cards/resources use the measured geometry and numeric typography; unavailable font glyph parity is not claimed.
+Question addition uses maximum five and edited data persists only through existing fixture update contracts.
+Validation/save/permission gates and model/resource/guardrail reachability survive regrouping.
+Lower content scrolls internally and workflow actions remain reachable across viewport sizes.
+All five association drawers open and close without association writes; existing configuration/selection controllers remain reachable.
+Populated tools/child Agents match the frozen selected-row numerical contract, resource/add ordering and responsive layout while current knowledge rows/drawers retain their presentation.
+Existing selected-resource configuration/removal and saved-version tooltips work; captured/reopened fixture state retains managed knowledge tools and unaffected selections, and read-only disables mutations.</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Do not call a real backend/provider, publish a real version, create real resources, or introduce a new endpoint.
+Do not write from render/collapse, silently truncate legacy data, or bypass read-only/validation/save gates.
+Do not fabricate optional metadata, discard managed knowledge tools or retained child versions, or change current knowledge/drawer presentation.</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>{"actor":"Agent editor user","failure_evidence":["Failure screenshot/trace plus violated geometry or control assertion.","Sanitized captured update payloads and unexpected request paths.","Missing controls, clipped content, or mismatched saved fixture values."],"final_business_result":["The user can configure an empty draft in the measured layout while keeping saved edits and existing workflow gates.","All mutations remain inside deterministic fixture state.","Populated selected tools and child Agents use consistent compact rows and retain their configuration/removal permissions and saved association data."],"journey":["Open an existing empty draft and inspect desktop composition.","Associate resources through the existing selection path and edit conversation guidance.","Wait for fixture autosave and invoke permission/validation guarded workflows.","Reopen fixture data and inspect a read-only/narrow-screen state.","Inspect populated tool/child rows, configure/remove selected resources, and reopen the saved fixture state while preserving knowledge associations and child versions."]}</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"mock","required_services":["http-fixture"]}],"timeout_seconds":120}</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d4/agent-config-layout.spec.mjs</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CONFIG-D4-001</t>
+        </is>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>http-fixture</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr"/>
+      <c r="Y2" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z2" s="5" t="inlineStr">
+        <is>
+          <t>sha256:5838edebe9452e43ecb1c573cd00bd5a64fd2f0562891f93f5bc4cefefc2258d</t>
+        </is>
+      </c>
+      <c r="AA2" s="5" t="inlineStr">
+        <is>
+          <t>sha256:67c8065cd1d5e5b2799cfb3688fd415858844226268e2704b60abb314c143d2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-DEBUG-D4-001</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-DEBUG-LAYOUT</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-DEBUG-REQ-001</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-DEBUG-RULE-001
+AGENT-DEBUG-RULE-002
+AGENT-DEBUG-RULE-003</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Debug a draft in measured layout through preserved runtime and panel controls</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Prove browser geometry and a complete deterministic question/send/stop/clear/layout journey without real writes or providers.</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Local frontend running; all API requests intercepted by deterministic draft/model/chat fixtures.</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>{"constrained_viewport":{"height":800,"width":1280},"draft":{"asset_ref":"debug_agent_draft"},"geometry_tolerance_px":1,"profile":"mock","viewport":{"height":1080,"width":1920}}</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a valid draft and invoke its guarded debug workflow. =&gt; Common tabs and identity remain above both panes; debug width488, padding24, gap10 and card-aligned top with measured header/welcome/question/composer styles.
+2. Select a question and send it through the mocked debug stream, then stop an active run. =&gt; Selection fills exact composer text without a request; send uses existing debug run payload and stop is reachable through existing cancel behavior.
+3. Maximize and restore, clear conversation, toggle comparison and close/reopen debug. =&gt; Layout changes retain existing conversation; clear restores welcome; comparison stays reachable; reopen retains mounted local state.
+4. Resize to constrained viewport and inspect default-chat presentation separately with deterministic fixtures. =&gt; No horizontal page overflow, internal welcome/messages scrolling and controls reachable; default chat has no debug geometry or disclaimer.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Measured desktop geometry within1px; deterministic chat and local controls work; responsive layout retains controls; default presentation unaffected.</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>No real provider/backend call; no configuration writes from selection or panel controls; no new endpoint; no bypass of existing guarded debug entry.</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>{"actor":"Agent editor user","failure_evidence":["Failure screenshot and trace","violated geometry or runtime assertion","unexpected HTTP writes"],"final_business_result":["User can debug the current draft in measured presentation while preserving runtime and configuration state."],"journey":["Open draft","invoke debug","select and send question","stop run","change pane layout","clear","compare and resize"]}</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"mock","required_services":["http-fixture"]}],"timeout_seconds":120}</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d4/agent-debug-layout.spec.mjs</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-DEBUG-D4-001</t>
+        </is>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>http-fixture</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr">
+        <is>
+          <t>sha256:de5e7b33a4bed63c56e6b36a2549125842c1b44e30dbf0ccca5d7945479067d2</t>
+        </is>
+      </c>
+      <c r="AA3" s="5" t="inlineStr">
+        <is>
+          <t>sha256:af5ff413a111fd51e3603dc72918f0677aec883a21cb38802a9aba321197dd6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-GUIDE-D4-001</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-CREATION-GUIDE</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-GUIDE-REQ-001</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-GUIDE-RULE-001
+AGENT-GUIDE-RULE-002
+AGENT-GUIDE-RULE-003</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Create an Agent and complete or skip its measured first-creation guide</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Prove complete creation-to-editor tour journey, geometry, remembered dismissal and safe responsive/read-only behavior.</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Local frontend running; HTTP intercepted by deterministic authenticated editable draft and creation fixtures; isolated preference storage.</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>{"constrained_viewport":{"height":800,"width":1280},"draft":{"asset_ref":"newly_created_agent"},"geometry_tolerance_px":1,"profile":"mock","viewport":{"height":1080,"width":1920}}</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>1. Open Agent list, create a named draft and enter editor. =&gt; One mocked creation succeeds; first guide appears only after correct draft load; measured body/type/padding/buttons/shadow and assistant highlight.
+2. Navigate next and previous through core, resources and workflow steps, then choose Start creation. =&gt; Exact four titles/descriptions and matching highlights/arrows; measured popovers within1px; final dismisses and focuses composer without draft updates or run/publication.
+3. Reload completed route, open ordinary editor, then reset local preference and skip a fresh creation entry. =&gt; Completed and ordinary routes do not replay; skip suppresses replay after reload.
+4. Open read-only marked route and a fresh editable route at constrained viewport. =&gt; Read-only has no guide; constrained steps keep buttons in viewport with no horizontal page overflow.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Full creation and four-step journey; source geometry within1px; remembered skip/finish; read-only exclusion and reachable constrained layout.</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>No real backend/provider invocation; no Agent update after initial mocked create; no debug or publish call caused by tour.</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>{"actor":"First-time Agent creator","failure_evidence":["Failure screenshot/trace","incorrect title or target","violated geometry","unexpected HTTP writes"],"final_business_result":["User understands configuration workflow and can start editing the created draft after completion or dismissal."],"journey":["Open Agent list","create draft","advance and return through guide","finish","reload","skip","check read-only and constrained viewport"]}</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"mock","required_services":["http-fixture"]}],"timeout_seconds":120}</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d4/agent-creation-guide.spec.mjs</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-GUIDE-D4-001</t>
+        </is>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>http-fixture</t>
+        </is>
+      </c>
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z4" s="5" t="inlineStr">
+        <is>
+          <t>sha256:b90762e85a71ff0d88345201247c01a559a1aff624324338c8b80a9604de96eb</t>
+        </is>
+      </c>
+      <c r="AA4" s="5" t="inlineStr">
+        <is>
+          <t>sha256:270648d673d9a74ec8aaa588c8415414cc5e8020ba7b84d7b04567344d43b723</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
           <t>AGENT-LIST-D4-001</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>AGENT-LIST-VIEWS</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>AGENT-LIST-REQ-001
 AGENT-LIST-REQ-002</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>AGENT-LIST-RULE-001
 AGENT-LIST-RULE-002
@@ -2370,47 +3912,47 @@
 AGENT-LIST-RULE-005</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Switch between the agent card and table presentations</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>E2E</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Verify Ant Design table separators and content-responsive sizing at desktop and constrained viewport widths, and confirm that table view retains existing list workflows.</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>Open the agent list with at least two mocked agents, including one with update_time and one without it.</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>{"agent_count":8,"profile":"mock","viewport":{"height":1080,"width":1920}}</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>1. Switch from card mode to table mode. =&gt; The page heading, guide, and tabs remain unchanged while the table and its pagination appear.
 2. Verify columns and representative row values. =&gt; The column order is 名称、类型、描述、状态、创建人、更新时间、操作; timestamps reflect update_time only.
@@ -2418,7 +3960,7 @@
 4. Search for an agent, activate its configure action, then return and switch back to card mode. =&gt; Search and navigation still work, and the card presentation returns with its prior layout and metadata.</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>At 1920×1080 the table occupies the measured 1807px content width; its height follows its rendered rows, grows no higher than 500px, and does not fill unused space.
 The table uses StandardTable with 14px/#191919/0px typography, white rows, a
@@ -2428,79 +3970,79 @@
 Page-level content above the list and existing card mode are unchanged.</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>No backend API or data mutation is introduced by switching views.
 Do not use create_time as update_time.
 Do not add body vertical separators or an outer table border; header separators remain centered and shorter than the 40px header cell.</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>{"actor":"Agent list user","failure_evidence":["Missing/incorrect table headings or row values.","Search, navigation, pagination, or view switching fails.","The table changes content above the list or mutates agent data."],"final_business_result":["The same agent collection remains available in either presentation.","Existing list operations remain reachable."],"journey":["Open the agent list.","Switch between card and table modes.","Search and open an agent configuration."]}</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr"/>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>implemented</t>
         </is>
       </c>
-      <c r="S2" s="5" t="inlineStr">
+      <c r="S5" s="5" t="inlineStr">
         <is>
           <t>custom</t>
         </is>
       </c>
-      <c r="T2" s="5" t="inlineStr">
+      <c r="T5" s="5" t="inlineStr">
         <is>
           <t>test/automation/d4/run_agent_list_views_e2e.mjs</t>
         </is>
       </c>
-      <c r="U2" s="5" t="inlineStr">
+      <c r="U5" s="5" t="inlineStr">
         <is>
           <t>agent-list-high-fidelity.spec.ts</t>
         </is>
       </c>
-      <c r="V2" s="5" t="inlineStr">
+      <c r="V5" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W2" s="5" t="inlineStr"/>
-      <c r="X2" s="5" t="inlineStr"/>
-      <c r="Y2" s="5" t="inlineStr">
+      <c r="W5" s="5" t="inlineStr"/>
+      <c r="X5" s="5" t="inlineStr"/>
+      <c r="Y5" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z2" s="5" t="inlineStr">
+      <c r="Z5" s="5" t="inlineStr">
         <is>
           <t>sha256:1093e9eea123f868058b2922bcb8becb7058e0378301e97276df51156c4ba9fc</t>
         </is>
       </c>
-      <c r="AA2" s="5" t="inlineStr">
+      <c r="AA5" s="5" t="inlineStr">
         <is>
           <t>sha256:a905ec4d8fcce1e93354988f937f8f560872b64738f762662e6250e2413b9b8b</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>CMSR-D4-001</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>CMSR-005</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>CMSR-RULE-013
 CMSR-RULE-014
@@ -2508,48 +4050,48 @@
 CMSR-RULE-016</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Browser shows retry output incrementally without blank steps</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>E2E</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>automated</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Verify a user sees only successful raw code and one executed action in a real conversation.</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>A local Nexent instance
 test tenant and controllable model provider are configured.</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>{"profile":"mock","sequences":["failed transport partial then success","step-one invalid protocol then valid paused repair"]}</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>1. Open Agent chat and send the fixed prompt. =&gt; Step 1 appears before the first model token; the first partial output is then rolled back while the label remains.
 2. Pause the second provider response after its first safe fragment. =&gt; The reasoning card displays the successful raw fragment before provider completion.
@@ -2557,7 +4099,7 @@
 4. Repeat in a new conversation with semantic repair at step one. =&gt; Corrected raw code is visible during the pause and after refresh; Connecting does not persist.</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>Running Step 1 is visible before content.
 No terminal label-only reasoning card.
@@ -2565,59 +4107,59 @@
 Refreshed history matches the final UI.</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>No failed partial text after rollback.
 No duplicate execution card.</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>{"actor":"Authenticated test tenant user","failure_evidence":["Retain browser screenshot","network timing and console trace on failure."],"final_business_result":["Only the committed attempt and its single executed code action are visible."],"journey":["Open the Agent conversation.","Trigger controlled retry.","Observe streaming.","Reload and inspect history."]}</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>{"profiles":[{"name":"mock","required_services":["model-provider"]}]}</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="R6" s="5" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="S3" s="5" t="inlineStr"/>
-      <c r="T3" s="5" t="inlineStr"/>
-      <c r="U3" s="5" t="inlineStr"/>
-      <c r="V3" s="5" t="inlineStr">
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
+      <c r="V6" s="5" t="inlineStr">
         <is>
           <t>mock</t>
         </is>
       </c>
-      <c r="W3" s="5" t="inlineStr">
+      <c r="W6" s="5" t="inlineStr">
         <is>
           <t>model-provider</t>
         </is>
       </c>
-      <c r="X3" s="5" t="inlineStr"/>
-      <c r="Y3" s="5" t="inlineStr">
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr">
         <is>
           <t>校验通过</t>
         </is>
       </c>
-      <c r="Z3" s="5" t="inlineStr">
+      <c r="Z6" s="5" t="inlineStr">
         <is>
           <t>sha256:f110f582fe091286fdaa5301f8bdc22703bf583fc7c6c95214ae8c8187a612a1</t>
         </is>
       </c>
-      <c r="AA3" s="5" t="inlineStr">
+      <c r="AA6" s="5" t="inlineStr">
         <is>
           <t>sha256:4f53cda18c2baa0c0354bb5f9a3ecbe5ed12ab4d8e11ba873c2f11161202b945</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA3"/>
+  <autoFilter ref="A1:AA6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/test/generated/Nexent_测试基线.xlsx
+++ b/test/generated/Nexent_测试基线.xlsx
@@ -1143,12 +1143,13 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>A controlled model yields an invalid response then a pausable valid code action at step one.</t>
+          <t>Protocol repair retry is enabled for the controlled Agent.
+A controlled model yields an invalid response then a pausable repair at step one.</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>{"profile":"mock","sequence":"invalid code, rollback, corrected code chunks, commit, parse"}</t>
+          <t>{"profile":"mock","sequence":"invalid code, rollback, pausable corrected code or clarification, commit; invalid code or clarification rolls back","suppression_capabilities":[true,false]}</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
@@ -1174,7 +1175,7 @@
       </c>
       <c r="P4" s="5" t="inlineStr">
         <is>
-          <t>{"assertions":["Step label occurs before both model attempts and only once.","Successful repair does not set stream suppression.","Corrected attempt commits once.","Invalid attempt rolls back once."],"inputs":["step one","invalid model content","valid streamed &lt;code&gt; action"],"unit_boundary":"CoreAgent semantic repair and deferred model attempt lifecycle"}</t>
+          <t>{"assertions":["Step label occurs before both model attempts and only once.","Successful repair does not set stream suppression.","Corrected attempt commits once.","Invalid attempt rolls back once.","Invalid repair rolls back without execution.","Accepted clarification commits before interaction."],"inputs":["step one","invalid model content","valid streamed &lt;code&gt; action"],"unit_boundary":"CoreAgent semantic repair and deferred model attempt lifecycle"}</t>
         </is>
       </c>
       <c r="Q4" s="5" t="inlineStr"/>
@@ -1212,12 +1213,12 @@
       </c>
       <c r="Z4" s="5" t="inlineStr">
         <is>
-          <t>sha256:7ef8664f2224d068d7deafecf80f09353d734bc10b35a1147b3cc58d1ae6eacd</t>
+          <t>sha256:c3d470f2b34d64b77b32c4e7f56e0ba90a1342dfe28fdbdfbdd1879bc008119d</t>
         </is>
       </c>
       <c r="AA4" s="5" t="inlineStr">
         <is>
-          <t>sha256:1dee7e7ce90f70c40d02907f11be7b55665495fdcaa3dfdec3ab478953c5c38c</t>
+          <t>sha256:cb7b08a8985cb407cb19b796efbc05df45c6cedd57b1deca1fe187ad199c9e51</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1664,7 @@
       </c>
       <c r="AA2" s="5" t="inlineStr">
         <is>
-          <t>sha256:570d7db5b7480c6b3a3a3adcc953158f7c496e44a79e90ad1ca3a4df676d573f</t>
+          <t>sha256:f8f1bc3e7a01d6ffd739d9fbe695e28533e4c410847a09b6405a7dbd4c2e948a</t>
         </is>
       </c>
     </row>

--- a/test/generated/Nexent_测试基线.xlsx
+++ b/test/generated/Nexent_测试基线.xlsx
@@ -16,12 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_D5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_功能清单'!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_D1'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_功能清单'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_D1'!$A$1:$AA$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_D2'!$A$1:$AA$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_D3'!$A$1:$AA$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_D4'!$A$1:$AA$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_D5'!$A$1:$AA$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_D3'!$A$1:$AA$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_D4'!$A$1:$AA$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_D5'!$A$1:$AA$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
@@ -551,11 +551,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
@@ -646,8 +646,52 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Official tool fast path with deferred Docker initialization</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>All Docker-configured Agents can execute approved simple tool steps locally before creating their ordinary executor.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>TFP-RULE-001
+TFP-RULE-002
+TFP-RULE-003
+TFP-RULE-004
+TFP-RULE-005</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>D1
+D3
+D4
+D5</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>{"requirement_ids":["TFP-001"],"spec_path":"nexent-doc/docs/Developing/runtime-sandbox-tool-fastpath/proposal.md"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -658,13 +702,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -679,9 +723,9 @@
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="29" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
-    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="42" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -1351,8 +1395,810 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>TFP-D1-001</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>TFP-RULE-001
+TFP-RULE-005</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Simple official tool steps and final answers never acquire Docker</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>SDK-UT</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Simple official tool steps and final answers never acquire Docker</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Use isolated official tool instances and a controlled executor factory.</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>1. Execute assignment, print and final_answer using an approved official tool. =&gt; The value, logs and final flag match the local interpreter.
+2. Official aidp_search uses its existing allowed KDS scope and emits real tool events without Docker, including an empty permission scope with no provider request. =&gt; The existing AIDP authorization and complete-step routing contract is preserved.</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>Factory acquisition and warm-up counts are zero.
+The wrapped tool is called once and final_answer returns the saved result.
+Official aidp_search uses its existing allowed KDS scope and emits real tool events without Docker, including an empty permission scope with no provider request.</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>No Docker bridge, container or kernel is created.</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Factory acquisition and warm-up counts are zero.","The wrapped tool is called once and final_answer returns the saved result.","Official aidp_search uses its existing allowed KDS scope and emits real tool events without Docker, including an empty permission scope with no provider request."],"inputs":["Simple official tool steps and final answers never acquire Docker"],"unit_boundary":"Restricted AST admission, real LocalPythonExecutor and NexentAgent executor lifecycle"}</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>pytest
+pytest</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_tool_fastpath.py
+test/automation/d1/test_tool_fastpath_aidp.py</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>test_tfp_d1_001
+test_tfp_d1_001_aidp</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z6" s="5" t="inlineStr">
+        <is>
+          <t>sha256:f49d99ec8a0bad9223bdd15df090912a0a2c67816b5857d6add0a9fbd42f851c</t>
+        </is>
+      </c>
+      <c r="AA6" s="5" t="inlineStr">
+        <is>
+          <t>sha256:01d39055c92bd0c0fe6e4360ed1345a6eae93173d20da7f1fea830c15a61839e</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>TFP-D1-002</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>TFP-RULE-002</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Full-step admission prevents partial local execution</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>SDK-UT</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Full-step admission prevents partial local execution</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Use isolated official tool instances and a controlled executor factory.</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>1. Submit a tool call followed by an import, an unapproved call or a bare data expression outside assignment and call arguments. =&gt; The whole step is delegated before any local call.
+2. An aidp_search step followed by ordinary code makes no provider request before whole-step delegation. =&gt; The existing AIDP authorization and complete-step routing contract is preserved.</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>Mixed code is passed once to the original executor.
+No approved tool is called by the fast path before delegation.
+An aidp_search step followed by ordinary code makes no provider request before whole-step delegation.</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>No partial execution or tool replay.</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Mixed code is passed once to the original executor.","No approved tool is called by the fast path before delegation.","An aidp_search step followed by ordinary code makes no provider request before whole-step delegation."],"inputs":["Full-step admission prevents partial local execution"],"unit_boundary":"Restricted AST admission, real LocalPythonExecutor and NexentAgent executor lifecycle"}</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="inlineStr">
+        <is>
+          <t>pytest
+pytest</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_tool_fastpath.py
+test/automation/d1/test_tool_fastpath_aidp.py</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>test_tfp_d1_002
+test_tfp_d1_002_aidp</t>
+        </is>
+      </c>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr"/>
+      <c r="X7" s="5" t="inlineStr"/>
+      <c r="Y7" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z7" s="5" t="inlineStr">
+        <is>
+          <t>sha256:45bd2b9559253a21e4b96e995b91daa065ff8f9ea28bf3c3908b9756b5791782</t>
+        </is>
+      </c>
+      <c r="AA7" s="5" t="inlineStr">
+        <is>
+          <t>sha256:01d39055c92bd0c0fe6e4360ed1345a6eae93173d20da7f1fea830c15a61839e</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>TFP-D1-003</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>TFP-RULE-003</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Promotion preserves user values and remains sticky</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>SDK-UT</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Promotion preserves user values and remains sticky</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Use isolated official tool instances and a controlled executor factory.</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>1. Produce aliased user containers and a tool result, then submit ordinary code. =&gt; One executor is initialized and receives the user namespace.
+2. Submit another approved step. =&gt; The initialized executor is reused.</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>Values and shared container references survive migration.
+Internal interpreter state and tool objects are not migrated.
+The factory is called once.</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>No repeated prior tool invocation.</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Values and shared container references survive migration.","Internal interpreter state and tool objects are not migrated.","The factory is called once."],"inputs":["Promotion preserves user values and remains sticky"],"unit_boundary":"Restricted AST admission, real LocalPythonExecutor and NexentAgent executor lifecycle"}</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_tool_fastpath.py</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>test_tfp_d1_003</t>
+        </is>
+      </c>
+      <c r="V8" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W8" s="5" t="inlineStr"/>
+      <c r="X8" s="5" t="inlineStr"/>
+      <c r="Y8" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z8" s="5" t="inlineStr">
+        <is>
+          <t>sha256:78c3f112432755e552f23bdb788339f518f550d911228d013071fc2c932db42d</t>
+        </is>
+      </c>
+      <c r="AA8" s="5" t="inlineStr">
+        <is>
+          <t>sha256:fba0f34909d32b214bd0a02edc0f4c28eaf34e88e682b3977a2f5a6ea22a64cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TFP-D1-004</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>TFP-RULE-002</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Tool identity cannot be forged by names or sources</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>SDK-UT</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Tool identity cannot be forged by names or sources</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Use isolated official tool instances and a controlled executor factory.</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>1. Provide an exact official tool, an unknown subclass, a same-name custom tool and an MCP source. =&gt; Only the approved official source and exact implementation qualify.
+2. Only exact AidpSearchTool from the local source qualifies; MCP, custom, subclass and IndependentAidpSearchTool identities cannot impersonate aidp_search. Explicit omission from the allowlist delegates. =&gt; The existing AIDP authorization and complete-step routing contract is preserved.</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>Unapproved identities delegate to the original executor.
+Reserved names and callable aliases do not qualify.
+Only exact AidpSearchTool from the local source qualifies; MCP, custom, subclass and IndependentAidpSearchTool identities cannot impersonate aidp_search. Explicit omission from the allowlist delegates.</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>No unauthorized local invocation.</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Unapproved identities delegate to the original executor.","Reserved names and callable aliases do not qualify.","Only exact AidpSearchTool from the local source qualifies; MCP, custom, subclass and IndependentAidpSearchTool identities cannot impersonate aidp_search. Explicit omission from the allowlist delegates."],"inputs":["Tool identity cannot be forged by names or sources"],"unit_boundary":"Restricted AST admission, real LocalPythonExecutor and NexentAgent executor lifecycle"}</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>pytest
+pytest</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_tool_fastpath.py
+test/automation/d1/test_tool_fastpath_aidp.py</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>test_tfp_d1_004
+test_tfp_d1_004_aidp</t>
+        </is>
+      </c>
+      <c r="V9" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W9" s="5" t="inlineStr"/>
+      <c r="X9" s="5" t="inlineStr"/>
+      <c r="Y9" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z9" s="5" t="inlineStr">
+        <is>
+          <t>sha256:2c10e437ccb446a0554d12e76188babbe4d97d0bffc4fd19f98498a86a05c17a</t>
+        </is>
+      </c>
+      <c r="AA9" s="5" t="inlineStr">
+        <is>
+          <t>sha256:01d39055c92bd0c0fe6e4360ed1345a6eae93173d20da7f1fea830c15a61839e</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TFP-D1-005</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>TFP-RULE-004</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Exceptions, cancellation and cleanup are safe</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>SDK-UT</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Exceptions, cancellation and cleanup are safe</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Use isolated official tool instances and a controlled executor factory.</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>1. Fail an approved tool, close an unused wrapper, fail workspace or variable initialization and cancel during acquisition. =&gt; No failed call is replayed and acquired resources close once.
+2. AIDP provider errors propagate without acquiring or replaying through Docker. =&gt; The existing AIDP authorization and complete-step routing contract is preserved.</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>Local errors do not trigger remote replay.
+Cleanup is idempotent.
+Cancellation before execution prevents tool calls and releases acquired resources.
+AIDP provider errors propagate without acquiring or replaying through Docker.</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>No initialization during cleanup.
+No execution after cancellation.</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Local errors do not trigger remote replay.","Cleanup is idempotent.","Cancellation before execution prevents tool calls and releases acquired resources.","AIDP provider errors propagate without acquiring or replaying through Docker."],"inputs":["Exceptions, cancellation and cleanup are safe"],"unit_boundary":"Restricted AST admission, real LocalPythonExecutor and NexentAgent executor lifecycle"}</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>pytest
+pytest
+pytest</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_tool_fastpath.py
+test/automation/d1/test_tool_fastpath.py
+test/automation/d1/test_tool_fastpath_aidp.py</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>test_tfp_d1_005
+test_tfp_d1_005_deferred_setup
+test_tfp_d1_005_aidp</t>
+        </is>
+      </c>
+      <c r="V10" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="inlineStr"/>
+      <c r="X10" s="5" t="inlineStr"/>
+      <c r="Y10" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z10" s="5" t="inlineStr">
+        <is>
+          <t>sha256:f9b9a844e326fc8cac16cb7fa2c69d2ea2f5604696c678c814dfa2ff0058d915</t>
+        </is>
+      </c>
+      <c r="AA10" s="5" t="inlineStr">
+        <is>
+          <t>sha256:e263aa60250b6329f8943aaa6a2f8f0be1b27c3a8dcdfc7364eff56c8ededcaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>TFP-D1-006</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>TFP-RULE-001
+TFP-RULE-004
+TFP-RULE-005</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Factory defers initialization and prepares promoted workspaces</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>SDK-UT</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Factory defers initialization and prepares promoted workspaces</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Use isolated official tool instances and a controlled executor factory.</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>1. Construct a root and child with Docker fast paths and omit the SDK enablement argument. =&gt; Both remain uninitialized.
+2. Activate root and child ordinary executors. =&gt; The session group is shared and each workspace is initialized when its executor appears.
+3. Omit the deployment enablement flag and SDK run-info field, then repeat with an explicit false flag. Exercise MCP and non-MCP run construction. =&gt; Omitted flags enable deferred execution; explicit false retains eager initialization in both paths. Default allowlists include AidpSearchTool, and explicit allowlists retain their configured contents.</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>Disabled mode keeps eager initialization.
+Omitted deployment and SDK flags enable the deferred Docker path, including missing-field fallbacks in MCP and non-MCP run construction.
+Enabled mode delays warm-up and script binding until activation.
+Workspace synchronization precedes ordinary code.
+Actual executors release exactly once.
+Deployment and SDK default allowlists include AidpSearchTool; explicit allowlists and explicit false opt-out remain respected.</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>No kernel for unused child.
+No duplicated session container.</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Disabled mode keeps eager initialization.","Omitted deployment and SDK flags enable the deferred Docker path, including missing-field fallbacks in MCP and non-MCP run construction.","Enabled mode delays warm-up and script binding until activation.","Workspace synchronization precedes ordinary code.","Actual executors release exactly once.","Deployment and SDK default allowlists include AidpSearchTool; explicit allowlists and explicit false opt-out remain respected."],"inputs":["Factory defers initialization and prepares promoted workspaces"],"unit_boundary":"Restricted AST admission, real LocalPythonExecutor and NexentAgent executor lifecycle"}</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>pytest
+pytest
+pytest
+pytest</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_tool_fastpath.py
+test/automation/d1/test_tool_fastpath.py
+test/automation/d1/test_tool_fastpath.py
+test/automation/d1/test_tool_fastpath_defaults.py</t>
+        </is>
+      </c>
+      <c r="U11" s="5" t="inlineStr">
+        <is>
+          <t>test_tfp_d1_006
+test_tfp_d1_006_backends
+test_tfp_d1_006_configuration
+test_tfp_d1_006_run_defaults</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="inlineStr"/>
+      <c r="X11" s="5" t="inlineStr"/>
+      <c r="Y11" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z11" s="5" t="inlineStr">
+        <is>
+          <t>sha256:2bd5d2095842fbb8b4a21db9116ddf8f82a85adfd71351b5084d0d8005a387dc</t>
+        </is>
+      </c>
+      <c r="AA11" s="5" t="inlineStr">
+        <is>
+          <t>sha256:071883550d50b75dd6588a75d883d5af51a92b6edadbf1c02b30412179705beb</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1653,7 +2499,7 @@
       <c r="X2" s="5" t="inlineStr"/>
       <c r="Y2" s="5" t="inlineStr">
         <is>
-          <t>校验通过</t>
+          <t>实现哈希失效</t>
         </is>
       </c>
       <c r="Z2" s="5" t="inlineStr">
@@ -1679,7 +2525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1981,8 +2827,136 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>TFP-D3-001</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>TFP-RULE-001
+TFP-RULE-003
+TFP-RULE-005</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Real Nexent runtime defers Docker until ordinary code</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-IT</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Real Nexent runtime defers Docker until ordinary code</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>A disposable Nexent deployment with this implementation and an approved controlled provider profile is available.
+The current sandbox image has its sandbox user and a reachable kernel service.</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>1. Run an approved knowledge query with a controlled model. =&gt; No kernel or warm-up appears.
+2. Run retrieval followed by ordinary Python and a script-produced artifact. =&gt; The saved variable is available and the artifact is downloadable.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Correct final answer and persisted tool events.
+One activation per Agent needing ordinary code.
+All run resources are reclaimed.</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>No duplicate tool call or cross-tenant access.</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>{"cleanup":["Remove disposable conversations and artifacts; release run kernels."],"integration_boundary":["Running Nexent API, SDK model loop, official tools, Docker kernel and artifact storage"],"observations":["Executor acquisition counters, warm-up traces, tool events, variable consumption and downloaded artifact"]}</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"mock","required_services":["model-provider"]},{"name":"real_smoke","required_services":["model-provider"]}]}</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="inlineStr"/>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>mock
+real_smoke</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>model-provider</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr">
+        <is>
+          <t>sha256:d0707e473b4368889ed27687c15f63d454b843ff2296508357797058551c52f3</t>
+        </is>
+      </c>
+      <c r="AA3" s="5" t="inlineStr">
+        <is>
+          <t>sha256:4f53cda18c2baa0c0354bb5f9a3ecbe5ed12ab4d8e11ba873c2f11161202b945</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA2"/>
+  <autoFilter ref="A1:AA3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1993,7 +2967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2294,8 +3268,134 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>TFP-D4-001</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>TFP-RULE-001
+TFP-RULE-003
+TFP-RULE-005</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Chat displays fast and promoted tool tasks correctly</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Chat displays fast and promoted tool tasks correctly</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>A disposable Nexent deployment with this implementation and an approved controlled provider profile is available.
+A disposable authenticated browser session and a working current sandbox image are available.</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>1. Open a disposable Agent chat and request a knowledge answer. =&gt; A single tool event and correct final answer appear.
+2. Request a task requiring Python and reload the conversation. =&gt; The task completes and history preserves the result without duplicates.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>The final answer and artifact are accessible.
+Refreshed history matches the live result.</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>No duplicate tool card or stale sibling output.</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>{"actor":"Authenticated disposable tenant user","failure_evidence":["Retain Playwright trace, screenshot and network evidence on failure."],"final_business_result":["Both task types complete with correct visible output."],"journey":["Open chat.","Run approved tool task.","Run ordinary Python task.","Reload history and download artifact."]}</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"mock","required_services":["model-provider"]}]}</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="inlineStr"/>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>model-provider</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr">
+        <is>
+          <t>sha256:82e008044b9a89dd07a01bdb8aba0553d5b2d2b173758d98b3011e370e0f6463</t>
+        </is>
+      </c>
+      <c r="AA3" s="5" t="inlineStr">
+        <is>
+          <t>sha256:4f53cda18c2baa0c0354bb5f9a3ecbe5ed12ab4d8e11ba873c2f11161202b945</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA2"/>
+  <autoFilter ref="A1:AA3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2306,7 +3406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2326,10 +3426,10 @@
     <col width="42" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="42" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -2599,8 +3699,262 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>TFP-D5-001</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>TFP-RULE-002</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Untrusted syntax and hostile tool identities cannot enter the local path</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>SECURITY</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Untrusted syntax and hostile tool identities cannot enter the local path</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Use isolated official tool instances and a controlled executor factory.</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>1. Submit attributes, imports, alias calls, unpacking, loops and reserved-variable assignments, including initial variables that shadow tool or framework call names. =&gt; All are rejected before execution.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Zero local tool calls for all rejected inputs.
+The full source is delegated unchanged.</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>No host file, shell or reflection operation is executed.</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>{"condition":["Controlled hostile source and same-name tool fixtures."],"metrics":["Local invocation count.","Admission result."],"recovery_expectations":["A later valid step can still use the ordinary executor."],"risk":"A permissive fast-path validator could allow arbitrary host code.","risk_type":"SECURITY","thresholds":["Zero unauthorized local invocations.","Every hostile sample rejects admission."]}</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d5/test_tool_fastpath_risks.py</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>test_tfp_d5_001</t>
+        </is>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr"/>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr">
+        <is>
+          <t>sha256:cad74b7982db6a898f9267891d908d5e4a026fff456b4e16172e26fa1f499f08</t>
+        </is>
+      </c>
+      <c r="AA3" s="5" t="inlineStr">
+        <is>
+          <t>sha256:6af5717e8cd49952880712aeb98f89e5242c74430374ce491d472e1f80f687cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>TFP-D5-002</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>TFP-001</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>TFP-RULE-001
+TFP-RULE-004</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Repeated simple actions avoid startup and cleanup overhead</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>PERFORMANCE</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Repeated simple actions avoid startup and cleanup overhead</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Use isolated official tool instances and a controlled executor factory.</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>1. Run one thousand small approved steps, then close the wrapper twice. =&gt; No ordinary executor is created and every intended tool call occurs once.</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>Factory count is zero.
+All one thousand results are correct.
+P95 local route time is at most 10 ms for small fixtures.</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>No kernel, bridge or container created by the fast-path wrapper.</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>{"condition":["One thousand warmed steps smaller than 4 KiB with a controlled immediate official tool."],"metrics":["Factory call count.","Per-step P95 duration."],"recovery_expectations":["Cleanup remains idempotent and does not acquire resources."],"risk":"Interpreter routing could erase the saved sandbox startup cost.","risk_type":"PERFORMANCE","thresholds":["Factory count equals zero.","P95 is at most 10 ms excluding provider and tool I/O."]}</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d5/test_tool_fastpath_risks.py</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>test_tfp_d5_002</t>
+        </is>
+      </c>
+      <c r="V4" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr"/>
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z4" s="5" t="inlineStr">
+        <is>
+          <t>sha256:29bfd14fe4f25184e0320e677b23279765cab9691cf05c6bbf44e76dc8bd0e73</t>
+        </is>
+      </c>
+      <c r="AA4" s="5" t="inlineStr">
+        <is>
+          <t>sha256:6af5717e8cd49952880712aeb98f89e5242c74430374ce491d472e1f80f687cc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA2"/>
+  <autoFilter ref="A1:AA4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/test/generated/Nexent_测试基线.xlsx
+++ b/test/generated/Nexent_测试基线.xlsx
@@ -1700,10 +1700,10 @@
     <col width="42" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="42" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="42" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
     <col width="17" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -1948,12 +1948,24 @@
       </c>
       <c r="R2" s="5" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="inlineStr"/>
-      <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d3/test_semantic_repair_runtime.py</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>test_cmsr_d3_001</t>
+        </is>
+      </c>
       <c r="V2" s="5" t="inlineStr">
         <is>
           <t>mock
@@ -1978,7 +1990,7 @@
       </c>
       <c r="AA2" s="5" t="inlineStr">
         <is>
-          <t>sha256:4f53cda18c2baa0c0354bb5f9a3ecbe5ed12ab4d8e11ba873c2f11161202b945</t>
+          <t>sha256:ae252be0da5024d144ae862cddaa9a71102050f2b43ed244fc8b29d1425bb901</t>
         </is>
       </c>
     </row>
@@ -2014,10 +2026,10 @@
     <col width="42" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="42" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="42" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -2262,12 +2274,24 @@
       </c>
       <c r="R2" s="5" t="inlineStr">
         <is>
-          <t>blocked</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="inlineStr"/>
-      <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr"/>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d4/semantic_repair_browser.mjs</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>test_cmsr_d4_001</t>
+        </is>
+      </c>
       <c r="V2" s="5" t="inlineStr">
         <is>
           <t>mock</t>
@@ -2291,7 +2315,7 @@
       </c>
       <c r="AA2" s="5" t="inlineStr">
         <is>
-          <t>sha256:4f53cda18c2baa0c0354bb5f9a3ecbe5ed12ab4d8e11ba873c2f11161202b945</t>
+          <t>sha256:9c83a2f64a371eae2149c016d79e511b8ef0d9171af65018c508fc676fe6d085</t>
         </is>
       </c>
     </row>

--- a/test/generated/Nexent_测试基线.xlsx
+++ b/test/generated/Nexent_测试基线.xlsx
@@ -1990,7 +1990,7 @@
       </c>
       <c r="AA2" s="5" t="inlineStr">
         <is>
-          <t>sha256:ae252be0da5024d144ae862cddaa9a71102050f2b43ed244fc8b29d1425bb901</t>
+          <t>sha256:8df5fe6baf3e04640581648de5e07f08d6113e32bd47f8a1eeecc827faae2796</t>
         </is>
       </c>
     </row>

--- a/test/generated/Nexent_测试基线.xlsx
+++ b/test/generated/Nexent_测试基线.xlsx
@@ -723,7 +723,7 @@
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="42" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
     <col width="42" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
@@ -1460,12 +1460,14 @@
       <c r="M6" s="5" t="inlineStr">
         <is>
           <t>1. Execute assignment, print and final_answer using an approved official tool. =&gt; The value, logs and final flag match the local interpreter.
-2. Official aidp_search uses its existing allowed KDS scope and emits real tool events without Docker, including an empty permission scope with no provider request. =&gt; The existing AIDP authorization and complete-step routing contract is preserved.</t>
+2. Official aidp_search uses its existing allowed KDS scope and emits real tool events without Docker, including an empty permission scope with no provider request. =&gt; The existing AIDP authorization and complete-step routing contract is preserved.
+3. Import json or loads/dumps using direct and aliased forms, parse an official tool result, serialize it with nested JSON calls and reuse aliases in later steps. =&gt; Values and logs match the real local interpreter with no ordinary executor.</t>
         </is>
       </c>
       <c r="N6" s="5" t="inlineStr">
         <is>
           <t>Factory acquisition and warm-up counts are zero.
+JSON loads/dumps and their import aliases work across steps without Docker.
 The wrapped tool is called once and final_answer returns the saved result.
 Official aidp_search uses its existing allowed KDS scope and emits real tool events without Docker, including an empty permission scope with no provider request.</t>
         </is>
@@ -1477,7 +1479,7 @@
       </c>
       <c r="P6" s="5" t="inlineStr">
         <is>
-          <t>{"assertions":["Factory acquisition and warm-up counts are zero.","The wrapped tool is called once and final_answer returns the saved result.","Official aidp_search uses its existing allowed KDS scope and emits real tool events without Docker, including an empty permission scope with no provider request."],"inputs":["Simple official tool steps and final answers never acquire Docker"],"unit_boundary":"Restricted AST admission, real LocalPythonExecutor and NexentAgent executor lifecycle"}</t>
+          <t>{"assertions":["Factory acquisition and warm-up counts are zero.","JSON loads/dumps and their import aliases work across steps without Docker.","The wrapped tool is called once and final_answer returns the saved result.","Official aidp_search uses its existing allowed KDS scope and emits real tool events without Docker, including an empty permission scope with no provider request."],"inputs":["Simple official tool steps and final answers never acquire Docker"],"unit_boundary":"Restricted AST admission, real LocalPythonExecutor and NexentAgent executor lifecycle"}</t>
         </is>
       </c>
       <c r="Q6" s="5" t="inlineStr"/>
@@ -1489,19 +1491,25 @@
       <c r="S6" s="5" t="inlineStr">
         <is>
           <t>pytest
+pytest
+pytest
 pytest</t>
         </is>
       </c>
       <c r="T6" s="5" t="inlineStr">
         <is>
           <t>test/automation/d1/test_tool_fastpath.py
-test/automation/d1/test_tool_fastpath_aidp.py</t>
+test/automation/d1/test_tool_fastpath_aidp.py
+test/automation/d1/test_tool_fastpath_json.py
+test/automation/d1/test_tool_fastpath_json.py</t>
         </is>
       </c>
       <c r="U6" s="5" t="inlineStr">
         <is>
           <t>test_tfp_d1_001
-test_tfp_d1_001_aidp</t>
+test_tfp_d1_001_aidp
+test_tfp_d1_001_json
+test_tfp_d1_001_json_tool_results</t>
         </is>
       </c>
       <c r="V6" s="5" t="inlineStr">
@@ -1518,12 +1526,12 @@
       </c>
       <c r="Z6" s="5" t="inlineStr">
         <is>
-          <t>sha256:f49d99ec8a0bad9223bdd15df090912a0a2c67816b5857d6add0a9fbd42f851c</t>
+          <t>sha256:7891191daf2e4c1801ad541da60c43d9185628c1903be8cc4fd92d5ed179b8c0</t>
         </is>
       </c>
       <c r="AA6" s="5" t="inlineStr">
         <is>
-          <t>sha256:01d39055c92bd0c0fe6e4360ed1345a6eae93173d20da7f1fea830c15a61839e</t>
+          <t>sha256:440cb5a48b22ca2a72b2000ec4d0af860f20a59b80d96212595e5b6d5bf92837</t>
         </is>
       </c>
     </row>
@@ -1590,13 +1598,15 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>1. Submit a tool call followed by an import, an unapproved call or a bare data expression outside assignment and call arguments. =&gt; The whole step is delegated before any local call.
-2. An aidp_search step followed by ordinary code makes no provider request before whole-step delegation. =&gt; The existing AIDP authorization and complete-step routing contract is preserved.</t>
+          <t>1. Submit a tool call followed by an unapproved import, an unapproved call or a bare data expression outside assignment and call arguments. =&gt; The whole step is delegated before any local call.
+2. An aidp_search step followed by ordinary code makes no provider request before whole-step delegation. =&gt; The existing AIDP authorization and complete-step routing contract is preserved.
+3. Submit JSON imports and tool calls mixed with file-oriented JSON operations, unapproved members, wildcard/relative/dynamic imports or ordinary Python syntax. =&gt; Delegate the entire source before executing any local import or tool.</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Mixed code is passed once to the original executor.
+Admitted JSON statements do not cause partial execution of rejected mixed steps.
 No approved tool is called by the fast path before delegation.
 An aidp_search step followed by ordinary code makes no provider request before whole-step delegation.</t>
         </is>
@@ -1608,7 +1618,7 @@
       </c>
       <c r="P7" s="5" t="inlineStr">
         <is>
-          <t>{"assertions":["Mixed code is passed once to the original executor.","No approved tool is called by the fast path before delegation.","An aidp_search step followed by ordinary code makes no provider request before whole-step delegation."],"inputs":["Full-step admission prevents partial local execution"],"unit_boundary":"Restricted AST admission, real LocalPythonExecutor and NexentAgent executor lifecycle"}</t>
+          <t>{"assertions":["Mixed code is passed once to the original executor.","Admitted JSON statements do not cause partial execution of rejected mixed steps.","No approved tool is called by the fast path before delegation.","An aidp_search step followed by ordinary code makes no provider request before whole-step delegation."],"inputs":["Full-step admission prevents partial local execution"],"unit_boundary":"Restricted AST admission, real LocalPythonExecutor and NexentAgent executor lifecycle"}</t>
         </is>
       </c>
       <c r="Q7" s="5" t="inlineStr"/>
@@ -1620,19 +1630,22 @@
       <c r="S7" s="5" t="inlineStr">
         <is>
           <t>pytest
+pytest
 pytest</t>
         </is>
       </c>
       <c r="T7" s="5" t="inlineStr">
         <is>
           <t>test/automation/d1/test_tool_fastpath.py
-test/automation/d1/test_tool_fastpath_aidp.py</t>
+test/automation/d1/test_tool_fastpath_aidp.py
+test/automation/d1/test_tool_fastpath_json.py</t>
         </is>
       </c>
       <c r="U7" s="5" t="inlineStr">
         <is>
           <t>test_tfp_d1_002
-test_tfp_d1_002_aidp</t>
+test_tfp_d1_002_aidp
+test_tfp_d1_002_json</t>
         </is>
       </c>
       <c r="V7" s="5" t="inlineStr">
@@ -1649,12 +1662,12 @@
       </c>
       <c r="Z7" s="5" t="inlineStr">
         <is>
-          <t>sha256:45bd2b9559253a21e4b96e995b91daa065ff8f9ea28bf3c3908b9756b5791782</t>
+          <t>sha256:97f3565d985b576df5e9a23518cb625ca0d4796b4bf0378a8f1773d4f38073e7</t>
         </is>
       </c>
       <c r="AA7" s="5" t="inlineStr">
         <is>
-          <t>sha256:01d39055c92bd0c0fe6e4360ed1345a6eae93173d20da7f1fea830c15a61839e</t>
+          <t>sha256:8fdbcb9d596383c8e5a55a84bc25f9f9033ad33cad2d2a91bc362ed09c3f4446</t>
         </is>
       </c>
     </row>
@@ -1722,13 +1735,15 @@
       <c r="M8" s="5" t="inlineStr">
         <is>
           <t>1. Produce aliased user containers and a tool result, then submit ordinary code. =&gt; One executor is initialized and receives the user namespace.
-2. Submit another approved step. =&gt; The initialized executor is reused.</t>
+2. Submit another approved step. =&gt; The initialized executor is reused.
+3. Import json/loads/dumps with aliases, save parsed data and then activate ordinary code that uses those aliases. Include prior data names replaced by imports. =&gt; Recreate the actual imports once before ordinary code; migrate only user data and preserve references without replaying prior tools.</t>
         </is>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
           <t>Values and shared container references survive migration.
 Internal interpreter state and tool objects are not migrated.
+JSON module/function objects are excluded; actual imported aliases are recreated.
 The factory is called once.</t>
         </is>
       </c>
@@ -1739,7 +1754,7 @@
       </c>
       <c r="P8" s="5" t="inlineStr">
         <is>
-          <t>{"assertions":["Values and shared container references survive migration.","Internal interpreter state and tool objects are not migrated.","The factory is called once."],"inputs":["Promotion preserves user values and remains sticky"],"unit_boundary":"Restricted AST admission, real LocalPythonExecutor and NexentAgent executor lifecycle"}</t>
+          <t>{"assertions":["Values and shared container references survive migration.","Internal interpreter state and tool objects are not migrated.","JSON module/function objects are excluded; actual imported aliases are recreated.","The factory is called once."],"inputs":["Promotion preserves user values and remains sticky"],"unit_boundary":"Restricted AST admission, real LocalPythonExecutor and NexentAgent executor lifecycle"}</t>
         </is>
       </c>
       <c r="Q8" s="5" t="inlineStr"/>
@@ -1750,17 +1765,23 @@
       </c>
       <c r="S8" s="5" t="inlineStr">
         <is>
-          <t>pytest</t>
+          <t>pytest
+pytest
+pytest</t>
         </is>
       </c>
       <c r="T8" s="5" t="inlineStr">
         <is>
-          <t>test/automation/d1/test_tool_fastpath.py</t>
+          <t>test/automation/d1/test_tool_fastpath.py
+test/automation/d1/test_tool_fastpath_json.py
+test/automation/d1/test_tool_fastpath_json.py</t>
         </is>
       </c>
       <c r="U8" s="5" t="inlineStr">
         <is>
-          <t>test_tfp_d1_003</t>
+          <t>test_tfp_d1_003
+test_tfp_d1_003_json
+test_tfp_d1_003_json_replaced_binding</t>
         </is>
       </c>
       <c r="V8" s="5" t="inlineStr">
@@ -1777,12 +1798,12 @@
       </c>
       <c r="Z8" s="5" t="inlineStr">
         <is>
-          <t>sha256:78c3f112432755e552f23bdb788339f518f550d911228d013071fc2c932db42d</t>
+          <t>sha256:f1bc59890f25b5b66c1816e60700a0c3fd04f3b3c72f42e1538ed10f90eee37c</t>
         </is>
       </c>
       <c r="AA8" s="5" t="inlineStr">
         <is>
-          <t>sha256:fba0f34909d32b214bd0a02edc0f4c28eaf34e88e682b3977a2f5a6ea22a64cb</t>
+          <t>sha256:0c084ac84eae8f370c9130fd6f12f32c7f66727ea8be97e748d131d09fc6a158</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1934,7 @@
       </c>
       <c r="AA9" s="5" t="inlineStr">
         <is>
-          <t>sha256:01d39055c92bd0c0fe6e4360ed1345a6eae93173d20da7f1fea830c15a61839e</t>
+          <t>sha256:d51fb991cae4fea09f646ea0e34dc9914cba84cd3a5834c2494eb30c77e5bc3c</t>
         </is>
       </c>
     </row>
@@ -1981,12 +2002,15 @@
       <c r="M10" s="5" t="inlineStr">
         <is>
           <t>1. Fail an approved tool, close an unused wrapper, fail workspace or variable initialization and cancel during acquisition. =&gt; No failed call is replayed and acquired resources close once.
-2. AIDP provider errors propagate without acquiring or replaying through Docker. =&gt; The existing AIDP authorization and complete-step routing contract is preserved.</t>
+2. AIDP provider errors propagate without acquiring or replaying through Docker. =&gt; The existing AIDP authorization and complete-step routing contract is preserved.
+3. Fail JSON parsing between admitted imports, then reuse completed imports or activate ordinary code. Fail or cancel import restoration during activation. =&gt; Do not replay errors, tools or unfinished imports; preserve actual bindings and release acquired executors exactly once.</t>
         </is>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
           <t>Local errors do not trigger remote replay.
+JSON errors retain only executed imports and never acquire an executor by themselves.
+Failed or cancelled import restoration releases the acquired executor without replay.
 Cleanup is idempotent.
 Cancellation before execution prevents tool calls and releases acquired resources.
 AIDP provider errors propagate without acquiring or replaying through Docker.</t>
@@ -2000,7 +2024,7 @@
       </c>
       <c r="P10" s="5" t="inlineStr">
         <is>
-          <t>{"assertions":["Local errors do not trigger remote replay.","Cleanup is idempotent.","Cancellation before execution prevents tool calls and releases acquired resources.","AIDP provider errors propagate without acquiring or replaying through Docker."],"inputs":["Exceptions, cancellation and cleanup are safe"],"unit_boundary":"Restricted AST admission, real LocalPythonExecutor and NexentAgent executor lifecycle"}</t>
+          <t>{"assertions":["Local errors do not trigger remote replay.","JSON errors retain only executed imports and never acquire an executor by themselves.","Failed or cancelled import restoration releases the acquired executor without replay.","Cleanup is idempotent.","Cancellation before execution prevents tool calls and releases acquired resources.","AIDP provider errors propagate without acquiring or replaying through Docker."],"inputs":["Exceptions, cancellation and cleanup are safe"],"unit_boundary":"Restricted AST admission, real LocalPythonExecutor and NexentAgent executor lifecycle"}</t>
         </is>
       </c>
       <c r="Q10" s="5" t="inlineStr"/>
@@ -2013,6 +2037,9 @@
         <is>
           <t>pytest
 pytest
+pytest
+pytest
+pytest
 pytest</t>
         </is>
       </c>
@@ -2020,14 +2047,20 @@
         <is>
           <t>test/automation/d1/test_tool_fastpath.py
 test/automation/d1/test_tool_fastpath.py
-test/automation/d1/test_tool_fastpath_aidp.py</t>
+test/automation/d1/test_tool_fastpath_aidp.py
+test/automation/d1/test_tool_fastpath_json.py
+test/automation/d1/test_tool_fastpath_json.py
+test/automation/d1/test_tool_fastpath_json.py</t>
         </is>
       </c>
       <c r="U10" s="5" t="inlineStr">
         <is>
           <t>test_tfp_d1_005
 test_tfp_d1_005_deferred_setup
-test_tfp_d1_005_aidp</t>
+test_tfp_d1_005_aidp
+test_tfp_d1_005_json_error
+test_tfp_d1_005_json_rebinding_error
+test_tfp_d1_005_json_restore_failure</t>
         </is>
       </c>
       <c r="V10" s="5" t="inlineStr">
@@ -2044,12 +2077,12 @@
       </c>
       <c r="Z10" s="5" t="inlineStr">
         <is>
-          <t>sha256:f9b9a844e326fc8cac16cb7fa2c69d2ea2f5604696c678c814dfa2ff0058d915</t>
+          <t>sha256:e1415a3a6af4da41671b4363b8c4b4eba52a6dd47b4b4296227c3f43d660734d</t>
         </is>
       </c>
       <c r="AA10" s="5" t="inlineStr">
         <is>
-          <t>sha256:e263aa60250b6329f8943aaa6a2f8f0be1b27c3a8dcdfc7364eff56c8ededcaa</t>
+          <t>sha256:9fa401f941bf919e6f8136c5e4ba60fa481f2c824e7b1c2b54b555ff9746b4fd</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2226,7 @@
       </c>
       <c r="AA11" s="5" t="inlineStr">
         <is>
-          <t>sha256:071883550d50b75dd6588a75d883d5af51a92b6edadbf1c02b30412179705beb</t>
+          <t>sha256:56280e4bb05195c39eb91616119beadf4479255a48d8db2a5a23db734b9f2371</t>
         </is>
       </c>
     </row>
@@ -3427,9 +3460,9 @@
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
-    <col width="17" customWidth="1" min="21" max="21"/>
+    <col width="42" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -3762,13 +3795,15 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>1. Submit attributes, imports, alias calls, unpacking, loops and reserved-variable assignments, including initial variables that shadow tool or framework call names. =&gt; All are rejected before execution.</t>
+          <t>1. Submit arbitrary attributes/imports, alias calls, unpacking, loops and reserved-variable assignments, including initial variables that shadow tool or framework call names. =&gt; All are rejected before execution.
+2. Forge JSON modules/functions through initial variables or change an admitted binding; use JSON file operations, dynamic callbacks, wildcard imports and reserved alias names. =&gt; Reject the entire step with no local import, callback or tool effects.</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
           <t>Zero local tool calls for all rejected inputs.
-The full source is delegated unchanged.</t>
+The full source is delegated unchanged.
+Only exact admitted JSON loads/dumps bindings qualify; shadowed bindings never invoke locally.</t>
         </is>
       </c>
       <c r="O3" s="5" t="inlineStr">
@@ -3789,17 +3824,23 @@
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>pytest</t>
+          <t>pytest
+pytest
+pytest</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>test/automation/d5/test_tool_fastpath_risks.py</t>
+          <t>test/automation/d5/test_tool_fastpath_risks.py
+test/automation/d5/test_tool_fastpath_json_risks.py
+test/automation/d5/test_tool_fastpath_json_risks.py</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>test_tfp_d5_001</t>
+          <t>test_tfp_d5_001
+test_tfp_d5_001_json_syntax
+test_tfp_d5_001_json_identity</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
@@ -3816,12 +3857,12 @@
       </c>
       <c r="Z3" s="5" t="inlineStr">
         <is>
-          <t>sha256:cad74b7982db6a898f9267891d908d5e4a026fff456b4e16172e26fa1f499f08</t>
+          <t>sha256:a95f4672fd09d8d82014f5b21de9850d7cf8d4dd7eb6c5bea2f8062f675ed512</t>
         </is>
       </c>
       <c r="AA3" s="5" t="inlineStr">
         <is>
-          <t>sha256:6af5717e8cd49952880712aeb98f89e5242c74430374ce491d472e1f80f687cc</t>
+          <t>sha256:4fd0bf1be9902c93374ec9c0e5145b2676d332ac3c2b7f8c70c62707af221a07</t>
         </is>
       </c>
     </row>

--- a/test/generated/Nexent_测试基线.xlsx
+++ b/test/generated/Nexent_测试基线.xlsx
@@ -16,12 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_D5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_功能清单'!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_D1'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_功能清单'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_D1'!$A$1:$AA$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_D2'!$A$1:$AA$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_D3'!$A$1:$AA$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_D4'!$A$1:$AA$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_D5'!$A$1:$AA$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_D3'!$A$1:$AA$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_D4'!$A$1:$AA$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_D5'!$A$1:$AA$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -646,8 +646,50 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>TPC-001</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Thinking prefix compatibility</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Reasoning markup does not block valid actions or authorize raw final answers.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>TPC-RULE-001
+TPC-RULE-002
+TPC-RULE-003</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>D1
+D3
+D4
+D5</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>{"requirement_ids":["TPC-001"],"spec_path":"nexent-doc/docs/Developing/codeagent-explicit-termination/changes/codeagent-think-prefix-compatibility/proposal.md"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -658,7 +700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1351,8 +1393,769 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>TPC-D1-001</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>TPC-001</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>TPC-001</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>TPC-RULE-001</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Compatible thinking prefixes yield the exact executable action</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>SDK-UT</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Compatible thinking prefixes yield the exact executable action</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Isolated strict ordinary CodeAgent with a controlled model and authorized skill-read tool.</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>1. Classify plain, paired-plus-narration, orphan, unclosed, repeated and nested thinking prefixes before complete code and run actions. =&gt; Every result is an executable action with the exact Python body.</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>All compatible prefixes accepted.</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>Prefix text is never executed.</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Exact executable body and legacy flag."],"inputs":["prefix matrix","code/run envelopes"],"unit_boundary":"classify_model_output"}</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_think_prefix_compatibility.py</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>test_tpc_d1_001</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z6" s="5" t="inlineStr">
+        <is>
+          <t>sha256:4f391cdcc5d8afa20a295a40d9739667d853c3099df0248d511947163488a722</t>
+        </is>
+      </c>
+      <c r="AA6" s="5" t="inlineStr">
+        <is>
+          <t>sha256:80150f5dbffa58305e628681d5dd93c39d59d2d701854cc6967112e494836fab</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>TPC-D1-002</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>TPC-001</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>TPC-001</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>TPC-RULE-001
+TPC-RULE-003</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Skill reads execute rather than finalize at first and third generations</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>SDK-UT</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Skill reads execute rather than finalize at first and third generations</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Isolated strict ordinary CodeAgent with a controlled model and authorized skill-read tool.</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>1. Run complete skill read under every compatible prefix with prior error counters zero and two. =&gt; One read executes; its result is an observation; no final answer is returned.</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>Exactly one tool effect per action.
+Model attempt commits.</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>No raw final answer.
+No extra model request.</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Skill call count one.","ActionOutput.is_final_answer false.","Accepted attempt commits without rollback."],"inputs":["prefix matrix","prior errors zero/two"],"unit_boundary":"CoreAgent._step_stream and Python executor boundary"}</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_think_prefix_compatibility.py</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>test_tpc_d1_002</t>
+        </is>
+      </c>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr"/>
+      <c r="X7" s="5" t="inlineStr"/>
+      <c r="Y7" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z7" s="5" t="inlineStr">
+        <is>
+          <t>sha256:bf3161e59bf8555b8eca4685fd76b62450ac76b189b1f54db8a6d943022475ed</t>
+        </is>
+      </c>
+      <c r="AA7" s="5" t="inlineStr">
+        <is>
+          <t>sha256:80150f5dbffa58305e628681d5dd93c39d59d2d701854cc6967112e494836fab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>TPC-D1-003</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>TPC-001</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>TPC-001</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>TPC-RULE-001
+TPC-RULE-002</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Malformed actions retain structural rejection</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>SDK-UT</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Malformed actions retain structural rejection</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Isolated strict ordinary CodeAgent with a controlled model and authorized skill-read tool.</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>1. Classify invalid Python, empty/unclosed action, inter-block text, trailing text, unknown tags and truncated output. =&gt; Protocol error occurs; no executor is called.</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>Invalid action bodies and boundaries remain rejected.</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>No execution of invalid code.</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Expected stable protocol-error reason."],"inputs":["invalid action/control matrix","length finish reason"],"unit_boundary":"classify_model_output"}</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_think_prefix_compatibility.py</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>test_tpc_d1_003</t>
+        </is>
+      </c>
+      <c r="V8" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W8" s="5" t="inlineStr"/>
+      <c r="X8" s="5" t="inlineStr"/>
+      <c r="Y8" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z8" s="5" t="inlineStr">
+        <is>
+          <t>sha256:100d35b68a2e856ce77afbea76a04f64cced55b7c6427ad4b682ff63a5512759</t>
+        </is>
+      </c>
+      <c r="AA8" s="5" t="inlineStr">
+        <is>
+          <t>sha256:80150f5dbffa58305e628681d5dd93c39d59d2d701854cc6967112e494836fab</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TPC-D1-004</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>TPC-001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>TPC-001</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>TPC-RULE-002</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Thinking-only and invalid marked output never use exhausted raw final</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>SDK-UT</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Thinking-only and invalid marked output never use exhausted raw final</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Isolated strict ordinary CodeAgent with a controlled model and authorized skill-read tool.</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>1. Run thinking-only and malformed action or final outputs with two prior protocol errors. =&gt; The attempt rolls back and no raw final is accepted.
+2. Run eligible complete plain text at exhaustion. =&gt; Existing raw candidate remains accepted.</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>Marked failures cannot finalize.
+Eligible plain text keeps existing fallback.</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>No invalid action final.
+No reasoning final.</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Failed attempt rollback.","No executor call on invalid output.","Plain raw fallback preserved."],"inputs":["marked output","plain text","error count two"],"unit_boundary":"CoreAgent._accept_exhausted_raw_output and _step_stream"}</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_think_prefix_compatibility.py</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>test_tpc_d1_004</t>
+        </is>
+      </c>
+      <c r="V9" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W9" s="5" t="inlineStr"/>
+      <c r="X9" s="5" t="inlineStr"/>
+      <c r="Y9" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z9" s="5" t="inlineStr">
+        <is>
+          <t>sha256:f2504ffd5633cd2255b5dbbd3f2265227f687a753a12a0145d193b141a18ef32</t>
+        </is>
+      </c>
+      <c r="AA9" s="5" t="inlineStr">
+        <is>
+          <t>sha256:80150f5dbffa58305e628681d5dd93c39d59d2d701854cc6967112e494836fab</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>TPC-D1-005</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>TPC-001</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>TPC-001</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>TPC-RULE-001
+TPC-RULE-002</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Ordinary explicit finals tolerate thinking prefix and keep boundaries</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>SDK-UT</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Ordinary explicit finals tolerate thinking prefix and keep boundaries</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Isolated strict ordinary CodeAgent with a controlled model and authorized skill-read tool.</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>1. Classify compatible prefix before valid ordinary final envelope. =&gt; Only the payload is ExplicitFinalAnswer.
+2. Classify duplicates, incomplete envelopes, suffix text and specialized prefixed envelopes. =&gt; Protocol errors remain.</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>Ordinary terminal prefix accepted.
+Specialized exact-envelope behavior retained.</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>No prefix in terminal payload.
+No malformed final accepted.</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Exact final payload.","Malformed and specialized prefixed forms reject."],"inputs":["prefix matrix","final envelope matrix","final_envelope protocol"],"unit_boundary":"classify_model_output terminal branch"}</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_think_prefix_compatibility.py</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>test_tpc_d1_005</t>
+        </is>
+      </c>
+      <c r="V10" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="inlineStr"/>
+      <c r="X10" s="5" t="inlineStr"/>
+      <c r="Y10" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z10" s="5" t="inlineStr">
+        <is>
+          <t>sha256:33d570993c8638b85cd01d13e5fde4178f0bae8302be5d3108471cb7fc0d257b</t>
+        </is>
+      </c>
+      <c r="AA10" s="5" t="inlineStr">
+        <is>
+          <t>sha256:80150f5dbffa58305e628681d5dd93c39d59d2d701854cc6967112e494836fab</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>TPC-D1-006</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>TPC-001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>TPC-001</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>TPC-RULE-001</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Python data containing protocol-like tags is preserved</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>SDK-UT</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Python data containing protocol-like tags is preserved</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Isolated strict ordinary CodeAgent with a controlled model and authorized skill-read tool.</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>1. Classify actions whose strings/comments contain think and code markers. =&gt; Python data remains unchanged and executable.</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>Only outer reasoning prefix is normalized.</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>No global tag replacement in action or final data.</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Exact code body retained."],"inputs":["Python literal/comment protocol-like text"],"unit_boundary":"classify_model_output Python data boundaries"}</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_think_prefix_compatibility.py</t>
+        </is>
+      </c>
+      <c r="U11" s="5" t="inlineStr">
+        <is>
+          <t>test_tpc_d1_006</t>
+        </is>
+      </c>
+      <c r="V11" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="inlineStr"/>
+      <c r="X11" s="5" t="inlineStr"/>
+      <c r="Y11" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z11" s="5" t="inlineStr">
+        <is>
+          <t>sha256:b76ef5ea9a602bd23ed01d075a888e34440cd8c9d6585726a2e366975f398087</t>
+        </is>
+      </c>
+      <c r="AA11" s="5" t="inlineStr">
+        <is>
+          <t>sha256:80150f5dbffa58305e628681d5dd93c39d59d2d701854cc6967112e494836fab</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1663,7 +2466,7 @@
       </c>
       <c r="AA2" s="5" t="inlineStr">
         <is>
-          <t>sha256:570d7db5b7480c6b3a3a3adcc953158f7c496e44a79e90ad1ca3a4df676d573f</t>
+          <t>sha256:f8f1bc3e7a01d6ffd739d9fbe695e28533e4c410847a09b6405a7dbd4c2e948a</t>
         </is>
       </c>
     </row>
@@ -1679,7 +2482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1699,10 +2502,10 @@
     <col width="42" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="42" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="42" customWidth="1" min="20" max="20"/>
+    <col width="42" customWidth="1" min="21" max="21"/>
     <col width="17" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -1981,8 +2784,154 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>TPC-D3-001</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>TPC-001</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>TPC-001</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>TPC-RULE-001
+TPC-RULE-003</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Deployed skill read completes with explicit final and persisted evidence</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>AGENT-IT</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Deployed skill read completes with explicit final and persisted evidence</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Disposable Nexent deployment, authorized skill and controlled provider are available.</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>1. Drive controlled think prefix then skill-read action through deployed Agent. =&gt; Read executes once and returns skill text.
+2. Return a separate explicit final and reload history. =&gt; Exactly one final payload and one read result are persisted.
+3. Exhaust three malformed marked responses without an executable action. =&gt; No skill effect or raw protocol final is emitted or stored.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Runtime executes the skill read.
+History matches committed stream.
+Malformed marked exhaustion does not execute or become a raw final.</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>No unexecuted action final.
+No duplicate tool effects.</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>{"cleanup":["Remove test conversation and provider fixture."],"integration_boundary":["Provider to classifier","Executor to skill tool","Observer to SSE/history"],"observations":["Raw content and parser classification","Skill tool effect","Final source and stored units"]}</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"mock","required_services":["model-provider"]},{"name":"real_smoke","required_services":["model-provider"]}]}</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>pytest
+pytest
+pytest</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d3/test_think_prefix_runtime.py
+test/automation/d3/test_think_prefix_runtime.py
+test/automation/d3/test_think_prefix_runtime.py</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>test_tpc_d3_001_skill_executes_once_and_history_matches
+test_tpc_d3_001_marked_exhaustion_never_executes_or_finalizes
+test_tpc_d3_001_real_model_reads_skill</t>
+        </is>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>mock
+real_smoke</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>model-provider</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr">
+        <is>
+          <t>sha256:2de8f6fa8b9e8b2e53318f71e08dccbb4cbe6e95935069f88ca84a3eebb66f0c</t>
+        </is>
+      </c>
+      <c r="AA3" s="5" t="inlineStr">
+        <is>
+          <t>sha256:aed01ec6f1542f3267c7c65eb7c60830b2150eb4fd123fa4c174e2b729753149</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA2"/>
+  <autoFilter ref="A1:AA3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1993,7 +2942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2013,10 +2962,10 @@
     <col width="42" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="42" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="42" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -2294,8 +3243,143 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>TPC-D4-001</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>TPC-001</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>TPC-001</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>TPC-RULE-003</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Skill journey remains correct after browser reload</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Skill journey remains correct after browser reload</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Disposable Nexent deployment, authorized skill and controlled provider are available.
+Fresh test tenant has default memory enabled and no embedding model; dismiss its warning without changing settings.</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>1. Open test Agent and request a skill-based check. =&gt; Skill read and result are visible.
+2. Wait for final, reload the workbench, then reopen the saved conversation from its sidebar entry. =&gt; Final contains the result, not the unexecuted action.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Skill check business result is visible after refresh.</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>No raw action final.</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>{"actor":"Tenant test user","failure_evidence":["Sanitized browser trace and failed assertion screenshot."],"final_business_result":["Completed skill check with preserved tool result and validated final."],"journey":["Open Agent","Submit check","Observe skill execution","Reload saved conversation"]}</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>{"profiles":[{"name":"mock","required_services":["model-provider"]}]}</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>playwright</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d4/think_prefix_browser.mjs</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>test_tpc_d4_001</t>
+        </is>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>model-provider</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr">
+        <is>
+          <t>sha256:a4396130631c96c17607bc377500d220995c93f701be28bdfbb7c96d2c66556c</t>
+        </is>
+      </c>
+      <c r="AA3" s="5" t="inlineStr">
+        <is>
+          <t>sha256:ed5c9e72e1af0ac98d23c22f314b32d163311a4e3bbca87dd9d77997576aedc8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA2"/>
+  <autoFilter ref="A1:AA3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2306,7 +3390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2326,10 +3410,10 @@
     <col width="42" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="42" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -2599,8 +3683,137 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>TPC-D5-001</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>TPC-001</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>TPC-001</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>TPC-RULE-002
+TPC-RULE-003</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Protocol exhaustion and truncation never authorize unsafe replay or final</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>RELIABILITY</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Protocol exhaustion and truncation never authorize unsafe replay or final</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Isolated strict ordinary CodeAgent with a controlled model and authorized skill-read tool.</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>{"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>1. Run two rejected actions then a third malformed action or length-truncated action. =&gt; No executor call or raw final occurs.
+2. Run a valid compatible skill action after two rejections. =&gt; Exactly one execution commits, with no replay.</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Invalid third attempt never finalizes.
+Valid action executes exactly once.</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>No invalid execution.
+No tool replay.</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>{"condition":["Prior error count two","Malformed/truncated third generation","Valid third compatible action"],"metrics":["Executor invocation count","Invalid raw final count","Accepted attempt count"],"recovery_expectations":["Valid actions recover; invalid exhausted responses stay bounded failures."],"risk":"Protocol repair can skip skills or publish unexecuted actions as final answers.","risk_type":"RELIABILITY","thresholds":["Zero executor invocations for invalid output","Zero invalid raw final answers","Exactly one invocation for valid action"]}</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d5/test_think_prefix_reliability.py</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>test_tpc_d5_001</t>
+        </is>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr"/>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z3" s="5" t="inlineStr">
+        <is>
+          <t>sha256:a56e85d3e652c38805e425c416214927664a2155d0836a31251fb4a10531659d</t>
+        </is>
+      </c>
+      <c r="AA3" s="5" t="inlineStr">
+        <is>
+          <t>sha256:a04e4124b9b4a97aaae836e61e9ccf12512e97957c4c232e3d52c7a593565ed9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA2"/>
+  <autoFilter ref="A1:AA3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/test/generated/Nexent_测试基线.xlsx
+++ b/test/generated/Nexent_测试基线.xlsx
@@ -16,8 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_D5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_功能清单'!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_D1'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_功能清单'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_D1'!$A$1:$AA$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_D2'!$A$1:$AA$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_D3'!$A$1:$AA$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_D4'!$A$1:$AA$2</definedName>
@@ -551,11 +551,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
@@ -646,8 +646,46 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>MSRF-001</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Model service ownership and preserved contracts</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Model services and utilities have one Management implementation with shared immutable contracts.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>MSRF-RULE-001
+MSRF-RULE-002</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>{"requirement_ids":["MSRF-001"],"spec_path":"nexent-doc/docs/Developing/four-service-runtime-decoupling/changes/model-service-refactor/proposal.md"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -658,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1351,8 +1389,263 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>MSRF-D1-001</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>MSRF-001</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>MSRF-001</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>MSRF-RULE-001</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Model implementation has one bounded canonical location</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>BE-UT</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Verify canonical locations and an acyclic internal import graph.</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Use repository Python sources without external services.</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>{"max_physical_lines":1500,"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>1. Inspect model sources and all backend SDK and test imports. =&gt; Canonical files exist and obsolete imports and duplicate implementations are absent.
+2. Traverse model internal imports including function-local imports. =&gt; No cycle connects provider health and probe.</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>Every model code file is at most 1500 lines.
+All internal dependencies are acyclic.</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>No database or provider connection occurs during source inspection.</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Required canonical modules exist.","Obsolete modules are absent.","Import graph has no cycle.","Names depends only on standard library."],"inputs":["Repository Python source files"],"unit_boundary":"Model source ownership and dependency graph"}</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_model_service_refactor.py</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>test_msrf_d1_001</t>
+        </is>
+      </c>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr"/>
+      <c r="X6" s="5" t="inlineStr"/>
+      <c r="Y6" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z6" s="5" t="inlineStr">
+        <is>
+          <t>sha256:c9f190fbea88ebaf8a22dd6172145101c7cdf404be72b1d36e4968d81a44ee32</t>
+        </is>
+      </c>
+      <c r="AA6" s="5" t="inlineStr">
+        <is>
+          <t>sha256:06eba556ec2713839a39898941ae1c72d98f1a1a43d282e30709d2cff5c7145f</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>MSRF-D1-002</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>MSRF-001</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>MSRF-001</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>MSRF-RULE-002</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Relocated model methods and shared types preserve their contracts</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>BE-UT</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>automated</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Compare signatures to the develop baseline and check immutable result defaults.</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Use the captured develop signature fixture and pure contracts.</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>{"configurations":["empty name","repository qualified name","legacy modelName"],"profile":"mock"}</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>1. Compare canonical function signatures to baseline declarations. =&gt; Arguments defaults return annotations and async declarations match.
+2. Construct model descriptors and capacity results and format model names. =&gt; Defaults enum values and name fallback behavior match the preserved contract.</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>All captured signatures match.
+Shared dataclasses remain frozen.
+Name formatting preserves legacy fields.</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>No model client database or telemetry initialization is required for contracts or names.</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>{"assertions":["Public signatures are unchanged.","Contract defaults and enum values match.","Dataclasses reject mutation.","Pure helpers use no business imports."],"inputs":["Baseline signatures","Empty and legacy model name dictionaries"],"unit_boundary":"Public model signatures immutable contracts and pure name helpers"}</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="inlineStr">
+        <is>
+          <t>pytest</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>test/automation/d1/test_model_service_refactor.py</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>test_msrf_d1_002</t>
+        </is>
+      </c>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>mock</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr"/>
+      <c r="X7" s="5" t="inlineStr"/>
+      <c r="Y7" s="5" t="inlineStr">
+        <is>
+          <t>校验通过</t>
+        </is>
+      </c>
+      <c r="Z7" s="5" t="inlineStr">
+        <is>
+          <t>sha256:370fa658828de25e16474d3dd8cfd8047f7e21e8bb5b1f8411a5d69ce2e13d58</t>
+        </is>
+      </c>
+      <c r="AA7" s="5" t="inlineStr">
+        <is>
+          <t>sha256:06eba556ec2713839a39898941ae1c72d98f1a1a43d282e30709d2cff5c7145f</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1663,7 +1956,7 @@
       </c>
       <c r="AA2" s="5" t="inlineStr">
         <is>
-          <t>sha256:570d7db5b7480c6b3a3a3adcc953158f7c496e44a79e90ad1ca3a4df676d573f</t>
+          <t>sha256:f8f1bc3e7a01d6ffd739d9fbe695e28533e4c410847a09b6405a7dbd4c2e948a</t>
         </is>
       </c>
     </row>
